--- a/MC1020_E25.xlsx
+++ b/MC1020_E25.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IDS_Instrutors\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assignment marks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B069F90-E11E-4CA3-85B1-CB24EEBA439F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA4CEB0A-6C47-4A49-8C08-6E37D4CD93CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="483">
   <si>
     <t xml:space="preserve"> Reg.number</t>
   </si>
@@ -1581,10 +1581,11 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Century Gothic"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1718,23 +1719,21 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="12">
     <cellStyle name="60% - Accent1 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -2068,15 +2067,17 @@
       <c r="C2" s="11">
         <v>45</v>
       </c>
-      <c r="D2" s="16"/>
-      <c r="E2" s="20">
+      <c r="D2" s="18"/>
+      <c r="E2" s="17">
         <v>49</v>
       </c>
-      <c r="F2" s="22"/>
+      <c r="F2" s="17">
+        <v>64</v>
+      </c>
       <c r="G2" s="11">
         <v>13</v>
       </c>
-      <c r="H2" s="17">
+      <c r="H2" s="22">
         <v>61.29032258064516</v>
       </c>
     </row>
@@ -2090,15 +2091,17 @@
       <c r="C3" s="11">
         <v>40</v>
       </c>
-      <c r="D3" s="16"/>
-      <c r="E3" s="20">
+      <c r="D3" s="18"/>
+      <c r="E3" s="17">
         <v>49</v>
       </c>
-      <c r="F3" s="22"/>
+      <c r="F3" s="17">
+        <v>54</v>
+      </c>
       <c r="G3" s="11">
         <v>24</v>
       </c>
-      <c r="H3" s="17">
+      <c r="H3" s="22">
         <v>74.193548387096769</v>
       </c>
     </row>
@@ -2112,15 +2115,17 @@
       <c r="C4" s="11">
         <v>53</v>
       </c>
-      <c r="D4" s="16"/>
-      <c r="E4" s="20">
+      <c r="D4" s="18"/>
+      <c r="E4" s="17">
         <v>66</v>
       </c>
-      <c r="F4" s="22"/>
+      <c r="F4" s="17">
+        <v>67.5</v>
+      </c>
       <c r="G4" s="11" t="s">
         <v>482</v>
       </c>
-      <c r="H4" s="17">
+      <c r="H4" s="22">
         <v>58.064516129032263</v>
       </c>
     </row>
@@ -2134,15 +2139,17 @@
       <c r="C5" s="11">
         <v>17</v>
       </c>
-      <c r="D5" s="16"/>
-      <c r="E5" s="20">
+      <c r="D5" s="18"/>
+      <c r="E5" s="17">
         <v>61</v>
       </c>
-      <c r="F5" s="22"/>
+      <c r="F5" s="17">
+        <v>61.5</v>
+      </c>
       <c r="G5" s="11">
         <v>26</v>
       </c>
-      <c r="H5" s="17">
+      <c r="H5" s="22">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -2156,15 +2163,17 @@
       <c r="C6" s="11">
         <v>44</v>
       </c>
-      <c r="D6" s="16"/>
-      <c r="E6" s="20">
+      <c r="D6" s="18"/>
+      <c r="E6" s="17">
         <v>47</v>
       </c>
-      <c r="F6" s="22"/>
+      <c r="F6" s="17">
+        <v>61</v>
+      </c>
       <c r="G6" s="11">
         <v>32</v>
       </c>
-      <c r="H6" s="17">
+      <c r="H6" s="22">
         <v>61.29032258064516</v>
       </c>
     </row>
@@ -2178,15 +2187,17 @@
       <c r="C7" s="11">
         <v>36</v>
       </c>
-      <c r="D7" s="16"/>
-      <c r="E7" s="20">
+      <c r="D7" s="18"/>
+      <c r="E7" s="17">
         <v>53</v>
       </c>
-      <c r="F7" s="22"/>
+      <c r="F7" s="17">
+        <v>16</v>
+      </c>
       <c r="G7" s="11">
         <v>20</v>
       </c>
-      <c r="H7" s="17">
+      <c r="H7" s="22">
         <v>83.870967741935488</v>
       </c>
     </row>
@@ -2200,15 +2211,17 @@
       <c r="C8" s="11">
         <v>32</v>
       </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="20">
+      <c r="D8" s="18"/>
+      <c r="E8" s="17">
         <v>50</v>
       </c>
-      <c r="F8" s="22"/>
+      <c r="F8" s="17">
+        <v>79</v>
+      </c>
       <c r="G8" s="11">
         <v>32</v>
       </c>
-      <c r="H8" s="17">
+      <c r="H8" s="22">
         <v>87.096774193548384</v>
       </c>
     </row>
@@ -2222,15 +2235,17 @@
       <c r="C9" s="11">
         <v>29</v>
       </c>
-      <c r="D9" s="16"/>
-      <c r="E9" s="20">
+      <c r="D9" s="18"/>
+      <c r="E9" s="17">
         <v>47</v>
       </c>
-      <c r="F9" s="22"/>
+      <c r="F9" s="17">
+        <v>36</v>
+      </c>
       <c r="G9" s="11">
         <v>12</v>
       </c>
-      <c r="H9" s="17">
+      <c r="H9" s="22">
         <v>83.870967741935488</v>
       </c>
     </row>
@@ -2244,15 +2259,17 @@
       <c r="C10" s="11">
         <v>8</v>
       </c>
-      <c r="D10" s="16"/>
-      <c r="E10" s="20">
+      <c r="D10" s="18"/>
+      <c r="E10" s="17">
         <v>47</v>
       </c>
-      <c r="F10" s="22"/>
+      <c r="F10" s="17">
+        <v>61</v>
+      </c>
       <c r="G10" s="11">
         <v>18</v>
       </c>
-      <c r="H10" s="17">
+      <c r="H10" s="22">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -2266,15 +2283,17 @@
       <c r="C11" s="11">
         <v>75</v>
       </c>
-      <c r="D11" s="16"/>
-      <c r="E11" s="20">
+      <c r="D11" s="18"/>
+      <c r="E11" s="17">
         <v>60</v>
       </c>
-      <c r="F11" s="22"/>
+      <c r="F11" s="17">
+        <v>59.5</v>
+      </c>
       <c r="G11" s="11">
         <v>58</v>
       </c>
-      <c r="H11" s="17">
+      <c r="H11" s="22">
         <v>83.870967741935488</v>
       </c>
     </row>
@@ -2288,17 +2307,17 @@
       <c r="C12" s="11">
         <v>42</v>
       </c>
-      <c r="D12" s="16"/>
-      <c r="E12" s="20">
+      <c r="D12" s="18"/>
+      <c r="E12" s="17">
         <v>47</v>
       </c>
-      <c r="F12" s="22">
-        <v>0</v>
+      <c r="F12" s="17">
+        <v>43.5</v>
       </c>
       <c r="G12" s="11">
         <v>22</v>
       </c>
-      <c r="H12" s="17">
+      <c r="H12" s="22">
         <v>80.645161290322577</v>
       </c>
     </row>
@@ -2312,15 +2331,17 @@
       <c r="C13" s="11">
         <v>34</v>
       </c>
-      <c r="D13" s="16"/>
-      <c r="E13" s="20">
+      <c r="D13" s="18"/>
+      <c r="E13" s="17">
         <v>60</v>
       </c>
-      <c r="F13" s="22"/>
+      <c r="F13" s="17">
+        <v>65.5</v>
+      </c>
       <c r="G13" s="11">
         <v>19</v>
       </c>
-      <c r="H13" s="17">
+      <c r="H13" s="22">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -2334,15 +2355,17 @@
       <c r="C14" s="11">
         <v>37</v>
       </c>
-      <c r="D14" s="16"/>
-      <c r="E14" s="20">
+      <c r="D14" s="18"/>
+      <c r="E14" s="17">
         <v>47</v>
       </c>
-      <c r="F14" s="22"/>
+      <c r="F14" s="17">
+        <v>60.5</v>
+      </c>
       <c r="G14" s="11">
         <v>34</v>
       </c>
-      <c r="H14" s="17">
+      <c r="H14" s="22">
         <v>87.096774193548384</v>
       </c>
     </row>
@@ -2356,15 +2379,17 @@
       <c r="C15" s="11">
         <v>51</v>
       </c>
-      <c r="D15" s="16"/>
-      <c r="E15" s="20">
+      <c r="D15" s="18"/>
+      <c r="E15" s="17">
         <v>87</v>
       </c>
-      <c r="F15" s="22"/>
+      <c r="F15" s="17">
+        <v>84.5</v>
+      </c>
       <c r="G15" s="11">
         <v>50</v>
       </c>
-      <c r="H15" s="17">
+      <c r="H15" s="22">
         <v>93.548387096774192</v>
       </c>
     </row>
@@ -2378,15 +2403,17 @@
       <c r="C16" s="11">
         <v>79</v>
       </c>
-      <c r="D16" s="16"/>
-      <c r="E16" s="20">
+      <c r="D16" s="18"/>
+      <c r="E16" s="17">
         <v>60</v>
       </c>
-      <c r="F16" s="22"/>
+      <c r="F16" s="17">
+        <v>58</v>
+      </c>
       <c r="G16" s="11">
         <v>54</v>
       </c>
-      <c r="H16" s="17">
+      <c r="H16" s="22">
         <v>83.870967741935488</v>
       </c>
     </row>
@@ -2400,15 +2427,17 @@
       <c r="C17" s="11">
         <v>44</v>
       </c>
-      <c r="D17" s="16"/>
-      <c r="E17" s="20">
+      <c r="D17" s="18"/>
+      <c r="E17" s="17">
         <v>46</v>
       </c>
-      <c r="F17" s="22"/>
+      <c r="F17" s="17">
+        <v>73.5</v>
+      </c>
       <c r="G17" s="11">
         <v>35</v>
       </c>
-      <c r="H17" s="17">
+      <c r="H17" s="22">
         <v>90.322580645161281</v>
       </c>
     </row>
@@ -2422,15 +2451,17 @@
       <c r="C18" s="11">
         <v>52</v>
       </c>
-      <c r="D18" s="16"/>
-      <c r="E18" s="20">
+      <c r="D18" s="18"/>
+      <c r="E18" s="17">
         <v>50</v>
       </c>
-      <c r="F18" s="22"/>
+      <c r="F18" s="17">
+        <v>17.5</v>
+      </c>
       <c r="G18" s="11">
         <v>33</v>
       </c>
-      <c r="H18" s="17">
+      <c r="H18" s="22">
         <v>54.838709677419352</v>
       </c>
     </row>
@@ -2444,15 +2475,17 @@
       <c r="C19" s="11">
         <v>46</v>
       </c>
-      <c r="D19" s="16"/>
-      <c r="E19" s="20">
+      <c r="D19" s="18"/>
+      <c r="E19" s="17">
         <v>87</v>
       </c>
-      <c r="F19" s="22"/>
+      <c r="F19" s="17">
+        <v>83</v>
+      </c>
       <c r="G19" s="11">
         <v>46</v>
       </c>
-      <c r="H19" s="17">
+      <c r="H19" s="22">
         <v>70.967741935483872</v>
       </c>
     </row>
@@ -2466,15 +2499,17 @@
       <c r="C20" s="11">
         <v>74</v>
       </c>
-      <c r="D20" s="16"/>
-      <c r="E20" s="20">
+      <c r="D20" s="18"/>
+      <c r="E20" s="17">
         <v>57</v>
       </c>
-      <c r="F20" s="22"/>
+      <c r="F20" s="17">
+        <v>55.5</v>
+      </c>
       <c r="G20" s="11">
         <v>57</v>
       </c>
-      <c r="H20" s="17">
+      <c r="H20" s="22">
         <v>83.870967741935488</v>
       </c>
     </row>
@@ -2488,15 +2523,17 @@
       <c r="C21" s="11">
         <v>48</v>
       </c>
-      <c r="D21" s="16"/>
-      <c r="E21" s="20">
+      <c r="D21" s="18"/>
+      <c r="E21" s="17">
         <v>50</v>
       </c>
-      <c r="F21" s="22"/>
+      <c r="F21" s="17">
+        <v>69.5</v>
+      </c>
       <c r="G21" s="11">
         <v>39</v>
       </c>
-      <c r="H21" s="17">
+      <c r="H21" s="22">
         <v>87.096774193548384</v>
       </c>
     </row>
@@ -2510,15 +2547,17 @@
       <c r="C22" s="11">
         <v>33</v>
       </c>
-      <c r="D22" s="16"/>
-      <c r="E22" s="20">
+      <c r="D22" s="18"/>
+      <c r="E22" s="17">
         <v>47</v>
       </c>
-      <c r="F22" s="22"/>
+      <c r="F22" s="17">
+        <v>50.5</v>
+      </c>
       <c r="G22" s="11">
         <v>37</v>
       </c>
-      <c r="H22" s="17">
+      <c r="H22" s="22">
         <v>93.548387096774192</v>
       </c>
     </row>
@@ -2532,15 +2571,17 @@
       <c r="C23" s="11">
         <v>39</v>
       </c>
-      <c r="D23" s="16"/>
-      <c r="E23" s="20">
+      <c r="D23" s="18"/>
+      <c r="E23" s="17">
         <v>46</v>
       </c>
-      <c r="F23" s="22"/>
+      <c r="F23" s="17">
+        <v>61</v>
+      </c>
       <c r="G23" s="11">
         <v>42</v>
       </c>
-      <c r="H23" s="17">
+      <c r="H23" s="22">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -2554,15 +2595,17 @@
       <c r="C24" s="11">
         <v>63</v>
       </c>
-      <c r="D24" s="16"/>
-      <c r="E24" s="20">
+      <c r="D24" s="18"/>
+      <c r="E24" s="17">
         <v>50</v>
       </c>
-      <c r="F24" s="22"/>
+      <c r="F24" s="17">
+        <v>69</v>
+      </c>
       <c r="G24" s="11">
         <v>36</v>
       </c>
-      <c r="H24" s="17">
+      <c r="H24" s="22">
         <v>83.870967741935488</v>
       </c>
     </row>
@@ -2576,17 +2619,17 @@
       <c r="C25" s="11">
         <v>49</v>
       </c>
-      <c r="D25" s="16"/>
-      <c r="E25" s="20">
+      <c r="D25" s="18"/>
+      <c r="E25" s="17">
         <v>50</v>
       </c>
-      <c r="F25" s="22">
-        <v>0</v>
+      <c r="F25" s="17">
+        <v>35</v>
       </c>
       <c r="G25" s="11">
         <v>19</v>
       </c>
-      <c r="H25" s="17">
+      <c r="H25" s="22">
         <v>80.645161290322577</v>
       </c>
     </row>
@@ -2600,15 +2643,17 @@
       <c r="C26" s="11">
         <v>31</v>
       </c>
-      <c r="D26" s="16"/>
-      <c r="E26" s="20">
+      <c r="D26" s="18"/>
+      <c r="E26" s="17">
         <v>46</v>
       </c>
-      <c r="F26" s="22"/>
+      <c r="F26" s="17">
+        <v>57.5</v>
+      </c>
       <c r="G26" s="11">
         <v>22</v>
       </c>
-      <c r="H26" s="17">
+      <c r="H26" s="22">
         <v>64.516129032258064</v>
       </c>
     </row>
@@ -2622,15 +2667,17 @@
       <c r="C27" s="11">
         <v>76</v>
       </c>
-      <c r="D27" s="16"/>
-      <c r="E27" s="20">
+      <c r="D27" s="18"/>
+      <c r="E27" s="17">
         <v>55</v>
       </c>
-      <c r="F27" s="22"/>
+      <c r="F27" s="17">
+        <v>64</v>
+      </c>
       <c r="G27" s="11">
         <v>48</v>
       </c>
-      <c r="H27" s="17">
+      <c r="H27" s="22">
         <v>74.193548387096769</v>
       </c>
     </row>
@@ -2644,15 +2691,17 @@
       <c r="C28" s="11">
         <v>72</v>
       </c>
-      <c r="D28" s="16"/>
-      <c r="E28" s="20">
+      <c r="D28" s="18"/>
+      <c r="E28" s="17">
         <v>50</v>
       </c>
-      <c r="F28" s="22"/>
+      <c r="F28" s="17">
+        <v>54.5</v>
+      </c>
       <c r="G28" s="11">
         <v>38</v>
       </c>
-      <c r="H28" s="17">
+      <c r="H28" s="22">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -2666,15 +2715,17 @@
       <c r="C29" s="11">
         <v>70</v>
       </c>
-      <c r="D29" s="16"/>
-      <c r="E29" s="20">
+      <c r="D29" s="18"/>
+      <c r="E29" s="17">
         <v>49</v>
       </c>
-      <c r="F29" s="22"/>
+      <c r="F29" s="17">
+        <v>43.5</v>
+      </c>
       <c r="G29" s="11">
         <v>49</v>
       </c>
-      <c r="H29" s="17">
+      <c r="H29" s="22">
         <v>74.193548387096769</v>
       </c>
     </row>
@@ -2688,15 +2739,17 @@
       <c r="C30" s="11">
         <v>48</v>
       </c>
-      <c r="D30" s="16"/>
-      <c r="E30" s="20">
+      <c r="D30" s="18"/>
+      <c r="E30" s="17">
         <v>47</v>
       </c>
-      <c r="F30" s="22"/>
+      <c r="F30" s="17">
+        <v>58.5</v>
+      </c>
       <c r="G30" s="11">
         <v>55</v>
       </c>
-      <c r="H30" s="17">
+      <c r="H30" s="22">
         <v>90.322580645161281</v>
       </c>
     </row>
@@ -2710,15 +2763,17 @@
       <c r="C31" s="11">
         <v>58</v>
       </c>
-      <c r="D31" s="16"/>
-      <c r="E31" s="20">
+      <c r="D31" s="18"/>
+      <c r="E31" s="17">
         <v>49</v>
       </c>
-      <c r="F31" s="22"/>
+      <c r="F31" s="17">
+        <v>79</v>
+      </c>
       <c r="G31" s="11">
         <v>50</v>
       </c>
-      <c r="H31" s="17">
+      <c r="H31" s="22">
         <v>80.645161290322577</v>
       </c>
     </row>
@@ -2732,15 +2787,17 @@
       <c r="C32" s="11">
         <v>32</v>
       </c>
-      <c r="D32" s="16"/>
-      <c r="E32" s="20">
+      <c r="D32" s="18"/>
+      <c r="E32" s="17">
         <v>52</v>
       </c>
-      <c r="F32" s="22"/>
+      <c r="F32" s="17">
+        <v>57.5</v>
+      </c>
       <c r="G32" s="11">
         <v>18</v>
       </c>
-      <c r="H32" s="17">
+      <c r="H32" s="22">
         <v>64.516129032258064</v>
       </c>
     </row>
@@ -2754,15 +2811,17 @@
       <c r="C33" s="11">
         <v>36</v>
       </c>
-      <c r="D33" s="16"/>
-      <c r="E33" s="20">
+      <c r="D33" s="18"/>
+      <c r="E33" s="17">
         <v>52</v>
       </c>
-      <c r="F33" s="22"/>
+      <c r="F33" s="17">
+        <v>68.5</v>
+      </c>
       <c r="G33" s="11">
         <v>31</v>
       </c>
-      <c r="H33" s="17">
+      <c r="H33" s="22">
         <v>70.967741935483872</v>
       </c>
     </row>
@@ -2776,15 +2835,17 @@
       <c r="C34" s="11">
         <v>57</v>
       </c>
-      <c r="D34" s="16"/>
-      <c r="E34" s="20">
+      <c r="D34" s="18"/>
+      <c r="E34" s="17">
         <v>81</v>
       </c>
-      <c r="F34" s="22"/>
+      <c r="F34" s="17">
+        <v>78</v>
+      </c>
       <c r="G34" s="11">
         <v>25</v>
       </c>
-      <c r="H34" s="17">
+      <c r="H34" s="22">
         <v>80.645161290322577</v>
       </c>
     </row>
@@ -2798,15 +2859,17 @@
       <c r="C35" s="11">
         <v>33</v>
       </c>
-      <c r="D35" s="16"/>
-      <c r="E35" s="20">
+      <c r="D35" s="18"/>
+      <c r="E35" s="17">
         <v>50</v>
       </c>
-      <c r="F35" s="22"/>
+      <c r="F35" s="17">
+        <v>49.5</v>
+      </c>
       <c r="G35" s="11">
         <v>32</v>
       </c>
-      <c r="H35" s="17">
+      <c r="H35" s="22">
         <v>87.096774193548384</v>
       </c>
     </row>
@@ -2820,15 +2883,17 @@
       <c r="C36" s="11">
         <v>53</v>
       </c>
-      <c r="D36" s="16"/>
-      <c r="E36" s="20">
+      <c r="D36" s="18"/>
+      <c r="E36" s="17">
         <v>81</v>
       </c>
-      <c r="F36" s="22"/>
+      <c r="F36" s="17">
+        <v>33.5</v>
+      </c>
       <c r="G36" s="11">
         <v>47</v>
       </c>
-      <c r="H36" s="17">
+      <c r="H36" s="22">
         <v>67.741935483870961</v>
       </c>
     </row>
@@ -2842,15 +2907,17 @@
       <c r="C37" s="11">
         <v>59</v>
       </c>
-      <c r="D37" s="16"/>
-      <c r="E37" s="20">
+      <c r="D37" s="18"/>
+      <c r="E37" s="17">
         <v>47</v>
       </c>
-      <c r="F37" s="22"/>
+      <c r="F37" s="17">
+        <v>60</v>
+      </c>
       <c r="G37" s="11">
         <v>50</v>
       </c>
-      <c r="H37" s="17">
+      <c r="H37" s="22">
         <v>70.967741935483872</v>
       </c>
     </row>
@@ -2864,15 +2931,17 @@
       <c r="C38" s="11">
         <v>58</v>
       </c>
-      <c r="D38" s="16"/>
-      <c r="E38" s="20">
+      <c r="D38" s="18"/>
+      <c r="E38" s="17">
         <v>52</v>
       </c>
-      <c r="F38" s="22"/>
+      <c r="F38" s="17">
+        <v>35</v>
+      </c>
       <c r="G38" s="11">
         <v>33</v>
       </c>
-      <c r="H38" s="17">
+      <c r="H38" s="22">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -2886,15 +2955,17 @@
       <c r="C39" s="11">
         <v>50</v>
       </c>
-      <c r="D39" s="16"/>
-      <c r="E39" s="20">
+      <c r="D39" s="18"/>
+      <c r="E39" s="17">
         <v>57</v>
       </c>
-      <c r="F39" s="22"/>
+      <c r="F39" s="17">
+        <v>72</v>
+      </c>
       <c r="G39" s="11">
         <v>16</v>
       </c>
-      <c r="H39" s="17">
+      <c r="H39" s="22">
         <v>83.870967741935488</v>
       </c>
     </row>
@@ -2908,15 +2979,17 @@
       <c r="C40" s="11">
         <v>64</v>
       </c>
-      <c r="D40" s="16"/>
-      <c r="E40" s="20">
+      <c r="D40" s="18"/>
+      <c r="E40" s="17">
         <v>57</v>
       </c>
-      <c r="F40" s="22"/>
+      <c r="F40" s="17">
+        <v>72</v>
+      </c>
       <c r="G40" s="11">
         <v>56</v>
       </c>
-      <c r="H40" s="17">
+      <c r="H40" s="22">
         <v>87.096774193548384</v>
       </c>
     </row>
@@ -2930,15 +3003,17 @@
       <c r="C41" s="11">
         <v>63</v>
       </c>
-      <c r="D41" s="16"/>
-      <c r="E41" s="20">
+      <c r="D41" s="18"/>
+      <c r="E41" s="17">
         <v>49</v>
       </c>
-      <c r="F41" s="22"/>
+      <c r="F41" s="17">
+        <v>53</v>
+      </c>
       <c r="G41" s="11">
         <v>54</v>
       </c>
-      <c r="H41" s="17">
+      <c r="H41" s="22">
         <v>87.096774193548384</v>
       </c>
     </row>
@@ -2952,15 +3027,17 @@
       <c r="C42" s="11">
         <v>32</v>
       </c>
-      <c r="D42" s="16"/>
-      <c r="E42" s="20">
+      <c r="D42" s="18"/>
+      <c r="E42" s="17">
         <v>47</v>
       </c>
-      <c r="F42" s="22"/>
+      <c r="F42" s="17">
+        <v>36</v>
+      </c>
       <c r="G42" s="11">
         <v>21</v>
       </c>
-      <c r="H42" s="17">
+      <c r="H42" s="22">
         <v>87.096774193548384</v>
       </c>
     </row>
@@ -2974,15 +3051,17 @@
       <c r="C43" s="11">
         <v>42</v>
       </c>
-      <c r="D43" s="16"/>
-      <c r="E43" s="20">
+      <c r="D43" s="18"/>
+      <c r="E43" s="17">
         <v>47</v>
       </c>
-      <c r="F43" s="22"/>
+      <c r="F43" s="17">
+        <v>49</v>
+      </c>
       <c r="G43" s="11">
         <v>46</v>
       </c>
-      <c r="H43" s="17">
+      <c r="H43" s="22">
         <v>61.29032258064516</v>
       </c>
     </row>
@@ -2996,15 +3075,17 @@
       <c r="C44" s="11">
         <v>41</v>
       </c>
-      <c r="D44" s="16"/>
-      <c r="E44" s="20">
+      <c r="D44" s="18"/>
+      <c r="E44" s="17">
         <v>55</v>
       </c>
-      <c r="F44" s="22"/>
+      <c r="F44" s="17">
+        <v>76</v>
+      </c>
       <c r="G44" s="11">
         <v>32</v>
       </c>
-      <c r="H44" s="17">
+      <c r="H44" s="22">
         <v>87.096774193548384</v>
       </c>
     </row>
@@ -3018,15 +3099,17 @@
       <c r="C45" s="11">
         <v>20</v>
       </c>
-      <c r="D45" s="16"/>
-      <c r="E45" s="20">
+      <c r="D45" s="18"/>
+      <c r="E45" s="17">
         <v>37</v>
       </c>
-      <c r="F45" s="22"/>
+      <c r="F45" s="17">
+        <v>52</v>
+      </c>
       <c r="G45" s="11">
         <v>36</v>
       </c>
-      <c r="H45" s="17">
+      <c r="H45" s="22">
         <v>74.193548387096769</v>
       </c>
     </row>
@@ -3040,15 +3123,17 @@
       <c r="C46" s="11">
         <v>23</v>
       </c>
-      <c r="D46" s="16"/>
-      <c r="E46" s="20">
+      <c r="D46" s="18"/>
+      <c r="E46" s="17">
         <v>47</v>
       </c>
-      <c r="F46" s="22"/>
+      <c r="F46" s="17">
+        <v>45</v>
+      </c>
       <c r="G46" s="11">
         <v>22</v>
       </c>
-      <c r="H46" s="17">
+      <c r="H46" s="22">
         <v>90.322580645161281</v>
       </c>
     </row>
@@ -3062,15 +3147,17 @@
       <c r="C47" s="11">
         <v>59</v>
       </c>
-      <c r="D47" s="16"/>
-      <c r="E47" s="20">
+      <c r="D47" s="18"/>
+      <c r="E47" s="17">
         <v>55</v>
       </c>
-      <c r="F47" s="22"/>
+      <c r="F47" s="17">
+        <v>86.5</v>
+      </c>
       <c r="G47" s="11">
         <v>50</v>
       </c>
-      <c r="H47" s="17">
+      <c r="H47" s="22">
         <v>80.645161290322577</v>
       </c>
     </row>
@@ -3084,15 +3171,17 @@
       <c r="C48" s="11">
         <v>77</v>
       </c>
-      <c r="D48" s="16"/>
-      <c r="E48" s="20">
+      <c r="D48" s="18"/>
+      <c r="E48" s="17">
         <v>49</v>
       </c>
-      <c r="F48" s="22"/>
+      <c r="F48" s="17">
+        <v>43</v>
+      </c>
       <c r="G48" s="11">
         <v>34</v>
       </c>
-      <c r="H48" s="17">
+      <c r="H48" s="22">
         <v>90.322580645161281</v>
       </c>
     </row>
@@ -3106,15 +3195,17 @@
       <c r="C49" s="11">
         <v>54</v>
       </c>
-      <c r="D49" s="16"/>
-      <c r="E49" s="20">
+      <c r="D49" s="18"/>
+      <c r="E49" s="17">
         <v>52</v>
       </c>
-      <c r="F49" s="22"/>
+      <c r="F49" s="17">
+        <v>60</v>
+      </c>
       <c r="G49" s="11">
         <v>46</v>
       </c>
-      <c r="H49" s="17">
+      <c r="H49" s="22">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -3128,15 +3219,17 @@
       <c r="C50" s="11">
         <v>47</v>
       </c>
-      <c r="D50" s="16"/>
-      <c r="E50" s="20">
+      <c r="D50" s="18"/>
+      <c r="E50" s="17">
         <v>50</v>
       </c>
-      <c r="F50" s="22"/>
+      <c r="F50" s="17">
+        <v>73.5</v>
+      </c>
       <c r="G50" s="11">
         <v>22</v>
       </c>
-      <c r="H50" s="17">
+      <c r="H50" s="22">
         <v>83.870967741935488</v>
       </c>
     </row>
@@ -3150,15 +3243,17 @@
       <c r="C51" s="11">
         <v>44</v>
       </c>
-      <c r="D51" s="16"/>
-      <c r="E51" s="20">
+      <c r="D51" s="18"/>
+      <c r="E51" s="17">
         <v>44</v>
       </c>
-      <c r="F51" s="22"/>
+      <c r="F51" s="17">
+        <v>52.5</v>
+      </c>
       <c r="G51" s="11">
         <v>18</v>
       </c>
-      <c r="H51" s="17">
+      <c r="H51" s="22">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -3172,15 +3267,17 @@
       <c r="C52" s="11">
         <v>55</v>
       </c>
-      <c r="D52" s="16"/>
-      <c r="E52" s="20">
+      <c r="D52" s="18"/>
+      <c r="E52" s="17">
         <v>52</v>
       </c>
-      <c r="F52" s="22"/>
+      <c r="F52" s="17">
+        <v>60.5</v>
+      </c>
       <c r="G52" s="11">
         <v>27</v>
       </c>
-      <c r="H52" s="17">
+      <c r="H52" s="22">
         <v>80.645161290322577</v>
       </c>
     </row>
@@ -3194,15 +3291,17 @@
       <c r="C53" s="11">
         <v>67</v>
       </c>
-      <c r="D53" s="16"/>
-      <c r="E53" s="20">
+      <c r="D53" s="18"/>
+      <c r="E53" s="17">
         <v>49</v>
       </c>
-      <c r="F53" s="22"/>
+      <c r="F53" s="17">
+        <v>63.5</v>
+      </c>
       <c r="G53" s="11">
         <v>45</v>
       </c>
-      <c r="H53" s="17">
+      <c r="H53" s="22">
         <v>96.774193548387103</v>
       </c>
     </row>
@@ -3216,15 +3315,17 @@
       <c r="C54" s="11">
         <v>40</v>
       </c>
-      <c r="D54" s="16"/>
-      <c r="E54" s="20">
+      <c r="D54" s="18"/>
+      <c r="E54" s="17">
         <v>50</v>
       </c>
-      <c r="F54" s="22"/>
+      <c r="F54" s="17">
+        <v>17.5</v>
+      </c>
       <c r="G54" s="11">
         <v>23</v>
       </c>
-      <c r="H54" s="17">
+      <c r="H54" s="22">
         <v>80.645161290322577</v>
       </c>
     </row>
@@ -3238,15 +3339,17 @@
       <c r="C55" s="11">
         <v>32</v>
       </c>
-      <c r="D55" s="16"/>
-      <c r="E55" s="20">
+      <c r="D55" s="18"/>
+      <c r="E55" s="17">
         <v>57</v>
       </c>
-      <c r="F55" s="22"/>
+      <c r="F55" s="17">
+        <v>75</v>
+      </c>
       <c r="G55" s="11">
         <v>35</v>
       </c>
-      <c r="H55" s="17">
+      <c r="H55" s="22">
         <v>90.322580645161281</v>
       </c>
     </row>
@@ -3260,15 +3363,17 @@
       <c r="C56" s="11">
         <v>60</v>
       </c>
-      <c r="D56" s="16"/>
-      <c r="E56" s="20">
+      <c r="D56" s="18"/>
+      <c r="E56" s="17">
         <v>66</v>
       </c>
-      <c r="F56" s="22"/>
+      <c r="F56" s="17">
+        <v>57</v>
+      </c>
       <c r="G56" s="11">
         <v>42</v>
       </c>
-      <c r="H56" s="17">
+      <c r="H56" s="22">
         <v>83.870967741935488</v>
       </c>
     </row>
@@ -3282,15 +3387,17 @@
       <c r="C57" s="11">
         <v>61</v>
       </c>
-      <c r="D57" s="16"/>
-      <c r="E57" s="20">
+      <c r="D57" s="18"/>
+      <c r="E57" s="17">
         <v>46</v>
       </c>
-      <c r="F57" s="22"/>
+      <c r="F57" s="17">
+        <v>76.5</v>
+      </c>
       <c r="G57" s="11">
         <v>29</v>
       </c>
-      <c r="H57" s="17">
+      <c r="H57" s="22">
         <v>90.322580645161281</v>
       </c>
     </row>
@@ -3304,15 +3411,17 @@
       <c r="C58" s="11">
         <v>38</v>
       </c>
-      <c r="D58" s="16"/>
-      <c r="E58" s="20">
+      <c r="D58" s="18"/>
+      <c r="E58" s="17">
         <v>46</v>
       </c>
-      <c r="F58" s="22"/>
+      <c r="F58" s="17">
+        <v>51.5</v>
+      </c>
       <c r="G58" s="11">
         <v>15</v>
       </c>
-      <c r="H58" s="17">
+      <c r="H58" s="22">
         <v>64.516129032258064</v>
       </c>
     </row>
@@ -3326,15 +3435,17 @@
       <c r="C59" s="11">
         <v>40</v>
       </c>
-      <c r="D59" s="16"/>
-      <c r="E59" s="20">
+      <c r="D59" s="18"/>
+      <c r="E59" s="17">
         <v>87</v>
       </c>
-      <c r="F59" s="22"/>
+      <c r="F59" s="17">
+        <v>85.5</v>
+      </c>
       <c r="G59" s="11">
         <v>34</v>
       </c>
-      <c r="H59" s="17">
+      <c r="H59" s="22">
         <v>83.870967741935488</v>
       </c>
     </row>
@@ -3348,15 +3459,17 @@
       <c r="C60" s="11">
         <v>63</v>
       </c>
-      <c r="D60" s="16"/>
-      <c r="E60" s="20">
+      <c r="D60" s="18"/>
+      <c r="E60" s="17">
         <v>70</v>
       </c>
-      <c r="F60" s="22"/>
+      <c r="F60" s="17">
+        <v>59.5</v>
+      </c>
       <c r="G60" s="11">
         <v>75</v>
       </c>
-      <c r="H60" s="17">
+      <c r="H60" s="22">
         <v>96.774193548387103</v>
       </c>
     </row>
@@ -3370,15 +3483,17 @@
       <c r="C61" s="11">
         <v>50</v>
       </c>
-      <c r="D61" s="16"/>
-      <c r="E61" s="20">
+      <c r="D61" s="18"/>
+      <c r="E61" s="17">
         <v>70</v>
       </c>
-      <c r="F61" s="22"/>
+      <c r="F61" s="17">
+        <v>57.5</v>
+      </c>
       <c r="G61" s="11">
         <v>35</v>
       </c>
-      <c r="H61" s="17">
+      <c r="H61" s="22">
         <v>93.548387096774192</v>
       </c>
     </row>
@@ -3392,15 +3507,17 @@
       <c r="C62" s="11">
         <v>19</v>
       </c>
-      <c r="D62" s="16"/>
-      <c r="E62" s="20">
+      <c r="D62" s="18"/>
+      <c r="E62" s="17">
         <v>47</v>
       </c>
-      <c r="F62" s="22"/>
+      <c r="F62" s="17">
+        <v>48</v>
+      </c>
       <c r="G62" s="11">
         <v>28</v>
       </c>
-      <c r="H62" s="17">
+      <c r="H62" s="22">
         <v>90.322580645161281</v>
       </c>
     </row>
@@ -3414,15 +3531,17 @@
       <c r="C63" s="11">
         <v>81</v>
       </c>
-      <c r="D63" s="16"/>
-      <c r="E63" s="20">
+      <c r="D63" s="18"/>
+      <c r="E63" s="17">
         <v>52</v>
       </c>
-      <c r="F63" s="22"/>
+      <c r="F63" s="17">
+        <v>95</v>
+      </c>
       <c r="G63" s="11">
         <v>56</v>
       </c>
-      <c r="H63" s="17">
+      <c r="H63" s="22">
         <v>93.548387096774192</v>
       </c>
     </row>
@@ -3436,15 +3555,17 @@
       <c r="C64" s="11">
         <v>27</v>
       </c>
-      <c r="D64" s="16"/>
-      <c r="E64" s="20">
+      <c r="D64" s="18"/>
+      <c r="E64" s="17">
         <v>52</v>
       </c>
-      <c r="F64" s="22"/>
+      <c r="F64" s="17">
+        <v>56</v>
+      </c>
       <c r="G64" s="11">
         <v>47</v>
       </c>
-      <c r="H64" s="17">
+      <c r="H64" s="22">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -3458,15 +3579,17 @@
       <c r="C65" s="11">
         <v>60</v>
       </c>
-      <c r="D65" s="16"/>
-      <c r="E65" s="20">
+      <c r="D65" s="18"/>
+      <c r="E65" s="17">
         <v>49</v>
       </c>
-      <c r="F65" s="22"/>
+      <c r="F65" s="17">
+        <v>79</v>
+      </c>
       <c r="G65" s="11">
         <v>53</v>
       </c>
-      <c r="H65" s="17">
+      <c r="H65" s="22">
         <v>90.322580645161281</v>
       </c>
     </row>
@@ -3480,15 +3603,17 @@
       <c r="C66" s="11">
         <v>33</v>
       </c>
-      <c r="D66" s="16"/>
-      <c r="E66" s="20">
+      <c r="D66" s="18"/>
+      <c r="E66" s="17">
         <v>60</v>
       </c>
-      <c r="F66" s="22"/>
+      <c r="F66" s="17">
+        <v>59</v>
+      </c>
       <c r="G66" s="11">
         <v>15</v>
       </c>
-      <c r="H66" s="17">
+      <c r="H66" s="22">
         <v>93.548387096774192</v>
       </c>
     </row>
@@ -3502,15 +3627,17 @@
       <c r="C67" s="11">
         <v>54</v>
       </c>
-      <c r="D67" s="16"/>
-      <c r="E67" s="20">
+      <c r="D67" s="18"/>
+      <c r="E67" s="17">
         <v>49</v>
       </c>
-      <c r="F67" s="22"/>
+      <c r="F67" s="17">
+        <v>79.5</v>
+      </c>
       <c r="G67" s="11">
         <v>43</v>
       </c>
-      <c r="H67" s="17">
+      <c r="H67" s="22">
         <v>87.096774193548384</v>
       </c>
     </row>
@@ -3524,15 +3651,17 @@
       <c r="C68" s="11">
         <v>54</v>
       </c>
-      <c r="D68" s="16"/>
-      <c r="E68" s="20">
+      <c r="D68" s="18"/>
+      <c r="E68" s="17">
         <v>81</v>
       </c>
-      <c r="F68" s="22"/>
+      <c r="F68" s="17">
+        <v>20</v>
+      </c>
       <c r="G68" s="11">
         <v>31</v>
       </c>
-      <c r="H68" s="17">
+      <c r="H68" s="22">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -3546,17 +3675,17 @@
       <c r="C69" s="11">
         <v>57</v>
       </c>
-      <c r="D69" s="16"/>
-      <c r="E69" s="20">
+      <c r="D69" s="18"/>
+      <c r="E69" s="17">
         <v>57</v>
       </c>
-      <c r="F69" s="22">
-        <v>0</v>
+      <c r="F69" s="17">
+        <v>74</v>
       </c>
       <c r="G69" s="11">
         <v>40</v>
       </c>
-      <c r="H69" s="17">
+      <c r="H69" s="22">
         <v>93.548387096774192</v>
       </c>
     </row>
@@ -3570,15 +3699,17 @@
       <c r="C70" s="11">
         <v>39</v>
       </c>
-      <c r="D70" s="16"/>
-      <c r="E70" s="20">
+      <c r="D70" s="18"/>
+      <c r="E70" s="17">
         <v>57</v>
       </c>
-      <c r="F70" s="22"/>
+      <c r="F70" s="17">
+        <v>50</v>
+      </c>
       <c r="G70" s="11">
         <v>62</v>
       </c>
-      <c r="H70" s="17">
+      <c r="H70" s="22">
         <v>93.548387096774192</v>
       </c>
     </row>
@@ -3592,15 +3723,17 @@
       <c r="C71" s="11">
         <v>44</v>
       </c>
-      <c r="D71" s="16"/>
-      <c r="E71" s="20">
+      <c r="D71" s="18"/>
+      <c r="E71" s="17">
         <v>37</v>
       </c>
-      <c r="F71" s="22"/>
+      <c r="F71" s="17">
+        <v>40.5</v>
+      </c>
       <c r="G71" s="11">
         <v>51</v>
       </c>
-      <c r="H71" s="17">
+      <c r="H71" s="22">
         <v>96.774193548387103</v>
       </c>
     </row>
@@ -3614,15 +3747,17 @@
       <c r="C72" s="11">
         <v>68</v>
       </c>
-      <c r="D72" s="16"/>
-      <c r="E72" s="20">
+      <c r="D72" s="18"/>
+      <c r="E72" s="17">
         <v>49</v>
       </c>
-      <c r="F72" s="22"/>
+      <c r="F72" s="17">
+        <v>75.5</v>
+      </c>
       <c r="G72" s="11">
         <v>31</v>
       </c>
-      <c r="H72" s="17">
+      <c r="H72" s="22">
         <v>74.193548387096769</v>
       </c>
     </row>
@@ -3636,15 +3771,17 @@
       <c r="C73" s="11">
         <v>35</v>
       </c>
-      <c r="D73" s="16"/>
-      <c r="E73" s="20">
+      <c r="D73" s="18"/>
+      <c r="E73" s="17">
         <v>44</v>
       </c>
-      <c r="F73" s="22"/>
+      <c r="F73" s="17">
+        <v>57.5</v>
+      </c>
       <c r="G73" s="11">
         <v>23</v>
       </c>
-      <c r="H73" s="17">
+      <c r="H73" s="22">
         <v>74.193548387096769</v>
       </c>
     </row>
@@ -3658,15 +3795,17 @@
       <c r="C74" s="11">
         <v>49</v>
       </c>
-      <c r="D74" s="16"/>
-      <c r="E74" s="19" t="s">
+      <c r="D74" s="18"/>
+      <c r="E74" s="20" t="s">
         <v>482</v>
       </c>
-      <c r="F74" s="22"/>
+      <c r="F74" s="17">
+        <v>30</v>
+      </c>
       <c r="G74" s="11">
         <v>28</v>
       </c>
-      <c r="H74" s="17">
+      <c r="H74" s="22">
         <v>38.70967741935484</v>
       </c>
     </row>
@@ -3680,15 +3819,17 @@
       <c r="C75" s="11">
         <v>52</v>
       </c>
-      <c r="D75" s="16"/>
-      <c r="E75" s="20">
+      <c r="D75" s="18"/>
+      <c r="E75" s="17">
         <v>47</v>
       </c>
-      <c r="F75" s="22"/>
+      <c r="F75" s="17">
+        <v>49.5</v>
+      </c>
       <c r="G75" s="11">
         <v>26</v>
       </c>
-      <c r="H75" s="17">
+      <c r="H75" s="22">
         <v>74.193548387096769</v>
       </c>
     </row>
@@ -3702,15 +3843,17 @@
       <c r="C76" s="11">
         <v>50</v>
       </c>
-      <c r="D76" s="16"/>
-      <c r="E76" s="20">
+      <c r="D76" s="18"/>
+      <c r="E76" s="17">
         <v>57</v>
       </c>
-      <c r="F76" s="22"/>
+      <c r="F76" s="17">
+        <v>88.5</v>
+      </c>
       <c r="G76" s="11">
         <v>58</v>
       </c>
-      <c r="H76" s="17">
+      <c r="H76" s="22">
         <v>96.774193548387103</v>
       </c>
     </row>
@@ -3724,15 +3867,17 @@
       <c r="C77" s="11">
         <v>54</v>
       </c>
-      <c r="D77" s="16"/>
-      <c r="E77" s="20">
+      <c r="D77" s="18"/>
+      <c r="E77" s="17">
         <v>52</v>
       </c>
-      <c r="F77" s="22"/>
+      <c r="F77" s="17">
+        <v>69</v>
+      </c>
       <c r="G77" s="11">
         <v>39</v>
       </c>
-      <c r="H77" s="17">
+      <c r="H77" s="22">
         <v>90.322580645161281</v>
       </c>
     </row>
@@ -3746,15 +3891,17 @@
       <c r="C78" s="11">
         <v>60</v>
       </c>
-      <c r="D78" s="16"/>
-      <c r="E78" s="20">
+      <c r="D78" s="18"/>
+      <c r="E78" s="17">
         <v>81</v>
       </c>
-      <c r="F78" s="22"/>
+      <c r="F78" s="17">
+        <v>69.5</v>
+      </c>
       <c r="G78" s="11">
         <v>24</v>
       </c>
-      <c r="H78" s="17">
+      <c r="H78" s="22">
         <v>80.645161290322577</v>
       </c>
     </row>
@@ -3768,15 +3915,17 @@
       <c r="C79" s="11">
         <v>55</v>
       </c>
-      <c r="D79" s="16"/>
-      <c r="E79" s="20">
+      <c r="D79" s="18"/>
+      <c r="E79" s="17">
         <v>47</v>
       </c>
-      <c r="F79" s="22"/>
+      <c r="F79" s="17">
+        <v>64</v>
+      </c>
       <c r="G79" s="11">
         <v>45</v>
       </c>
-      <c r="H79" s="17">
+      <c r="H79" s="22">
         <v>87.096774193548384</v>
       </c>
     </row>
@@ -3790,15 +3939,17 @@
       <c r="C80" s="11">
         <v>54</v>
       </c>
-      <c r="D80" s="16"/>
-      <c r="E80" s="20">
+      <c r="D80" s="18"/>
+      <c r="E80" s="17">
         <v>49</v>
       </c>
-      <c r="F80" s="22"/>
+      <c r="F80" s="17">
+        <v>67.5</v>
+      </c>
       <c r="G80" s="11">
         <v>19</v>
       </c>
-      <c r="H80" s="17">
+      <c r="H80" s="22">
         <v>80.645161290322577</v>
       </c>
     </row>
@@ -3812,15 +3963,17 @@
       <c r="C81" s="11">
         <v>54</v>
       </c>
-      <c r="D81" s="16"/>
-      <c r="E81" s="20">
+      <c r="D81" s="18"/>
+      <c r="E81" s="17">
         <v>49</v>
       </c>
-      <c r="F81" s="22"/>
+      <c r="F81" s="17">
+        <v>76.5</v>
+      </c>
       <c r="G81" s="11">
         <v>48</v>
       </c>
-      <c r="H81" s="17">
+      <c r="H81" s="22">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -3834,15 +3987,17 @@
       <c r="C82" s="11">
         <v>62</v>
       </c>
-      <c r="D82" s="16"/>
-      <c r="E82" s="20">
+      <c r="D82" s="18"/>
+      <c r="E82" s="17">
         <v>37</v>
       </c>
-      <c r="F82" s="22"/>
+      <c r="F82" s="17">
+        <v>72</v>
+      </c>
       <c r="G82" s="11">
         <v>45</v>
       </c>
-      <c r="H82" s="17">
+      <c r="H82" s="22">
         <v>90.322580645161281</v>
       </c>
     </row>
@@ -3856,15 +4011,17 @@
       <c r="C83" s="11">
         <v>59</v>
       </c>
-      <c r="D83" s="16"/>
-      <c r="E83" s="20">
+      <c r="D83" s="18"/>
+      <c r="E83" s="17">
         <v>57</v>
       </c>
-      <c r="F83" s="22"/>
+      <c r="F83" s="17">
+        <v>62.5</v>
+      </c>
       <c r="G83" s="11">
         <v>29</v>
       </c>
-      <c r="H83" s="17">
+      <c r="H83" s="22">
         <v>90.322580645161281</v>
       </c>
     </row>
@@ -3878,15 +4035,17 @@
       <c r="C84" s="11">
         <v>60</v>
       </c>
-      <c r="D84" s="16"/>
-      <c r="E84" s="20">
+      <c r="D84" s="18"/>
+      <c r="E84" s="17">
         <v>37</v>
       </c>
-      <c r="F84" s="22"/>
+      <c r="F84" s="17">
+        <v>45.5</v>
+      </c>
       <c r="G84" s="11">
         <v>36</v>
       </c>
-      <c r="H84" s="17">
+      <c r="H84" s="22">
         <v>93.548387096774192</v>
       </c>
     </row>
@@ -3900,17 +4059,17 @@
       <c r="C85" s="11">
         <v>43</v>
       </c>
-      <c r="D85" s="16"/>
-      <c r="E85" s="20">
+      <c r="D85" s="18"/>
+      <c r="E85" s="17">
         <v>57</v>
       </c>
-      <c r="F85" s="22">
-        <v>0</v>
+      <c r="F85" s="17">
+        <v>55.5</v>
       </c>
       <c r="G85" s="11">
         <v>41</v>
       </c>
-      <c r="H85" s="17">
+      <c r="H85" s="22">
         <v>93.548387096774192</v>
       </c>
     </row>
@@ -3924,17 +4083,17 @@
       <c r="C86" s="11">
         <v>41</v>
       </c>
-      <c r="D86" s="16"/>
-      <c r="E86" s="20">
+      <c r="D86" s="18"/>
+      <c r="E86" s="17">
         <v>61</v>
       </c>
-      <c r="F86" s="22">
-        <v>0</v>
+      <c r="F86" s="17">
+        <v>72.5</v>
       </c>
       <c r="G86" s="11">
         <v>17</v>
       </c>
-      <c r="H86" s="17">
+      <c r="H86" s="22">
         <v>74.193548387096769</v>
       </c>
     </row>
@@ -3948,15 +4107,17 @@
       <c r="C87" s="11">
         <v>41</v>
       </c>
-      <c r="D87" s="16"/>
-      <c r="E87" s="20">
+      <c r="D87" s="18"/>
+      <c r="E87" s="17">
         <v>87</v>
       </c>
-      <c r="F87" s="22"/>
+      <c r="F87" s="17">
+        <v>39</v>
+      </c>
       <c r="G87" s="11">
         <v>32</v>
       </c>
-      <c r="H87" s="17">
+      <c r="H87" s="22">
         <v>96.774193548387103</v>
       </c>
     </row>
@@ -3970,15 +4131,17 @@
       <c r="C88" s="11">
         <v>48</v>
       </c>
-      <c r="D88" s="16"/>
-      <c r="E88" s="20">
+      <c r="D88" s="18"/>
+      <c r="E88" s="17">
         <v>47</v>
       </c>
-      <c r="F88" s="22"/>
+      <c r="F88" s="17">
+        <v>17.5</v>
+      </c>
       <c r="G88" s="11">
         <v>23</v>
       </c>
-      <c r="H88" s="17">
+      <c r="H88" s="22">
         <v>54.838709677419352</v>
       </c>
     </row>
@@ -3992,15 +4155,17 @@
       <c r="C89" s="11">
         <v>38</v>
       </c>
-      <c r="D89" s="16"/>
-      <c r="E89" s="20">
+      <c r="D89" s="18"/>
+      <c r="E89" s="17">
         <v>44</v>
       </c>
-      <c r="F89" s="22"/>
+      <c r="F89" s="17">
+        <v>47.5</v>
+      </c>
       <c r="G89" s="11">
         <v>38</v>
       </c>
-      <c r="H89" s="17">
+      <c r="H89" s="22">
         <v>90.322580645161281</v>
       </c>
     </row>
@@ -4014,15 +4179,17 @@
       <c r="C90" s="11">
         <v>43</v>
       </c>
-      <c r="D90" s="16"/>
-      <c r="E90" s="20">
+      <c r="D90" s="18"/>
+      <c r="E90" s="17">
         <v>55</v>
       </c>
-      <c r="F90" s="22"/>
+      <c r="F90" s="17">
+        <v>60.5</v>
+      </c>
       <c r="G90" s="11">
         <v>38</v>
       </c>
-      <c r="H90" s="17">
+      <c r="H90" s="22">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -4036,15 +4203,17 @@
       <c r="C91" s="11">
         <v>52</v>
       </c>
-      <c r="D91" s="16"/>
-      <c r="E91" s="20">
+      <c r="D91" s="18"/>
+      <c r="E91" s="17">
         <v>66</v>
       </c>
-      <c r="F91" s="22"/>
+      <c r="F91" s="17">
+        <v>92.5</v>
+      </c>
       <c r="G91" s="11" t="s">
         <v>482</v>
       </c>
-      <c r="H91" s="17">
+      <c r="H91" s="22">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -4058,15 +4227,17 @@
       <c r="C92" s="11">
         <v>49</v>
       </c>
-      <c r="D92" s="16"/>
-      <c r="E92" s="20">
+      <c r="D92" s="18"/>
+      <c r="E92" s="17">
         <v>50</v>
       </c>
-      <c r="F92" s="22"/>
+      <c r="F92" s="17">
+        <v>70</v>
+      </c>
       <c r="G92" s="11">
         <v>52</v>
       </c>
-      <c r="H92" s="17">
+      <c r="H92" s="22">
         <v>87.096774193548384</v>
       </c>
     </row>
@@ -4080,15 +4251,17 @@
       <c r="C93" s="11">
         <v>41</v>
       </c>
-      <c r="D93" s="16"/>
-      <c r="E93" s="20">
+      <c r="D93" s="18"/>
+      <c r="E93" s="17">
         <v>55</v>
       </c>
-      <c r="F93" s="22"/>
+      <c r="F93" s="17">
+        <v>40</v>
+      </c>
       <c r="G93" s="11">
         <v>32</v>
       </c>
-      <c r="H93" s="17">
+      <c r="H93" s="22">
         <v>87.096774193548384</v>
       </c>
     </row>
@@ -4102,15 +4275,17 @@
       <c r="C94" s="11">
         <v>15</v>
       </c>
-      <c r="D94" s="16"/>
-      <c r="E94" s="20">
+      <c r="D94" s="18"/>
+      <c r="E94" s="17">
         <v>46</v>
       </c>
-      <c r="F94" s="22"/>
+      <c r="F94" s="17">
+        <v>0</v>
+      </c>
       <c r="G94" s="11">
         <v>17</v>
       </c>
-      <c r="H94" s="17">
+      <c r="H94" s="22">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -4124,15 +4299,17 @@
       <c r="C95" s="11">
         <v>41</v>
       </c>
-      <c r="D95" s="16"/>
-      <c r="E95" s="20">
+      <c r="D95" s="18"/>
+      <c r="E95" s="17">
         <v>49</v>
       </c>
-      <c r="F95" s="22"/>
+      <c r="F95" s="17">
+        <v>64.5</v>
+      </c>
       <c r="G95" s="11">
         <v>41</v>
       </c>
-      <c r="H95" s="17">
+      <c r="H95" s="22">
         <v>45.161290322580641</v>
       </c>
     </row>
@@ -4146,15 +4323,17 @@
       <c r="C96" s="11">
         <v>41</v>
       </c>
-      <c r="D96" s="16"/>
-      <c r="E96" s="20">
+      <c r="D96" s="18"/>
+      <c r="E96" s="17">
         <v>66</v>
       </c>
-      <c r="F96" s="22"/>
+      <c r="F96" s="17">
+        <v>33.5</v>
+      </c>
       <c r="G96" s="11">
         <v>25</v>
       </c>
-      <c r="H96" s="17">
+      <c r="H96" s="22">
         <v>87.096774193548384</v>
       </c>
     </row>
@@ -4168,15 +4347,17 @@
       <c r="C97" s="11">
         <v>46</v>
       </c>
-      <c r="D97" s="16"/>
-      <c r="E97" s="20">
+      <c r="D97" s="18"/>
+      <c r="E97" s="17">
         <v>49</v>
       </c>
-      <c r="F97" s="22"/>
+      <c r="F97" s="17">
+        <v>71.5</v>
+      </c>
       <c r="G97" s="11">
         <v>30</v>
       </c>
-      <c r="H97" s="17">
+      <c r="H97" s="22">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -4190,15 +4371,17 @@
       <c r="C98" s="11">
         <v>40</v>
       </c>
-      <c r="D98" s="16"/>
-      <c r="E98" s="20">
+      <c r="D98" s="18"/>
+      <c r="E98" s="17">
         <v>66</v>
       </c>
-      <c r="F98" s="22"/>
+      <c r="F98" s="17">
+        <v>78.5</v>
+      </c>
       <c r="G98" s="11">
         <v>41</v>
       </c>
-      <c r="H98" s="17">
+      <c r="H98" s="22">
         <v>74.193548387096769</v>
       </c>
     </row>
@@ -4212,15 +4395,17 @@
       <c r="C99" s="11">
         <v>53</v>
       </c>
-      <c r="D99" s="16"/>
-      <c r="E99" s="20">
+      <c r="D99" s="18"/>
+      <c r="E99" s="17">
         <v>50</v>
       </c>
-      <c r="F99" s="22"/>
+      <c r="F99" s="17">
+        <v>70.5</v>
+      </c>
       <c r="G99" s="11">
         <v>31</v>
       </c>
-      <c r="H99" s="17">
+      <c r="H99" s="22">
         <v>90.322580645161281</v>
       </c>
     </row>
@@ -4234,15 +4419,17 @@
       <c r="C100" s="11">
         <v>35</v>
       </c>
-      <c r="D100" s="16"/>
-      <c r="E100" s="20">
+      <c r="D100" s="18"/>
+      <c r="E100" s="17">
         <v>81</v>
       </c>
-      <c r="F100" s="22"/>
+      <c r="F100" s="17">
+        <v>65.5</v>
+      </c>
       <c r="G100" s="11">
         <v>19</v>
       </c>
-      <c r="H100" s="17">
+      <c r="H100" s="22">
         <v>87.096774193548384</v>
       </c>
     </row>
@@ -4256,15 +4443,17 @@
       <c r="C101" s="11">
         <v>41</v>
       </c>
-      <c r="D101" s="16"/>
-      <c r="E101" s="20">
+      <c r="D101" s="18"/>
+      <c r="E101" s="17">
         <v>60</v>
       </c>
-      <c r="F101" s="22"/>
+      <c r="F101" s="17">
+        <v>46</v>
+      </c>
       <c r="G101" s="11">
         <v>17</v>
       </c>
-      <c r="H101" s="17">
+      <c r="H101" s="22">
         <v>87.096774193548384</v>
       </c>
     </row>
@@ -4278,15 +4467,17 @@
       <c r="C102" s="11">
         <v>38</v>
       </c>
-      <c r="D102" s="16"/>
-      <c r="E102" s="20">
+      <c r="D102" s="18"/>
+      <c r="E102" s="17">
         <v>61</v>
       </c>
-      <c r="F102" s="22"/>
+      <c r="F102" s="17">
+        <v>28</v>
+      </c>
       <c r="G102" s="11">
         <v>10</v>
       </c>
-      <c r="H102" s="17">
+      <c r="H102" s="22">
         <v>51.612903225806448</v>
       </c>
     </row>
@@ -4300,15 +4491,17 @@
       <c r="C103" s="11" t="s">
         <v>482</v>
       </c>
-      <c r="D103" s="16"/>
-      <c r="E103" s="19" t="s">
+      <c r="D103" s="18"/>
+      <c r="E103" s="20" t="s">
         <v>482</v>
       </c>
-      <c r="F103" s="22"/>
+      <c r="F103" s="17" t="s">
+        <v>482</v>
+      </c>
       <c r="G103" s="11" t="s">
         <v>482</v>
       </c>
-      <c r="H103" s="17">
+      <c r="H103" s="22">
         <v>16.129032258064516</v>
       </c>
     </row>
@@ -4322,15 +4515,17 @@
       <c r="C104" s="11">
         <v>65</v>
       </c>
-      <c r="D104" s="16"/>
-      <c r="E104" s="20">
+      <c r="D104" s="18"/>
+      <c r="E104" s="17">
         <v>57</v>
       </c>
-      <c r="F104" s="22"/>
+      <c r="F104" s="17">
+        <v>55</v>
+      </c>
       <c r="G104" s="11">
         <v>61</v>
       </c>
-      <c r="H104" s="17">
+      <c r="H104" s="22">
         <v>83.870967741935488</v>
       </c>
     </row>
@@ -4344,15 +4539,17 @@
       <c r="C105" s="11">
         <v>46</v>
       </c>
-      <c r="D105" s="16"/>
-      <c r="E105" s="20">
+      <c r="D105" s="18"/>
+      <c r="E105" s="17">
         <v>55</v>
       </c>
-      <c r="F105" s="22"/>
+      <c r="F105" s="17">
+        <v>42</v>
+      </c>
       <c r="G105" s="11">
         <v>48</v>
       </c>
-      <c r="H105" s="17">
+      <c r="H105" s="22">
         <v>80.645161290322577</v>
       </c>
     </row>
@@ -4366,17 +4563,17 @@
       <c r="C106" s="11">
         <v>45</v>
       </c>
-      <c r="D106" s="16"/>
-      <c r="E106" s="20">
+      <c r="D106" s="18"/>
+      <c r="E106" s="17">
         <v>70</v>
       </c>
-      <c r="F106" s="22">
-        <v>0</v>
+      <c r="F106" s="17">
+        <v>48</v>
       </c>
       <c r="G106" s="11">
         <v>28</v>
       </c>
-      <c r="H106" s="17">
+      <c r="H106" s="22">
         <v>45.161290322580641</v>
       </c>
     </row>
@@ -4390,15 +4587,17 @@
       <c r="C107" s="11">
         <v>46</v>
       </c>
-      <c r="D107" s="16"/>
-      <c r="E107" s="20">
+      <c r="D107" s="18"/>
+      <c r="E107" s="17">
         <v>52</v>
       </c>
-      <c r="F107" s="22"/>
+      <c r="F107" s="17">
+        <v>22</v>
+      </c>
       <c r="G107" s="11">
         <v>35</v>
       </c>
-      <c r="H107" s="17">
+      <c r="H107" s="22">
         <v>83.870967741935488</v>
       </c>
     </row>
@@ -4412,15 +4611,17 @@
       <c r="C108" s="11">
         <v>41</v>
       </c>
-      <c r="D108" s="16"/>
-      <c r="E108" s="20">
+      <c r="D108" s="18"/>
+      <c r="E108" s="17">
         <v>49</v>
       </c>
-      <c r="F108" s="22"/>
+      <c r="F108" s="17">
+        <v>25</v>
+      </c>
       <c r="G108" s="11">
         <v>41</v>
       </c>
-      <c r="H108" s="17">
+      <c r="H108" s="22">
         <v>93.548387096774192</v>
       </c>
     </row>
@@ -4434,15 +4635,17 @@
       <c r="C109" s="11">
         <v>24</v>
       </c>
-      <c r="D109" s="16"/>
-      <c r="E109" s="20">
+      <c r="D109" s="18"/>
+      <c r="E109" s="17">
         <v>60</v>
       </c>
-      <c r="F109" s="22"/>
+      <c r="F109" s="17">
+        <v>44.5</v>
+      </c>
       <c r="G109" s="11">
         <v>21</v>
       </c>
-      <c r="H109" s="17">
+      <c r="H109" s="22">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -4456,15 +4659,17 @@
       <c r="C110" s="11">
         <v>70</v>
       </c>
-      <c r="D110" s="16"/>
-      <c r="E110" s="20">
+      <c r="D110" s="18"/>
+      <c r="E110" s="17">
         <v>49</v>
       </c>
-      <c r="F110" s="22"/>
+      <c r="F110" s="17">
+        <v>78</v>
+      </c>
       <c r="G110" s="11">
         <v>59</v>
       </c>
-      <c r="H110" s="17">
+      <c r="H110" s="22">
         <v>87.096774193548384</v>
       </c>
     </row>
@@ -4478,15 +4683,17 @@
       <c r="C111" s="11">
         <v>52</v>
       </c>
-      <c r="D111" s="16"/>
-      <c r="E111" s="20">
+      <c r="D111" s="18"/>
+      <c r="E111" s="17">
         <v>44</v>
       </c>
-      <c r="F111" s="22"/>
+      <c r="F111" s="17">
+        <v>64</v>
+      </c>
       <c r="G111" s="11">
         <v>40</v>
       </c>
-      <c r="H111" s="17">
+      <c r="H111" s="22">
         <v>58.064516129032263</v>
       </c>
     </row>
@@ -4500,15 +4707,17 @@
       <c r="C112" s="11">
         <v>50</v>
       </c>
-      <c r="D112" s="16"/>
-      <c r="E112" s="20">
+      <c r="D112" s="18"/>
+      <c r="E112" s="17">
         <v>49</v>
       </c>
-      <c r="F112" s="22"/>
+      <c r="F112" s="17">
+        <v>49</v>
+      </c>
       <c r="G112" s="11">
         <v>35</v>
       </c>
-      <c r="H112" s="17">
+      <c r="H112" s="22">
         <v>48.387096774193552</v>
       </c>
     </row>
@@ -4522,17 +4731,17 @@
       <c r="C113" s="11">
         <v>52</v>
       </c>
-      <c r="D113" s="16"/>
-      <c r="E113" s="20">
+      <c r="D113" s="18"/>
+      <c r="E113" s="17">
         <v>47</v>
       </c>
-      <c r="F113" s="22">
-        <v>0</v>
+      <c r="F113" s="17">
+        <v>44</v>
       </c>
       <c r="G113" s="11">
         <v>46</v>
       </c>
-      <c r="H113" s="17">
+      <c r="H113" s="22">
         <v>83.870967741935488</v>
       </c>
     </row>
@@ -4546,15 +4755,17 @@
       <c r="C114" s="11">
         <v>64</v>
       </c>
-      <c r="D114" s="16"/>
-      <c r="E114" s="20">
+      <c r="D114" s="18"/>
+      <c r="E114" s="17">
         <v>64</v>
       </c>
-      <c r="F114" s="22"/>
+      <c r="F114" s="17">
+        <v>58.5</v>
+      </c>
       <c r="G114" s="11">
         <v>55</v>
       </c>
-      <c r="H114" s="17">
+      <c r="H114" s="22">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -4568,15 +4779,17 @@
       <c r="C115" s="11">
         <v>60</v>
       </c>
-      <c r="D115" s="16"/>
-      <c r="E115" s="20">
+      <c r="D115" s="18"/>
+      <c r="E115" s="17">
         <v>50</v>
       </c>
-      <c r="F115" s="22"/>
+      <c r="F115" s="17">
+        <v>64</v>
+      </c>
       <c r="G115" s="11">
         <v>49</v>
       </c>
-      <c r="H115" s="17">
+      <c r="H115" s="22">
         <v>90.322580645161281</v>
       </c>
     </row>
@@ -4590,15 +4803,17 @@
       <c r="C116" s="11">
         <v>53</v>
       </c>
-      <c r="D116" s="16"/>
-      <c r="E116" s="20">
+      <c r="D116" s="18"/>
+      <c r="E116" s="17">
         <v>64</v>
       </c>
-      <c r="F116" s="22"/>
+      <c r="F116" s="17">
+        <v>40</v>
+      </c>
       <c r="G116" s="11">
         <v>63</v>
       </c>
-      <c r="H116" s="17">
+      <c r="H116" s="22">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -4612,15 +4827,17 @@
       <c r="C117" s="11">
         <v>60</v>
       </c>
-      <c r="D117" s="16"/>
-      <c r="E117" s="20">
+      <c r="D117" s="18"/>
+      <c r="E117" s="17">
         <v>46</v>
       </c>
-      <c r="F117" s="22"/>
+      <c r="F117" s="17">
+        <v>83.5</v>
+      </c>
       <c r="G117" s="11">
         <v>43</v>
       </c>
-      <c r="H117" s="17">
+      <c r="H117" s="22">
         <v>83.870967741935488</v>
       </c>
     </row>
@@ -4634,15 +4851,17 @@
       <c r="C118" s="11">
         <v>44</v>
       </c>
-      <c r="D118" s="16"/>
-      <c r="E118" s="20">
+      <c r="D118" s="18"/>
+      <c r="E118" s="17">
         <v>50</v>
       </c>
-      <c r="F118" s="22"/>
+      <c r="F118" s="17">
+        <v>82</v>
+      </c>
       <c r="G118" s="11">
         <v>24</v>
       </c>
-      <c r="H118" s="17">
+      <c r="H118" s="22">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -4656,15 +4875,17 @@
       <c r="C119" s="11">
         <v>61</v>
       </c>
-      <c r="D119" s="16"/>
-      <c r="E119" s="20">
+      <c r="D119" s="18"/>
+      <c r="E119" s="17">
         <v>55</v>
       </c>
-      <c r="F119" s="22"/>
+      <c r="F119" s="17">
+        <v>56.5</v>
+      </c>
       <c r="G119" s="11">
         <v>43</v>
       </c>
-      <c r="H119" s="17">
+      <c r="H119" s="22">
         <v>80.645161290322577</v>
       </c>
     </row>
@@ -4678,15 +4899,17 @@
       <c r="C120" s="11">
         <v>45</v>
       </c>
-      <c r="D120" s="16"/>
-      <c r="E120" s="20">
+      <c r="D120" s="18"/>
+      <c r="E120" s="17">
         <v>64</v>
       </c>
-      <c r="F120" s="22"/>
+      <c r="F120" s="17">
+        <v>42.5</v>
+      </c>
       <c r="G120" s="11">
         <v>37</v>
       </c>
-      <c r="H120" s="17">
+      <c r="H120" s="22">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -4700,15 +4923,17 @@
       <c r="C121" s="11">
         <v>31</v>
       </c>
-      <c r="D121" s="16"/>
-      <c r="E121" s="20">
+      <c r="D121" s="18"/>
+      <c r="E121" s="17">
         <v>70</v>
       </c>
-      <c r="F121" s="22"/>
+      <c r="F121" s="17">
+        <v>59</v>
+      </c>
       <c r="G121" s="11">
         <v>28</v>
       </c>
-      <c r="H121" s="17">
+      <c r="H121" s="22">
         <v>67.741935483870961</v>
       </c>
     </row>
@@ -4722,15 +4947,17 @@
       <c r="C122" s="11">
         <v>15</v>
       </c>
-      <c r="D122" s="16"/>
-      <c r="E122" s="20">
+      <c r="D122" s="18"/>
+      <c r="E122" s="17">
         <v>46</v>
       </c>
-      <c r="F122" s="22"/>
+      <c r="F122" s="17">
+        <v>41.5</v>
+      </c>
       <c r="G122" s="11">
         <v>19</v>
       </c>
-      <c r="H122" s="17">
+      <c r="H122" s="22">
         <v>87.096774193548384</v>
       </c>
     </row>
@@ -4744,15 +4971,17 @@
       <c r="C123" s="11">
         <v>56</v>
       </c>
-      <c r="D123" s="16"/>
-      <c r="E123" s="20">
+      <c r="D123" s="18"/>
+      <c r="E123" s="17">
         <v>50</v>
       </c>
-      <c r="F123" s="22"/>
+      <c r="F123" s="17">
+        <v>59</v>
+      </c>
       <c r="G123" s="11">
         <v>34</v>
       </c>
-      <c r="H123" s="17">
+      <c r="H123" s="22">
         <v>83.870967741935488</v>
       </c>
     </row>
@@ -4766,15 +4995,17 @@
       <c r="C124" s="11">
         <v>27</v>
       </c>
-      <c r="D124" s="16"/>
-      <c r="E124" s="20">
+      <c r="D124" s="18"/>
+      <c r="E124" s="17">
         <v>47</v>
       </c>
-      <c r="F124" s="22"/>
+      <c r="F124" s="17">
+        <v>41.5</v>
+      </c>
       <c r="G124" s="11">
         <v>17</v>
       </c>
-      <c r="H124" s="17">
+      <c r="H124" s="22">
         <v>83.870967741935488</v>
       </c>
     </row>
@@ -4788,15 +5019,17 @@
       <c r="C125" s="11">
         <v>81</v>
       </c>
-      <c r="D125" s="16"/>
-      <c r="E125" s="20">
+      <c r="D125" s="18"/>
+      <c r="E125" s="17">
         <v>70</v>
       </c>
-      <c r="F125" s="22"/>
+      <c r="F125" s="17">
+        <v>77.5</v>
+      </c>
       <c r="G125" s="11">
         <v>73</v>
       </c>
-      <c r="H125" s="17">
+      <c r="H125" s="22">
         <v>96.774193548387103</v>
       </c>
     </row>
@@ -4810,15 +5043,17 @@
       <c r="C126" s="11">
         <v>44</v>
       </c>
-      <c r="D126" s="16"/>
-      <c r="E126" s="20">
+      <c r="D126" s="18"/>
+      <c r="E126" s="17">
         <v>87</v>
       </c>
-      <c r="F126" s="22"/>
+      <c r="F126" s="17">
+        <v>81.5</v>
+      </c>
       <c r="G126" s="11">
         <v>43</v>
       </c>
-      <c r="H126" s="17">
+      <c r="H126" s="22">
         <v>80.645161290322577</v>
       </c>
     </row>
@@ -4832,15 +5067,17 @@
       <c r="C127" s="11">
         <v>46</v>
       </c>
-      <c r="D127" s="16"/>
-      <c r="E127" s="20">
+      <c r="D127" s="18"/>
+      <c r="E127" s="17">
         <v>50</v>
       </c>
-      <c r="F127" s="22"/>
+      <c r="F127" s="17">
+        <v>51.5</v>
+      </c>
       <c r="G127" s="11">
         <v>45</v>
       </c>
-      <c r="H127" s="17">
+      <c r="H127" s="22">
         <v>83.870967741935488</v>
       </c>
     </row>
@@ -4854,15 +5091,17 @@
       <c r="C128" s="11">
         <v>48</v>
       </c>
-      <c r="D128" s="16"/>
-      <c r="E128" s="20">
+      <c r="D128" s="18"/>
+      <c r="E128" s="17">
         <v>47</v>
       </c>
-      <c r="F128" s="22"/>
+      <c r="F128" s="17">
+        <v>48.5</v>
+      </c>
       <c r="G128" s="11">
         <v>56</v>
       </c>
-      <c r="H128" s="17">
+      <c r="H128" s="22">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -4876,17 +5115,17 @@
       <c r="C129" s="11">
         <v>29</v>
       </c>
-      <c r="D129" s="16"/>
-      <c r="E129" s="20">
+      <c r="D129" s="18"/>
+      <c r="E129" s="17">
         <v>49</v>
       </c>
-      <c r="F129" s="22">
-        <v>0</v>
+      <c r="F129" s="17">
+        <v>56.5</v>
       </c>
       <c r="G129" s="11">
         <v>27</v>
       </c>
-      <c r="H129" s="17">
+      <c r="H129" s="22">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -4900,15 +5139,17 @@
       <c r="C130" s="11">
         <v>53</v>
       </c>
-      <c r="D130" s="16"/>
-      <c r="E130" s="20">
+      <c r="D130" s="18"/>
+      <c r="E130" s="17">
         <v>61</v>
       </c>
-      <c r="F130" s="22"/>
+      <c r="F130" s="17">
+        <v>37</v>
+      </c>
       <c r="G130" s="11">
         <v>33</v>
       </c>
-      <c r="H130" s="17">
+      <c r="H130" s="22">
         <v>67.741935483870961</v>
       </c>
     </row>
@@ -4922,15 +5163,17 @@
       <c r="C131" s="11">
         <v>50</v>
       </c>
-      <c r="D131" s="16"/>
-      <c r="E131" s="20">
+      <c r="D131" s="18"/>
+      <c r="E131" s="17">
         <v>61</v>
       </c>
-      <c r="F131" s="22"/>
+      <c r="F131" s="17">
+        <v>57</v>
+      </c>
       <c r="G131" s="11">
         <v>30</v>
       </c>
-      <c r="H131" s="17">
+      <c r="H131" s="22">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -4944,15 +5187,17 @@
       <c r="C132" s="11">
         <v>52</v>
       </c>
-      <c r="D132" s="16"/>
-      <c r="E132" s="20">
+      <c r="D132" s="18"/>
+      <c r="E132" s="17">
         <v>49</v>
       </c>
-      <c r="F132" s="22"/>
+      <c r="F132" s="17">
+        <v>50.5</v>
+      </c>
       <c r="G132" s="11">
         <v>42</v>
       </c>
-      <c r="H132" s="17">
+      <c r="H132" s="22">
         <v>83.870967741935488</v>
       </c>
     </row>
@@ -4966,15 +5211,17 @@
       <c r="C133" s="11">
         <v>69</v>
       </c>
-      <c r="D133" s="16"/>
-      <c r="E133" s="20">
+      <c r="D133" s="18"/>
+      <c r="E133" s="17">
         <v>60</v>
       </c>
-      <c r="F133" s="22"/>
+      <c r="F133" s="17">
+        <v>60.5</v>
+      </c>
       <c r="G133" s="11">
         <v>54</v>
       </c>
-      <c r="H133" s="17">
+      <c r="H133" s="22">
         <v>93.548387096774192</v>
       </c>
     </row>
@@ -4988,15 +5235,17 @@
       <c r="C134" s="11">
         <v>64</v>
       </c>
-      <c r="D134" s="16"/>
-      <c r="E134" s="20">
+      <c r="D134" s="18"/>
+      <c r="E134" s="17">
         <v>55</v>
       </c>
-      <c r="F134" s="22"/>
+      <c r="F134" s="17">
+        <v>67.5</v>
+      </c>
       <c r="G134" s="11">
         <v>34</v>
       </c>
-      <c r="H134" s="17">
+      <c r="H134" s="22">
         <v>96.774193548387103</v>
       </c>
     </row>
@@ -5010,15 +5259,17 @@
       <c r="C135" s="11">
         <v>35</v>
       </c>
-      <c r="D135" s="16"/>
-      <c r="E135" s="20">
+      <c r="D135" s="18"/>
+      <c r="E135" s="17">
         <v>70</v>
       </c>
-      <c r="F135" s="22"/>
+      <c r="F135" s="17">
+        <v>42</v>
+      </c>
       <c r="G135" s="11">
         <v>39</v>
       </c>
-      <c r="H135" s="17">
+      <c r="H135" s="22">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -5032,15 +5283,17 @@
       <c r="C136" s="11">
         <v>35</v>
       </c>
-      <c r="D136" s="16"/>
-      <c r="E136" s="20">
+      <c r="D136" s="18"/>
+      <c r="E136" s="17">
         <v>52</v>
       </c>
-      <c r="F136" s="22"/>
+      <c r="F136" s="17">
+        <v>30.5</v>
+      </c>
       <c r="G136" s="11">
         <v>29</v>
       </c>
-      <c r="H136" s="17">
+      <c r="H136" s="22">
         <v>80.645161290322577</v>
       </c>
     </row>
@@ -5054,15 +5307,17 @@
       <c r="C137" s="11">
         <v>61</v>
       </c>
-      <c r="D137" s="16"/>
-      <c r="E137" s="20">
+      <c r="D137" s="18"/>
+      <c r="E137" s="17">
         <v>55</v>
       </c>
-      <c r="F137" s="22"/>
+      <c r="F137" s="17">
+        <v>35.5</v>
+      </c>
       <c r="G137" s="11">
         <v>40</v>
       </c>
-      <c r="H137" s="17">
+      <c r="H137" s="22">
         <v>90.322580645161281</v>
       </c>
     </row>
@@ -5076,15 +5331,17 @@
       <c r="C138" s="11">
         <v>60</v>
       </c>
-      <c r="D138" s="16"/>
-      <c r="E138" s="20">
+      <c r="D138" s="18"/>
+      <c r="E138" s="17">
         <v>57</v>
       </c>
-      <c r="F138" s="22"/>
+      <c r="F138" s="17">
+        <v>56</v>
+      </c>
       <c r="G138" s="11">
         <v>44</v>
       </c>
-      <c r="H138" s="17">
+      <c r="H138" s="22">
         <v>93.548387096774192</v>
       </c>
     </row>
@@ -5098,15 +5355,17 @@
       <c r="C139" s="11">
         <v>47</v>
       </c>
-      <c r="D139" s="16"/>
-      <c r="E139" s="20">
+      <c r="D139" s="18"/>
+      <c r="E139" s="17">
         <v>52</v>
       </c>
-      <c r="F139" s="22"/>
+      <c r="F139" s="17">
+        <v>0</v>
+      </c>
       <c r="G139" s="11">
         <v>39</v>
       </c>
-      <c r="H139" s="17">
+      <c r="H139" s="22">
         <v>67.741935483870961</v>
       </c>
     </row>
@@ -5120,15 +5379,17 @@
       <c r="C140" s="11">
         <v>59</v>
       </c>
-      <c r="D140" s="16"/>
-      <c r="E140" s="20">
+      <c r="D140" s="18"/>
+      <c r="E140" s="17">
         <v>49</v>
       </c>
-      <c r="F140" s="22"/>
+      <c r="F140" s="17">
+        <v>17.5</v>
+      </c>
       <c r="G140" s="11">
         <v>29</v>
       </c>
-      <c r="H140" s="17">
+      <c r="H140" s="22">
         <v>67.741935483870961</v>
       </c>
     </row>
@@ -5142,15 +5403,17 @@
       <c r="C141" s="11">
         <v>44</v>
       </c>
-      <c r="D141" s="16"/>
-      <c r="E141" s="20">
+      <c r="D141" s="18"/>
+      <c r="E141" s="17">
         <v>70</v>
       </c>
-      <c r="F141" s="22"/>
+      <c r="F141" s="17">
+        <v>62</v>
+      </c>
       <c r="G141" s="11">
         <v>15</v>
       </c>
-      <c r="H141" s="17">
+      <c r="H141" s="22">
         <v>54.838709677419352</v>
       </c>
     </row>
@@ -5164,15 +5427,17 @@
       <c r="C142" s="11">
         <v>40</v>
       </c>
-      <c r="D142" s="16"/>
-      <c r="E142" s="20">
+      <c r="D142" s="18"/>
+      <c r="E142" s="17">
         <v>70</v>
       </c>
-      <c r="F142" s="22"/>
+      <c r="F142" s="17">
+        <v>50.5</v>
+      </c>
       <c r="G142" s="11">
         <v>35</v>
       </c>
-      <c r="H142" s="17">
+      <c r="H142" s="22">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -5186,15 +5451,17 @@
       <c r="C143" s="11">
         <v>57</v>
       </c>
-      <c r="D143" s="16"/>
-      <c r="E143" s="20">
+      <c r="D143" s="18"/>
+      <c r="E143" s="17">
         <v>57</v>
       </c>
-      <c r="F143" s="22"/>
+      <c r="F143" s="17">
+        <v>72.5</v>
+      </c>
       <c r="G143" s="11">
         <v>66</v>
       </c>
-      <c r="H143" s="17">
+      <c r="H143" s="22">
         <v>80.645161290322577</v>
       </c>
     </row>
@@ -5208,15 +5475,17 @@
       <c r="C144" s="11">
         <v>57</v>
       </c>
-      <c r="D144" s="16"/>
-      <c r="E144" s="20">
+      <c r="D144" s="18"/>
+      <c r="E144" s="17">
         <v>57</v>
       </c>
-      <c r="F144" s="22"/>
+      <c r="F144" s="17">
+        <v>57.5</v>
+      </c>
       <c r="G144" s="11">
         <v>37</v>
       </c>
-      <c r="H144" s="17">
+      <c r="H144" s="22">
         <v>90.322580645161281</v>
       </c>
     </row>
@@ -5230,15 +5499,17 @@
       <c r="C145" s="11">
         <v>42</v>
       </c>
-      <c r="D145" s="16"/>
-      <c r="E145" s="20">
+      <c r="D145" s="18"/>
+      <c r="E145" s="17">
         <v>47</v>
       </c>
-      <c r="F145" s="22"/>
+      <c r="F145" s="17">
+        <v>71.5</v>
+      </c>
       <c r="G145" s="11">
         <v>29</v>
       </c>
-      <c r="H145" s="17">
+      <c r="H145" s="22">
         <v>87.096774193548384</v>
       </c>
     </row>
@@ -5252,15 +5523,17 @@
       <c r="C146" s="11">
         <v>58</v>
       </c>
-      <c r="D146" s="16"/>
-      <c r="E146" s="20">
+      <c r="D146" s="18"/>
+      <c r="E146" s="17">
         <v>44</v>
       </c>
-      <c r="F146" s="22"/>
+      <c r="F146" s="17">
+        <v>76.5</v>
+      </c>
       <c r="G146" s="11">
         <v>45</v>
       </c>
-      <c r="H146" s="17">
+      <c r="H146" s="22">
         <v>80.645161290322577</v>
       </c>
     </row>
@@ -5274,17 +5547,17 @@
       <c r="C147" s="11">
         <v>48</v>
       </c>
-      <c r="D147" s="16"/>
-      <c r="E147" s="20">
+      <c r="D147" s="18"/>
+      <c r="E147" s="17">
         <v>70</v>
       </c>
-      <c r="F147" s="22">
-        <v>0</v>
+      <c r="F147" s="17">
+        <v>60</v>
       </c>
       <c r="G147" s="11">
         <v>37</v>
       </c>
-      <c r="H147" s="17">
+      <c r="H147" s="22">
         <v>83.870967741935488</v>
       </c>
     </row>
@@ -5298,15 +5571,17 @@
       <c r="C148" s="11">
         <v>67</v>
       </c>
-      <c r="D148" s="16"/>
-      <c r="E148" s="20">
+      <c r="D148" s="18"/>
+      <c r="E148" s="17">
         <v>64</v>
       </c>
-      <c r="F148" s="22"/>
+      <c r="F148" s="17">
+        <v>40</v>
+      </c>
       <c r="G148" s="11">
         <v>63</v>
       </c>
-      <c r="H148" s="17">
+      <c r="H148" s="22">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -5320,15 +5595,17 @@
       <c r="C149" s="11">
         <v>65</v>
       </c>
-      <c r="D149" s="16"/>
-      <c r="E149" s="20">
+      <c r="D149" s="18"/>
+      <c r="E149" s="17">
         <v>55</v>
       </c>
-      <c r="F149" s="22"/>
+      <c r="F149" s="17">
+        <v>56</v>
+      </c>
       <c r="G149" s="11">
         <v>48</v>
       </c>
-      <c r="H149" s="17">
+      <c r="H149" s="22">
         <v>80.645161290322577</v>
       </c>
     </row>
@@ -5342,15 +5619,17 @@
       <c r="C150" s="11">
         <v>22</v>
       </c>
-      <c r="D150" s="16"/>
-      <c r="E150" s="20">
+      <c r="D150" s="18"/>
+      <c r="E150" s="17">
         <v>52</v>
       </c>
-      <c r="F150" s="22"/>
+      <c r="F150" s="17">
+        <v>68</v>
+      </c>
       <c r="G150" s="11">
         <v>30</v>
       </c>
-      <c r="H150" s="17">
+      <c r="H150" s="22">
         <v>61.29032258064516</v>
       </c>
     </row>
@@ -5364,15 +5643,17 @@
       <c r="C151" s="11">
         <v>66</v>
       </c>
-      <c r="D151" s="16"/>
-      <c r="E151" s="20">
+      <c r="D151" s="18"/>
+      <c r="E151" s="17">
         <v>46</v>
       </c>
-      <c r="F151" s="22"/>
+      <c r="F151" s="17">
+        <v>46.5</v>
+      </c>
       <c r="G151" s="11">
         <v>17</v>
       </c>
-      <c r="H151" s="17">
+      <c r="H151" s="22">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -5386,17 +5667,17 @@
       <c r="C152" s="11">
         <v>49</v>
       </c>
-      <c r="D152" s="16"/>
-      <c r="E152" s="20">
+      <c r="D152" s="18"/>
+      <c r="E152" s="17">
         <v>52</v>
       </c>
-      <c r="F152" s="22">
-        <v>0</v>
+      <c r="F152" s="17">
+        <v>26.5</v>
       </c>
       <c r="G152" s="11">
         <v>26</v>
       </c>
-      <c r="H152" s="17">
+      <c r="H152" s="22">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -5410,15 +5691,17 @@
       <c r="C153" s="11">
         <v>42</v>
       </c>
-      <c r="D153" s="16"/>
-      <c r="E153" s="20">
+      <c r="D153" s="18"/>
+      <c r="E153" s="17">
         <v>70</v>
       </c>
-      <c r="F153" s="22"/>
+      <c r="F153" s="17">
+        <v>61</v>
+      </c>
       <c r="G153" s="11">
         <v>31</v>
       </c>
-      <c r="H153" s="17">
+      <c r="H153" s="22">
         <v>51.612903225806448</v>
       </c>
     </row>
@@ -5432,15 +5715,17 @@
       <c r="C154" s="11">
         <v>59</v>
       </c>
-      <c r="D154" s="16"/>
-      <c r="E154" s="20">
+      <c r="D154" s="18"/>
+      <c r="E154" s="17">
         <v>55</v>
       </c>
-      <c r="F154" s="22"/>
+      <c r="F154" s="17">
+        <v>60</v>
+      </c>
       <c r="G154" s="11">
         <v>65</v>
       </c>
-      <c r="H154" s="17">
+      <c r="H154" s="22">
         <v>80.645161290322577</v>
       </c>
     </row>
@@ -5454,15 +5739,17 @@
       <c r="C155" s="11">
         <v>45</v>
       </c>
-      <c r="D155" s="16"/>
-      <c r="E155" s="20">
+      <c r="D155" s="18"/>
+      <c r="E155" s="17">
         <v>55</v>
       </c>
-      <c r="F155" s="22"/>
+      <c r="F155" s="17">
+        <v>28</v>
+      </c>
       <c r="G155" s="11">
         <v>36</v>
       </c>
-      <c r="H155" s="17">
+      <c r="H155" s="22">
         <v>64.516129032258064</v>
       </c>
     </row>
@@ -5476,15 +5763,17 @@
       <c r="C156" s="11">
         <v>76</v>
       </c>
-      <c r="D156" s="16"/>
-      <c r="E156" s="20">
+      <c r="D156" s="18"/>
+      <c r="E156" s="17">
         <v>55</v>
       </c>
-      <c r="F156" s="22"/>
+      <c r="F156" s="17">
+        <v>53.5</v>
+      </c>
       <c r="G156" s="11">
         <v>34</v>
       </c>
-      <c r="H156" s="17">
+      <c r="H156" s="22">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -5498,15 +5787,17 @@
       <c r="C157" s="11">
         <v>47</v>
       </c>
-      <c r="D157" s="16"/>
-      <c r="E157" s="20">
+      <c r="D157" s="18"/>
+      <c r="E157" s="17">
         <v>50</v>
       </c>
-      <c r="F157" s="22"/>
+      <c r="F157" s="17">
+        <v>53</v>
+      </c>
       <c r="G157" s="11">
         <v>39</v>
       </c>
-      <c r="H157" s="17">
+      <c r="H157" s="22">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -5520,15 +5811,17 @@
       <c r="C158" s="11">
         <v>52</v>
       </c>
-      <c r="D158" s="16"/>
-      <c r="E158" s="20">
+      <c r="D158" s="18"/>
+      <c r="E158" s="17">
         <v>57</v>
       </c>
-      <c r="F158" s="22"/>
+      <c r="F158" s="17">
+        <v>40.5</v>
+      </c>
       <c r="G158" s="11">
         <v>45</v>
       </c>
-      <c r="H158" s="17">
+      <c r="H158" s="22">
         <v>67.741935483870961</v>
       </c>
     </row>
@@ -5542,15 +5835,17 @@
       <c r="C159" s="11">
         <v>38</v>
       </c>
-      <c r="D159" s="16"/>
-      <c r="E159" s="20">
+      <c r="D159" s="18"/>
+      <c r="E159" s="17">
         <v>50</v>
       </c>
-      <c r="F159" s="22"/>
+      <c r="F159" s="17">
+        <v>33.5</v>
+      </c>
       <c r="G159" s="11">
         <v>43</v>
       </c>
-      <c r="H159" s="17">
+      <c r="H159" s="22">
         <v>74.193548387096769</v>
       </c>
     </row>
@@ -5564,15 +5859,17 @@
       <c r="C160" s="11">
         <v>59</v>
       </c>
-      <c r="D160" s="16"/>
-      <c r="E160" s="20">
+      <c r="D160" s="18"/>
+      <c r="E160" s="17">
         <v>50</v>
       </c>
-      <c r="F160" s="22"/>
+      <c r="F160" s="17">
+        <v>73</v>
+      </c>
       <c r="G160" s="11">
         <v>40</v>
       </c>
-      <c r="H160" s="17">
+      <c r="H160" s="22">
         <v>100</v>
       </c>
     </row>
@@ -5586,17 +5883,17 @@
       <c r="C161" s="11">
         <v>42</v>
       </c>
-      <c r="D161" s="16"/>
-      <c r="E161" s="20">
+      <c r="D161" s="18"/>
+      <c r="E161" s="17">
         <v>46</v>
       </c>
-      <c r="F161" s="22">
-        <v>0</v>
+      <c r="F161" s="17">
+        <v>51.5</v>
       </c>
       <c r="G161" s="11">
         <v>39</v>
       </c>
-      <c r="H161" s="17">
+      <c r="H161" s="22">
         <v>74.193548387096769</v>
       </c>
     </row>
@@ -5610,15 +5907,17 @@
       <c r="C162" s="11">
         <v>54</v>
       </c>
-      <c r="D162" s="16"/>
-      <c r="E162" s="20">
+      <c r="D162" s="18"/>
+      <c r="E162" s="17">
         <v>44</v>
       </c>
-      <c r="F162" s="22"/>
+      <c r="F162" s="17">
+        <v>40</v>
+      </c>
       <c r="G162" s="11">
         <v>18</v>
       </c>
-      <c r="H162" s="17">
+      <c r="H162" s="22">
         <v>74.193548387096769</v>
       </c>
     </row>
@@ -5632,15 +5931,17 @@
       <c r="C163" s="11">
         <v>50</v>
       </c>
-      <c r="D163" s="16"/>
-      <c r="E163" s="20">
+      <c r="D163" s="18"/>
+      <c r="E163" s="17">
         <v>60</v>
       </c>
-      <c r="F163" s="22"/>
+      <c r="F163" s="17">
+        <v>60</v>
+      </c>
       <c r="G163" s="11">
         <v>45</v>
       </c>
-      <c r="H163" s="17">
+      <c r="H163" s="22">
         <v>87.096774193548384</v>
       </c>
     </row>
@@ -5654,17 +5955,17 @@
       <c r="C164" s="11">
         <v>48</v>
       </c>
-      <c r="D164" s="16"/>
-      <c r="E164" s="20">
+      <c r="D164" s="18"/>
+      <c r="E164" s="17">
         <v>49</v>
       </c>
-      <c r="F164" s="22">
-        <v>0</v>
+      <c r="F164" s="17">
+        <v>66.5</v>
       </c>
       <c r="G164" s="11">
         <v>45</v>
       </c>
-      <c r="H164" s="17">
+      <c r="H164" s="22">
         <v>83.870967741935488</v>
       </c>
     </row>
@@ -5678,15 +5979,17 @@
       <c r="C165" s="11">
         <v>67</v>
       </c>
-      <c r="D165" s="16"/>
-      <c r="E165" s="20">
+      <c r="D165" s="18"/>
+      <c r="E165" s="17">
         <v>49</v>
       </c>
-      <c r="F165" s="22"/>
+      <c r="F165" s="17">
+        <v>72</v>
+      </c>
       <c r="G165" s="11">
         <v>69</v>
       </c>
-      <c r="H165" s="17">
+      <c r="H165" s="22">
         <v>66.666666666666657</v>
       </c>
     </row>
@@ -5700,15 +6003,17 @@
       <c r="C166" s="11">
         <v>59</v>
       </c>
-      <c r="D166" s="16"/>
-      <c r="E166" s="20">
+      <c r="D166" s="18"/>
+      <c r="E166" s="17">
         <v>37</v>
       </c>
-      <c r="F166" s="22"/>
+      <c r="F166" s="17">
+        <v>64</v>
+      </c>
       <c r="G166" s="11">
         <v>43</v>
       </c>
-      <c r="H166" s="17">
+      <c r="H166" s="22">
         <v>80.645161290322577</v>
       </c>
     </row>
@@ -5722,15 +6027,17 @@
       <c r="C167" s="11">
         <v>41</v>
       </c>
-      <c r="D167" s="16"/>
-      <c r="E167" s="20">
+      <c r="D167" s="18"/>
+      <c r="E167" s="17">
         <v>60</v>
       </c>
-      <c r="F167" s="22"/>
+      <c r="F167" s="17">
+        <v>40.5</v>
+      </c>
       <c r="G167" s="11">
         <v>27</v>
       </c>
-      <c r="H167" s="17">
+      <c r="H167" s="22">
         <v>80.645161290322577</v>
       </c>
     </row>
@@ -5744,15 +6051,17 @@
       <c r="C168" s="11">
         <v>50</v>
       </c>
-      <c r="D168" s="16"/>
-      <c r="E168" s="20">
+      <c r="D168" s="18"/>
+      <c r="E168" s="17">
         <v>50</v>
       </c>
-      <c r="F168" s="22"/>
+      <c r="F168" s="17">
+        <v>62</v>
+      </c>
       <c r="G168" s="11">
         <v>36</v>
       </c>
-      <c r="H168" s="17">
+      <c r="H168" s="22">
         <v>90.322580645161281</v>
       </c>
     </row>
@@ -5766,15 +6075,17 @@
       <c r="C169" s="11">
         <v>51</v>
       </c>
-      <c r="D169" s="16"/>
-      <c r="E169" s="20">
+      <c r="D169" s="18"/>
+      <c r="E169" s="17">
         <v>47</v>
       </c>
-      <c r="F169" s="22"/>
+      <c r="F169" s="17">
+        <v>40</v>
+      </c>
       <c r="G169" s="11">
         <v>34</v>
       </c>
-      <c r="H169" s="17">
+      <c r="H169" s="22">
         <v>83.870967741935488</v>
       </c>
     </row>
@@ -5788,15 +6099,17 @@
       <c r="C170" s="11">
         <v>59</v>
       </c>
-      <c r="D170" s="16"/>
-      <c r="E170" s="20">
+      <c r="D170" s="18"/>
+      <c r="E170" s="17">
         <v>57</v>
       </c>
-      <c r="F170" s="22"/>
+      <c r="F170" s="17">
+        <v>79</v>
+      </c>
       <c r="G170" s="11">
         <v>18</v>
       </c>
-      <c r="H170" s="17">
+      <c r="H170" s="22">
         <v>74.193548387096769</v>
       </c>
     </row>
@@ -5810,15 +6123,17 @@
       <c r="C171" s="11">
         <v>47</v>
       </c>
-      <c r="D171" s="16"/>
-      <c r="E171" s="20">
+      <c r="D171" s="18"/>
+      <c r="E171" s="17">
         <v>49</v>
       </c>
-      <c r="F171" s="22"/>
+      <c r="F171" s="17">
+        <v>75</v>
+      </c>
       <c r="G171" s="11">
         <v>56</v>
       </c>
-      <c r="H171" s="17">
+      <c r="H171" s="22">
         <v>87.096774193548384</v>
       </c>
     </row>
@@ -5832,20 +6147,22 @@
       <c r="C172" s="11">
         <v>59</v>
       </c>
-      <c r="D172" s="16"/>
-      <c r="E172" s="20">
+      <c r="D172" s="18"/>
+      <c r="E172" s="17">
         <v>55</v>
       </c>
-      <c r="F172" s="22"/>
+      <c r="F172" s="17">
+        <v>74.5</v>
+      </c>
       <c r="G172" s="11">
         <v>69</v>
       </c>
-      <c r="H172" s="17">
+      <c r="H172" s="22">
         <v>83.870967741935488</v>
       </c>
     </row>
     <row r="173" spans="1:8" ht="15.75">
-      <c r="A173" s="18" t="s">
+      <c r="A173" s="16" t="s">
         <v>350</v>
       </c>
       <c r="B173" s="15" t="s">
@@ -5854,20 +6171,22 @@
       <c r="C173" s="11">
         <v>58</v>
       </c>
-      <c r="D173" s="16"/>
-      <c r="E173" s="20">
+      <c r="D173" s="18"/>
+      <c r="E173" s="17">
         <v>55</v>
       </c>
-      <c r="F173" s="22"/>
+      <c r="F173" s="17">
+        <v>59.5</v>
+      </c>
       <c r="G173" s="11">
         <v>45</v>
       </c>
-      <c r="H173" s="17">
+      <c r="H173" s="22">
         <v>80.645161290322577</v>
       </c>
     </row>
     <row r="174" spans="1:8" ht="15.75">
-      <c r="A174" s="18" t="s">
+      <c r="A174" s="16" t="s">
         <v>352</v>
       </c>
       <c r="B174" s="15" t="s">
@@ -5876,20 +6195,22 @@
       <c r="C174" s="11">
         <v>49</v>
       </c>
-      <c r="D174" s="16"/>
-      <c r="E174" s="20">
+      <c r="D174" s="18"/>
+      <c r="E174" s="17">
         <v>47</v>
       </c>
-      <c r="F174" s="22"/>
+      <c r="F174" s="17">
+        <v>48.5</v>
+      </c>
       <c r="G174" s="11">
         <v>60</v>
       </c>
-      <c r="H174" s="17">
+      <c r="H174" s="22">
         <v>80.645161290322577</v>
       </c>
     </row>
     <row r="175" spans="1:8" ht="15.75">
-      <c r="A175" s="18" t="s">
+      <c r="A175" s="16" t="s">
         <v>354</v>
       </c>
       <c r="B175" s="15" t="s">
@@ -5898,20 +6219,22 @@
       <c r="C175" s="11">
         <v>45</v>
       </c>
-      <c r="D175" s="16"/>
-      <c r="E175" s="20">
+      <c r="D175" s="18"/>
+      <c r="E175" s="17">
         <v>60</v>
       </c>
-      <c r="F175" s="22"/>
+      <c r="F175" s="17">
+        <v>23.5</v>
+      </c>
       <c r="G175" s="11">
         <v>46</v>
       </c>
-      <c r="H175" s="17">
+      <c r="H175" s="22">
         <v>74.193548387096769</v>
       </c>
     </row>
     <row r="176" spans="1:8" ht="15.75">
-      <c r="A176" s="18" t="s">
+      <c r="A176" s="16" t="s">
         <v>356</v>
       </c>
       <c r="B176" s="15" t="s">
@@ -5920,20 +6243,22 @@
       <c r="C176" s="11">
         <v>64</v>
       </c>
-      <c r="D176" s="16"/>
-      <c r="E176" s="20">
+      <c r="D176" s="18"/>
+      <c r="E176" s="17">
         <v>49</v>
       </c>
-      <c r="F176" s="22"/>
+      <c r="F176" s="17">
+        <v>69.5</v>
+      </c>
       <c r="G176" s="11">
         <v>55</v>
       </c>
-      <c r="H176" s="17">
+      <c r="H176" s="22">
         <v>74.193548387096769</v>
       </c>
     </row>
     <row r="177" spans="1:8" ht="15.75">
-      <c r="A177" s="18" t="s">
+      <c r="A177" s="16" t="s">
         <v>358</v>
       </c>
       <c r="B177" s="15" t="s">
@@ -5942,20 +6267,22 @@
       <c r="C177" s="11">
         <v>62</v>
       </c>
-      <c r="D177" s="16"/>
-      <c r="E177" s="20">
+      <c r="D177" s="18"/>
+      <c r="E177" s="17">
         <v>47</v>
       </c>
-      <c r="F177" s="22"/>
+      <c r="F177" s="17">
+        <v>66.5</v>
+      </c>
       <c r="G177" s="11">
         <v>42</v>
       </c>
-      <c r="H177" s="17">
+      <c r="H177" s="22">
         <v>80.645161290322577</v>
       </c>
     </row>
     <row r="178" spans="1:8" ht="15.75">
-      <c r="A178" s="18" t="s">
+      <c r="A178" s="16" t="s">
         <v>360</v>
       </c>
       <c r="B178" s="15" t="s">
@@ -5964,20 +6291,22 @@
       <c r="C178" s="11">
         <v>79</v>
       </c>
-      <c r="D178" s="16"/>
-      <c r="E178" s="20">
+      <c r="D178" s="18"/>
+      <c r="E178" s="17">
         <v>52</v>
       </c>
-      <c r="F178" s="22"/>
+      <c r="F178" s="17">
+        <v>96.5</v>
+      </c>
       <c r="G178" s="11">
         <v>49</v>
       </c>
-      <c r="H178" s="17">
+      <c r="H178" s="22">
         <v>77.41935483870968</v>
       </c>
     </row>
     <row r="179" spans="1:8" ht="15.75">
-      <c r="A179" s="18" t="s">
+      <c r="A179" s="16" t="s">
         <v>362</v>
       </c>
       <c r="B179" s="15" t="s">
@@ -5986,20 +6315,22 @@
       <c r="C179" s="11">
         <v>65</v>
       </c>
-      <c r="D179" s="16"/>
-      <c r="E179" s="20">
+      <c r="D179" s="18"/>
+      <c r="E179" s="17">
         <v>49</v>
       </c>
-      <c r="F179" s="22"/>
+      <c r="F179" s="17">
+        <v>55</v>
+      </c>
       <c r="G179" s="11">
         <v>35</v>
       </c>
-      <c r="H179" s="17">
+      <c r="H179" s="22">
         <v>93.548387096774192</v>
       </c>
     </row>
     <row r="180" spans="1:8" ht="15.75">
-      <c r="A180" s="18" t="s">
+      <c r="A180" s="16" t="s">
         <v>364</v>
       </c>
       <c r="B180" s="15" t="s">
@@ -6008,20 +6339,22 @@
       <c r="C180" s="11">
         <v>49</v>
       </c>
-      <c r="D180" s="16"/>
-      <c r="E180" s="20">
+      <c r="D180" s="18"/>
+      <c r="E180" s="17">
         <v>52</v>
       </c>
-      <c r="F180" s="22"/>
+      <c r="F180" s="17">
+        <v>71.5</v>
+      </c>
       <c r="G180" s="11">
         <v>46</v>
       </c>
-      <c r="H180" s="17">
+      <c r="H180" s="22">
         <v>74.193548387096769</v>
       </c>
     </row>
     <row r="181" spans="1:8" ht="15.75">
-      <c r="A181" s="18" t="s">
+      <c r="A181" s="16" t="s">
         <v>366</v>
       </c>
       <c r="B181" s="15" t="s">
@@ -6030,20 +6363,22 @@
       <c r="C181" s="11">
         <v>55</v>
       </c>
-      <c r="D181" s="16"/>
-      <c r="E181" s="20">
+      <c r="D181" s="18"/>
+      <c r="E181" s="17">
         <v>50</v>
       </c>
-      <c r="F181" s="22"/>
+      <c r="F181" s="17">
+        <v>49.5</v>
+      </c>
       <c r="G181" s="11">
         <v>19</v>
       </c>
-      <c r="H181" s="17">
+      <c r="H181" s="22">
         <v>70.967741935483872</v>
       </c>
     </row>
     <row r="182" spans="1:8" ht="15.75">
-      <c r="A182" s="18" t="s">
+      <c r="A182" s="16" t="s">
         <v>368</v>
       </c>
       <c r="B182" s="15" t="s">
@@ -6052,20 +6387,22 @@
       <c r="C182" s="11">
         <v>19</v>
       </c>
-      <c r="D182" s="16"/>
-      <c r="E182" s="20">
+      <c r="D182" s="18"/>
+      <c r="E182" s="17">
         <v>64</v>
       </c>
-      <c r="F182" s="22"/>
+      <c r="F182" s="17">
+        <v>32.5</v>
+      </c>
       <c r="G182" s="11">
         <v>11</v>
       </c>
-      <c r="H182" s="17">
+      <c r="H182" s="22">
         <v>64.516129032258064</v>
       </c>
     </row>
     <row r="183" spans="1:8" ht="15.75">
-      <c r="A183" s="18" t="s">
+      <c r="A183" s="16" t="s">
         <v>370</v>
       </c>
       <c r="B183" s="15" t="s">
@@ -6074,22 +6411,22 @@
       <c r="C183" s="11">
         <v>22</v>
       </c>
-      <c r="D183" s="16"/>
-      <c r="E183" s="20">
+      <c r="D183" s="18"/>
+      <c r="E183" s="17">
         <v>47</v>
       </c>
-      <c r="F183" s="22">
-        <v>0</v>
+      <c r="F183" s="17">
+        <v>71</v>
       </c>
       <c r="G183" s="11">
         <v>28</v>
       </c>
-      <c r="H183" s="17">
+      <c r="H183" s="22">
         <v>77.41935483870968</v>
       </c>
     </row>
     <row r="184" spans="1:8" ht="15.75">
-      <c r="A184" s="18" t="s">
+      <c r="A184" s="16" t="s">
         <v>372</v>
       </c>
       <c r="B184" s="15" t="s">
@@ -6098,20 +6435,22 @@
       <c r="C184" s="11">
         <v>63</v>
       </c>
-      <c r="D184" s="16"/>
-      <c r="E184" s="20">
+      <c r="D184" s="18"/>
+      <c r="E184" s="17">
         <v>47</v>
       </c>
-      <c r="F184" s="22"/>
+      <c r="F184" s="17">
+        <v>28.5</v>
+      </c>
       <c r="G184" s="11">
         <v>61</v>
       </c>
-      <c r="H184" s="17">
+      <c r="H184" s="22">
         <v>54.838709677419352</v>
       </c>
     </row>
     <row r="185" spans="1:8" ht="15.75">
-      <c r="A185" s="18" t="s">
+      <c r="A185" s="16" t="s">
         <v>374</v>
       </c>
       <c r="B185" s="15" t="s">
@@ -6120,20 +6459,22 @@
       <c r="C185" s="11">
         <v>76</v>
       </c>
-      <c r="D185" s="16"/>
-      <c r="E185" s="20">
+      <c r="D185" s="18"/>
+      <c r="E185" s="17">
         <v>44</v>
       </c>
-      <c r="F185" s="22"/>
+      <c r="F185" s="17">
+        <v>60.5</v>
+      </c>
       <c r="G185" s="11">
         <v>56</v>
       </c>
-      <c r="H185" s="17">
+      <c r="H185" s="22">
         <v>87.096774193548384</v>
       </c>
     </row>
     <row r="186" spans="1:8" ht="15.75">
-      <c r="A186" s="18" t="s">
+      <c r="A186" s="16" t="s">
         <v>376</v>
       </c>
       <c r="B186" s="15" t="s">
@@ -6142,20 +6483,22 @@
       <c r="C186" s="11">
         <v>77</v>
       </c>
-      <c r="D186" s="16"/>
-      <c r="E186" s="20">
+      <c r="D186" s="18"/>
+      <c r="E186" s="17">
         <v>44</v>
       </c>
-      <c r="F186" s="22"/>
+      <c r="F186" s="17">
+        <v>61</v>
+      </c>
       <c r="G186" s="11">
         <v>64</v>
       </c>
-      <c r="H186" s="17">
+      <c r="H186" s="22">
         <v>83.333333333333343</v>
       </c>
     </row>
     <row r="187" spans="1:8">
-      <c r="A187" s="18" t="s">
+      <c r="A187" s="16" t="s">
         <v>378</v>
       </c>
       <c r="B187" s="1" t="s">
@@ -6164,20 +6507,22 @@
       <c r="C187" s="11">
         <v>52</v>
       </c>
-      <c r="D187" s="16"/>
-      <c r="E187" s="20">
+      <c r="D187" s="18"/>
+      <c r="E187" s="17">
         <v>43</v>
       </c>
-      <c r="F187" s="22"/>
+      <c r="F187" s="17">
+        <v>0.5</v>
+      </c>
       <c r="G187" s="11">
         <v>46</v>
       </c>
-      <c r="H187" s="17">
+      <c r="H187" s="22">
         <v>62.5</v>
       </c>
     </row>
     <row r="188" spans="1:8">
-      <c r="A188" s="18" t="s">
+      <c r="A188" s="16" t="s">
         <v>380</v>
       </c>
       <c r="B188" s="1" t="s">
@@ -6186,20 +6531,22 @@
       <c r="C188" s="11">
         <v>50</v>
       </c>
-      <c r="D188" s="16"/>
-      <c r="E188" s="20">
+      <c r="D188" s="18"/>
+      <c r="E188" s="17">
         <v>43</v>
       </c>
-      <c r="F188" s="22"/>
+      <c r="F188" s="17">
+        <v>38.5</v>
+      </c>
       <c r="G188" s="11">
         <v>28</v>
       </c>
-      <c r="H188" s="17">
+      <c r="H188" s="22">
         <v>83.333333333333343</v>
       </c>
     </row>
     <row r="189" spans="1:8">
-      <c r="A189" s="18" t="s">
+      <c r="A189" s="16" t="s">
         <v>382</v>
       </c>
       <c r="B189" s="1" t="s">
@@ -6208,20 +6555,22 @@
       <c r="C189" s="11">
         <v>51</v>
       </c>
-      <c r="D189" s="16"/>
-      <c r="E189" s="20">
+      <c r="D189" s="18"/>
+      <c r="E189" s="17">
         <v>43</v>
       </c>
-      <c r="F189" s="22"/>
+      <c r="F189" s="17">
+        <v>17.5</v>
+      </c>
       <c r="G189" s="11">
         <v>41</v>
       </c>
-      <c r="H189" s="17">
+      <c r="H189" s="22">
         <v>79.166666666666657</v>
       </c>
     </row>
     <row r="190" spans="1:8">
-      <c r="A190" s="18" t="s">
+      <c r="A190" s="16" t="s">
         <v>384</v>
       </c>
       <c r="B190" s="1" t="s">
@@ -6230,22 +6579,22 @@
       <c r="C190" s="11">
         <v>63</v>
       </c>
-      <c r="D190" s="16"/>
-      <c r="E190" s="20">
+      <c r="D190" s="18"/>
+      <c r="E190" s="17">
         <v>44</v>
       </c>
-      <c r="F190" s="22">
-        <v>0</v>
+      <c r="F190" s="17">
+        <v>72.5</v>
       </c>
       <c r="G190" s="11">
         <v>55</v>
       </c>
-      <c r="H190" s="17">
+      <c r="H190" s="22">
         <v>75</v>
       </c>
     </row>
     <row r="191" spans="1:8">
-      <c r="A191" s="18" t="s">
+      <c r="A191" s="16" t="s">
         <v>386</v>
       </c>
       <c r="B191" s="1" t="s">
@@ -6254,20 +6603,22 @@
       <c r="C191" s="11">
         <v>57</v>
       </c>
-      <c r="D191" s="16"/>
-      <c r="E191" s="20">
+      <c r="D191" s="18"/>
+      <c r="E191" s="17">
         <v>44</v>
       </c>
-      <c r="F191" s="22"/>
+      <c r="F191" s="17">
+        <v>55.5</v>
+      </c>
       <c r="G191" s="11">
         <v>38</v>
       </c>
-      <c r="H191" s="17">
+      <c r="H191" s="22">
         <v>75</v>
       </c>
     </row>
     <row r="192" spans="1:8">
-      <c r="A192" s="18" t="s">
+      <c r="A192" s="16" t="s">
         <v>388</v>
       </c>
       <c r="B192" s="1" t="s">
@@ -6276,22 +6627,22 @@
       <c r="C192" s="11">
         <v>55</v>
       </c>
-      <c r="D192" s="16"/>
-      <c r="E192" s="20">
+      <c r="D192" s="18"/>
+      <c r="E192" s="17">
         <v>43</v>
       </c>
-      <c r="F192" s="22">
-        <v>0</v>
+      <c r="F192" s="17">
+        <v>43.5</v>
       </c>
       <c r="G192" s="11">
         <v>30</v>
       </c>
-      <c r="H192" s="17">
+      <c r="H192" s="22">
         <v>83.333333333333343</v>
       </c>
     </row>
-    <row r="193" spans="1:8" ht="16.5">
-      <c r="A193" s="18" t="s">
+    <row r="193" spans="1:8">
+      <c r="A193" s="16" t="s">
         <v>390</v>
       </c>
       <c r="B193" s="1" t="s">
@@ -6300,19 +6651,21 @@
       <c r="C193" s="11">
         <v>35</v>
       </c>
-      <c r="D193" s="16"/>
-      <c r="E193" s="20">
+      <c r="D193" s="18"/>
+      <c r="E193" s="17">
         <v>43</v>
       </c>
-      <c r="F193" s="21"/>
+      <c r="F193" s="17">
+        <v>24.5</v>
+      </c>
       <c r="G193" s="11">
         <v>22</v>
       </c>
-      <c r="H193" s="17">
+      <c r="H193" s="22">
         <v>58.333333333333336</v>
       </c>
     </row>
-    <row r="194" spans="1:8" ht="16.5">
+    <row r="194" spans="1:8">
       <c r="A194" s="4" t="s">
         <v>392</v>
       </c>
@@ -6322,15 +6675,17 @@
       <c r="C194" s="11">
         <v>23</v>
       </c>
-      <c r="D194" s="16"/>
-      <c r="E194" s="20">
+      <c r="D194" s="18"/>
+      <c r="E194" s="17">
         <v>47</v>
       </c>
-      <c r="F194" s="21"/>
+      <c r="F194" s="17">
+        <v>65.5</v>
+      </c>
       <c r="G194" s="11">
         <v>14</v>
       </c>
-      <c r="H194" s="17"/>
+      <c r="H194" s="19"/>
     </row>
     <row r="195" spans="1:8">
       <c r="A195" s="10" t="s">
@@ -6343,14 +6698,16 @@
         <v>44</v>
       </c>
       <c r="D195" s="11"/>
-      <c r="E195" s="20">
+      <c r="E195" s="17">
         <v>49</v>
       </c>
-      <c r="F195" s="11"/>
+      <c r="F195" s="17">
+        <v>72</v>
+      </c>
       <c r="G195" s="11">
         <v>47</v>
       </c>
-      <c r="H195" s="17"/>
+      <c r="H195" s="19"/>
     </row>
     <row r="196" spans="1:8">
       <c r="A196" s="10" t="s">
@@ -6363,14 +6720,16 @@
         <v>59</v>
       </c>
       <c r="D196" s="11"/>
-      <c r="E196" s="20">
+      <c r="E196" s="17">
         <v>49</v>
       </c>
-      <c r="F196" s="11"/>
+      <c r="F196" s="17">
+        <v>83</v>
+      </c>
       <c r="G196" s="11">
         <v>39</v>
       </c>
-      <c r="H196" s="17"/>
+      <c r="H196" s="19"/>
     </row>
     <row r="197" spans="1:8">
       <c r="A197" s="10" t="s">
@@ -6383,14 +6742,16 @@
         <v>42</v>
       </c>
       <c r="D197" s="11"/>
-      <c r="E197" s="20">
+      <c r="E197" s="17">
         <v>47</v>
       </c>
-      <c r="F197" s="11"/>
+      <c r="F197" s="17">
+        <v>74</v>
+      </c>
       <c r="G197" s="11">
         <v>39</v>
       </c>
-      <c r="H197" s="17"/>
+      <c r="H197" s="19"/>
     </row>
     <row r="198" spans="1:8">
       <c r="A198" s="10" t="s">
@@ -6403,16 +6764,16 @@
         <v>23</v>
       </c>
       <c r="D198" s="11"/>
-      <c r="E198" s="20">
+      <c r="E198" s="17">
         <v>44</v>
       </c>
-      <c r="F198" s="11">
-        <v>0</v>
+      <c r="F198" s="17">
+        <v>69</v>
       </c>
       <c r="G198" s="11">
         <v>35</v>
       </c>
-      <c r="H198" s="17"/>
+      <c r="H198" s="19"/>
     </row>
     <row r="199" spans="1:8">
       <c r="A199" s="10" t="s">
@@ -6425,14 +6786,16 @@
         <v>46</v>
       </c>
       <c r="D199" s="11"/>
-      <c r="E199" s="20">
+      <c r="E199" s="17">
         <v>47</v>
       </c>
-      <c r="F199" s="11"/>
+      <c r="F199" s="17" t="s">
+        <v>482</v>
+      </c>
       <c r="G199" s="11">
         <v>26</v>
       </c>
-      <c r="H199" s="17"/>
+      <c r="H199" s="19"/>
     </row>
     <row r="200" spans="1:8">
       <c r="A200" s="10" t="s">
@@ -6445,14 +6808,16 @@
         <v>59</v>
       </c>
       <c r="D200" s="11"/>
-      <c r="E200" s="20">
+      <c r="E200" s="17">
         <v>44</v>
       </c>
-      <c r="F200" s="11"/>
+      <c r="F200" s="17">
+        <v>88</v>
+      </c>
       <c r="G200" s="11">
         <v>52</v>
       </c>
-      <c r="H200" s="17"/>
+      <c r="H200" s="19"/>
     </row>
     <row r="201" spans="1:8">
       <c r="A201" s="10" t="s">
@@ -6465,14 +6830,16 @@
         <v>66</v>
       </c>
       <c r="D201" s="11"/>
-      <c r="E201" s="20">
+      <c r="E201" s="17">
         <v>55</v>
       </c>
-      <c r="F201" s="11"/>
+      <c r="F201" s="17">
+        <v>59</v>
+      </c>
       <c r="G201" s="11">
         <v>41</v>
       </c>
-      <c r="H201" s="17"/>
+      <c r="H201" s="19"/>
     </row>
     <row r="202" spans="1:8">
       <c r="A202" s="10" t="s">
@@ -6485,14 +6852,16 @@
         <v>53</v>
       </c>
       <c r="D202" s="11"/>
-      <c r="E202" s="20">
+      <c r="E202" s="17">
         <v>55</v>
       </c>
-      <c r="F202" s="11"/>
+      <c r="F202" s="17">
+        <v>33</v>
+      </c>
       <c r="G202" s="11">
         <v>27</v>
       </c>
-      <c r="H202" s="17"/>
+      <c r="H202" s="19"/>
     </row>
     <row r="203" spans="1:8">
       <c r="A203" s="10" t="s">
@@ -6505,14 +6874,16 @@
         <v>60</v>
       </c>
       <c r="D203" s="11"/>
-      <c r="E203" s="20">
+      <c r="E203" s="17">
         <v>47</v>
       </c>
-      <c r="F203" s="11"/>
+      <c r="F203" s="17">
+        <v>71</v>
+      </c>
       <c r="G203" s="11">
         <v>42</v>
       </c>
-      <c r="H203" s="17"/>
+      <c r="H203" s="19"/>
     </row>
     <row r="204" spans="1:8">
       <c r="A204" s="10" t="s">
@@ -6525,14 +6896,16 @@
         <v>29</v>
       </c>
       <c r="D204" s="11"/>
-      <c r="E204" s="20">
+      <c r="E204" s="17">
         <v>43</v>
       </c>
-      <c r="F204" s="11"/>
+      <c r="F204" s="17">
+        <v>77</v>
+      </c>
       <c r="G204" s="11">
         <v>31</v>
       </c>
-      <c r="H204" s="17"/>
+      <c r="H204" s="19"/>
     </row>
     <row r="205" spans="1:8">
       <c r="A205" s="10" t="s">
@@ -6545,14 +6918,16 @@
         <v>55</v>
       </c>
       <c r="D205" s="11"/>
-      <c r="E205" s="20">
+      <c r="E205" s="17">
         <v>44</v>
       </c>
-      <c r="F205" s="11"/>
+      <c r="F205" s="17">
+        <v>53</v>
+      </c>
       <c r="G205" s="11">
         <v>47</v>
       </c>
-      <c r="H205" s="17"/>
+      <c r="H205" s="19"/>
     </row>
     <row r="206" spans="1:8">
       <c r="A206" s="10" t="s">
@@ -6565,14 +6940,16 @@
         <v>33</v>
       </c>
       <c r="D206" s="11"/>
-      <c r="E206" s="20">
+      <c r="E206" s="17">
         <v>53</v>
       </c>
-      <c r="F206" s="11"/>
+      <c r="F206" s="17">
+        <v>76</v>
+      </c>
       <c r="G206" s="11">
         <v>30</v>
       </c>
-      <c r="H206" s="17"/>
+      <c r="H206" s="19"/>
     </row>
     <row r="207" spans="1:8">
       <c r="A207" s="10" t="s">
@@ -6585,14 +6962,16 @@
         <v>51</v>
       </c>
       <c r="D207" s="11"/>
-      <c r="E207" s="20">
+      <c r="E207" s="17">
         <v>53</v>
       </c>
-      <c r="F207" s="11"/>
+      <c r="F207" s="21">
+        <v>0</v>
+      </c>
       <c r="G207" s="11">
         <v>21</v>
       </c>
-      <c r="H207" s="17"/>
+      <c r="H207" s="19"/>
     </row>
     <row r="208" spans="1:8">
       <c r="A208" s="10" t="s">
@@ -6605,14 +6984,16 @@
         <v>43</v>
       </c>
       <c r="D208" s="11"/>
-      <c r="E208" s="20">
+      <c r="E208" s="17">
         <v>43</v>
       </c>
-      <c r="F208" s="11"/>
+      <c r="F208" s="17">
+        <v>41</v>
+      </c>
       <c r="G208" s="11">
         <v>35</v>
       </c>
-      <c r="H208" s="17"/>
+      <c r="H208" s="19"/>
     </row>
     <row r="209" spans="1:8">
       <c r="A209" s="10" t="s">
@@ -6625,14 +7006,16 @@
         <v>50</v>
       </c>
       <c r="D209" s="11"/>
-      <c r="E209" s="20">
+      <c r="E209" s="17">
         <v>43</v>
       </c>
-      <c r="F209" s="11"/>
+      <c r="F209" s="17">
+        <v>77</v>
+      </c>
       <c r="G209" s="11">
         <v>17</v>
       </c>
-      <c r="H209" s="17"/>
+      <c r="H209" s="19"/>
     </row>
     <row r="210" spans="1:8">
       <c r="A210" s="10" t="s">
@@ -6645,14 +7028,16 @@
         <v>30</v>
       </c>
       <c r="D210" s="11"/>
-      <c r="E210" s="20">
+      <c r="E210" s="17">
         <v>44</v>
       </c>
-      <c r="F210" s="11"/>
+      <c r="F210" s="17">
+        <v>87</v>
+      </c>
       <c r="G210" s="11">
         <v>30</v>
       </c>
-      <c r="H210" s="17"/>
+      <c r="H210" s="19"/>
     </row>
     <row r="211" spans="1:8">
       <c r="A211" s="10" t="s">
@@ -6665,14 +7050,16 @@
         <v>42</v>
       </c>
       <c r="D211" s="11"/>
-      <c r="E211" s="20">
+      <c r="E211" s="17">
         <v>53</v>
       </c>
-      <c r="F211" s="11"/>
+      <c r="F211" s="17">
+        <v>40</v>
+      </c>
       <c r="G211" s="11">
         <v>28</v>
       </c>
-      <c r="H211" s="17"/>
+      <c r="H211" s="19"/>
     </row>
     <row r="212" spans="1:8">
       <c r="A212" s="10" t="s">
@@ -6685,14 +7072,16 @@
         <v>50</v>
       </c>
       <c r="D212" s="11"/>
-      <c r="E212" s="20">
+      <c r="E212" s="17">
         <v>49</v>
       </c>
-      <c r="F212" s="11"/>
+      <c r="F212" s="17">
+        <v>44</v>
+      </c>
       <c r="G212" s="11">
         <v>47</v>
       </c>
-      <c r="H212" s="17"/>
+      <c r="H212" s="19"/>
     </row>
     <row r="213" spans="1:8">
       <c r="A213" s="10" t="s">
@@ -6705,14 +7094,16 @@
         <v>37</v>
       </c>
       <c r="D213" s="11"/>
-      <c r="E213" s="20">
+      <c r="E213" s="17">
         <v>43</v>
       </c>
-      <c r="F213" s="11"/>
+      <c r="F213" s="17">
+        <v>88</v>
+      </c>
       <c r="G213" s="11">
         <v>48</v>
       </c>
-      <c r="H213" s="17"/>
+      <c r="H213" s="19"/>
     </row>
     <row r="214" spans="1:8">
       <c r="A214" s="10" t="s">
@@ -6725,14 +7116,16 @@
         <v>41</v>
       </c>
       <c r="D214" s="11"/>
-      <c r="E214" s="20">
+      <c r="E214" s="17">
         <v>47</v>
       </c>
-      <c r="F214" s="11"/>
+      <c r="F214" s="17">
+        <v>90</v>
+      </c>
       <c r="G214" s="11">
         <v>28</v>
       </c>
-      <c r="H214" s="17"/>
+      <c r="H214" s="19"/>
     </row>
     <row r="215" spans="1:8">
       <c r="A215" s="10" t="s">
@@ -6745,14 +7138,16 @@
         <v>42</v>
       </c>
       <c r="D215" s="11"/>
-      <c r="E215" s="20">
+      <c r="E215" s="17">
         <v>73</v>
       </c>
-      <c r="F215" s="11"/>
+      <c r="F215" s="17">
+        <v>49</v>
+      </c>
       <c r="G215" s="11">
         <v>27</v>
       </c>
-      <c r="H215" s="17"/>
+      <c r="H215" s="19"/>
     </row>
     <row r="216" spans="1:8">
       <c r="A216" s="10" t="s">
@@ -6765,14 +7160,16 @@
         <v>57</v>
       </c>
       <c r="D216" s="11"/>
-      <c r="E216" s="20">
+      <c r="E216" s="17">
         <v>44</v>
       </c>
-      <c r="F216" s="11"/>
+      <c r="F216" s="17">
+        <v>76</v>
+      </c>
       <c r="G216" s="11" t="s">
         <v>482</v>
       </c>
-      <c r="H216" s="17"/>
+      <c r="H216" s="19"/>
     </row>
     <row r="217" spans="1:8">
       <c r="A217" s="10" t="s">
@@ -6785,14 +7182,16 @@
         <v>4</v>
       </c>
       <c r="D217" s="11"/>
-      <c r="E217" s="19" t="s">
+      <c r="E217" s="20" t="s">
         <v>482</v>
       </c>
-      <c r="F217" s="11"/>
+      <c r="F217" s="17" t="s">
+        <v>482</v>
+      </c>
       <c r="G217" s="11" t="s">
         <v>482</v>
       </c>
-      <c r="H217" s="17"/>
+      <c r="H217" s="19"/>
     </row>
     <row r="218" spans="1:8">
       <c r="A218" s="10" t="s">
@@ -6805,14 +7204,16 @@
         <v>60</v>
       </c>
       <c r="D218" s="11"/>
-      <c r="E218" s="20">
+      <c r="E218" s="17">
         <v>47</v>
       </c>
-      <c r="F218" s="11"/>
+      <c r="F218" s="17">
+        <v>56</v>
+      </c>
       <c r="G218" s="11">
         <v>62</v>
       </c>
-      <c r="H218" s="17"/>
+      <c r="H218" s="19"/>
     </row>
     <row r="219" spans="1:8">
       <c r="A219" s="10" t="s">
@@ -6825,14 +7226,16 @@
         <v>69</v>
       </c>
       <c r="D219" s="11"/>
-      <c r="E219" s="20">
+      <c r="E219" s="17">
         <v>49</v>
       </c>
-      <c r="F219" s="11"/>
+      <c r="F219" s="17">
+        <v>66</v>
+      </c>
       <c r="G219" s="11">
         <v>28</v>
       </c>
-      <c r="H219" s="17"/>
+      <c r="H219" s="19"/>
     </row>
     <row r="220" spans="1:8">
       <c r="A220" s="10" t="s">
@@ -6845,14 +7248,16 @@
         <v>49</v>
       </c>
       <c r="D220" s="11"/>
-      <c r="E220" s="20">
+      <c r="E220" s="17">
         <v>53</v>
       </c>
-      <c r="F220" s="11"/>
+      <c r="F220" s="17">
+        <v>44</v>
+      </c>
       <c r="G220" s="11">
         <v>34</v>
       </c>
-      <c r="H220" s="17"/>
+      <c r="H220" s="19"/>
     </row>
     <row r="221" spans="1:8">
       <c r="A221" s="10" t="s">
@@ -6865,14 +7270,16 @@
         <v>43</v>
       </c>
       <c r="D221" s="11"/>
-      <c r="E221" s="20">
+      <c r="E221" s="17">
         <v>47</v>
       </c>
-      <c r="F221" s="11"/>
+      <c r="F221" s="17">
+        <v>96</v>
+      </c>
       <c r="G221" s="11">
         <v>28</v>
       </c>
-      <c r="H221" s="17"/>
+      <c r="H221" s="19"/>
     </row>
     <row r="222" spans="1:8">
       <c r="A222" s="10" t="s">
@@ -6885,14 +7292,16 @@
         <v>45</v>
       </c>
       <c r="D222" s="11"/>
-      <c r="E222" s="20">
+      <c r="E222" s="17">
         <v>47</v>
       </c>
-      <c r="F222" s="11"/>
+      <c r="F222" s="17">
+        <v>88</v>
+      </c>
       <c r="G222" s="11">
         <v>33</v>
       </c>
-      <c r="H222" s="17"/>
+      <c r="H222" s="19"/>
     </row>
     <row r="223" spans="1:8">
       <c r="A223" s="10" t="s">
@@ -6905,14 +7314,16 @@
         <v>59</v>
       </c>
       <c r="D223" s="11"/>
-      <c r="E223" s="20">
+      <c r="E223" s="17">
         <v>47</v>
       </c>
-      <c r="F223" s="11"/>
+      <c r="F223" s="17">
+        <v>51</v>
+      </c>
       <c r="G223" s="11">
         <v>33</v>
       </c>
-      <c r="H223" s="17"/>
+      <c r="H223" s="19"/>
     </row>
     <row r="224" spans="1:8">
       <c r="A224" s="10" t="s">
@@ -6925,14 +7336,16 @@
         <v>45</v>
       </c>
       <c r="D224" s="11"/>
-      <c r="E224" s="20">
+      <c r="E224" s="17">
         <v>43</v>
       </c>
-      <c r="F224" s="11"/>
+      <c r="F224" s="17">
+        <v>89</v>
+      </c>
       <c r="G224" s="11">
         <v>31</v>
       </c>
-      <c r="H224" s="17"/>
+      <c r="H224" s="19"/>
     </row>
     <row r="225" spans="1:8">
       <c r="A225" s="10" t="s">
@@ -6945,14 +7358,16 @@
         <v>47</v>
       </c>
       <c r="D225" s="11"/>
-      <c r="E225" s="20">
+      <c r="E225" s="17">
         <v>73</v>
       </c>
-      <c r="F225" s="11"/>
+      <c r="F225" s="17">
+        <v>70</v>
+      </c>
       <c r="G225" s="11">
         <v>48</v>
       </c>
-      <c r="H225" s="17"/>
+      <c r="H225" s="19"/>
     </row>
     <row r="226" spans="1:8">
       <c r="A226" s="10" t="s">
@@ -6965,14 +7380,16 @@
         <v>49</v>
       </c>
       <c r="D226" s="11"/>
-      <c r="E226" s="20">
+      <c r="E226" s="17">
         <v>47</v>
       </c>
-      <c r="F226" s="11"/>
+      <c r="F226" s="17">
+        <v>82</v>
+      </c>
       <c r="G226" s="11">
         <v>31</v>
       </c>
-      <c r="H226" s="17"/>
+      <c r="H226" s="19"/>
     </row>
     <row r="227" spans="1:8">
       <c r="A227" s="10" t="s">
@@ -6985,14 +7402,16 @@
         <v>482</v>
       </c>
       <c r="D227" s="11"/>
-      <c r="E227" s="20">
+      <c r="E227" s="17">
         <v>73</v>
       </c>
-      <c r="F227" s="11"/>
+      <c r="F227" s="17" t="s">
+        <v>482</v>
+      </c>
       <c r="G227" s="11">
         <v>37</v>
       </c>
-      <c r="H227" s="17"/>
+      <c r="H227" s="19"/>
     </row>
     <row r="228" spans="1:8">
       <c r="A228" s="10" t="s">
@@ -7005,14 +7424,16 @@
         <v>44</v>
       </c>
       <c r="D228" s="11"/>
-      <c r="E228" s="20">
+      <c r="E228" s="17">
         <v>55</v>
       </c>
-      <c r="F228" s="11"/>
+      <c r="F228" s="17">
+        <v>65</v>
+      </c>
       <c r="G228" s="11">
         <v>34</v>
       </c>
-      <c r="H228" s="17"/>
+      <c r="H228" s="19"/>
     </row>
     <row r="229" spans="1:8">
       <c r="A229" s="10" t="s">
@@ -7025,14 +7446,16 @@
         <v>56</v>
       </c>
       <c r="D229" s="11"/>
-      <c r="E229" s="20">
+      <c r="E229" s="17">
         <v>49</v>
       </c>
-      <c r="F229" s="11"/>
+      <c r="F229" s="17">
+        <v>80</v>
+      </c>
       <c r="G229" s="11">
         <v>24</v>
       </c>
-      <c r="H229" s="17"/>
+      <c r="H229" s="19"/>
     </row>
     <row r="230" spans="1:8">
       <c r="A230" s="10" t="s">
@@ -7045,14 +7468,16 @@
         <v>51</v>
       </c>
       <c r="D230" s="11"/>
-      <c r="E230" s="20">
+      <c r="E230" s="17">
         <v>55</v>
       </c>
-      <c r="F230" s="11"/>
+      <c r="F230" s="17">
+        <v>85</v>
+      </c>
       <c r="G230" s="11">
         <v>59</v>
       </c>
-      <c r="H230" s="17"/>
+      <c r="H230" s="19"/>
     </row>
     <row r="231" spans="1:8">
       <c r="A231" s="10" t="s">
@@ -7065,14 +7490,16 @@
         <v>58</v>
       </c>
       <c r="D231" s="11"/>
-      <c r="E231" s="20">
+      <c r="E231" s="17">
         <v>73</v>
       </c>
-      <c r="F231" s="11"/>
+      <c r="F231" s="17">
+        <v>61</v>
+      </c>
       <c r="G231" s="11">
         <v>53</v>
       </c>
-      <c r="H231" s="17"/>
+      <c r="H231" s="19"/>
     </row>
     <row r="232" spans="1:8">
       <c r="A232" s="10" t="s">
@@ -7085,14 +7512,16 @@
         <v>62</v>
       </c>
       <c r="D232" s="11"/>
-      <c r="E232" s="20">
+      <c r="E232" s="17">
         <v>47</v>
       </c>
-      <c r="F232" s="11"/>
+      <c r="F232" s="17">
+        <v>67</v>
+      </c>
       <c r="G232" s="11">
         <v>33</v>
       </c>
-      <c r="H232" s="17"/>
+      <c r="H232" s="19"/>
     </row>
     <row r="233" spans="1:8">
       <c r="A233" s="10" t="s">
@@ -7105,14 +7534,16 @@
         <v>482</v>
       </c>
       <c r="D233" s="11"/>
-      <c r="E233" s="19" t="s">
+      <c r="E233" s="20" t="s">
         <v>482</v>
       </c>
-      <c r="F233" s="11"/>
+      <c r="F233" s="17" t="s">
+        <v>482</v>
+      </c>
       <c r="G233" s="11" t="s">
         <v>482</v>
       </c>
-      <c r="H233" s="17"/>
+      <c r="H233" s="19"/>
     </row>
     <row r="234" spans="1:8">
       <c r="A234" s="4" t="s">
@@ -7125,14 +7556,16 @@
         <v>41</v>
       </c>
       <c r="D234" s="11"/>
-      <c r="E234" s="20">
+      <c r="E234" s="17">
         <v>74</v>
       </c>
-      <c r="F234" s="11"/>
+      <c r="F234" s="17">
+        <v>40</v>
+      </c>
       <c r="G234" s="11">
         <v>62</v>
       </c>
-      <c r="H234" s="17"/>
+      <c r="H234" s="19"/>
     </row>
     <row r="235" spans="1:8">
       <c r="A235" s="4" t="s">
@@ -7145,14 +7578,16 @@
         <v>482</v>
       </c>
       <c r="D235" s="11"/>
-      <c r="E235" s="20">
+      <c r="E235" s="17">
         <v>74</v>
       </c>
-      <c r="F235" s="11"/>
+      <c r="F235" s="17">
+        <v>55</v>
+      </c>
       <c r="G235" s="11">
         <v>53</v>
       </c>
-      <c r="H235" s="17"/>
+      <c r="H235" s="19"/>
     </row>
     <row r="236" spans="1:8">
       <c r="A236" s="4" t="s">
@@ -7165,14 +7600,16 @@
         <v>51</v>
       </c>
       <c r="D236" s="11"/>
-      <c r="E236" s="20">
+      <c r="E236" s="17">
         <v>74</v>
       </c>
-      <c r="F236" s="11"/>
+      <c r="F236" s="17">
+        <v>90</v>
+      </c>
       <c r="G236" s="11">
         <v>41</v>
       </c>
-      <c r="H236" s="17"/>
+      <c r="H236" s="19"/>
     </row>
     <row r="237" spans="1:8">
       <c r="A237" s="4" t="s">
@@ -7188,11 +7625,13 @@
       <c r="E237" s="11" t="s">
         <v>482</v>
       </c>
-      <c r="F237" s="11"/>
+      <c r="F237" s="17" t="s">
+        <v>482</v>
+      </c>
       <c r="G237" s="11">
         <v>29</v>
       </c>
-      <c r="H237" s="17"/>
+      <c r="H237" s="19"/>
     </row>
     <row r="238" spans="1:8">
       <c r="A238" s="6" t="s">
@@ -7208,11 +7647,13 @@
       <c r="E238" s="11" t="s">
         <v>482</v>
       </c>
-      <c r="F238" s="11"/>
+      <c r="F238" s="17" t="s">
+        <v>482</v>
+      </c>
       <c r="G238" s="11" t="s">
         <v>482</v>
       </c>
-      <c r="H238" s="17"/>
+      <c r="H238" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7221,9 +7662,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7371,15 +7815,24 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82FD49CE-D196-4C00-BC5E-382EDDDD004F}">
+  <ds:schemaRefs/>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F334BD5B-9873-472F-B0A9-4AE19CD21D29}">
+  <ds:schemaRefs/>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B92832D-94CC-4C5E-A4E8-2D2A44869573}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
@@ -7393,16 +7846,4 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F334BD5B-9873-472F-B0A9-4AE19CD21D29}">
-  <ds:schemaRefs/>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82FD49CE-D196-4C00-BC5E-382EDDDD004F}">
-  <ds:schemaRefs/>
-</ds:datastoreItem>
 </file>
--- a/MC1020_E25.xlsx
+++ b/MC1020_E25.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assignment marks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA4CEB0A-6C47-4A49-8C08-6E37D4CD93CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83B410DE-7FA8-42A1-A743-BAFBD2CE3467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="483">
   <si>
     <t xml:space="preserve"> Reg.number</t>
   </si>
@@ -1725,15 +1725,17 @@
     <xf numFmtId="2" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="12">
     <cellStyle name="60% - Accent1 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -2067,7 +2069,9 @@
       <c r="C2" s="11">
         <v>45</v>
       </c>
-      <c r="D2" s="18"/>
+      <c r="D2" s="22">
+        <v>51</v>
+      </c>
       <c r="E2" s="17">
         <v>49</v>
       </c>
@@ -2077,7 +2081,7 @@
       <c r="G2" s="11">
         <v>13</v>
       </c>
-      <c r="H2" s="22">
+      <c r="H2" s="21">
         <v>61.29032258064516</v>
       </c>
     </row>
@@ -2091,7 +2095,9 @@
       <c r="C3" s="11">
         <v>40</v>
       </c>
-      <c r="D3" s="18"/>
+      <c r="D3" s="22">
+        <v>13</v>
+      </c>
       <c r="E3" s="17">
         <v>49</v>
       </c>
@@ -2101,7 +2107,7 @@
       <c r="G3" s="11">
         <v>24</v>
       </c>
-      <c r="H3" s="22">
+      <c r="H3" s="21">
         <v>74.193548387096769</v>
       </c>
     </row>
@@ -2115,7 +2121,9 @@
       <c r="C4" s="11">
         <v>53</v>
       </c>
-      <c r="D4" s="18"/>
+      <c r="D4" s="22">
+        <v>37</v>
+      </c>
       <c r="E4" s="17">
         <v>66</v>
       </c>
@@ -2125,7 +2133,7 @@
       <c r="G4" s="11" t="s">
         <v>482</v>
       </c>
-      <c r="H4" s="22">
+      <c r="H4" s="21">
         <v>58.064516129032263</v>
       </c>
     </row>
@@ -2139,7 +2147,9 @@
       <c r="C5" s="11">
         <v>17</v>
       </c>
-      <c r="D5" s="18"/>
+      <c r="D5" s="22">
+        <v>32</v>
+      </c>
       <c r="E5" s="17">
         <v>61</v>
       </c>
@@ -2149,7 +2159,7 @@
       <c r="G5" s="11">
         <v>26</v>
       </c>
-      <c r="H5" s="22">
+      <c r="H5" s="21">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -2163,7 +2173,9 @@
       <c r="C6" s="11">
         <v>44</v>
       </c>
-      <c r="D6" s="18"/>
+      <c r="D6" s="22">
+        <v>54</v>
+      </c>
       <c r="E6" s="17">
         <v>47</v>
       </c>
@@ -2173,7 +2185,7 @@
       <c r="G6" s="11">
         <v>32</v>
       </c>
-      <c r="H6" s="22">
+      <c r="H6" s="21">
         <v>61.29032258064516</v>
       </c>
     </row>
@@ -2187,7 +2199,9 @@
       <c r="C7" s="11">
         <v>36</v>
       </c>
-      <c r="D7" s="18"/>
+      <c r="D7" s="22">
+        <v>20</v>
+      </c>
       <c r="E7" s="17">
         <v>53</v>
       </c>
@@ -2197,7 +2211,7 @@
       <c r="G7" s="11">
         <v>20</v>
       </c>
-      <c r="H7" s="22">
+      <c r="H7" s="21">
         <v>83.870967741935488</v>
       </c>
     </row>
@@ -2211,7 +2225,9 @@
       <c r="C8" s="11">
         <v>32</v>
       </c>
-      <c r="D8" s="18"/>
+      <c r="D8" s="22">
+        <v>58</v>
+      </c>
       <c r="E8" s="17">
         <v>50</v>
       </c>
@@ -2221,7 +2237,7 @@
       <c r="G8" s="11">
         <v>32</v>
       </c>
-      <c r="H8" s="22">
+      <c r="H8" s="21">
         <v>87.096774193548384</v>
       </c>
     </row>
@@ -2235,7 +2251,9 @@
       <c r="C9" s="11">
         <v>29</v>
       </c>
-      <c r="D9" s="18"/>
+      <c r="D9" s="22">
+        <v>24</v>
+      </c>
       <c r="E9" s="17">
         <v>47</v>
       </c>
@@ -2245,7 +2263,7 @@
       <c r="G9" s="11">
         <v>12</v>
       </c>
-      <c r="H9" s="22">
+      <c r="H9" s="21">
         <v>83.870967741935488</v>
       </c>
     </row>
@@ -2259,7 +2277,9 @@
       <c r="C10" s="11">
         <v>8</v>
       </c>
-      <c r="D10" s="18"/>
+      <c r="D10" s="22">
+        <v>53</v>
+      </c>
       <c r="E10" s="17">
         <v>47</v>
       </c>
@@ -2269,7 +2289,7 @@
       <c r="G10" s="11">
         <v>18</v>
       </c>
-      <c r="H10" s="22">
+      <c r="H10" s="21">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -2283,7 +2303,9 @@
       <c r="C11" s="11">
         <v>75</v>
       </c>
-      <c r="D11" s="18"/>
+      <c r="D11" s="22">
+        <v>43</v>
+      </c>
       <c r="E11" s="17">
         <v>60</v>
       </c>
@@ -2293,7 +2315,7 @@
       <c r="G11" s="11">
         <v>58</v>
       </c>
-      <c r="H11" s="22">
+      <c r="H11" s="21">
         <v>83.870967741935488</v>
       </c>
     </row>
@@ -2307,7 +2329,9 @@
       <c r="C12" s="11">
         <v>42</v>
       </c>
-      <c r="D12" s="18"/>
+      <c r="D12" s="22">
+        <v>54</v>
+      </c>
       <c r="E12" s="17">
         <v>47</v>
       </c>
@@ -2317,7 +2341,7 @@
       <c r="G12" s="11">
         <v>22</v>
       </c>
-      <c r="H12" s="22">
+      <c r="H12" s="21">
         <v>80.645161290322577</v>
       </c>
     </row>
@@ -2331,7 +2355,9 @@
       <c r="C13" s="11">
         <v>34</v>
       </c>
-      <c r="D13" s="18"/>
+      <c r="D13" s="22">
+        <v>25</v>
+      </c>
       <c r="E13" s="17">
         <v>60</v>
       </c>
@@ -2341,7 +2367,7 @@
       <c r="G13" s="11">
         <v>19</v>
       </c>
-      <c r="H13" s="22">
+      <c r="H13" s="21">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -2355,7 +2381,9 @@
       <c r="C14" s="11">
         <v>37</v>
       </c>
-      <c r="D14" s="18"/>
+      <c r="D14" s="22">
+        <v>56</v>
+      </c>
       <c r="E14" s="17">
         <v>47</v>
       </c>
@@ -2365,7 +2393,7 @@
       <c r="G14" s="11">
         <v>34</v>
       </c>
-      <c r="H14" s="22">
+      <c r="H14" s="21">
         <v>87.096774193548384</v>
       </c>
     </row>
@@ -2379,7 +2407,9 @@
       <c r="C15" s="11">
         <v>51</v>
       </c>
-      <c r="D15" s="18"/>
+      <c r="D15" s="22">
+        <v>69</v>
+      </c>
       <c r="E15" s="17">
         <v>87</v>
       </c>
@@ -2389,7 +2419,7 @@
       <c r="G15" s="11">
         <v>50</v>
       </c>
-      <c r="H15" s="22">
+      <c r="H15" s="21">
         <v>93.548387096774192</v>
       </c>
     </row>
@@ -2403,7 +2433,9 @@
       <c r="C16" s="11">
         <v>79</v>
       </c>
-      <c r="D16" s="18"/>
+      <c r="D16" s="22">
+        <v>73</v>
+      </c>
       <c r="E16" s="17">
         <v>60</v>
       </c>
@@ -2413,7 +2445,7 @@
       <c r="G16" s="11">
         <v>54</v>
       </c>
-      <c r="H16" s="22">
+      <c r="H16" s="21">
         <v>83.870967741935488</v>
       </c>
     </row>
@@ -2427,7 +2459,9 @@
       <c r="C17" s="11">
         <v>44</v>
       </c>
-      <c r="D17" s="18"/>
+      <c r="D17" s="22">
+        <v>44</v>
+      </c>
       <c r="E17" s="17">
         <v>46</v>
       </c>
@@ -2437,7 +2471,7 @@
       <c r="G17" s="11">
         <v>35</v>
       </c>
-      <c r="H17" s="22">
+      <c r="H17" s="21">
         <v>90.322580645161281</v>
       </c>
     </row>
@@ -2451,7 +2485,9 @@
       <c r="C18" s="11">
         <v>52</v>
       </c>
-      <c r="D18" s="18"/>
+      <c r="D18" s="22">
+        <v>55</v>
+      </c>
       <c r="E18" s="17">
         <v>50</v>
       </c>
@@ -2461,7 +2497,7 @@
       <c r="G18" s="11">
         <v>33</v>
       </c>
-      <c r="H18" s="22">
+      <c r="H18" s="21">
         <v>54.838709677419352</v>
       </c>
     </row>
@@ -2475,7 +2511,9 @@
       <c r="C19" s="11">
         <v>46</v>
       </c>
-      <c r="D19" s="18"/>
+      <c r="D19" s="22">
+        <v>41</v>
+      </c>
       <c r="E19" s="17">
         <v>87</v>
       </c>
@@ -2485,7 +2523,7 @@
       <c r="G19" s="11">
         <v>46</v>
       </c>
-      <c r="H19" s="22">
+      <c r="H19" s="21">
         <v>70.967741935483872</v>
       </c>
     </row>
@@ -2499,7 +2537,9 @@
       <c r="C20" s="11">
         <v>74</v>
       </c>
-      <c r="D20" s="18"/>
+      <c r="D20" s="22">
+        <v>70</v>
+      </c>
       <c r="E20" s="17">
         <v>57</v>
       </c>
@@ -2509,7 +2549,7 @@
       <c r="G20" s="11">
         <v>57</v>
       </c>
-      <c r="H20" s="22">
+      <c r="H20" s="21">
         <v>83.870967741935488</v>
       </c>
     </row>
@@ -2523,7 +2563,9 @@
       <c r="C21" s="11">
         <v>48</v>
       </c>
-      <c r="D21" s="18"/>
+      <c r="D21" s="22">
+        <v>51</v>
+      </c>
       <c r="E21" s="17">
         <v>50</v>
       </c>
@@ -2533,7 +2575,7 @@
       <c r="G21" s="11">
         <v>39</v>
       </c>
-      <c r="H21" s="22">
+      <c r="H21" s="21">
         <v>87.096774193548384</v>
       </c>
     </row>
@@ -2547,7 +2589,9 @@
       <c r="C22" s="11">
         <v>33</v>
       </c>
-      <c r="D22" s="18"/>
+      <c r="D22" s="22">
+        <v>67</v>
+      </c>
       <c r="E22" s="17">
         <v>47</v>
       </c>
@@ -2557,7 +2601,7 @@
       <c r="G22" s="11">
         <v>37</v>
       </c>
-      <c r="H22" s="22">
+      <c r="H22" s="21">
         <v>93.548387096774192</v>
       </c>
     </row>
@@ -2571,7 +2615,9 @@
       <c r="C23" s="11">
         <v>39</v>
       </c>
-      <c r="D23" s="18"/>
+      <c r="D23" s="22">
+        <v>53</v>
+      </c>
       <c r="E23" s="17">
         <v>46</v>
       </c>
@@ -2581,7 +2627,7 @@
       <c r="G23" s="11">
         <v>42</v>
       </c>
-      <c r="H23" s="22">
+      <c r="H23" s="21">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -2595,7 +2641,9 @@
       <c r="C24" s="11">
         <v>63</v>
       </c>
-      <c r="D24" s="18"/>
+      <c r="D24" s="22">
+        <v>54</v>
+      </c>
       <c r="E24" s="17">
         <v>50</v>
       </c>
@@ -2605,7 +2653,7 @@
       <c r="G24" s="11">
         <v>36</v>
       </c>
-      <c r="H24" s="22">
+      <c r="H24" s="21">
         <v>83.870967741935488</v>
       </c>
     </row>
@@ -2619,7 +2667,9 @@
       <c r="C25" s="11">
         <v>49</v>
       </c>
-      <c r="D25" s="18"/>
+      <c r="D25" s="22">
+        <v>31</v>
+      </c>
       <c r="E25" s="17">
         <v>50</v>
       </c>
@@ -2629,7 +2679,7 @@
       <c r="G25" s="11">
         <v>19</v>
       </c>
-      <c r="H25" s="22">
+      <c r="H25" s="21">
         <v>80.645161290322577</v>
       </c>
     </row>
@@ -2643,7 +2693,9 @@
       <c r="C26" s="11">
         <v>31</v>
       </c>
-      <c r="D26" s="18"/>
+      <c r="D26" s="22">
+        <v>31</v>
+      </c>
       <c r="E26" s="17">
         <v>46</v>
       </c>
@@ -2653,7 +2705,7 @@
       <c r="G26" s="11">
         <v>22</v>
       </c>
-      <c r="H26" s="22">
+      <c r="H26" s="21">
         <v>64.516129032258064</v>
       </c>
     </row>
@@ -2667,7 +2719,9 @@
       <c r="C27" s="11">
         <v>76</v>
       </c>
-      <c r="D27" s="18"/>
+      <c r="D27" s="22">
+        <v>68</v>
+      </c>
       <c r="E27" s="17">
         <v>55</v>
       </c>
@@ -2677,7 +2731,7 @@
       <c r="G27" s="11">
         <v>48</v>
       </c>
-      <c r="H27" s="22">
+      <c r="H27" s="21">
         <v>74.193548387096769</v>
       </c>
     </row>
@@ -2691,7 +2745,9 @@
       <c r="C28" s="11">
         <v>72</v>
       </c>
-      <c r="D28" s="18"/>
+      <c r="D28" s="22">
+        <v>53</v>
+      </c>
       <c r="E28" s="17">
         <v>50</v>
       </c>
@@ -2701,7 +2757,7 @@
       <c r="G28" s="11">
         <v>38</v>
       </c>
-      <c r="H28" s="22">
+      <c r="H28" s="21">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -2715,7 +2771,9 @@
       <c r="C29" s="11">
         <v>70</v>
       </c>
-      <c r="D29" s="18"/>
+      <c r="D29" s="22">
+        <v>77</v>
+      </c>
       <c r="E29" s="17">
         <v>49</v>
       </c>
@@ -2725,7 +2783,7 @@
       <c r="G29" s="11">
         <v>49</v>
       </c>
-      <c r="H29" s="22">
+      <c r="H29" s="21">
         <v>74.193548387096769</v>
       </c>
     </row>
@@ -2739,7 +2797,9 @@
       <c r="C30" s="11">
         <v>48</v>
       </c>
-      <c r="D30" s="18"/>
+      <c r="D30" s="22">
+        <v>79</v>
+      </c>
       <c r="E30" s="17">
         <v>47</v>
       </c>
@@ -2749,7 +2809,7 @@
       <c r="G30" s="11">
         <v>55</v>
       </c>
-      <c r="H30" s="22">
+      <c r="H30" s="21">
         <v>90.322580645161281</v>
       </c>
     </row>
@@ -2763,7 +2823,9 @@
       <c r="C31" s="11">
         <v>58</v>
       </c>
-      <c r="D31" s="18"/>
+      <c r="D31" s="22">
+        <v>45</v>
+      </c>
       <c r="E31" s="17">
         <v>49</v>
       </c>
@@ -2773,7 +2835,7 @@
       <c r="G31" s="11">
         <v>50</v>
       </c>
-      <c r="H31" s="22">
+      <c r="H31" s="21">
         <v>80.645161290322577</v>
       </c>
     </row>
@@ -2787,7 +2849,9 @@
       <c r="C32" s="11">
         <v>32</v>
       </c>
-      <c r="D32" s="18"/>
+      <c r="D32" s="22">
+        <v>82</v>
+      </c>
       <c r="E32" s="17">
         <v>52</v>
       </c>
@@ -2797,7 +2861,7 @@
       <c r="G32" s="11">
         <v>18</v>
       </c>
-      <c r="H32" s="22">
+      <c r="H32" s="21">
         <v>64.516129032258064</v>
       </c>
     </row>
@@ -2811,7 +2875,9 @@
       <c r="C33" s="11">
         <v>36</v>
       </c>
-      <c r="D33" s="18"/>
+      <c r="D33" s="22">
+        <v>18</v>
+      </c>
       <c r="E33" s="17">
         <v>52</v>
       </c>
@@ -2821,7 +2887,7 @@
       <c r="G33" s="11">
         <v>31</v>
       </c>
-      <c r="H33" s="22">
+      <c r="H33" s="21">
         <v>70.967741935483872</v>
       </c>
     </row>
@@ -2835,7 +2901,9 @@
       <c r="C34" s="11">
         <v>57</v>
       </c>
-      <c r="D34" s="18"/>
+      <c r="D34" s="22">
+        <v>36</v>
+      </c>
       <c r="E34" s="17">
         <v>81</v>
       </c>
@@ -2845,7 +2913,7 @@
       <c r="G34" s="11">
         <v>25</v>
       </c>
-      <c r="H34" s="22">
+      <c r="H34" s="21">
         <v>80.645161290322577</v>
       </c>
     </row>
@@ -2859,7 +2927,9 @@
       <c r="C35" s="11">
         <v>33</v>
       </c>
-      <c r="D35" s="18"/>
+      <c r="D35" s="22">
+        <v>56</v>
+      </c>
       <c r="E35" s="17">
         <v>50</v>
       </c>
@@ -2869,7 +2939,7 @@
       <c r="G35" s="11">
         <v>32</v>
       </c>
-      <c r="H35" s="22">
+      <c r="H35" s="21">
         <v>87.096774193548384</v>
       </c>
     </row>
@@ -2883,7 +2953,9 @@
       <c r="C36" s="11">
         <v>53</v>
       </c>
-      <c r="D36" s="18"/>
+      <c r="D36" s="22">
+        <v>49</v>
+      </c>
       <c r="E36" s="17">
         <v>81</v>
       </c>
@@ -2893,7 +2965,7 @@
       <c r="G36" s="11">
         <v>47</v>
       </c>
-      <c r="H36" s="22">
+      <c r="H36" s="21">
         <v>67.741935483870961</v>
       </c>
     </row>
@@ -2907,7 +2979,9 @@
       <c r="C37" s="11">
         <v>59</v>
       </c>
-      <c r="D37" s="18"/>
+      <c r="D37" s="22">
+        <v>90</v>
+      </c>
       <c r="E37" s="17">
         <v>47</v>
       </c>
@@ -2917,7 +2991,7 @@
       <c r="G37" s="11">
         <v>50</v>
       </c>
-      <c r="H37" s="22">
+      <c r="H37" s="21">
         <v>70.967741935483872</v>
       </c>
     </row>
@@ -2931,7 +3005,9 @@
       <c r="C38" s="11">
         <v>58</v>
       </c>
-      <c r="D38" s="18"/>
+      <c r="D38" s="22">
+        <v>19</v>
+      </c>
       <c r="E38" s="17">
         <v>52</v>
       </c>
@@ -2941,7 +3017,7 @@
       <c r="G38" s="11">
         <v>33</v>
       </c>
-      <c r="H38" s="22">
+      <c r="H38" s="21">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -2955,7 +3031,9 @@
       <c r="C39" s="11">
         <v>50</v>
       </c>
-      <c r="D39" s="18"/>
+      <c r="D39" s="22">
+        <v>51</v>
+      </c>
       <c r="E39" s="17">
         <v>57</v>
       </c>
@@ -2965,7 +3043,7 @@
       <c r="G39" s="11">
         <v>16</v>
       </c>
-      <c r="H39" s="22">
+      <c r="H39" s="21">
         <v>83.870967741935488</v>
       </c>
     </row>
@@ -2979,7 +3057,9 @@
       <c r="C40" s="11">
         <v>64</v>
       </c>
-      <c r="D40" s="18"/>
+      <c r="D40" s="22">
+        <v>70</v>
+      </c>
       <c r="E40" s="17">
         <v>57</v>
       </c>
@@ -2989,7 +3069,7 @@
       <c r="G40" s="11">
         <v>56</v>
       </c>
-      <c r="H40" s="22">
+      <c r="H40" s="21">
         <v>87.096774193548384</v>
       </c>
     </row>
@@ -3003,7 +3083,9 @@
       <c r="C41" s="11">
         <v>63</v>
       </c>
-      <c r="D41" s="18"/>
+      <c r="D41" s="22">
+        <v>80</v>
+      </c>
       <c r="E41" s="17">
         <v>49</v>
       </c>
@@ -3013,7 +3095,7 @@
       <c r="G41" s="11">
         <v>54</v>
       </c>
-      <c r="H41" s="22">
+      <c r="H41" s="21">
         <v>87.096774193548384</v>
       </c>
     </row>
@@ -3027,7 +3109,9 @@
       <c r="C42" s="11">
         <v>32</v>
       </c>
-      <c r="D42" s="18"/>
+      <c r="D42" s="22">
+        <v>55</v>
+      </c>
       <c r="E42" s="17">
         <v>47</v>
       </c>
@@ -3037,7 +3121,7 @@
       <c r="G42" s="11">
         <v>21</v>
       </c>
-      <c r="H42" s="22">
+      <c r="H42" s="21">
         <v>87.096774193548384</v>
       </c>
     </row>
@@ -3051,7 +3135,9 @@
       <c r="C43" s="11">
         <v>42</v>
       </c>
-      <c r="D43" s="18"/>
+      <c r="D43" s="22">
+        <v>48</v>
+      </c>
       <c r="E43" s="17">
         <v>47</v>
       </c>
@@ -3061,7 +3147,7 @@
       <c r="G43" s="11">
         <v>46</v>
       </c>
-      <c r="H43" s="22">
+      <c r="H43" s="21">
         <v>61.29032258064516</v>
       </c>
     </row>
@@ -3075,7 +3161,9 @@
       <c r="C44" s="11">
         <v>41</v>
       </c>
-      <c r="D44" s="18"/>
+      <c r="D44" s="22">
+        <v>39</v>
+      </c>
       <c r="E44" s="17">
         <v>55</v>
       </c>
@@ -3085,7 +3173,7 @@
       <c r="G44" s="11">
         <v>32</v>
       </c>
-      <c r="H44" s="22">
+      <c r="H44" s="21">
         <v>87.096774193548384</v>
       </c>
     </row>
@@ -3099,7 +3187,9 @@
       <c r="C45" s="11">
         <v>20</v>
       </c>
-      <c r="D45" s="18"/>
+      <c r="D45" s="22">
+        <v>43</v>
+      </c>
       <c r="E45" s="17">
         <v>37</v>
       </c>
@@ -3109,7 +3199,7 @@
       <c r="G45" s="11">
         <v>36</v>
       </c>
-      <c r="H45" s="22">
+      <c r="H45" s="21">
         <v>74.193548387096769</v>
       </c>
     </row>
@@ -3123,7 +3213,9 @@
       <c r="C46" s="11">
         <v>23</v>
       </c>
-      <c r="D46" s="18"/>
+      <c r="D46" s="22">
+        <v>60</v>
+      </c>
       <c r="E46" s="17">
         <v>47</v>
       </c>
@@ -3133,7 +3225,7 @@
       <c r="G46" s="11">
         <v>22</v>
       </c>
-      <c r="H46" s="22">
+      <c r="H46" s="21">
         <v>90.322580645161281</v>
       </c>
     </row>
@@ -3147,7 +3239,9 @@
       <c r="C47" s="11">
         <v>59</v>
       </c>
-      <c r="D47" s="18"/>
+      <c r="D47" s="22">
+        <v>85</v>
+      </c>
       <c r="E47" s="17">
         <v>55</v>
       </c>
@@ -3157,7 +3251,7 @@
       <c r="G47" s="11">
         <v>50</v>
       </c>
-      <c r="H47" s="22">
+      <c r="H47" s="21">
         <v>80.645161290322577</v>
       </c>
     </row>
@@ -3171,7 +3265,9 @@
       <c r="C48" s="11">
         <v>77</v>
       </c>
-      <c r="D48" s="18"/>
+      <c r="D48" s="22">
+        <v>44</v>
+      </c>
       <c r="E48" s="17">
         <v>49</v>
       </c>
@@ -3181,7 +3277,7 @@
       <c r="G48" s="11">
         <v>34</v>
       </c>
-      <c r="H48" s="22">
+      <c r="H48" s="21">
         <v>90.322580645161281</v>
       </c>
     </row>
@@ -3195,7 +3291,9 @@
       <c r="C49" s="11">
         <v>54</v>
       </c>
-      <c r="D49" s="18"/>
+      <c r="D49" s="22">
+        <v>78</v>
+      </c>
       <c r="E49" s="17">
         <v>52</v>
       </c>
@@ -3205,7 +3303,7 @@
       <c r="G49" s="11">
         <v>46</v>
       </c>
-      <c r="H49" s="22">
+      <c r="H49" s="21">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -3219,7 +3317,9 @@
       <c r="C50" s="11">
         <v>47</v>
       </c>
-      <c r="D50" s="18"/>
+      <c r="D50" s="22">
+        <v>75</v>
+      </c>
       <c r="E50" s="17">
         <v>50</v>
       </c>
@@ -3229,7 +3329,7 @@
       <c r="G50" s="11">
         <v>22</v>
       </c>
-      <c r="H50" s="22">
+      <c r="H50" s="21">
         <v>83.870967741935488</v>
       </c>
     </row>
@@ -3243,7 +3343,9 @@
       <c r="C51" s="11">
         <v>44</v>
       </c>
-      <c r="D51" s="18"/>
+      <c r="D51" s="22">
+        <v>27</v>
+      </c>
       <c r="E51" s="17">
         <v>44</v>
       </c>
@@ -3253,7 +3355,7 @@
       <c r="G51" s="11">
         <v>18</v>
       </c>
-      <c r="H51" s="22">
+      <c r="H51" s="21">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -3267,7 +3369,9 @@
       <c r="C52" s="11">
         <v>55</v>
       </c>
-      <c r="D52" s="18"/>
+      <c r="D52" s="22">
+        <v>65</v>
+      </c>
       <c r="E52" s="17">
         <v>52</v>
       </c>
@@ -3277,7 +3381,7 @@
       <c r="G52" s="11">
         <v>27</v>
       </c>
-      <c r="H52" s="22">
+      <c r="H52" s="21">
         <v>80.645161290322577</v>
       </c>
     </row>
@@ -3291,7 +3395,9 @@
       <c r="C53" s="11">
         <v>67</v>
       </c>
-      <c r="D53" s="18"/>
+      <c r="D53" s="22">
+        <v>63</v>
+      </c>
       <c r="E53" s="17">
         <v>49</v>
       </c>
@@ -3301,7 +3407,7 @@
       <c r="G53" s="11">
         <v>45</v>
       </c>
-      <c r="H53" s="22">
+      <c r="H53" s="21">
         <v>96.774193548387103</v>
       </c>
     </row>
@@ -3315,7 +3421,9 @@
       <c r="C54" s="11">
         <v>40</v>
       </c>
-      <c r="D54" s="18"/>
+      <c r="D54" s="22">
+        <v>29</v>
+      </c>
       <c r="E54" s="17">
         <v>50</v>
       </c>
@@ -3325,7 +3433,7 @@
       <c r="G54" s="11">
         <v>23</v>
       </c>
-      <c r="H54" s="22">
+      <c r="H54" s="21">
         <v>80.645161290322577</v>
       </c>
     </row>
@@ -3339,7 +3447,9 @@
       <c r="C55" s="11">
         <v>32</v>
       </c>
-      <c r="D55" s="18"/>
+      <c r="D55" s="22">
+        <v>42</v>
+      </c>
       <c r="E55" s="17">
         <v>57</v>
       </c>
@@ -3349,7 +3459,7 @@
       <c r="G55" s="11">
         <v>35</v>
       </c>
-      <c r="H55" s="22">
+      <c r="H55" s="21">
         <v>90.322580645161281</v>
       </c>
     </row>
@@ -3363,7 +3473,9 @@
       <c r="C56" s="11">
         <v>60</v>
       </c>
-      <c r="D56" s="18"/>
+      <c r="D56" s="22">
+        <v>46</v>
+      </c>
       <c r="E56" s="17">
         <v>66</v>
       </c>
@@ -3373,7 +3485,7 @@
       <c r="G56" s="11">
         <v>42</v>
       </c>
-      <c r="H56" s="22">
+      <c r="H56" s="21">
         <v>83.870967741935488</v>
       </c>
     </row>
@@ -3387,7 +3499,9 @@
       <c r="C57" s="11">
         <v>61</v>
       </c>
-      <c r="D57" s="18"/>
+      <c r="D57" s="22">
+        <v>69</v>
+      </c>
       <c r="E57" s="17">
         <v>46</v>
       </c>
@@ -3397,7 +3511,7 @@
       <c r="G57" s="11">
         <v>29</v>
       </c>
-      <c r="H57" s="22">
+      <c r="H57" s="21">
         <v>90.322580645161281</v>
       </c>
     </row>
@@ -3411,7 +3525,9 @@
       <c r="C58" s="11">
         <v>38</v>
       </c>
-      <c r="D58" s="18"/>
+      <c r="D58" s="22">
+        <v>9</v>
+      </c>
       <c r="E58" s="17">
         <v>46</v>
       </c>
@@ -3421,7 +3537,7 @@
       <c r="G58" s="11">
         <v>15</v>
       </c>
-      <c r="H58" s="22">
+      <c r="H58" s="21">
         <v>64.516129032258064</v>
       </c>
     </row>
@@ -3435,7 +3551,9 @@
       <c r="C59" s="11">
         <v>40</v>
       </c>
-      <c r="D59" s="18"/>
+      <c r="D59" s="22">
+        <v>40</v>
+      </c>
       <c r="E59" s="17">
         <v>87</v>
       </c>
@@ -3445,7 +3563,7 @@
       <c r="G59" s="11">
         <v>34</v>
       </c>
-      <c r="H59" s="22">
+      <c r="H59" s="21">
         <v>83.870967741935488</v>
       </c>
     </row>
@@ -3459,7 +3577,9 @@
       <c r="C60" s="11">
         <v>63</v>
       </c>
-      <c r="D60" s="18"/>
+      <c r="D60" s="22">
+        <v>82</v>
+      </c>
       <c r="E60" s="17">
         <v>70</v>
       </c>
@@ -3469,7 +3589,7 @@
       <c r="G60" s="11">
         <v>75</v>
       </c>
-      <c r="H60" s="22">
+      <c r="H60" s="21">
         <v>96.774193548387103</v>
       </c>
     </row>
@@ -3483,7 +3603,9 @@
       <c r="C61" s="11">
         <v>50</v>
       </c>
-      <c r="D61" s="18"/>
+      <c r="D61" s="22">
+        <v>45</v>
+      </c>
       <c r="E61" s="17">
         <v>70</v>
       </c>
@@ -3493,7 +3615,7 @@
       <c r="G61" s="11">
         <v>35</v>
       </c>
-      <c r="H61" s="22">
+      <c r="H61" s="21">
         <v>93.548387096774192</v>
       </c>
     </row>
@@ -3507,7 +3629,9 @@
       <c r="C62" s="11">
         <v>19</v>
       </c>
-      <c r="D62" s="18"/>
+      <c r="D62" s="22">
+        <v>42</v>
+      </c>
       <c r="E62" s="17">
         <v>47</v>
       </c>
@@ -3517,7 +3641,7 @@
       <c r="G62" s="11">
         <v>28</v>
       </c>
-      <c r="H62" s="22">
+      <c r="H62" s="21">
         <v>90.322580645161281</v>
       </c>
     </row>
@@ -3531,7 +3655,9 @@
       <c r="C63" s="11">
         <v>81</v>
       </c>
-      <c r="D63" s="18"/>
+      <c r="D63" s="22">
+        <v>67</v>
+      </c>
       <c r="E63" s="17">
         <v>52</v>
       </c>
@@ -3541,7 +3667,7 @@
       <c r="G63" s="11">
         <v>56</v>
       </c>
-      <c r="H63" s="22">
+      <c r="H63" s="21">
         <v>93.548387096774192</v>
       </c>
     </row>
@@ -3555,7 +3681,9 @@
       <c r="C64" s="11">
         <v>27</v>
       </c>
-      <c r="D64" s="18"/>
+      <c r="D64" s="22">
+        <v>57</v>
+      </c>
       <c r="E64" s="17">
         <v>52</v>
       </c>
@@ -3565,7 +3693,7 @@
       <c r="G64" s="11">
         <v>47</v>
       </c>
-      <c r="H64" s="22">
+      <c r="H64" s="21">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -3579,7 +3707,9 @@
       <c r="C65" s="11">
         <v>60</v>
       </c>
-      <c r="D65" s="18"/>
+      <c r="D65" s="22">
+        <v>55</v>
+      </c>
       <c r="E65" s="17">
         <v>49</v>
       </c>
@@ -3589,7 +3719,7 @@
       <c r="G65" s="11">
         <v>53</v>
       </c>
-      <c r="H65" s="22">
+      <c r="H65" s="21">
         <v>90.322580645161281</v>
       </c>
     </row>
@@ -3603,7 +3733,9 @@
       <c r="C66" s="11">
         <v>33</v>
       </c>
-      <c r="D66" s="18"/>
+      <c r="D66" s="22">
+        <v>60</v>
+      </c>
       <c r="E66" s="17">
         <v>60</v>
       </c>
@@ -3613,7 +3745,7 @@
       <c r="G66" s="11">
         <v>15</v>
       </c>
-      <c r="H66" s="22">
+      <c r="H66" s="21">
         <v>93.548387096774192</v>
       </c>
     </row>
@@ -3627,7 +3759,9 @@
       <c r="C67" s="11">
         <v>54</v>
       </c>
-      <c r="D67" s="18"/>
+      <c r="D67" s="22">
+        <v>73</v>
+      </c>
       <c r="E67" s="17">
         <v>49</v>
       </c>
@@ -3637,7 +3771,7 @@
       <c r="G67" s="11">
         <v>43</v>
       </c>
-      <c r="H67" s="22">
+      <c r="H67" s="21">
         <v>87.096774193548384</v>
       </c>
     </row>
@@ -3651,7 +3785,9 @@
       <c r="C68" s="11">
         <v>54</v>
       </c>
-      <c r="D68" s="18"/>
+      <c r="D68" s="22">
+        <v>52</v>
+      </c>
       <c r="E68" s="17">
         <v>81</v>
       </c>
@@ -3661,7 +3797,7 @@
       <c r="G68" s="11">
         <v>31</v>
       </c>
-      <c r="H68" s="22">
+      <c r="H68" s="21">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -3675,7 +3811,9 @@
       <c r="C69" s="11">
         <v>57</v>
       </c>
-      <c r="D69" s="18"/>
+      <c r="D69" s="22">
+        <v>60</v>
+      </c>
       <c r="E69" s="17">
         <v>57</v>
       </c>
@@ -3685,7 +3823,7 @@
       <c r="G69" s="11">
         <v>40</v>
       </c>
-      <c r="H69" s="22">
+      <c r="H69" s="21">
         <v>93.548387096774192</v>
       </c>
     </row>
@@ -3699,7 +3837,9 @@
       <c r="C70" s="11">
         <v>39</v>
       </c>
-      <c r="D70" s="18"/>
+      <c r="D70" s="22">
+        <v>72</v>
+      </c>
       <c r="E70" s="17">
         <v>57</v>
       </c>
@@ -3709,7 +3849,7 @@
       <c r="G70" s="11">
         <v>62</v>
       </c>
-      <c r="H70" s="22">
+      <c r="H70" s="21">
         <v>93.548387096774192</v>
       </c>
     </row>
@@ -3723,7 +3863,9 @@
       <c r="C71" s="11">
         <v>44</v>
       </c>
-      <c r="D71" s="18"/>
+      <c r="D71" s="22">
+        <v>44</v>
+      </c>
       <c r="E71" s="17">
         <v>37</v>
       </c>
@@ -3733,7 +3875,7 @@
       <c r="G71" s="11">
         <v>51</v>
       </c>
-      <c r="H71" s="22">
+      <c r="H71" s="21">
         <v>96.774193548387103</v>
       </c>
     </row>
@@ -3747,7 +3889,9 @@
       <c r="C72" s="11">
         <v>68</v>
       </c>
-      <c r="D72" s="18"/>
+      <c r="D72" s="22">
+        <v>51</v>
+      </c>
       <c r="E72" s="17">
         <v>49</v>
       </c>
@@ -3757,7 +3901,7 @@
       <c r="G72" s="11">
         <v>31</v>
       </c>
-      <c r="H72" s="22">
+      <c r="H72" s="21">
         <v>74.193548387096769</v>
       </c>
     </row>
@@ -3771,7 +3915,9 @@
       <c r="C73" s="11">
         <v>35</v>
       </c>
-      <c r="D73" s="18"/>
+      <c r="D73" s="22">
+        <v>72</v>
+      </c>
       <c r="E73" s="17">
         <v>44</v>
       </c>
@@ -3781,7 +3927,7 @@
       <c r="G73" s="11">
         <v>23</v>
       </c>
-      <c r="H73" s="22">
+      <c r="H73" s="21">
         <v>74.193548387096769</v>
       </c>
     </row>
@@ -3795,8 +3941,10 @@
       <c r="C74" s="11">
         <v>49</v>
       </c>
-      <c r="D74" s="18"/>
-      <c r="E74" s="20" t="s">
+      <c r="D74" s="22" t="s">
+        <v>482</v>
+      </c>
+      <c r="E74" s="19" t="s">
         <v>482</v>
       </c>
       <c r="F74" s="17">
@@ -3805,7 +3953,7 @@
       <c r="G74" s="11">
         <v>28</v>
       </c>
-      <c r="H74" s="22">
+      <c r="H74" s="21">
         <v>38.70967741935484</v>
       </c>
     </row>
@@ -3819,7 +3967,9 @@
       <c r="C75" s="11">
         <v>52</v>
       </c>
-      <c r="D75" s="18"/>
+      <c r="D75" s="22">
+        <v>36</v>
+      </c>
       <c r="E75" s="17">
         <v>47</v>
       </c>
@@ -3829,7 +3979,7 @@
       <c r="G75" s="11">
         <v>26</v>
       </c>
-      <c r="H75" s="22">
+      <c r="H75" s="21">
         <v>74.193548387096769</v>
       </c>
     </row>
@@ -3843,7 +3993,9 @@
       <c r="C76" s="11">
         <v>50</v>
       </c>
-      <c r="D76" s="18"/>
+      <c r="D76" s="22">
+        <v>47</v>
+      </c>
       <c r="E76" s="17">
         <v>57</v>
       </c>
@@ -3853,7 +4005,7 @@
       <c r="G76" s="11">
         <v>58</v>
       </c>
-      <c r="H76" s="22">
+      <c r="H76" s="21">
         <v>96.774193548387103</v>
       </c>
     </row>
@@ -3867,7 +4019,9 @@
       <c r="C77" s="11">
         <v>54</v>
       </c>
-      <c r="D77" s="18"/>
+      <c r="D77" s="22">
+        <v>57</v>
+      </c>
       <c r="E77" s="17">
         <v>52</v>
       </c>
@@ -3877,7 +4031,7 @@
       <c r="G77" s="11">
         <v>39</v>
       </c>
-      <c r="H77" s="22">
+      <c r="H77" s="21">
         <v>90.322580645161281</v>
       </c>
     </row>
@@ -3891,7 +4045,9 @@
       <c r="C78" s="11">
         <v>60</v>
       </c>
-      <c r="D78" s="18"/>
+      <c r="D78" s="22">
+        <v>13</v>
+      </c>
       <c r="E78" s="17">
         <v>81</v>
       </c>
@@ -3901,7 +4057,7 @@
       <c r="G78" s="11">
         <v>24</v>
       </c>
-      <c r="H78" s="22">
+      <c r="H78" s="21">
         <v>80.645161290322577</v>
       </c>
     </row>
@@ -3915,7 +4071,9 @@
       <c r="C79" s="11">
         <v>55</v>
       </c>
-      <c r="D79" s="18"/>
+      <c r="D79" s="22">
+        <v>66</v>
+      </c>
       <c r="E79" s="17">
         <v>47</v>
       </c>
@@ -3925,7 +4083,7 @@
       <c r="G79" s="11">
         <v>45</v>
       </c>
-      <c r="H79" s="22">
+      <c r="H79" s="21">
         <v>87.096774193548384</v>
       </c>
     </row>
@@ -3939,7 +4097,9 @@
       <c r="C80" s="11">
         <v>54</v>
       </c>
-      <c r="D80" s="18"/>
+      <c r="D80" s="22">
+        <v>49</v>
+      </c>
       <c r="E80" s="17">
         <v>49</v>
       </c>
@@ -3949,7 +4109,7 @@
       <c r="G80" s="11">
         <v>19</v>
       </c>
-      <c r="H80" s="22">
+      <c r="H80" s="21">
         <v>80.645161290322577</v>
       </c>
     </row>
@@ -3963,7 +4123,9 @@
       <c r="C81" s="11">
         <v>54</v>
       </c>
-      <c r="D81" s="18"/>
+      <c r="D81" s="22">
+        <v>87</v>
+      </c>
       <c r="E81" s="17">
         <v>49</v>
       </c>
@@ -3973,7 +4135,7 @@
       <c r="G81" s="11">
         <v>48</v>
       </c>
-      <c r="H81" s="22">
+      <c r="H81" s="21">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -3987,7 +4149,9 @@
       <c r="C82" s="11">
         <v>62</v>
       </c>
-      <c r="D82" s="18"/>
+      <c r="D82" s="22">
+        <v>72</v>
+      </c>
       <c r="E82" s="17">
         <v>37</v>
       </c>
@@ -3997,7 +4161,7 @@
       <c r="G82" s="11">
         <v>45</v>
       </c>
-      <c r="H82" s="22">
+      <c r="H82" s="21">
         <v>90.322580645161281</v>
       </c>
     </row>
@@ -4011,7 +4175,9 @@
       <c r="C83" s="11">
         <v>59</v>
       </c>
-      <c r="D83" s="18"/>
+      <c r="D83" s="22">
+        <v>52</v>
+      </c>
       <c r="E83" s="17">
         <v>57</v>
       </c>
@@ -4021,7 +4187,7 @@
       <c r="G83" s="11">
         <v>29</v>
       </c>
-      <c r="H83" s="22">
+      <c r="H83" s="21">
         <v>90.322580645161281</v>
       </c>
     </row>
@@ -4035,7 +4201,9 @@
       <c r="C84" s="11">
         <v>60</v>
       </c>
-      <c r="D84" s="18"/>
+      <c r="D84" s="22">
+        <v>58</v>
+      </c>
       <c r="E84" s="17">
         <v>37</v>
       </c>
@@ -4045,7 +4213,7 @@
       <c r="G84" s="11">
         <v>36</v>
       </c>
-      <c r="H84" s="22">
+      <c r="H84" s="21">
         <v>93.548387096774192</v>
       </c>
     </row>
@@ -4059,7 +4227,9 @@
       <c r="C85" s="11">
         <v>43</v>
       </c>
-      <c r="D85" s="18"/>
+      <c r="D85" s="22">
+        <v>74</v>
+      </c>
       <c r="E85" s="17">
         <v>57</v>
       </c>
@@ -4069,7 +4239,7 @@
       <c r="G85" s="11">
         <v>41</v>
       </c>
-      <c r="H85" s="22">
+      <c r="H85" s="21">
         <v>93.548387096774192</v>
       </c>
     </row>
@@ -4083,7 +4253,9 @@
       <c r="C86" s="11">
         <v>41</v>
       </c>
-      <c r="D86" s="18"/>
+      <c r="D86" s="22">
+        <v>44</v>
+      </c>
       <c r="E86" s="17">
         <v>61</v>
       </c>
@@ -4093,7 +4265,7 @@
       <c r="G86" s="11">
         <v>17</v>
       </c>
-      <c r="H86" s="22">
+      <c r="H86" s="21">
         <v>74.193548387096769</v>
       </c>
     </row>
@@ -4107,7 +4279,9 @@
       <c r="C87" s="11">
         <v>41</v>
       </c>
-      <c r="D87" s="18"/>
+      <c r="D87" s="22">
+        <v>58</v>
+      </c>
       <c r="E87" s="17">
         <v>87</v>
       </c>
@@ -4117,7 +4291,7 @@
       <c r="G87" s="11">
         <v>32</v>
       </c>
-      <c r="H87" s="22">
+      <c r="H87" s="21">
         <v>96.774193548387103</v>
       </c>
     </row>
@@ -4131,7 +4305,9 @@
       <c r="C88" s="11">
         <v>48</v>
       </c>
-      <c r="D88" s="18"/>
+      <c r="D88" s="22">
+        <v>12</v>
+      </c>
       <c r="E88" s="17">
         <v>47</v>
       </c>
@@ -4141,7 +4317,7 @@
       <c r="G88" s="11">
         <v>23</v>
       </c>
-      <c r="H88" s="22">
+      <c r="H88" s="21">
         <v>54.838709677419352</v>
       </c>
     </row>
@@ -4155,7 +4331,9 @@
       <c r="C89" s="11">
         <v>38</v>
       </c>
-      <c r="D89" s="18"/>
+      <c r="D89" s="22">
+        <v>53</v>
+      </c>
       <c r="E89" s="17">
         <v>44</v>
       </c>
@@ -4165,7 +4343,7 @@
       <c r="G89" s="11">
         <v>38</v>
       </c>
-      <c r="H89" s="22">
+      <c r="H89" s="21">
         <v>90.322580645161281</v>
       </c>
     </row>
@@ -4179,7 +4357,9 @@
       <c r="C90" s="11">
         <v>43</v>
       </c>
-      <c r="D90" s="18"/>
+      <c r="D90" s="22">
+        <v>27</v>
+      </c>
       <c r="E90" s="17">
         <v>55</v>
       </c>
@@ -4189,7 +4369,7 @@
       <c r="G90" s="11">
         <v>38</v>
       </c>
-      <c r="H90" s="22">
+      <c r="H90" s="21">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -4203,7 +4383,9 @@
       <c r="C91" s="11">
         <v>52</v>
       </c>
-      <c r="D91" s="18"/>
+      <c r="D91" s="22">
+        <v>65</v>
+      </c>
       <c r="E91" s="17">
         <v>66</v>
       </c>
@@ -4213,7 +4395,7 @@
       <c r="G91" s="11" t="s">
         <v>482</v>
       </c>
-      <c r="H91" s="22">
+      <c r="H91" s="21">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -4227,7 +4409,9 @@
       <c r="C92" s="11">
         <v>49</v>
       </c>
-      <c r="D92" s="18"/>
+      <c r="D92" s="22">
+        <v>55</v>
+      </c>
       <c r="E92" s="17">
         <v>50</v>
       </c>
@@ -4237,7 +4421,7 @@
       <c r="G92" s="11">
         <v>52</v>
       </c>
-      <c r="H92" s="22">
+      <c r="H92" s="21">
         <v>87.096774193548384</v>
       </c>
     </row>
@@ -4251,7 +4435,9 @@
       <c r="C93" s="11">
         <v>41</v>
       </c>
-      <c r="D93" s="18"/>
+      <c r="D93" s="22">
+        <v>63</v>
+      </c>
       <c r="E93" s="17">
         <v>55</v>
       </c>
@@ -4261,7 +4447,7 @@
       <c r="G93" s="11">
         <v>32</v>
       </c>
-      <c r="H93" s="22">
+      <c r="H93" s="21">
         <v>87.096774193548384</v>
       </c>
     </row>
@@ -4275,7 +4461,9 @@
       <c r="C94" s="11">
         <v>15</v>
       </c>
-      <c r="D94" s="18"/>
+      <c r="D94" s="22" t="s">
+        <v>482</v>
+      </c>
       <c r="E94" s="17">
         <v>46</v>
       </c>
@@ -4285,7 +4473,7 @@
       <c r="G94" s="11">
         <v>17</v>
       </c>
-      <c r="H94" s="22">
+      <c r="H94" s="21">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -4299,7 +4487,9 @@
       <c r="C95" s="11">
         <v>41</v>
       </c>
-      <c r="D95" s="18"/>
+      <c r="D95" s="22">
+        <v>20</v>
+      </c>
       <c r="E95" s="17">
         <v>49</v>
       </c>
@@ -4309,7 +4499,7 @@
       <c r="G95" s="11">
         <v>41</v>
       </c>
-      <c r="H95" s="22">
+      <c r="H95" s="21">
         <v>45.161290322580641</v>
       </c>
     </row>
@@ -4323,7 +4513,9 @@
       <c r="C96" s="11">
         <v>41</v>
       </c>
-      <c r="D96" s="18"/>
+      <c r="D96" s="22">
+        <v>42</v>
+      </c>
       <c r="E96" s="17">
         <v>66</v>
       </c>
@@ -4333,7 +4525,7 @@
       <c r="G96" s="11">
         <v>25</v>
       </c>
-      <c r="H96" s="22">
+      <c r="H96" s="21">
         <v>87.096774193548384</v>
       </c>
     </row>
@@ -4347,7 +4539,9 @@
       <c r="C97" s="11">
         <v>46</v>
       </c>
-      <c r="D97" s="18"/>
+      <c r="D97" s="22">
+        <v>18</v>
+      </c>
       <c r="E97" s="17">
         <v>49</v>
       </c>
@@ -4357,7 +4551,7 @@
       <c r="G97" s="11">
         <v>30</v>
       </c>
-      <c r="H97" s="22">
+      <c r="H97" s="21">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -4371,7 +4565,9 @@
       <c r="C98" s="11">
         <v>40</v>
       </c>
-      <c r="D98" s="18"/>
+      <c r="D98" s="22">
+        <v>57</v>
+      </c>
       <c r="E98" s="17">
         <v>66</v>
       </c>
@@ -4381,7 +4577,7 @@
       <c r="G98" s="11">
         <v>41</v>
       </c>
-      <c r="H98" s="22">
+      <c r="H98" s="21">
         <v>74.193548387096769</v>
       </c>
     </row>
@@ -4395,7 +4591,9 @@
       <c r="C99" s="11">
         <v>53</v>
       </c>
-      <c r="D99" s="18"/>
+      <c r="D99" s="22">
+        <v>49</v>
+      </c>
       <c r="E99" s="17">
         <v>50</v>
       </c>
@@ -4405,7 +4603,7 @@
       <c r="G99" s="11">
         <v>31</v>
       </c>
-      <c r="H99" s="22">
+      <c r="H99" s="21">
         <v>90.322580645161281</v>
       </c>
     </row>
@@ -4419,7 +4617,9 @@
       <c r="C100" s="11">
         <v>35</v>
       </c>
-      <c r="D100" s="18"/>
+      <c r="D100" s="22">
+        <v>46</v>
+      </c>
       <c r="E100" s="17">
         <v>81</v>
       </c>
@@ -4429,7 +4629,7 @@
       <c r="G100" s="11">
         <v>19</v>
       </c>
-      <c r="H100" s="22">
+      <c r="H100" s="21">
         <v>87.096774193548384</v>
       </c>
     </row>
@@ -4443,7 +4643,9 @@
       <c r="C101" s="11">
         <v>41</v>
       </c>
-      <c r="D101" s="18"/>
+      <c r="D101" s="22">
+        <v>55</v>
+      </c>
       <c r="E101" s="17">
         <v>60</v>
       </c>
@@ -4453,7 +4655,7 @@
       <c r="G101" s="11">
         <v>17</v>
       </c>
-      <c r="H101" s="22">
+      <c r="H101" s="21">
         <v>87.096774193548384</v>
       </c>
     </row>
@@ -4467,7 +4669,9 @@
       <c r="C102" s="11">
         <v>38</v>
       </c>
-      <c r="D102" s="18"/>
+      <c r="D102" s="22">
+        <v>14</v>
+      </c>
       <c r="E102" s="17">
         <v>61</v>
       </c>
@@ -4477,7 +4681,7 @@
       <c r="G102" s="11">
         <v>10</v>
       </c>
-      <c r="H102" s="22">
+      <c r="H102" s="21">
         <v>51.612903225806448</v>
       </c>
     </row>
@@ -4491,8 +4695,10 @@
       <c r="C103" s="11" t="s">
         <v>482</v>
       </c>
-      <c r="D103" s="18"/>
-      <c r="E103" s="20" t="s">
+      <c r="D103" s="22" t="s">
+        <v>482</v>
+      </c>
+      <c r="E103" s="19" t="s">
         <v>482</v>
       </c>
       <c r="F103" s="17" t="s">
@@ -4501,7 +4707,7 @@
       <c r="G103" s="11" t="s">
         <v>482</v>
       </c>
-      <c r="H103" s="22">
+      <c r="H103" s="21">
         <v>16.129032258064516</v>
       </c>
     </row>
@@ -4515,7 +4721,9 @@
       <c r="C104" s="11">
         <v>65</v>
       </c>
-      <c r="D104" s="18"/>
+      <c r="D104" s="22">
+        <v>81</v>
+      </c>
       <c r="E104" s="17">
         <v>57</v>
       </c>
@@ -4525,7 +4733,7 @@
       <c r="G104" s="11">
         <v>61</v>
       </c>
-      <c r="H104" s="22">
+      <c r="H104" s="21">
         <v>83.870967741935488</v>
       </c>
     </row>
@@ -4539,7 +4747,9 @@
       <c r="C105" s="11">
         <v>46</v>
       </c>
-      <c r="D105" s="18"/>
+      <c r="D105" s="22">
+        <v>56</v>
+      </c>
       <c r="E105" s="17">
         <v>55</v>
       </c>
@@ -4549,7 +4759,7 @@
       <c r="G105" s="11">
         <v>48</v>
       </c>
-      <c r="H105" s="22">
+      <c r="H105" s="21">
         <v>80.645161290322577</v>
       </c>
     </row>
@@ -4563,7 +4773,9 @@
       <c r="C106" s="11">
         <v>45</v>
       </c>
-      <c r="D106" s="18"/>
+      <c r="D106" s="22">
+        <v>13</v>
+      </c>
       <c r="E106" s="17">
         <v>70</v>
       </c>
@@ -4573,7 +4785,7 @@
       <c r="G106" s="11">
         <v>28</v>
       </c>
-      <c r="H106" s="22">
+      <c r="H106" s="21">
         <v>45.161290322580641</v>
       </c>
     </row>
@@ -4587,7 +4799,9 @@
       <c r="C107" s="11">
         <v>46</v>
       </c>
-      <c r="D107" s="18"/>
+      <c r="D107" s="22">
+        <v>75</v>
+      </c>
       <c r="E107" s="17">
         <v>52</v>
       </c>
@@ -4597,7 +4811,7 @@
       <c r="G107" s="11">
         <v>35</v>
       </c>
-      <c r="H107" s="22">
+      <c r="H107" s="21">
         <v>83.870967741935488</v>
       </c>
     </row>
@@ -4611,7 +4825,9 @@
       <c r="C108" s="11">
         <v>41</v>
       </c>
-      <c r="D108" s="18"/>
+      <c r="D108" s="22">
+        <v>27</v>
+      </c>
       <c r="E108" s="17">
         <v>49</v>
       </c>
@@ -4621,7 +4837,7 @@
       <c r="G108" s="11">
         <v>41</v>
       </c>
-      <c r="H108" s="22">
+      <c r="H108" s="21">
         <v>93.548387096774192</v>
       </c>
     </row>
@@ -4635,7 +4851,9 @@
       <c r="C109" s="11">
         <v>24</v>
       </c>
-      <c r="D109" s="18"/>
+      <c r="D109" s="22">
+        <v>36</v>
+      </c>
       <c r="E109" s="17">
         <v>60</v>
       </c>
@@ -4645,7 +4863,7 @@
       <c r="G109" s="11">
         <v>21</v>
       </c>
-      <c r="H109" s="22">
+      <c r="H109" s="21">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -4659,7 +4877,9 @@
       <c r="C110" s="11">
         <v>70</v>
       </c>
-      <c r="D110" s="18"/>
+      <c r="D110" s="22">
+        <v>89</v>
+      </c>
       <c r="E110" s="17">
         <v>49</v>
       </c>
@@ -4669,7 +4889,7 @@
       <c r="G110" s="11">
         <v>59</v>
       </c>
-      <c r="H110" s="22">
+      <c r="H110" s="21">
         <v>87.096774193548384</v>
       </c>
     </row>
@@ -4683,7 +4903,9 @@
       <c r="C111" s="11">
         <v>52</v>
       </c>
-      <c r="D111" s="18"/>
+      <c r="D111" s="22">
+        <v>68</v>
+      </c>
       <c r="E111" s="17">
         <v>44</v>
       </c>
@@ -4693,7 +4915,7 @@
       <c r="G111" s="11">
         <v>40</v>
       </c>
-      <c r="H111" s="22">
+      <c r="H111" s="21">
         <v>58.064516129032263</v>
       </c>
     </row>
@@ -4707,7 +4929,9 @@
       <c r="C112" s="11">
         <v>50</v>
       </c>
-      <c r="D112" s="18"/>
+      <c r="D112" s="22">
+        <v>66</v>
+      </c>
       <c r="E112" s="17">
         <v>49</v>
       </c>
@@ -4717,7 +4941,7 @@
       <c r="G112" s="11">
         <v>35</v>
       </c>
-      <c r="H112" s="22">
+      <c r="H112" s="21">
         <v>48.387096774193552</v>
       </c>
     </row>
@@ -4731,7 +4955,9 @@
       <c r="C113" s="11">
         <v>52</v>
       </c>
-      <c r="D113" s="18"/>
+      <c r="D113" s="22">
+        <v>83</v>
+      </c>
       <c r="E113" s="17">
         <v>47</v>
       </c>
@@ -4741,7 +4967,7 @@
       <c r="G113" s="11">
         <v>46</v>
       </c>
-      <c r="H113" s="22">
+      <c r="H113" s="21">
         <v>83.870967741935488</v>
       </c>
     </row>
@@ -4755,7 +4981,9 @@
       <c r="C114" s="11">
         <v>64</v>
       </c>
-      <c r="D114" s="18"/>
+      <c r="D114" s="22">
+        <v>92</v>
+      </c>
       <c r="E114" s="17">
         <v>64</v>
       </c>
@@ -4765,7 +4993,7 @@
       <c r="G114" s="11">
         <v>55</v>
       </c>
-      <c r="H114" s="22">
+      <c r="H114" s="21">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -4779,7 +5007,9 @@
       <c r="C115" s="11">
         <v>60</v>
       </c>
-      <c r="D115" s="18"/>
+      <c r="D115" s="22">
+        <v>85</v>
+      </c>
       <c r="E115" s="17">
         <v>50</v>
       </c>
@@ -4789,7 +5019,7 @@
       <c r="G115" s="11">
         <v>49</v>
       </c>
-      <c r="H115" s="22">
+      <c r="H115" s="21">
         <v>90.322580645161281</v>
       </c>
     </row>
@@ -4803,7 +5033,9 @@
       <c r="C116" s="11">
         <v>53</v>
       </c>
-      <c r="D116" s="18"/>
+      <c r="D116" s="22">
+        <v>80</v>
+      </c>
       <c r="E116" s="17">
         <v>64</v>
       </c>
@@ -4813,7 +5045,7 @@
       <c r="G116" s="11">
         <v>63</v>
       </c>
-      <c r="H116" s="22">
+      <c r="H116" s="21">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -4827,7 +5059,9 @@
       <c r="C117" s="11">
         <v>60</v>
       </c>
-      <c r="D117" s="18"/>
+      <c r="D117" s="22">
+        <v>82</v>
+      </c>
       <c r="E117" s="17">
         <v>46</v>
       </c>
@@ -4837,7 +5071,7 @@
       <c r="G117" s="11">
         <v>43</v>
       </c>
-      <c r="H117" s="22">
+      <c r="H117" s="21">
         <v>83.870967741935488</v>
       </c>
     </row>
@@ -4851,7 +5085,9 @@
       <c r="C118" s="11">
         <v>44</v>
       </c>
-      <c r="D118" s="18"/>
+      <c r="D118" s="22">
+        <v>46</v>
+      </c>
       <c r="E118" s="17">
         <v>50</v>
       </c>
@@ -4861,7 +5097,7 @@
       <c r="G118" s="11">
         <v>24</v>
       </c>
-      <c r="H118" s="22">
+      <c r="H118" s="21">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -4875,7 +5111,9 @@
       <c r="C119" s="11">
         <v>61</v>
       </c>
-      <c r="D119" s="18"/>
+      <c r="D119" s="22">
+        <v>69</v>
+      </c>
       <c r="E119" s="17">
         <v>55</v>
       </c>
@@ -4885,7 +5123,7 @@
       <c r="G119" s="11">
         <v>43</v>
       </c>
-      <c r="H119" s="22">
+      <c r="H119" s="21">
         <v>80.645161290322577</v>
       </c>
     </row>
@@ -4899,7 +5137,9 @@
       <c r="C120" s="11">
         <v>45</v>
       </c>
-      <c r="D120" s="18"/>
+      <c r="D120" s="22">
+        <v>72</v>
+      </c>
       <c r="E120" s="17">
         <v>64</v>
       </c>
@@ -4909,7 +5149,7 @@
       <c r="G120" s="11">
         <v>37</v>
       </c>
-      <c r="H120" s="22">
+      <c r="H120" s="21">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -4923,7 +5163,9 @@
       <c r="C121" s="11">
         <v>31</v>
       </c>
-      <c r="D121" s="18"/>
+      <c r="D121" s="22">
+        <v>22</v>
+      </c>
       <c r="E121" s="17">
         <v>70</v>
       </c>
@@ -4933,7 +5175,7 @@
       <c r="G121" s="11">
         <v>28</v>
       </c>
-      <c r="H121" s="22">
+      <c r="H121" s="21">
         <v>67.741935483870961</v>
       </c>
     </row>
@@ -4947,7 +5189,9 @@
       <c r="C122" s="11">
         <v>15</v>
       </c>
-      <c r="D122" s="18"/>
+      <c r="D122" s="22">
+        <v>53</v>
+      </c>
       <c r="E122" s="17">
         <v>46</v>
       </c>
@@ -4957,7 +5201,7 @@
       <c r="G122" s="11">
         <v>19</v>
       </c>
-      <c r="H122" s="22">
+      <c r="H122" s="21">
         <v>87.096774193548384</v>
       </c>
     </row>
@@ -4971,7 +5215,9 @@
       <c r="C123" s="11">
         <v>56</v>
       </c>
-      <c r="D123" s="18"/>
+      <c r="D123" s="22">
+        <v>70</v>
+      </c>
       <c r="E123" s="17">
         <v>50</v>
       </c>
@@ -4981,7 +5227,7 @@
       <c r="G123" s="11">
         <v>34</v>
       </c>
-      <c r="H123" s="22">
+      <c r="H123" s="21">
         <v>83.870967741935488</v>
       </c>
     </row>
@@ -4995,7 +5241,9 @@
       <c r="C124" s="11">
         <v>27</v>
       </c>
-      <c r="D124" s="18"/>
+      <c r="D124" s="22">
+        <v>43</v>
+      </c>
       <c r="E124" s="17">
         <v>47</v>
       </c>
@@ -5005,7 +5253,7 @@
       <c r="G124" s="11">
         <v>17</v>
       </c>
-      <c r="H124" s="22">
+      <c r="H124" s="21">
         <v>83.870967741935488</v>
       </c>
     </row>
@@ -5019,7 +5267,9 @@
       <c r="C125" s="11">
         <v>81</v>
       </c>
-      <c r="D125" s="18"/>
+      <c r="D125" s="22">
+        <v>80</v>
+      </c>
       <c r="E125" s="17">
         <v>70</v>
       </c>
@@ -5029,7 +5279,7 @@
       <c r="G125" s="11">
         <v>73</v>
       </c>
-      <c r="H125" s="22">
+      <c r="H125" s="21">
         <v>96.774193548387103</v>
       </c>
     </row>
@@ -5043,7 +5293,9 @@
       <c r="C126" s="11">
         <v>44</v>
       </c>
-      <c r="D126" s="18"/>
+      <c r="D126" s="22">
+        <v>45</v>
+      </c>
       <c r="E126" s="17">
         <v>87</v>
       </c>
@@ -5053,7 +5305,7 @@
       <c r="G126" s="11">
         <v>43</v>
       </c>
-      <c r="H126" s="22">
+      <c r="H126" s="21">
         <v>80.645161290322577</v>
       </c>
     </row>
@@ -5067,7 +5319,9 @@
       <c r="C127" s="11">
         <v>46</v>
       </c>
-      <c r="D127" s="18"/>
+      <c r="D127" s="22">
+        <v>85</v>
+      </c>
       <c r="E127" s="17">
         <v>50</v>
       </c>
@@ -5077,7 +5331,7 @@
       <c r="G127" s="11">
         <v>45</v>
       </c>
-      <c r="H127" s="22">
+      <c r="H127" s="21">
         <v>83.870967741935488</v>
       </c>
     </row>
@@ -5091,7 +5345,9 @@
       <c r="C128" s="11">
         <v>48</v>
       </c>
-      <c r="D128" s="18"/>
+      <c r="D128" s="22">
+        <v>92</v>
+      </c>
       <c r="E128" s="17">
         <v>47</v>
       </c>
@@ -5101,7 +5357,7 @@
       <c r="G128" s="11">
         <v>56</v>
       </c>
-      <c r="H128" s="22">
+      <c r="H128" s="21">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -5115,7 +5371,9 @@
       <c r="C129" s="11">
         <v>29</v>
       </c>
-      <c r="D129" s="18"/>
+      <c r="D129" s="22">
+        <v>33</v>
+      </c>
       <c r="E129" s="17">
         <v>49</v>
       </c>
@@ -5125,7 +5383,7 @@
       <c r="G129" s="11">
         <v>27</v>
       </c>
-      <c r="H129" s="22">
+      <c r="H129" s="21">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -5139,7 +5397,9 @@
       <c r="C130" s="11">
         <v>53</v>
       </c>
-      <c r="D130" s="18"/>
+      <c r="D130" s="22">
+        <v>36</v>
+      </c>
       <c r="E130" s="17">
         <v>61</v>
       </c>
@@ -5149,7 +5409,7 @@
       <c r="G130" s="11">
         <v>33</v>
       </c>
-      <c r="H130" s="22">
+      <c r="H130" s="21">
         <v>67.741935483870961</v>
       </c>
     </row>
@@ -5163,7 +5423,9 @@
       <c r="C131" s="11">
         <v>50</v>
       </c>
-      <c r="D131" s="18"/>
+      <c r="D131" s="22">
+        <v>33</v>
+      </c>
       <c r="E131" s="17">
         <v>61</v>
       </c>
@@ -5173,7 +5435,7 @@
       <c r="G131" s="11">
         <v>30</v>
       </c>
-      <c r="H131" s="22">
+      <c r="H131" s="21">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -5187,7 +5449,9 @@
       <c r="C132" s="11">
         <v>52</v>
       </c>
-      <c r="D132" s="18"/>
+      <c r="D132" s="22">
+        <v>81</v>
+      </c>
       <c r="E132" s="17">
         <v>49</v>
       </c>
@@ -5197,7 +5461,7 @@
       <c r="G132" s="11">
         <v>42</v>
       </c>
-      <c r="H132" s="22">
+      <c r="H132" s="21">
         <v>83.870967741935488</v>
       </c>
     </row>
@@ -5211,7 +5475,9 @@
       <c r="C133" s="11">
         <v>69</v>
       </c>
-      <c r="D133" s="18"/>
+      <c r="D133" s="22">
+        <v>63</v>
+      </c>
       <c r="E133" s="17">
         <v>60</v>
       </c>
@@ -5221,7 +5487,7 @@
       <c r="G133" s="11">
         <v>54</v>
       </c>
-      <c r="H133" s="22">
+      <c r="H133" s="21">
         <v>93.548387096774192</v>
       </c>
     </row>
@@ -5235,7 +5501,9 @@
       <c r="C134" s="11">
         <v>64</v>
       </c>
-      <c r="D134" s="18"/>
+      <c r="D134" s="22">
+        <v>60</v>
+      </c>
       <c r="E134" s="17">
         <v>55</v>
       </c>
@@ -5245,7 +5513,7 @@
       <c r="G134" s="11">
         <v>34</v>
       </c>
-      <c r="H134" s="22">
+      <c r="H134" s="21">
         <v>96.774193548387103</v>
       </c>
     </row>
@@ -5259,7 +5527,9 @@
       <c r="C135" s="11">
         <v>35</v>
       </c>
-      <c r="D135" s="18"/>
+      <c r="D135" s="22">
+        <v>76</v>
+      </c>
       <c r="E135" s="17">
         <v>70</v>
       </c>
@@ -5269,7 +5539,7 @@
       <c r="G135" s="11">
         <v>39</v>
       </c>
-      <c r="H135" s="22">
+      <c r="H135" s="21">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -5283,7 +5553,9 @@
       <c r="C136" s="11">
         <v>35</v>
       </c>
-      <c r="D136" s="18"/>
+      <c r="D136" s="22">
+        <v>62</v>
+      </c>
       <c r="E136" s="17">
         <v>52</v>
       </c>
@@ -5293,7 +5565,7 @@
       <c r="G136" s="11">
         <v>29</v>
       </c>
-      <c r="H136" s="22">
+      <c r="H136" s="21">
         <v>80.645161290322577</v>
       </c>
     </row>
@@ -5307,7 +5579,9 @@
       <c r="C137" s="11">
         <v>61</v>
       </c>
-      <c r="D137" s="18"/>
+      <c r="D137" s="22">
+        <v>61</v>
+      </c>
       <c r="E137" s="17">
         <v>55</v>
       </c>
@@ -5317,7 +5591,7 @@
       <c r="G137" s="11">
         <v>40</v>
       </c>
-      <c r="H137" s="22">
+      <c r="H137" s="21">
         <v>90.322580645161281</v>
       </c>
     </row>
@@ -5331,7 +5605,9 @@
       <c r="C138" s="11">
         <v>60</v>
       </c>
-      <c r="D138" s="18"/>
+      <c r="D138" s="22">
+        <v>53</v>
+      </c>
       <c r="E138" s="17">
         <v>57</v>
       </c>
@@ -5341,7 +5617,7 @@
       <c r="G138" s="11">
         <v>44</v>
       </c>
-      <c r="H138" s="22">
+      <c r="H138" s="21">
         <v>93.548387096774192</v>
       </c>
     </row>
@@ -5355,7 +5631,9 @@
       <c r="C139" s="11">
         <v>47</v>
       </c>
-      <c r="D139" s="18"/>
+      <c r="D139" s="22">
+        <v>73</v>
+      </c>
       <c r="E139" s="17">
         <v>52</v>
       </c>
@@ -5365,7 +5643,7 @@
       <c r="G139" s="11">
         <v>39</v>
       </c>
-      <c r="H139" s="22">
+      <c r="H139" s="21">
         <v>67.741935483870961</v>
       </c>
     </row>
@@ -5379,7 +5657,9 @@
       <c r="C140" s="11">
         <v>59</v>
       </c>
-      <c r="D140" s="18"/>
+      <c r="D140" s="22">
+        <v>47</v>
+      </c>
       <c r="E140" s="17">
         <v>49</v>
       </c>
@@ -5389,7 +5669,7 @@
       <c r="G140" s="11">
         <v>29</v>
       </c>
-      <c r="H140" s="22">
+      <c r="H140" s="21">
         <v>67.741935483870961</v>
       </c>
     </row>
@@ -5403,7 +5683,9 @@
       <c r="C141" s="11">
         <v>44</v>
       </c>
-      <c r="D141" s="18"/>
+      <c r="D141" s="22">
+        <v>33</v>
+      </c>
       <c r="E141" s="17">
         <v>70</v>
       </c>
@@ -5413,7 +5695,7 @@
       <c r="G141" s="11">
         <v>15</v>
       </c>
-      <c r="H141" s="22">
+      <c r="H141" s="21">
         <v>54.838709677419352</v>
       </c>
     </row>
@@ -5427,7 +5709,9 @@
       <c r="C142" s="11">
         <v>40</v>
       </c>
-      <c r="D142" s="18"/>
+      <c r="D142" s="22">
+        <v>52</v>
+      </c>
       <c r="E142" s="17">
         <v>70</v>
       </c>
@@ -5437,7 +5721,7 @@
       <c r="G142" s="11">
         <v>35</v>
       </c>
-      <c r="H142" s="22">
+      <c r="H142" s="21">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -5451,7 +5735,9 @@
       <c r="C143" s="11">
         <v>57</v>
       </c>
-      <c r="D143" s="18"/>
+      <c r="D143" s="22">
+        <v>81</v>
+      </c>
       <c r="E143" s="17">
         <v>57</v>
       </c>
@@ -5461,7 +5747,7 @@
       <c r="G143" s="11">
         <v>66</v>
       </c>
-      <c r="H143" s="22">
+      <c r="H143" s="21">
         <v>80.645161290322577</v>
       </c>
     </row>
@@ -5475,7 +5761,9 @@
       <c r="C144" s="11">
         <v>57</v>
       </c>
-      <c r="D144" s="18"/>
+      <c r="D144" s="22">
+        <v>74</v>
+      </c>
       <c r="E144" s="17">
         <v>57</v>
       </c>
@@ -5485,7 +5773,7 @@
       <c r="G144" s="11">
         <v>37</v>
       </c>
-      <c r="H144" s="22">
+      <c r="H144" s="21">
         <v>90.322580645161281</v>
       </c>
     </row>
@@ -5499,7 +5787,9 @@
       <c r="C145" s="11">
         <v>42</v>
       </c>
-      <c r="D145" s="18"/>
+      <c r="D145" s="22">
+        <v>22</v>
+      </c>
       <c r="E145" s="17">
         <v>47</v>
       </c>
@@ -5509,7 +5799,7 @@
       <c r="G145" s="11">
         <v>29</v>
       </c>
-      <c r="H145" s="22">
+      <c r="H145" s="21">
         <v>87.096774193548384</v>
       </c>
     </row>
@@ -5523,7 +5813,9 @@
       <c r="C146" s="11">
         <v>58</v>
       </c>
-      <c r="D146" s="18"/>
+      <c r="D146" s="22">
+        <v>78</v>
+      </c>
       <c r="E146" s="17">
         <v>44</v>
       </c>
@@ -5533,7 +5825,7 @@
       <c r="G146" s="11">
         <v>45</v>
       </c>
-      <c r="H146" s="22">
+      <c r="H146" s="21">
         <v>80.645161290322577</v>
       </c>
     </row>
@@ -5547,7 +5839,9 @@
       <c r="C147" s="11">
         <v>48</v>
       </c>
-      <c r="D147" s="18"/>
+      <c r="D147" s="22">
+        <v>80</v>
+      </c>
       <c r="E147" s="17">
         <v>70</v>
       </c>
@@ -5557,7 +5851,7 @@
       <c r="G147" s="11">
         <v>37</v>
       </c>
-      <c r="H147" s="22">
+      <c r="H147" s="21">
         <v>83.870967741935488</v>
       </c>
     </row>
@@ -5571,7 +5865,9 @@
       <c r="C148" s="11">
         <v>67</v>
       </c>
-      <c r="D148" s="18"/>
+      <c r="D148" s="22">
+        <v>73</v>
+      </c>
       <c r="E148" s="17">
         <v>64</v>
       </c>
@@ -5581,7 +5877,7 @@
       <c r="G148" s="11">
         <v>63</v>
       </c>
-      <c r="H148" s="22">
+      <c r="H148" s="21">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -5595,7 +5891,9 @@
       <c r="C149" s="11">
         <v>65</v>
       </c>
-      <c r="D149" s="18"/>
+      <c r="D149" s="22">
+        <v>81</v>
+      </c>
       <c r="E149" s="17">
         <v>55</v>
       </c>
@@ -5605,7 +5903,7 @@
       <c r="G149" s="11">
         <v>48</v>
       </c>
-      <c r="H149" s="22">
+      <c r="H149" s="21">
         <v>80.645161290322577</v>
       </c>
     </row>
@@ -5619,7 +5917,9 @@
       <c r="C150" s="11">
         <v>22</v>
       </c>
-      <c r="D150" s="18"/>
+      <c r="D150" s="22">
+        <v>64</v>
+      </c>
       <c r="E150" s="17">
         <v>52</v>
       </c>
@@ -5629,7 +5929,7 @@
       <c r="G150" s="11">
         <v>30</v>
       </c>
-      <c r="H150" s="22">
+      <c r="H150" s="21">
         <v>61.29032258064516</v>
       </c>
     </row>
@@ -5643,7 +5943,9 @@
       <c r="C151" s="11">
         <v>66</v>
       </c>
-      <c r="D151" s="18"/>
+      <c r="D151" s="22">
+        <v>79</v>
+      </c>
       <c r="E151" s="17">
         <v>46</v>
       </c>
@@ -5653,7 +5955,7 @@
       <c r="G151" s="11">
         <v>17</v>
       </c>
-      <c r="H151" s="22">
+      <c r="H151" s="21">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -5667,7 +5969,9 @@
       <c r="C152" s="11">
         <v>49</v>
       </c>
-      <c r="D152" s="18"/>
+      <c r="D152" s="22">
+        <v>61</v>
+      </c>
       <c r="E152" s="17">
         <v>52</v>
       </c>
@@ -5677,7 +5981,7 @@
       <c r="G152" s="11">
         <v>26</v>
       </c>
-      <c r="H152" s="22">
+      <c r="H152" s="21">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -5691,7 +5995,9 @@
       <c r="C153" s="11">
         <v>42</v>
       </c>
-      <c r="D153" s="18"/>
+      <c r="D153" s="22">
+        <v>67</v>
+      </c>
       <c r="E153" s="17">
         <v>70</v>
       </c>
@@ -5701,7 +6007,7 @@
       <c r="G153" s="11">
         <v>31</v>
       </c>
-      <c r="H153" s="22">
+      <c r="H153" s="21">
         <v>51.612903225806448</v>
       </c>
     </row>
@@ -5715,7 +6021,9 @@
       <c r="C154" s="11">
         <v>59</v>
       </c>
-      <c r="D154" s="18"/>
+      <c r="D154" s="22">
+        <v>79</v>
+      </c>
       <c r="E154" s="17">
         <v>55</v>
       </c>
@@ -5725,7 +6033,7 @@
       <c r="G154" s="11">
         <v>65</v>
       </c>
-      <c r="H154" s="22">
+      <c r="H154" s="21">
         <v>80.645161290322577</v>
       </c>
     </row>
@@ -5739,7 +6047,9 @@
       <c r="C155" s="11">
         <v>45</v>
       </c>
-      <c r="D155" s="18"/>
+      <c r="D155" s="22">
+        <v>34</v>
+      </c>
       <c r="E155" s="17">
         <v>55</v>
       </c>
@@ -5749,7 +6059,7 @@
       <c r="G155" s="11">
         <v>36</v>
       </c>
-      <c r="H155" s="22">
+      <c r="H155" s="21">
         <v>64.516129032258064</v>
       </c>
     </row>
@@ -5763,7 +6073,9 @@
       <c r="C156" s="11">
         <v>76</v>
       </c>
-      <c r="D156" s="18"/>
+      <c r="D156" s="22">
+        <v>46</v>
+      </c>
       <c r="E156" s="17">
         <v>55</v>
       </c>
@@ -5773,7 +6085,7 @@
       <c r="G156" s="11">
         <v>34</v>
       </c>
-      <c r="H156" s="22">
+      <c r="H156" s="21">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -5787,7 +6099,9 @@
       <c r="C157" s="11">
         <v>47</v>
       </c>
-      <c r="D157" s="18"/>
+      <c r="D157" s="22">
+        <v>40</v>
+      </c>
       <c r="E157" s="17">
         <v>50</v>
       </c>
@@ -5797,7 +6111,7 @@
       <c r="G157" s="11">
         <v>39</v>
       </c>
-      <c r="H157" s="22">
+      <c r="H157" s="21">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -5811,7 +6125,9 @@
       <c r="C158" s="11">
         <v>52</v>
       </c>
-      <c r="D158" s="18"/>
+      <c r="D158" s="22">
+        <v>74</v>
+      </c>
       <c r="E158" s="17">
         <v>57</v>
       </c>
@@ -5821,7 +6137,7 @@
       <c r="G158" s="11">
         <v>45</v>
       </c>
-      <c r="H158" s="22">
+      <c r="H158" s="21">
         <v>67.741935483870961</v>
       </c>
     </row>
@@ -5835,7 +6151,9 @@
       <c r="C159" s="11">
         <v>38</v>
       </c>
-      <c r="D159" s="18"/>
+      <c r="D159" s="22">
+        <v>37</v>
+      </c>
       <c r="E159" s="17">
         <v>50</v>
       </c>
@@ -5845,7 +6163,7 @@
       <c r="G159" s="11">
         <v>43</v>
       </c>
-      <c r="H159" s="22">
+      <c r="H159" s="21">
         <v>74.193548387096769</v>
       </c>
     </row>
@@ -5859,7 +6177,9 @@
       <c r="C160" s="11">
         <v>59</v>
       </c>
-      <c r="D160" s="18"/>
+      <c r="D160" s="22">
+        <v>64</v>
+      </c>
       <c r="E160" s="17">
         <v>50</v>
       </c>
@@ -5869,7 +6189,7 @@
       <c r="G160" s="11">
         <v>40</v>
       </c>
-      <c r="H160" s="22">
+      <c r="H160" s="21">
         <v>100</v>
       </c>
     </row>
@@ -5883,7 +6203,9 @@
       <c r="C161" s="11">
         <v>42</v>
       </c>
-      <c r="D161" s="18"/>
+      <c r="D161" s="22">
+        <v>57</v>
+      </c>
       <c r="E161" s="17">
         <v>46</v>
       </c>
@@ -5893,7 +6215,7 @@
       <c r="G161" s="11">
         <v>39</v>
       </c>
-      <c r="H161" s="22">
+      <c r="H161" s="21">
         <v>74.193548387096769</v>
       </c>
     </row>
@@ -5907,7 +6229,9 @@
       <c r="C162" s="11">
         <v>54</v>
       </c>
-      <c r="D162" s="18"/>
+      <c r="D162" s="22">
+        <v>63</v>
+      </c>
       <c r="E162" s="17">
         <v>44</v>
       </c>
@@ -5917,7 +6241,7 @@
       <c r="G162" s="11">
         <v>18</v>
       </c>
-      <c r="H162" s="22">
+      <c r="H162" s="21">
         <v>74.193548387096769</v>
       </c>
     </row>
@@ -5931,7 +6255,9 @@
       <c r="C163" s="11">
         <v>50</v>
       </c>
-      <c r="D163" s="18"/>
+      <c r="D163" s="22">
+        <v>51</v>
+      </c>
       <c r="E163" s="17">
         <v>60</v>
       </c>
@@ -5941,7 +6267,7 @@
       <c r="G163" s="11">
         <v>45</v>
       </c>
-      <c r="H163" s="22">
+      <c r="H163" s="21">
         <v>87.096774193548384</v>
       </c>
     </row>
@@ -5955,7 +6281,9 @@
       <c r="C164" s="11">
         <v>48</v>
       </c>
-      <c r="D164" s="18"/>
+      <c r="D164" s="22">
+        <v>48</v>
+      </c>
       <c r="E164" s="17">
         <v>49</v>
       </c>
@@ -5965,7 +6293,7 @@
       <c r="G164" s="11">
         <v>45</v>
       </c>
-      <c r="H164" s="22">
+      <c r="H164" s="21">
         <v>83.870967741935488</v>
       </c>
     </row>
@@ -5979,7 +6307,9 @@
       <c r="C165" s="11">
         <v>67</v>
       </c>
-      <c r="D165" s="18"/>
+      <c r="D165" s="22">
+        <v>84</v>
+      </c>
       <c r="E165" s="17">
         <v>49</v>
       </c>
@@ -5989,7 +6319,7 @@
       <c r="G165" s="11">
         <v>69</v>
       </c>
-      <c r="H165" s="22">
+      <c r="H165" s="21">
         <v>66.666666666666657</v>
       </c>
     </row>
@@ -6003,7 +6333,9 @@
       <c r="C166" s="11">
         <v>59</v>
       </c>
-      <c r="D166" s="18"/>
+      <c r="D166" s="22">
+        <v>64</v>
+      </c>
       <c r="E166" s="17">
         <v>37</v>
       </c>
@@ -6013,7 +6345,7 @@
       <c r="G166" s="11">
         <v>43</v>
       </c>
-      <c r="H166" s="22">
+      <c r="H166" s="21">
         <v>80.645161290322577</v>
       </c>
     </row>
@@ -6027,7 +6359,9 @@
       <c r="C167" s="11">
         <v>41</v>
       </c>
-      <c r="D167" s="18"/>
+      <c r="D167" s="22">
+        <v>24</v>
+      </c>
       <c r="E167" s="17">
         <v>60</v>
       </c>
@@ -6037,7 +6371,7 @@
       <c r="G167" s="11">
         <v>27</v>
       </c>
-      <c r="H167" s="22">
+      <c r="H167" s="21">
         <v>80.645161290322577</v>
       </c>
     </row>
@@ -6051,7 +6385,9 @@
       <c r="C168" s="11">
         <v>50</v>
       </c>
-      <c r="D168" s="18"/>
+      <c r="D168" s="22">
+        <v>42</v>
+      </c>
       <c r="E168" s="17">
         <v>50</v>
       </c>
@@ -6061,7 +6397,7 @@
       <c r="G168" s="11">
         <v>36</v>
       </c>
-      <c r="H168" s="22">
+      <c r="H168" s="21">
         <v>90.322580645161281</v>
       </c>
     </row>
@@ -6075,7 +6411,9 @@
       <c r="C169" s="11">
         <v>51</v>
       </c>
-      <c r="D169" s="18"/>
+      <c r="D169" s="22">
+        <v>84</v>
+      </c>
       <c r="E169" s="17">
         <v>47</v>
       </c>
@@ -6085,7 +6423,7 @@
       <c r="G169" s="11">
         <v>34</v>
       </c>
-      <c r="H169" s="22">
+      <c r="H169" s="21">
         <v>83.870967741935488</v>
       </c>
     </row>
@@ -6099,7 +6437,9 @@
       <c r="C170" s="11">
         <v>59</v>
       </c>
-      <c r="D170" s="18"/>
+      <c r="D170" s="22">
+        <v>33</v>
+      </c>
       <c r="E170" s="17">
         <v>57</v>
       </c>
@@ -6109,7 +6449,7 @@
       <c r="G170" s="11">
         <v>18</v>
       </c>
-      <c r="H170" s="22">
+      <c r="H170" s="21">
         <v>74.193548387096769</v>
       </c>
     </row>
@@ -6123,7 +6463,9 @@
       <c r="C171" s="11">
         <v>47</v>
       </c>
-      <c r="D171" s="18"/>
+      <c r="D171" s="22">
+        <v>78</v>
+      </c>
       <c r="E171" s="17">
         <v>49</v>
       </c>
@@ -6133,7 +6475,7 @@
       <c r="G171" s="11">
         <v>56</v>
       </c>
-      <c r="H171" s="22">
+      <c r="H171" s="21">
         <v>87.096774193548384</v>
       </c>
     </row>
@@ -6147,7 +6489,9 @@
       <c r="C172" s="11">
         <v>59</v>
       </c>
-      <c r="D172" s="18"/>
+      <c r="D172" s="22">
+        <v>79</v>
+      </c>
       <c r="E172" s="17">
         <v>55</v>
       </c>
@@ -6157,7 +6501,7 @@
       <c r="G172" s="11">
         <v>69</v>
       </c>
-      <c r="H172" s="22">
+      <c r="H172" s="21">
         <v>83.870967741935488</v>
       </c>
     </row>
@@ -6171,7 +6515,9 @@
       <c r="C173" s="11">
         <v>58</v>
       </c>
-      <c r="D173" s="18"/>
+      <c r="D173" s="22">
+        <v>85</v>
+      </c>
       <c r="E173" s="17">
         <v>55</v>
       </c>
@@ -6181,7 +6527,7 @@
       <c r="G173" s="11">
         <v>45</v>
       </c>
-      <c r="H173" s="22">
+      <c r="H173" s="21">
         <v>80.645161290322577</v>
       </c>
     </row>
@@ -6195,7 +6541,9 @@
       <c r="C174" s="11">
         <v>49</v>
       </c>
-      <c r="D174" s="18"/>
+      <c r="D174" s="22">
+        <v>72</v>
+      </c>
       <c r="E174" s="17">
         <v>47</v>
       </c>
@@ -6205,7 +6553,7 @@
       <c r="G174" s="11">
         <v>60</v>
       </c>
-      <c r="H174" s="22">
+      <c r="H174" s="21">
         <v>80.645161290322577</v>
       </c>
     </row>
@@ -6219,7 +6567,9 @@
       <c r="C175" s="11">
         <v>45</v>
       </c>
-      <c r="D175" s="18"/>
+      <c r="D175" s="22">
+        <v>61</v>
+      </c>
       <c r="E175" s="17">
         <v>60</v>
       </c>
@@ -6229,7 +6579,7 @@
       <c r="G175" s="11">
         <v>46</v>
       </c>
-      <c r="H175" s="22">
+      <c r="H175" s="21">
         <v>74.193548387096769</v>
       </c>
     </row>
@@ -6243,7 +6593,9 @@
       <c r="C176" s="11">
         <v>64</v>
       </c>
-      <c r="D176" s="18"/>
+      <c r="D176" s="22">
+        <v>86</v>
+      </c>
       <c r="E176" s="17">
         <v>49</v>
       </c>
@@ -6253,7 +6605,7 @@
       <c r="G176" s="11">
         <v>55</v>
       </c>
-      <c r="H176" s="22">
+      <c r="H176" s="21">
         <v>74.193548387096769</v>
       </c>
     </row>
@@ -6267,7 +6619,9 @@
       <c r="C177" s="11">
         <v>62</v>
       </c>
-      <c r="D177" s="18"/>
+      <c r="D177" s="22">
+        <v>83</v>
+      </c>
       <c r="E177" s="17">
         <v>47</v>
       </c>
@@ -6277,7 +6631,7 @@
       <c r="G177" s="11">
         <v>42</v>
       </c>
-      <c r="H177" s="22">
+      <c r="H177" s="21">
         <v>80.645161290322577</v>
       </c>
     </row>
@@ -6291,7 +6645,9 @@
       <c r="C178" s="11">
         <v>79</v>
       </c>
-      <c r="D178" s="18"/>
+      <c r="D178" s="22">
+        <v>81</v>
+      </c>
       <c r="E178" s="17">
         <v>52</v>
       </c>
@@ -6301,7 +6657,7 @@
       <c r="G178" s="11">
         <v>49</v>
       </c>
-      <c r="H178" s="22">
+      <c r="H178" s="21">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -6315,7 +6671,9 @@
       <c r="C179" s="11">
         <v>65</v>
       </c>
-      <c r="D179" s="18"/>
+      <c r="D179" s="22">
+        <v>44</v>
+      </c>
       <c r="E179" s="17">
         <v>49</v>
       </c>
@@ -6325,7 +6683,7 @@
       <c r="G179" s="11">
         <v>35</v>
       </c>
-      <c r="H179" s="22">
+      <c r="H179" s="21">
         <v>93.548387096774192</v>
       </c>
     </row>
@@ -6339,7 +6697,9 @@
       <c r="C180" s="11">
         <v>49</v>
       </c>
-      <c r="D180" s="18"/>
+      <c r="D180" s="22">
+        <v>67</v>
+      </c>
       <c r="E180" s="17">
         <v>52</v>
       </c>
@@ -6349,7 +6709,7 @@
       <c r="G180" s="11">
         <v>46</v>
       </c>
-      <c r="H180" s="22">
+      <c r="H180" s="21">
         <v>74.193548387096769</v>
       </c>
     </row>
@@ -6363,7 +6723,9 @@
       <c r="C181" s="11">
         <v>55</v>
       </c>
-      <c r="D181" s="18"/>
+      <c r="D181" s="22">
+        <v>43</v>
+      </c>
       <c r="E181" s="17">
         <v>50</v>
       </c>
@@ -6373,7 +6735,7 @@
       <c r="G181" s="11">
         <v>19</v>
       </c>
-      <c r="H181" s="22">
+      <c r="H181" s="21">
         <v>70.967741935483872</v>
       </c>
     </row>
@@ -6387,7 +6749,9 @@
       <c r="C182" s="11">
         <v>19</v>
       </c>
-      <c r="D182" s="18"/>
+      <c r="D182" s="22">
+        <v>59</v>
+      </c>
       <c r="E182" s="17">
         <v>64</v>
       </c>
@@ -6397,7 +6761,7 @@
       <c r="G182" s="11">
         <v>11</v>
       </c>
-      <c r="H182" s="22">
+      <c r="H182" s="21">
         <v>64.516129032258064</v>
       </c>
     </row>
@@ -6411,7 +6775,9 @@
       <c r="C183" s="11">
         <v>22</v>
       </c>
-      <c r="D183" s="18"/>
+      <c r="D183" s="22">
+        <v>26</v>
+      </c>
       <c r="E183" s="17">
         <v>47</v>
       </c>
@@ -6421,7 +6787,7 @@
       <c r="G183" s="11">
         <v>28</v>
       </c>
-      <c r="H183" s="22">
+      <c r="H183" s="21">
         <v>77.41935483870968</v>
       </c>
     </row>
@@ -6435,7 +6801,9 @@
       <c r="C184" s="11">
         <v>63</v>
       </c>
-      <c r="D184" s="18"/>
+      <c r="D184" s="22">
+        <v>63</v>
+      </c>
       <c r="E184" s="17">
         <v>47</v>
       </c>
@@ -6445,7 +6813,7 @@
       <c r="G184" s="11">
         <v>61</v>
       </c>
-      <c r="H184" s="22">
+      <c r="H184" s="21">
         <v>54.838709677419352</v>
       </c>
     </row>
@@ -6459,7 +6827,9 @@
       <c r="C185" s="11">
         <v>76</v>
       </c>
-      <c r="D185" s="18"/>
+      <c r="D185" s="22">
+        <v>87</v>
+      </c>
       <c r="E185" s="17">
         <v>44</v>
       </c>
@@ -6469,7 +6839,7 @@
       <c r="G185" s="11">
         <v>56</v>
       </c>
-      <c r="H185" s="22">
+      <c r="H185" s="21">
         <v>87.096774193548384</v>
       </c>
     </row>
@@ -6483,7 +6853,9 @@
       <c r="C186" s="11">
         <v>77</v>
       </c>
-      <c r="D186" s="18"/>
+      <c r="D186" s="22">
+        <v>88</v>
+      </c>
       <c r="E186" s="17">
         <v>44</v>
       </c>
@@ -6493,7 +6865,7 @@
       <c r="G186" s="11">
         <v>64</v>
       </c>
-      <c r="H186" s="22">
+      <c r="H186" s="21">
         <v>83.333333333333343</v>
       </c>
     </row>
@@ -6507,7 +6879,9 @@
       <c r="C187" s="11">
         <v>52</v>
       </c>
-      <c r="D187" s="18"/>
+      <c r="D187" s="22">
+        <v>59</v>
+      </c>
       <c r="E187" s="17">
         <v>43</v>
       </c>
@@ -6517,7 +6891,7 @@
       <c r="G187" s="11">
         <v>46</v>
       </c>
-      <c r="H187" s="22">
+      <c r="H187" s="21">
         <v>62.5</v>
       </c>
     </row>
@@ -6531,7 +6905,9 @@
       <c r="C188" s="11">
         <v>50</v>
       </c>
-      <c r="D188" s="18"/>
+      <c r="D188" s="22">
+        <v>57</v>
+      </c>
       <c r="E188" s="17">
         <v>43</v>
       </c>
@@ -6541,7 +6917,7 @@
       <c r="G188" s="11">
         <v>28</v>
       </c>
-      <c r="H188" s="22">
+      <c r="H188" s="21">
         <v>83.333333333333343</v>
       </c>
     </row>
@@ -6555,7 +6931,9 @@
       <c r="C189" s="11">
         <v>51</v>
       </c>
-      <c r="D189" s="18"/>
+      <c r="D189" s="22">
+        <v>48</v>
+      </c>
       <c r="E189" s="17">
         <v>43</v>
       </c>
@@ -6565,7 +6943,7 @@
       <c r="G189" s="11">
         <v>41</v>
       </c>
-      <c r="H189" s="22">
+      <c r="H189" s="21">
         <v>79.166666666666657</v>
       </c>
     </row>
@@ -6579,7 +6957,9 @@
       <c r="C190" s="11">
         <v>63</v>
       </c>
-      <c r="D190" s="18"/>
+      <c r="D190" s="22">
+        <v>98</v>
+      </c>
       <c r="E190" s="17">
         <v>44</v>
       </c>
@@ -6589,7 +6969,7 @@
       <c r="G190" s="11">
         <v>55</v>
       </c>
-      <c r="H190" s="22">
+      <c r="H190" s="21">
         <v>75</v>
       </c>
     </row>
@@ -6603,7 +6983,9 @@
       <c r="C191" s="11">
         <v>57</v>
       </c>
-      <c r="D191" s="18"/>
+      <c r="D191" s="22">
+        <v>56</v>
+      </c>
       <c r="E191" s="17">
         <v>44</v>
       </c>
@@ -6613,7 +6995,7 @@
       <c r="G191" s="11">
         <v>38</v>
       </c>
-      <c r="H191" s="22">
+      <c r="H191" s="21">
         <v>75</v>
       </c>
     </row>
@@ -6627,7 +7009,9 @@
       <c r="C192" s="11">
         <v>55</v>
       </c>
-      <c r="D192" s="18"/>
+      <c r="D192" s="22">
+        <v>82</v>
+      </c>
       <c r="E192" s="17">
         <v>43</v>
       </c>
@@ -6637,7 +7021,7 @@
       <c r="G192" s="11">
         <v>30</v>
       </c>
-      <c r="H192" s="22">
+      <c r="H192" s="21">
         <v>83.333333333333343</v>
       </c>
     </row>
@@ -6651,7 +7035,9 @@
       <c r="C193" s="11">
         <v>35</v>
       </c>
-      <c r="D193" s="18"/>
+      <c r="D193" s="22">
+        <v>37</v>
+      </c>
       <c r="E193" s="17">
         <v>43</v>
       </c>
@@ -6661,7 +7047,7 @@
       <c r="G193" s="11">
         <v>22</v>
       </c>
-      <c r="H193" s="22">
+      <c r="H193" s="21">
         <v>58.333333333333336</v>
       </c>
     </row>
@@ -6675,7 +7061,9 @@
       <c r="C194" s="11">
         <v>23</v>
       </c>
-      <c r="D194" s="18"/>
+      <c r="D194" s="22">
+        <v>11</v>
+      </c>
       <c r="E194" s="17">
         <v>47</v>
       </c>
@@ -6685,7 +7073,7 @@
       <c r="G194" s="11">
         <v>14</v>
       </c>
-      <c r="H194" s="19"/>
+      <c r="H194" s="18"/>
     </row>
     <row r="195" spans="1:8">
       <c r="A195" s="10" t="s">
@@ -6697,7 +7085,9 @@
       <c r="C195" s="11">
         <v>44</v>
       </c>
-      <c r="D195" s="11"/>
+      <c r="D195" s="22">
+        <v>57</v>
+      </c>
       <c r="E195" s="17">
         <v>49</v>
       </c>
@@ -6707,7 +7097,7 @@
       <c r="G195" s="11">
         <v>47</v>
       </c>
-      <c r="H195" s="19"/>
+      <c r="H195" s="18"/>
     </row>
     <row r="196" spans="1:8">
       <c r="A196" s="10" t="s">
@@ -6719,7 +7109,9 @@
       <c r="C196" s="11">
         <v>59</v>
       </c>
-      <c r="D196" s="11"/>
+      <c r="D196" s="22">
+        <v>94</v>
+      </c>
       <c r="E196" s="17">
         <v>49</v>
       </c>
@@ -6729,7 +7121,7 @@
       <c r="G196" s="11">
         <v>39</v>
       </c>
-      <c r="H196" s="19"/>
+      <c r="H196" s="18"/>
     </row>
     <row r="197" spans="1:8">
       <c r="A197" s="10" t="s">
@@ -6741,7 +7133,9 @@
       <c r="C197" s="11">
         <v>42</v>
       </c>
-      <c r="D197" s="11"/>
+      <c r="D197" s="22">
+        <v>58</v>
+      </c>
       <c r="E197" s="17">
         <v>47</v>
       </c>
@@ -6751,7 +7145,7 @@
       <c r="G197" s="11">
         <v>39</v>
       </c>
-      <c r="H197" s="19"/>
+      <c r="H197" s="18"/>
     </row>
     <row r="198" spans="1:8">
       <c r="A198" s="10" t="s">
@@ -6763,7 +7157,9 @@
       <c r="C198" s="11">
         <v>23</v>
       </c>
-      <c r="D198" s="11"/>
+      <c r="D198" s="22">
+        <v>64</v>
+      </c>
       <c r="E198" s="17">
         <v>44</v>
       </c>
@@ -6773,7 +7169,7 @@
       <c r="G198" s="11">
         <v>35</v>
       </c>
-      <c r="H198" s="19"/>
+      <c r="H198" s="18"/>
     </row>
     <row r="199" spans="1:8">
       <c r="A199" s="10" t="s">
@@ -6785,7 +7181,9 @@
       <c r="C199" s="11">
         <v>46</v>
       </c>
-      <c r="D199" s="11"/>
+      <c r="D199" s="22">
+        <v>50</v>
+      </c>
       <c r="E199" s="17">
         <v>47</v>
       </c>
@@ -6795,7 +7193,7 @@
       <c r="G199" s="11">
         <v>26</v>
       </c>
-      <c r="H199" s="19"/>
+      <c r="H199" s="18"/>
     </row>
     <row r="200" spans="1:8">
       <c r="A200" s="10" t="s">
@@ -6807,7 +7205,9 @@
       <c r="C200" s="11">
         <v>59</v>
       </c>
-      <c r="D200" s="11"/>
+      <c r="D200" s="22">
+        <v>99</v>
+      </c>
       <c r="E200" s="17">
         <v>44</v>
       </c>
@@ -6817,7 +7217,7 @@
       <c r="G200" s="11">
         <v>52</v>
       </c>
-      <c r="H200" s="19"/>
+      <c r="H200" s="18"/>
     </row>
     <row r="201" spans="1:8">
       <c r="A201" s="10" t="s">
@@ -6829,7 +7229,9 @@
       <c r="C201" s="11">
         <v>66</v>
       </c>
-      <c r="D201" s="11"/>
+      <c r="D201" s="22">
+        <v>45</v>
+      </c>
       <c r="E201" s="17">
         <v>55</v>
       </c>
@@ -6839,7 +7241,7 @@
       <c r="G201" s="11">
         <v>41</v>
       </c>
-      <c r="H201" s="19"/>
+      <c r="H201" s="18"/>
     </row>
     <row r="202" spans="1:8">
       <c r="A202" s="10" t="s">
@@ -6851,7 +7253,9 @@
       <c r="C202" s="11">
         <v>53</v>
       </c>
-      <c r="D202" s="11"/>
+      <c r="D202" s="22">
+        <v>61</v>
+      </c>
       <c r="E202" s="17">
         <v>55</v>
       </c>
@@ -6861,7 +7265,7 @@
       <c r="G202" s="11">
         <v>27</v>
       </c>
-      <c r="H202" s="19"/>
+      <c r="H202" s="18"/>
     </row>
     <row r="203" spans="1:8">
       <c r="A203" s="10" t="s">
@@ -6873,7 +7277,9 @@
       <c r="C203" s="11">
         <v>60</v>
       </c>
-      <c r="D203" s="11"/>
+      <c r="D203" s="22">
+        <v>69</v>
+      </c>
       <c r="E203" s="17">
         <v>47</v>
       </c>
@@ -6883,7 +7289,7 @@
       <c r="G203" s="11">
         <v>42</v>
       </c>
-      <c r="H203" s="19"/>
+      <c r="H203" s="18"/>
     </row>
     <row r="204" spans="1:8">
       <c r="A204" s="10" t="s">
@@ -6895,7 +7301,9 @@
       <c r="C204" s="11">
         <v>29</v>
       </c>
-      <c r="D204" s="11"/>
+      <c r="D204" s="22">
+        <v>54</v>
+      </c>
       <c r="E204" s="17">
         <v>43</v>
       </c>
@@ -6905,7 +7313,7 @@
       <c r="G204" s="11">
         <v>31</v>
       </c>
-      <c r="H204" s="19"/>
+      <c r="H204" s="18"/>
     </row>
     <row r="205" spans="1:8">
       <c r="A205" s="10" t="s">
@@ -6917,7 +7325,9 @@
       <c r="C205" s="11">
         <v>55</v>
       </c>
-      <c r="D205" s="11"/>
+      <c r="D205" s="22">
+        <v>51</v>
+      </c>
       <c r="E205" s="17">
         <v>44</v>
       </c>
@@ -6927,7 +7337,7 @@
       <c r="G205" s="11">
         <v>47</v>
       </c>
-      <c r="H205" s="19"/>
+      <c r="H205" s="18"/>
     </row>
     <row r="206" spans="1:8">
       <c r="A206" s="10" t="s">
@@ -6939,7 +7349,9 @@
       <c r="C206" s="11">
         <v>33</v>
       </c>
-      <c r="D206" s="11"/>
+      <c r="D206" s="22">
+        <v>63</v>
+      </c>
       <c r="E206" s="17">
         <v>53</v>
       </c>
@@ -6949,7 +7361,7 @@
       <c r="G206" s="11">
         <v>30</v>
       </c>
-      <c r="H206" s="19"/>
+      <c r="H206" s="18"/>
     </row>
     <row r="207" spans="1:8">
       <c r="A207" s="10" t="s">
@@ -6961,17 +7373,19 @@
       <c r="C207" s="11">
         <v>51</v>
       </c>
-      <c r="D207" s="11"/>
+      <c r="D207" s="22">
+        <v>63</v>
+      </c>
       <c r="E207" s="17">
         <v>53</v>
       </c>
-      <c r="F207" s="21">
-        <v>0</v>
+      <c r="F207" s="20">
+        <v>68</v>
       </c>
       <c r="G207" s="11">
         <v>21</v>
       </c>
-      <c r="H207" s="19"/>
+      <c r="H207" s="18"/>
     </row>
     <row r="208" spans="1:8">
       <c r="A208" s="10" t="s">
@@ -6983,7 +7397,9 @@
       <c r="C208" s="11">
         <v>43</v>
       </c>
-      <c r="D208" s="11"/>
+      <c r="D208" s="22">
+        <v>38</v>
+      </c>
       <c r="E208" s="17">
         <v>43</v>
       </c>
@@ -6993,7 +7409,7 @@
       <c r="G208" s="11">
         <v>35</v>
       </c>
-      <c r="H208" s="19"/>
+      <c r="H208" s="18"/>
     </row>
     <row r="209" spans="1:8">
       <c r="A209" s="10" t="s">
@@ -7005,7 +7421,9 @@
       <c r="C209" s="11">
         <v>50</v>
       </c>
-      <c r="D209" s="11"/>
+      <c r="D209" s="22">
+        <v>38</v>
+      </c>
       <c r="E209" s="17">
         <v>43</v>
       </c>
@@ -7015,7 +7433,7 @@
       <c r="G209" s="11">
         <v>17</v>
       </c>
-      <c r="H209" s="19"/>
+      <c r="H209" s="18"/>
     </row>
     <row r="210" spans="1:8">
       <c r="A210" s="10" t="s">
@@ -7027,7 +7445,9 @@
       <c r="C210" s="11">
         <v>30</v>
       </c>
-      <c r="D210" s="11"/>
+      <c r="D210" s="22">
+        <v>56</v>
+      </c>
       <c r="E210" s="17">
         <v>44</v>
       </c>
@@ -7037,7 +7457,7 @@
       <c r="G210" s="11">
         <v>30</v>
       </c>
-      <c r="H210" s="19"/>
+      <c r="H210" s="18"/>
     </row>
     <row r="211" spans="1:8">
       <c r="A211" s="10" t="s">
@@ -7049,7 +7469,9 @@
       <c r="C211" s="11">
         <v>42</v>
       </c>
-      <c r="D211" s="11"/>
+      <c r="D211" s="22">
+        <v>13</v>
+      </c>
       <c r="E211" s="17">
         <v>53</v>
       </c>
@@ -7059,7 +7481,7 @@
       <c r="G211" s="11">
         <v>28</v>
       </c>
-      <c r="H211" s="19"/>
+      <c r="H211" s="18"/>
     </row>
     <row r="212" spans="1:8">
       <c r="A212" s="10" t="s">
@@ -7071,7 +7493,9 @@
       <c r="C212" s="11">
         <v>50</v>
       </c>
-      <c r="D212" s="11"/>
+      <c r="D212" s="22">
+        <v>78</v>
+      </c>
       <c r="E212" s="17">
         <v>49</v>
       </c>
@@ -7081,7 +7505,7 @@
       <c r="G212" s="11">
         <v>47</v>
       </c>
-      <c r="H212" s="19"/>
+      <c r="H212" s="18"/>
     </row>
     <row r="213" spans="1:8">
       <c r="A213" s="10" t="s">
@@ -7093,7 +7517,9 @@
       <c r="C213" s="11">
         <v>37</v>
       </c>
-      <c r="D213" s="11"/>
+      <c r="D213" s="22">
+        <v>71</v>
+      </c>
       <c r="E213" s="17">
         <v>43</v>
       </c>
@@ -7103,7 +7529,7 @@
       <c r="G213" s="11">
         <v>48</v>
       </c>
-      <c r="H213" s="19"/>
+      <c r="H213" s="18"/>
     </row>
     <row r="214" spans="1:8">
       <c r="A214" s="10" t="s">
@@ -7115,7 +7541,9 @@
       <c r="C214" s="11">
         <v>41</v>
       </c>
-      <c r="D214" s="11"/>
+      <c r="D214" s="22">
+        <v>58</v>
+      </c>
       <c r="E214" s="17">
         <v>47</v>
       </c>
@@ -7125,7 +7553,7 @@
       <c r="G214" s="11">
         <v>28</v>
       </c>
-      <c r="H214" s="19"/>
+      <c r="H214" s="18"/>
     </row>
     <row r="215" spans="1:8">
       <c r="A215" s="10" t="s">
@@ -7137,7 +7565,9 @@
       <c r="C215" s="11">
         <v>42</v>
       </c>
-      <c r="D215" s="11"/>
+      <c r="D215" s="22">
+        <v>64</v>
+      </c>
       <c r="E215" s="17">
         <v>73</v>
       </c>
@@ -7147,7 +7577,7 @@
       <c r="G215" s="11">
         <v>27</v>
       </c>
-      <c r="H215" s="19"/>
+      <c r="H215" s="18"/>
     </row>
     <row r="216" spans="1:8">
       <c r="A216" s="10" t="s">
@@ -7159,7 +7589,9 @@
       <c r="C216" s="11">
         <v>57</v>
       </c>
-      <c r="D216" s="11"/>
+      <c r="D216" s="22">
+        <v>74</v>
+      </c>
       <c r="E216" s="17">
         <v>44</v>
       </c>
@@ -7169,7 +7601,7 @@
       <c r="G216" s="11" t="s">
         <v>482</v>
       </c>
-      <c r="H216" s="19"/>
+      <c r="H216" s="18"/>
     </row>
     <row r="217" spans="1:8">
       <c r="A217" s="10" t="s">
@@ -7181,8 +7613,10 @@
       <c r="C217" s="11">
         <v>4</v>
       </c>
-      <c r="D217" s="11"/>
-      <c r="E217" s="20" t="s">
+      <c r="D217" s="22" t="s">
+        <v>482</v>
+      </c>
+      <c r="E217" s="19" t="s">
         <v>482</v>
       </c>
       <c r="F217" s="17" t="s">
@@ -7191,7 +7625,7 @@
       <c r="G217" s="11" t="s">
         <v>482</v>
       </c>
-      <c r="H217" s="19"/>
+      <c r="H217" s="18"/>
     </row>
     <row r="218" spans="1:8">
       <c r="A218" s="10" t="s">
@@ -7203,7 +7637,9 @@
       <c r="C218" s="11">
         <v>60</v>
       </c>
-      <c r="D218" s="11"/>
+      <c r="D218" s="22">
+        <v>81</v>
+      </c>
       <c r="E218" s="17">
         <v>47</v>
       </c>
@@ -7213,7 +7649,7 @@
       <c r="G218" s="11">
         <v>62</v>
       </c>
-      <c r="H218" s="19"/>
+      <c r="H218" s="18"/>
     </row>
     <row r="219" spans="1:8">
       <c r="A219" s="10" t="s">
@@ -7225,7 +7661,9 @@
       <c r="C219" s="11">
         <v>69</v>
       </c>
-      <c r="D219" s="11"/>
+      <c r="D219" s="22">
+        <v>74</v>
+      </c>
       <c r="E219" s="17">
         <v>49</v>
       </c>
@@ -7235,7 +7673,7 @@
       <c r="G219" s="11">
         <v>28</v>
       </c>
-      <c r="H219" s="19"/>
+      <c r="H219" s="18"/>
     </row>
     <row r="220" spans="1:8">
       <c r="A220" s="10" t="s">
@@ -7247,7 +7685,9 @@
       <c r="C220" s="11">
         <v>49</v>
       </c>
-      <c r="D220" s="11"/>
+      <c r="D220" s="22">
+        <v>29</v>
+      </c>
       <c r="E220" s="17">
         <v>53</v>
       </c>
@@ -7257,7 +7697,7 @@
       <c r="G220" s="11">
         <v>34</v>
       </c>
-      <c r="H220" s="19"/>
+      <c r="H220" s="18"/>
     </row>
     <row r="221" spans="1:8">
       <c r="A221" s="10" t="s">
@@ -7269,7 +7709,9 @@
       <c r="C221" s="11">
         <v>43</v>
       </c>
-      <c r="D221" s="11"/>
+      <c r="D221" s="22">
+        <v>53</v>
+      </c>
       <c r="E221" s="17">
         <v>47</v>
       </c>
@@ -7279,7 +7721,7 @@
       <c r="G221" s="11">
         <v>28</v>
       </c>
-      <c r="H221" s="19"/>
+      <c r="H221" s="18"/>
     </row>
     <row r="222" spans="1:8">
       <c r="A222" s="10" t="s">
@@ -7291,7 +7733,9 @@
       <c r="C222" s="11">
         <v>45</v>
       </c>
-      <c r="D222" s="11"/>
+      <c r="D222" s="22">
+        <v>55</v>
+      </c>
       <c r="E222" s="17">
         <v>47</v>
       </c>
@@ -7301,7 +7745,7 @@
       <c r="G222" s="11">
         <v>33</v>
       </c>
-      <c r="H222" s="19"/>
+      <c r="H222" s="18"/>
     </row>
     <row r="223" spans="1:8">
       <c r="A223" s="10" t="s">
@@ -7313,7 +7757,9 @@
       <c r="C223" s="11">
         <v>59</v>
       </c>
-      <c r="D223" s="11"/>
+      <c r="D223" s="22">
+        <v>57</v>
+      </c>
       <c r="E223" s="17">
         <v>47</v>
       </c>
@@ -7323,7 +7769,7 @@
       <c r="G223" s="11">
         <v>33</v>
       </c>
-      <c r="H223" s="19"/>
+      <c r="H223" s="18"/>
     </row>
     <row r="224" spans="1:8">
       <c r="A224" s="10" t="s">
@@ -7335,7 +7781,9 @@
       <c r="C224" s="11">
         <v>45</v>
       </c>
-      <c r="D224" s="11"/>
+      <c r="D224" s="22">
+        <v>49</v>
+      </c>
       <c r="E224" s="17">
         <v>43</v>
       </c>
@@ -7345,7 +7793,7 @@
       <c r="G224" s="11">
         <v>31</v>
       </c>
-      <c r="H224" s="19"/>
+      <c r="H224" s="18"/>
     </row>
     <row r="225" spans="1:8">
       <c r="A225" s="10" t="s">
@@ -7357,7 +7805,9 @@
       <c r="C225" s="11">
         <v>47</v>
       </c>
-      <c r="D225" s="11"/>
+      <c r="D225" s="22">
+        <v>80</v>
+      </c>
       <c r="E225" s="17">
         <v>73</v>
       </c>
@@ -7367,7 +7817,7 @@
       <c r="G225" s="11">
         <v>48</v>
       </c>
-      <c r="H225" s="19"/>
+      <c r="H225" s="18"/>
     </row>
     <row r="226" spans="1:8">
       <c r="A226" s="10" t="s">
@@ -7379,7 +7829,9 @@
       <c r="C226" s="11">
         <v>49</v>
       </c>
-      <c r="D226" s="11"/>
+      <c r="D226" s="22">
+        <v>29</v>
+      </c>
       <c r="E226" s="17">
         <v>47</v>
       </c>
@@ -7389,7 +7841,7 @@
       <c r="G226" s="11">
         <v>31</v>
       </c>
-      <c r="H226" s="19"/>
+      <c r="H226" s="18"/>
     </row>
     <row r="227" spans="1:8">
       <c r="A227" s="10" t="s">
@@ -7401,7 +7853,9 @@
       <c r="C227" s="11" t="s">
         <v>482</v>
       </c>
-      <c r="D227" s="11"/>
+      <c r="D227" s="22">
+        <v>33</v>
+      </c>
       <c r="E227" s="17">
         <v>73</v>
       </c>
@@ -7411,7 +7865,7 @@
       <c r="G227" s="11">
         <v>37</v>
       </c>
-      <c r="H227" s="19"/>
+      <c r="H227" s="18"/>
     </row>
     <row r="228" spans="1:8">
       <c r="A228" s="10" t="s">
@@ -7423,7 +7877,9 @@
       <c r="C228" s="11">
         <v>44</v>
       </c>
-      <c r="D228" s="11"/>
+      <c r="D228" s="22">
+        <v>47</v>
+      </c>
       <c r="E228" s="17">
         <v>55</v>
       </c>
@@ -7433,7 +7889,7 @@
       <c r="G228" s="11">
         <v>34</v>
       </c>
-      <c r="H228" s="19"/>
+      <c r="H228" s="18"/>
     </row>
     <row r="229" spans="1:8">
       <c r="A229" s="10" t="s">
@@ -7445,7 +7901,9 @@
       <c r="C229" s="11">
         <v>56</v>
       </c>
-      <c r="D229" s="11"/>
+      <c r="D229" s="22">
+        <v>52</v>
+      </c>
       <c r="E229" s="17">
         <v>49</v>
       </c>
@@ -7455,7 +7913,7 @@
       <c r="G229" s="11">
         <v>24</v>
       </c>
-      <c r="H229" s="19"/>
+      <c r="H229" s="18"/>
     </row>
     <row r="230" spans="1:8">
       <c r="A230" s="10" t="s">
@@ -7467,7 +7925,9 @@
       <c r="C230" s="11">
         <v>51</v>
       </c>
-      <c r="D230" s="11"/>
+      <c r="D230" s="22">
+        <v>57</v>
+      </c>
       <c r="E230" s="17">
         <v>55</v>
       </c>
@@ -7477,7 +7937,7 @@
       <c r="G230" s="11">
         <v>59</v>
       </c>
-      <c r="H230" s="19"/>
+      <c r="H230" s="18"/>
     </row>
     <row r="231" spans="1:8">
       <c r="A231" s="10" t="s">
@@ -7489,7 +7949,9 @@
       <c r="C231" s="11">
         <v>58</v>
       </c>
-      <c r="D231" s="11"/>
+      <c r="D231" s="22">
+        <v>74</v>
+      </c>
       <c r="E231" s="17">
         <v>73</v>
       </c>
@@ -7499,7 +7961,7 @@
       <c r="G231" s="11">
         <v>53</v>
       </c>
-      <c r="H231" s="19"/>
+      <c r="H231" s="18"/>
     </row>
     <row r="232" spans="1:8">
       <c r="A232" s="10" t="s">
@@ -7511,7 +7973,9 @@
       <c r="C232" s="11">
         <v>62</v>
       </c>
-      <c r="D232" s="11"/>
+      <c r="D232" s="22">
+        <v>65</v>
+      </c>
       <c r="E232" s="17">
         <v>47</v>
       </c>
@@ -7521,7 +7985,7 @@
       <c r="G232" s="11">
         <v>33</v>
       </c>
-      <c r="H232" s="19"/>
+      <c r="H232" s="18"/>
     </row>
     <row r="233" spans="1:8">
       <c r="A233" s="10" t="s">
@@ -7533,8 +7997,10 @@
       <c r="C233" s="11" t="s">
         <v>482</v>
       </c>
-      <c r="D233" s="11"/>
-      <c r="E233" s="20" t="s">
+      <c r="D233" s="22" t="s">
+        <v>482</v>
+      </c>
+      <c r="E233" s="19" t="s">
         <v>482</v>
       </c>
       <c r="F233" s="17" t="s">
@@ -7543,7 +8009,7 @@
       <c r="G233" s="11" t="s">
         <v>482</v>
       </c>
-      <c r="H233" s="19"/>
+      <c r="H233" s="18"/>
     </row>
     <row r="234" spans="1:8">
       <c r="A234" s="4" t="s">
@@ -7555,7 +8021,9 @@
       <c r="C234" s="11">
         <v>41</v>
       </c>
-      <c r="D234" s="11"/>
+      <c r="D234" s="22">
+        <v>60</v>
+      </c>
       <c r="E234" s="17">
         <v>74</v>
       </c>
@@ -7565,7 +8033,7 @@
       <c r="G234" s="11">
         <v>62</v>
       </c>
-      <c r="H234" s="19"/>
+      <c r="H234" s="18"/>
     </row>
     <row r="235" spans="1:8">
       <c r="A235" s="4" t="s">
@@ -7577,7 +8045,9 @@
       <c r="C235" s="11" t="s">
         <v>482</v>
       </c>
-      <c r="D235" s="11"/>
+      <c r="D235" s="22">
+        <v>46</v>
+      </c>
       <c r="E235" s="17">
         <v>74</v>
       </c>
@@ -7587,7 +8057,7 @@
       <c r="G235" s="11">
         <v>53</v>
       </c>
-      <c r="H235" s="19"/>
+      <c r="H235" s="18"/>
     </row>
     <row r="236" spans="1:8">
       <c r="A236" s="4" t="s">
@@ -7599,7 +8069,9 @@
       <c r="C236" s="11">
         <v>51</v>
       </c>
-      <c r="D236" s="11"/>
+      <c r="D236" s="22">
+        <v>78</v>
+      </c>
       <c r="E236" s="17">
         <v>74</v>
       </c>
@@ -7609,7 +8081,7 @@
       <c r="G236" s="11">
         <v>41</v>
       </c>
-      <c r="H236" s="19"/>
+      <c r="H236" s="18"/>
     </row>
     <row r="237" spans="1:8">
       <c r="A237" s="4" t="s">
@@ -7621,7 +8093,9 @@
       <c r="C237" s="11" t="s">
         <v>482</v>
       </c>
-      <c r="D237" s="11"/>
+      <c r="D237" s="22">
+        <v>61</v>
+      </c>
       <c r="E237" s="11" t="s">
         <v>482</v>
       </c>
@@ -7631,7 +8105,7 @@
       <c r="G237" s="11">
         <v>29</v>
       </c>
-      <c r="H237" s="19"/>
+      <c r="H237" s="18"/>
     </row>
     <row r="238" spans="1:8">
       <c r="A238" s="6" t="s">
@@ -7643,7 +8117,9 @@
       <c r="C238" s="11" t="s">
         <v>482</v>
       </c>
-      <c r="D238" s="11"/>
+      <c r="D238" s="22" t="s">
+        <v>482</v>
+      </c>
       <c r="E238" s="11" t="s">
         <v>482</v>
       </c>
@@ -7653,7 +8129,7 @@
       <c r="G238" s="11" t="s">
         <v>482</v>
       </c>
-      <c r="H238" s="19"/>
+      <c r="H238" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/MC1020_E25.xlsx
+++ b/MC1020_E25.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assignment marks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83B410DE-7FA8-42A1-A743-BAFBD2CE3467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA9CCB9F-9AE5-424F-BFB2-A51D85F17874}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="483">
   <si>
     <t xml:space="preserve"> Reg.number</t>
   </si>
@@ -2078,9 +2078,7 @@
       <c r="F2" s="17">
         <v>64</v>
       </c>
-      <c r="G2" s="11">
-        <v>13</v>
-      </c>
+      <c r="G2" s="11"/>
       <c r="H2" s="21">
         <v>61.29032258064516</v>
       </c>
@@ -2104,9 +2102,7 @@
       <c r="F3" s="17">
         <v>54</v>
       </c>
-      <c r="G3" s="11">
-        <v>24</v>
-      </c>
+      <c r="G3" s="11"/>
       <c r="H3" s="21">
         <v>74.193548387096769</v>
       </c>
@@ -2130,9 +2126,7 @@
       <c r="F4" s="17">
         <v>67.5</v>
       </c>
-      <c r="G4" s="11" t="s">
-        <v>482</v>
-      </c>
+      <c r="G4" s="11"/>
       <c r="H4" s="21">
         <v>58.064516129032263</v>
       </c>
@@ -2156,9 +2150,7 @@
       <c r="F5" s="17">
         <v>61.5</v>
       </c>
-      <c r="G5" s="11">
-        <v>26</v>
-      </c>
+      <c r="G5" s="11"/>
       <c r="H5" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -2182,9 +2174,7 @@
       <c r="F6" s="17">
         <v>61</v>
       </c>
-      <c r="G6" s="11">
-        <v>32</v>
-      </c>
+      <c r="G6" s="11"/>
       <c r="H6" s="21">
         <v>61.29032258064516</v>
       </c>
@@ -2208,9 +2198,7 @@
       <c r="F7" s="17">
         <v>16</v>
       </c>
-      <c r="G7" s="11">
-        <v>20</v>
-      </c>
+      <c r="G7" s="11"/>
       <c r="H7" s="21">
         <v>83.870967741935488</v>
       </c>
@@ -2234,9 +2222,7 @@
       <c r="F8" s="17">
         <v>79</v>
       </c>
-      <c r="G8" s="11">
-        <v>32</v>
-      </c>
+      <c r="G8" s="11"/>
       <c r="H8" s="21">
         <v>87.096774193548384</v>
       </c>
@@ -2260,9 +2246,7 @@
       <c r="F9" s="17">
         <v>36</v>
       </c>
-      <c r="G9" s="11">
-        <v>12</v>
-      </c>
+      <c r="G9" s="11"/>
       <c r="H9" s="21">
         <v>83.870967741935488</v>
       </c>
@@ -2286,9 +2270,7 @@
       <c r="F10" s="17">
         <v>61</v>
       </c>
-      <c r="G10" s="11">
-        <v>18</v>
-      </c>
+      <c r="G10" s="11"/>
       <c r="H10" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -2312,9 +2294,7 @@
       <c r="F11" s="17">
         <v>59.5</v>
       </c>
-      <c r="G11" s="11">
-        <v>58</v>
-      </c>
+      <c r="G11" s="11"/>
       <c r="H11" s="21">
         <v>83.870967741935488</v>
       </c>
@@ -2338,9 +2318,7 @@
       <c r="F12" s="17">
         <v>43.5</v>
       </c>
-      <c r="G12" s="11">
-        <v>22</v>
-      </c>
+      <c r="G12" s="11"/>
       <c r="H12" s="21">
         <v>80.645161290322577</v>
       </c>
@@ -2364,9 +2342,7 @@
       <c r="F13" s="17">
         <v>65.5</v>
       </c>
-      <c r="G13" s="11">
-        <v>19</v>
-      </c>
+      <c r="G13" s="11"/>
       <c r="H13" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -2390,9 +2366,7 @@
       <c r="F14" s="17">
         <v>60.5</v>
       </c>
-      <c r="G14" s="11">
-        <v>34</v>
-      </c>
+      <c r="G14" s="11"/>
       <c r="H14" s="21">
         <v>87.096774193548384</v>
       </c>
@@ -2416,9 +2390,7 @@
       <c r="F15" s="17">
         <v>84.5</v>
       </c>
-      <c r="G15" s="11">
-        <v>50</v>
-      </c>
+      <c r="G15" s="11"/>
       <c r="H15" s="21">
         <v>93.548387096774192</v>
       </c>
@@ -2442,9 +2414,7 @@
       <c r="F16" s="17">
         <v>58</v>
       </c>
-      <c r="G16" s="11">
-        <v>54</v>
-      </c>
+      <c r="G16" s="11"/>
       <c r="H16" s="21">
         <v>83.870967741935488</v>
       </c>
@@ -2468,9 +2438,7 @@
       <c r="F17" s="17">
         <v>73.5</v>
       </c>
-      <c r="G17" s="11">
-        <v>35</v>
-      </c>
+      <c r="G17" s="11"/>
       <c r="H17" s="21">
         <v>90.322580645161281</v>
       </c>
@@ -2494,9 +2462,7 @@
       <c r="F18" s="17">
         <v>17.5</v>
       </c>
-      <c r="G18" s="11">
-        <v>33</v>
-      </c>
+      <c r="G18" s="11"/>
       <c r="H18" s="21">
         <v>54.838709677419352</v>
       </c>
@@ -2520,9 +2486,7 @@
       <c r="F19" s="17">
         <v>83</v>
       </c>
-      <c r="G19" s="11">
-        <v>46</v>
-      </c>
+      <c r="G19" s="11"/>
       <c r="H19" s="21">
         <v>70.967741935483872</v>
       </c>
@@ -2546,9 +2510,7 @@
       <c r="F20" s="17">
         <v>55.5</v>
       </c>
-      <c r="G20" s="11">
-        <v>57</v>
-      </c>
+      <c r="G20" s="11"/>
       <c r="H20" s="21">
         <v>83.870967741935488</v>
       </c>
@@ -2572,9 +2534,7 @@
       <c r="F21" s="17">
         <v>69.5</v>
       </c>
-      <c r="G21" s="11">
-        <v>39</v>
-      </c>
+      <c r="G21" s="11"/>
       <c r="H21" s="21">
         <v>87.096774193548384</v>
       </c>
@@ -2598,9 +2558,7 @@
       <c r="F22" s="17">
         <v>50.5</v>
       </c>
-      <c r="G22" s="11">
-        <v>37</v>
-      </c>
+      <c r="G22" s="11"/>
       <c r="H22" s="21">
         <v>93.548387096774192</v>
       </c>
@@ -2624,9 +2582,7 @@
       <c r="F23" s="17">
         <v>61</v>
       </c>
-      <c r="G23" s="11">
-        <v>42</v>
-      </c>
+      <c r="G23" s="11"/>
       <c r="H23" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -2650,9 +2606,7 @@
       <c r="F24" s="17">
         <v>69</v>
       </c>
-      <c r="G24" s="11">
-        <v>36</v>
-      </c>
+      <c r="G24" s="11"/>
       <c r="H24" s="21">
         <v>83.870967741935488</v>
       </c>
@@ -2676,9 +2630,7 @@
       <c r="F25" s="17">
         <v>35</v>
       </c>
-      <c r="G25" s="11">
-        <v>19</v>
-      </c>
+      <c r="G25" s="11"/>
       <c r="H25" s="21">
         <v>80.645161290322577</v>
       </c>
@@ -2702,9 +2654,7 @@
       <c r="F26" s="17">
         <v>57.5</v>
       </c>
-      <c r="G26" s="11">
-        <v>22</v>
-      </c>
+      <c r="G26" s="11"/>
       <c r="H26" s="21">
         <v>64.516129032258064</v>
       </c>
@@ -2728,9 +2678,7 @@
       <c r="F27" s="17">
         <v>64</v>
       </c>
-      <c r="G27" s="11">
-        <v>48</v>
-      </c>
+      <c r="G27" s="11"/>
       <c r="H27" s="21">
         <v>74.193548387096769</v>
       </c>
@@ -2754,9 +2702,7 @@
       <c r="F28" s="17">
         <v>54.5</v>
       </c>
-      <c r="G28" s="11">
-        <v>38</v>
-      </c>
+      <c r="G28" s="11"/>
       <c r="H28" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -2780,9 +2726,7 @@
       <c r="F29" s="17">
         <v>43.5</v>
       </c>
-      <c r="G29" s="11">
-        <v>49</v>
-      </c>
+      <c r="G29" s="11"/>
       <c r="H29" s="21">
         <v>74.193548387096769</v>
       </c>
@@ -2806,9 +2750,7 @@
       <c r="F30" s="17">
         <v>58.5</v>
       </c>
-      <c r="G30" s="11">
-        <v>55</v>
-      </c>
+      <c r="G30" s="11"/>
       <c r="H30" s="21">
         <v>90.322580645161281</v>
       </c>
@@ -2832,9 +2774,7 @@
       <c r="F31" s="17">
         <v>79</v>
       </c>
-      <c r="G31" s="11">
-        <v>50</v>
-      </c>
+      <c r="G31" s="11"/>
       <c r="H31" s="21">
         <v>80.645161290322577</v>
       </c>
@@ -2858,9 +2798,7 @@
       <c r="F32" s="17">
         <v>57.5</v>
       </c>
-      <c r="G32" s="11">
-        <v>18</v>
-      </c>
+      <c r="G32" s="11"/>
       <c r="H32" s="21">
         <v>64.516129032258064</v>
       </c>
@@ -2884,9 +2822,7 @@
       <c r="F33" s="17">
         <v>68.5</v>
       </c>
-      <c r="G33" s="11">
-        <v>31</v>
-      </c>
+      <c r="G33" s="11"/>
       <c r="H33" s="21">
         <v>70.967741935483872</v>
       </c>
@@ -2910,9 +2846,7 @@
       <c r="F34" s="17">
         <v>78</v>
       </c>
-      <c r="G34" s="11">
-        <v>25</v>
-      </c>
+      <c r="G34" s="11"/>
       <c r="H34" s="21">
         <v>80.645161290322577</v>
       </c>
@@ -2936,9 +2870,7 @@
       <c r="F35" s="17">
         <v>49.5</v>
       </c>
-      <c r="G35" s="11">
-        <v>32</v>
-      </c>
+      <c r="G35" s="11"/>
       <c r="H35" s="21">
         <v>87.096774193548384</v>
       </c>
@@ -2962,9 +2894,7 @@
       <c r="F36" s="17">
         <v>33.5</v>
       </c>
-      <c r="G36" s="11">
-        <v>47</v>
-      </c>
+      <c r="G36" s="11"/>
       <c r="H36" s="21">
         <v>67.741935483870961</v>
       </c>
@@ -2988,9 +2918,7 @@
       <c r="F37" s="17">
         <v>60</v>
       </c>
-      <c r="G37" s="11">
-        <v>50</v>
-      </c>
+      <c r="G37" s="11"/>
       <c r="H37" s="21">
         <v>70.967741935483872</v>
       </c>
@@ -3014,9 +2942,7 @@
       <c r="F38" s="17">
         <v>35</v>
       </c>
-      <c r="G38" s="11">
-        <v>33</v>
-      </c>
+      <c r="G38" s="11"/>
       <c r="H38" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -3040,9 +2966,7 @@
       <c r="F39" s="17">
         <v>72</v>
       </c>
-      <c r="G39" s="11">
-        <v>16</v>
-      </c>
+      <c r="G39" s="11"/>
       <c r="H39" s="21">
         <v>83.870967741935488</v>
       </c>
@@ -3066,9 +2990,7 @@
       <c r="F40" s="17">
         <v>72</v>
       </c>
-      <c r="G40" s="11">
-        <v>56</v>
-      </c>
+      <c r="G40" s="11"/>
       <c r="H40" s="21">
         <v>87.096774193548384</v>
       </c>
@@ -3092,9 +3014,7 @@
       <c r="F41" s="17">
         <v>53</v>
       </c>
-      <c r="G41" s="11">
-        <v>54</v>
-      </c>
+      <c r="G41" s="11"/>
       <c r="H41" s="21">
         <v>87.096774193548384</v>
       </c>
@@ -3118,9 +3038,7 @@
       <c r="F42" s="17">
         <v>36</v>
       </c>
-      <c r="G42" s="11">
-        <v>21</v>
-      </c>
+      <c r="G42" s="11"/>
       <c r="H42" s="21">
         <v>87.096774193548384</v>
       </c>
@@ -3144,9 +3062,7 @@
       <c r="F43" s="17">
         <v>49</v>
       </c>
-      <c r="G43" s="11">
-        <v>46</v>
-      </c>
+      <c r="G43" s="11"/>
       <c r="H43" s="21">
         <v>61.29032258064516</v>
       </c>
@@ -3170,9 +3086,7 @@
       <c r="F44" s="17">
         <v>76</v>
       </c>
-      <c r="G44" s="11">
-        <v>32</v>
-      </c>
+      <c r="G44" s="11"/>
       <c r="H44" s="21">
         <v>87.096774193548384</v>
       </c>
@@ -3196,9 +3110,7 @@
       <c r="F45" s="17">
         <v>52</v>
       </c>
-      <c r="G45" s="11">
-        <v>36</v>
-      </c>
+      <c r="G45" s="11"/>
       <c r="H45" s="21">
         <v>74.193548387096769</v>
       </c>
@@ -3222,9 +3134,7 @@
       <c r="F46" s="17">
         <v>45</v>
       </c>
-      <c r="G46" s="11">
-        <v>22</v>
-      </c>
+      <c r="G46" s="11"/>
       <c r="H46" s="21">
         <v>90.322580645161281</v>
       </c>
@@ -3248,9 +3158,7 @@
       <c r="F47" s="17">
         <v>86.5</v>
       </c>
-      <c r="G47" s="11">
-        <v>50</v>
-      </c>
+      <c r="G47" s="11"/>
       <c r="H47" s="21">
         <v>80.645161290322577</v>
       </c>
@@ -3274,9 +3182,7 @@
       <c r="F48" s="17">
         <v>43</v>
       </c>
-      <c r="G48" s="11">
-        <v>34</v>
-      </c>
+      <c r="G48" s="11"/>
       <c r="H48" s="21">
         <v>90.322580645161281</v>
       </c>
@@ -3300,9 +3206,7 @@
       <c r="F49" s="17">
         <v>60</v>
       </c>
-      <c r="G49" s="11">
-        <v>46</v>
-      </c>
+      <c r="G49" s="11"/>
       <c r="H49" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -3326,9 +3230,7 @@
       <c r="F50" s="17">
         <v>73.5</v>
       </c>
-      <c r="G50" s="11">
-        <v>22</v>
-      </c>
+      <c r="G50" s="11"/>
       <c r="H50" s="21">
         <v>83.870967741935488</v>
       </c>
@@ -3352,9 +3254,7 @@
       <c r="F51" s="17">
         <v>52.5</v>
       </c>
-      <c r="G51" s="11">
-        <v>18</v>
-      </c>
+      <c r="G51" s="11"/>
       <c r="H51" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -3378,9 +3278,7 @@
       <c r="F52" s="17">
         <v>60.5</v>
       </c>
-      <c r="G52" s="11">
-        <v>27</v>
-      </c>
+      <c r="G52" s="11"/>
       <c r="H52" s="21">
         <v>80.645161290322577</v>
       </c>
@@ -3404,9 +3302,7 @@
       <c r="F53" s="17">
         <v>63.5</v>
       </c>
-      <c r="G53" s="11">
-        <v>45</v>
-      </c>
+      <c r="G53" s="11"/>
       <c r="H53" s="21">
         <v>96.774193548387103</v>
       </c>
@@ -3430,9 +3326,7 @@
       <c r="F54" s="17">
         <v>17.5</v>
       </c>
-      <c r="G54" s="11">
-        <v>23</v>
-      </c>
+      <c r="G54" s="11"/>
       <c r="H54" s="21">
         <v>80.645161290322577</v>
       </c>
@@ -3456,9 +3350,7 @@
       <c r="F55" s="17">
         <v>75</v>
       </c>
-      <c r="G55" s="11">
-        <v>35</v>
-      </c>
+      <c r="G55" s="11"/>
       <c r="H55" s="21">
         <v>90.322580645161281</v>
       </c>
@@ -3482,9 +3374,7 @@
       <c r="F56" s="17">
         <v>57</v>
       </c>
-      <c r="G56" s="11">
-        <v>42</v>
-      </c>
+      <c r="G56" s="11"/>
       <c r="H56" s="21">
         <v>83.870967741935488</v>
       </c>
@@ -3508,9 +3398,7 @@
       <c r="F57" s="17">
         <v>76.5</v>
       </c>
-      <c r="G57" s="11">
-        <v>29</v>
-      </c>
+      <c r="G57" s="11"/>
       <c r="H57" s="21">
         <v>90.322580645161281</v>
       </c>
@@ -3534,9 +3422,7 @@
       <c r="F58" s="17">
         <v>51.5</v>
       </c>
-      <c r="G58" s="11">
-        <v>15</v>
-      </c>
+      <c r="G58" s="11"/>
       <c r="H58" s="21">
         <v>64.516129032258064</v>
       </c>
@@ -3560,9 +3446,7 @@
       <c r="F59" s="17">
         <v>85.5</v>
       </c>
-      <c r="G59" s="11">
-        <v>34</v>
-      </c>
+      <c r="G59" s="11"/>
       <c r="H59" s="21">
         <v>83.870967741935488</v>
       </c>
@@ -3586,9 +3470,7 @@
       <c r="F60" s="17">
         <v>59.5</v>
       </c>
-      <c r="G60" s="11">
-        <v>75</v>
-      </c>
+      <c r="G60" s="11"/>
       <c r="H60" s="21">
         <v>96.774193548387103</v>
       </c>
@@ -3612,9 +3494,7 @@
       <c r="F61" s="17">
         <v>57.5</v>
       </c>
-      <c r="G61" s="11">
-        <v>35</v>
-      </c>
+      <c r="G61" s="11"/>
       <c r="H61" s="21">
         <v>93.548387096774192</v>
       </c>
@@ -3638,9 +3518,7 @@
       <c r="F62" s="17">
         <v>48</v>
       </c>
-      <c r="G62" s="11">
-        <v>28</v>
-      </c>
+      <c r="G62" s="11"/>
       <c r="H62" s="21">
         <v>90.322580645161281</v>
       </c>
@@ -3664,9 +3542,7 @@
       <c r="F63" s="17">
         <v>95</v>
       </c>
-      <c r="G63" s="11">
-        <v>56</v>
-      </c>
+      <c r="G63" s="11"/>
       <c r="H63" s="21">
         <v>93.548387096774192</v>
       </c>
@@ -3690,9 +3566,7 @@
       <c r="F64" s="17">
         <v>56</v>
       </c>
-      <c r="G64" s="11">
-        <v>47</v>
-      </c>
+      <c r="G64" s="11"/>
       <c r="H64" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -3716,9 +3590,7 @@
       <c r="F65" s="17">
         <v>79</v>
       </c>
-      <c r="G65" s="11">
-        <v>53</v>
-      </c>
+      <c r="G65" s="11"/>
       <c r="H65" s="21">
         <v>90.322580645161281</v>
       </c>
@@ -3742,9 +3614,7 @@
       <c r="F66" s="17">
         <v>59</v>
       </c>
-      <c r="G66" s="11">
-        <v>15</v>
-      </c>
+      <c r="G66" s="11"/>
       <c r="H66" s="21">
         <v>93.548387096774192</v>
       </c>
@@ -3768,9 +3638,7 @@
       <c r="F67" s="17">
         <v>79.5</v>
       </c>
-      <c r="G67" s="11">
-        <v>43</v>
-      </c>
+      <c r="G67" s="11"/>
       <c r="H67" s="21">
         <v>87.096774193548384</v>
       </c>
@@ -3794,9 +3662,7 @@
       <c r="F68" s="17">
         <v>20</v>
       </c>
-      <c r="G68" s="11">
-        <v>31</v>
-      </c>
+      <c r="G68" s="11"/>
       <c r="H68" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -3820,9 +3686,7 @@
       <c r="F69" s="17">
         <v>74</v>
       </c>
-      <c r="G69" s="11">
-        <v>40</v>
-      </c>
+      <c r="G69" s="11"/>
       <c r="H69" s="21">
         <v>93.548387096774192</v>
       </c>
@@ -3846,9 +3710,7 @@
       <c r="F70" s="17">
         <v>50</v>
       </c>
-      <c r="G70" s="11">
-        <v>62</v>
-      </c>
+      <c r="G70" s="11"/>
       <c r="H70" s="21">
         <v>93.548387096774192</v>
       </c>
@@ -3872,9 +3734,7 @@
       <c r="F71" s="17">
         <v>40.5</v>
       </c>
-      <c r="G71" s="11">
-        <v>51</v>
-      </c>
+      <c r="G71" s="11"/>
       <c r="H71" s="21">
         <v>96.774193548387103</v>
       </c>
@@ -3898,9 +3758,7 @@
       <c r="F72" s="17">
         <v>75.5</v>
       </c>
-      <c r="G72" s="11">
-        <v>31</v>
-      </c>
+      <c r="G72" s="11"/>
       <c r="H72" s="21">
         <v>74.193548387096769</v>
       </c>
@@ -3924,9 +3782,7 @@
       <c r="F73" s="17">
         <v>57.5</v>
       </c>
-      <c r="G73" s="11">
-        <v>23</v>
-      </c>
+      <c r="G73" s="11"/>
       <c r="H73" s="21">
         <v>74.193548387096769</v>
       </c>
@@ -3950,9 +3806,7 @@
       <c r="F74" s="17">
         <v>30</v>
       </c>
-      <c r="G74" s="11">
-        <v>28</v>
-      </c>
+      <c r="G74" s="11"/>
       <c r="H74" s="21">
         <v>38.70967741935484</v>
       </c>
@@ -3976,9 +3830,7 @@
       <c r="F75" s="17">
         <v>49.5</v>
       </c>
-      <c r="G75" s="11">
-        <v>26</v>
-      </c>
+      <c r="G75" s="11"/>
       <c r="H75" s="21">
         <v>74.193548387096769</v>
       </c>
@@ -4002,9 +3854,7 @@
       <c r="F76" s="17">
         <v>88.5</v>
       </c>
-      <c r="G76" s="11">
-        <v>58</v>
-      </c>
+      <c r="G76" s="11"/>
       <c r="H76" s="21">
         <v>96.774193548387103</v>
       </c>
@@ -4028,9 +3878,7 @@
       <c r="F77" s="17">
         <v>69</v>
       </c>
-      <c r="G77" s="11">
-        <v>39</v>
-      </c>
+      <c r="G77" s="11"/>
       <c r="H77" s="21">
         <v>90.322580645161281</v>
       </c>
@@ -4054,9 +3902,7 @@
       <c r="F78" s="17">
         <v>69.5</v>
       </c>
-      <c r="G78" s="11">
-        <v>24</v>
-      </c>
+      <c r="G78" s="11"/>
       <c r="H78" s="21">
         <v>80.645161290322577</v>
       </c>
@@ -4080,9 +3926,7 @@
       <c r="F79" s="17">
         <v>64</v>
       </c>
-      <c r="G79" s="11">
-        <v>45</v>
-      </c>
+      <c r="G79" s="11"/>
       <c r="H79" s="21">
         <v>87.096774193548384</v>
       </c>
@@ -4106,9 +3950,7 @@
       <c r="F80" s="17">
         <v>67.5</v>
       </c>
-      <c r="G80" s="11">
-        <v>19</v>
-      </c>
+      <c r="G80" s="11"/>
       <c r="H80" s="21">
         <v>80.645161290322577</v>
       </c>
@@ -4132,9 +3974,7 @@
       <c r="F81" s="17">
         <v>76.5</v>
       </c>
-      <c r="G81" s="11">
-        <v>48</v>
-      </c>
+      <c r="G81" s="11"/>
       <c r="H81" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -4158,9 +3998,7 @@
       <c r="F82" s="17">
         <v>72</v>
       </c>
-      <c r="G82" s="11">
-        <v>45</v>
-      </c>
+      <c r="G82" s="11"/>
       <c r="H82" s="21">
         <v>90.322580645161281</v>
       </c>
@@ -4184,9 +4022,7 @@
       <c r="F83" s="17">
         <v>62.5</v>
       </c>
-      <c r="G83" s="11">
-        <v>29</v>
-      </c>
+      <c r="G83" s="11"/>
       <c r="H83" s="21">
         <v>90.322580645161281</v>
       </c>
@@ -4210,9 +4046,7 @@
       <c r="F84" s="17">
         <v>45.5</v>
       </c>
-      <c r="G84" s="11">
-        <v>36</v>
-      </c>
+      <c r="G84" s="11"/>
       <c r="H84" s="21">
         <v>93.548387096774192</v>
       </c>
@@ -4236,9 +4070,7 @@
       <c r="F85" s="17">
         <v>55.5</v>
       </c>
-      <c r="G85" s="11">
-        <v>41</v>
-      </c>
+      <c r="G85" s="11"/>
       <c r="H85" s="21">
         <v>93.548387096774192</v>
       </c>
@@ -4262,9 +4094,7 @@
       <c r="F86" s="17">
         <v>72.5</v>
       </c>
-      <c r="G86" s="11">
-        <v>17</v>
-      </c>
+      <c r="G86" s="11"/>
       <c r="H86" s="21">
         <v>74.193548387096769</v>
       </c>
@@ -4288,9 +4118,7 @@
       <c r="F87" s="17">
         <v>39</v>
       </c>
-      <c r="G87" s="11">
-        <v>32</v>
-      </c>
+      <c r="G87" s="11"/>
       <c r="H87" s="21">
         <v>96.774193548387103</v>
       </c>
@@ -4314,9 +4142,7 @@
       <c r="F88" s="17">
         <v>17.5</v>
       </c>
-      <c r="G88" s="11">
-        <v>23</v>
-      </c>
+      <c r="G88" s="11"/>
       <c r="H88" s="21">
         <v>54.838709677419352</v>
       </c>
@@ -4340,9 +4166,7 @@
       <c r="F89" s="17">
         <v>47.5</v>
       </c>
-      <c r="G89" s="11">
-        <v>38</v>
-      </c>
+      <c r="G89" s="11"/>
       <c r="H89" s="21">
         <v>90.322580645161281</v>
       </c>
@@ -4366,9 +4190,7 @@
       <c r="F90" s="17">
         <v>60.5</v>
       </c>
-      <c r="G90" s="11">
-        <v>38</v>
-      </c>
+      <c r="G90" s="11"/>
       <c r="H90" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -4392,9 +4214,7 @@
       <c r="F91" s="17">
         <v>92.5</v>
       </c>
-      <c r="G91" s="11" t="s">
-        <v>482</v>
-      </c>
+      <c r="G91" s="11"/>
       <c r="H91" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -4418,9 +4238,7 @@
       <c r="F92" s="17">
         <v>70</v>
       </c>
-      <c r="G92" s="11">
-        <v>52</v>
-      </c>
+      <c r="G92" s="11"/>
       <c r="H92" s="21">
         <v>87.096774193548384</v>
       </c>
@@ -4444,9 +4262,7 @@
       <c r="F93" s="17">
         <v>40</v>
       </c>
-      <c r="G93" s="11">
-        <v>32</v>
-      </c>
+      <c r="G93" s="11"/>
       <c r="H93" s="21">
         <v>87.096774193548384</v>
       </c>
@@ -4470,9 +4286,7 @@
       <c r="F94" s="17">
         <v>0</v>
       </c>
-      <c r="G94" s="11">
-        <v>17</v>
-      </c>
+      <c r="G94" s="11"/>
       <c r="H94" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -4496,9 +4310,7 @@
       <c r="F95" s="17">
         <v>64.5</v>
       </c>
-      <c r="G95" s="11">
-        <v>41</v>
-      </c>
+      <c r="G95" s="11"/>
       <c r="H95" s="21">
         <v>45.161290322580641</v>
       </c>
@@ -4522,9 +4334,7 @@
       <c r="F96" s="17">
         <v>33.5</v>
       </c>
-      <c r="G96" s="11">
-        <v>25</v>
-      </c>
+      <c r="G96" s="11"/>
       <c r="H96" s="21">
         <v>87.096774193548384</v>
       </c>
@@ -4548,9 +4358,7 @@
       <c r="F97" s="17">
         <v>71.5</v>
       </c>
-      <c r="G97" s="11">
-        <v>30</v>
-      </c>
+      <c r="G97" s="11"/>
       <c r="H97" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -4574,9 +4382,7 @@
       <c r="F98" s="17">
         <v>78.5</v>
       </c>
-      <c r="G98" s="11">
-        <v>41</v>
-      </c>
+      <c r="G98" s="11"/>
       <c r="H98" s="21">
         <v>74.193548387096769</v>
       </c>
@@ -4600,9 +4406,7 @@
       <c r="F99" s="17">
         <v>70.5</v>
       </c>
-      <c r="G99" s="11">
-        <v>31</v>
-      </c>
+      <c r="G99" s="11"/>
       <c r="H99" s="21">
         <v>90.322580645161281</v>
       </c>
@@ -4626,9 +4430,7 @@
       <c r="F100" s="17">
         <v>65.5</v>
       </c>
-      <c r="G100" s="11">
-        <v>19</v>
-      </c>
+      <c r="G100" s="11"/>
       <c r="H100" s="21">
         <v>87.096774193548384</v>
       </c>
@@ -4652,9 +4454,7 @@
       <c r="F101" s="17">
         <v>46</v>
       </c>
-      <c r="G101" s="11">
-        <v>17</v>
-      </c>
+      <c r="G101" s="11"/>
       <c r="H101" s="21">
         <v>87.096774193548384</v>
       </c>
@@ -4678,9 +4478,7 @@
       <c r="F102" s="17">
         <v>28</v>
       </c>
-      <c r="G102" s="11">
-        <v>10</v>
-      </c>
+      <c r="G102" s="11"/>
       <c r="H102" s="21">
         <v>51.612903225806448</v>
       </c>
@@ -4704,9 +4502,7 @@
       <c r="F103" s="17" t="s">
         <v>482</v>
       </c>
-      <c r="G103" s="11" t="s">
-        <v>482</v>
-      </c>
+      <c r="G103" s="11"/>
       <c r="H103" s="21">
         <v>16.129032258064516</v>
       </c>
@@ -4730,9 +4526,7 @@
       <c r="F104" s="17">
         <v>55</v>
       </c>
-      <c r="G104" s="11">
-        <v>61</v>
-      </c>
+      <c r="G104" s="11"/>
       <c r="H104" s="21">
         <v>83.870967741935488</v>
       </c>
@@ -4756,9 +4550,7 @@
       <c r="F105" s="17">
         <v>42</v>
       </c>
-      <c r="G105" s="11">
-        <v>48</v>
-      </c>
+      <c r="G105" s="11"/>
       <c r="H105" s="21">
         <v>80.645161290322577</v>
       </c>
@@ -4782,9 +4574,7 @@
       <c r="F106" s="17">
         <v>48</v>
       </c>
-      <c r="G106" s="11">
-        <v>28</v>
-      </c>
+      <c r="G106" s="11"/>
       <c r="H106" s="21">
         <v>45.161290322580641</v>
       </c>
@@ -4808,9 +4598,7 @@
       <c r="F107" s="17">
         <v>22</v>
       </c>
-      <c r="G107" s="11">
-        <v>35</v>
-      </c>
+      <c r="G107" s="11"/>
       <c r="H107" s="21">
         <v>83.870967741935488</v>
       </c>
@@ -4834,9 +4622,7 @@
       <c r="F108" s="17">
         <v>25</v>
       </c>
-      <c r="G108" s="11">
-        <v>41</v>
-      </c>
+      <c r="G108" s="11"/>
       <c r="H108" s="21">
         <v>93.548387096774192</v>
       </c>
@@ -4860,9 +4646,7 @@
       <c r="F109" s="17">
         <v>44.5</v>
       </c>
-      <c r="G109" s="11">
-        <v>21</v>
-      </c>
+      <c r="G109" s="11"/>
       <c r="H109" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -4886,9 +4670,7 @@
       <c r="F110" s="17">
         <v>78</v>
       </c>
-      <c r="G110" s="11">
-        <v>59</v>
-      </c>
+      <c r="G110" s="11"/>
       <c r="H110" s="21">
         <v>87.096774193548384</v>
       </c>
@@ -4912,9 +4694,7 @@
       <c r="F111" s="17">
         <v>64</v>
       </c>
-      <c r="G111" s="11">
-        <v>40</v>
-      </c>
+      <c r="G111" s="11"/>
       <c r="H111" s="21">
         <v>58.064516129032263</v>
       </c>
@@ -4938,9 +4718,7 @@
       <c r="F112" s="17">
         <v>49</v>
       </c>
-      <c r="G112" s="11">
-        <v>35</v>
-      </c>
+      <c r="G112" s="11"/>
       <c r="H112" s="21">
         <v>48.387096774193552</v>
       </c>
@@ -4964,9 +4742,7 @@
       <c r="F113" s="17">
         <v>44</v>
       </c>
-      <c r="G113" s="11">
-        <v>46</v>
-      </c>
+      <c r="G113" s="11"/>
       <c r="H113" s="21">
         <v>83.870967741935488</v>
       </c>
@@ -4990,9 +4766,7 @@
       <c r="F114" s="17">
         <v>58.5</v>
       </c>
-      <c r="G114" s="11">
-        <v>55</v>
-      </c>
+      <c r="G114" s="11"/>
       <c r="H114" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -5016,9 +4790,7 @@
       <c r="F115" s="17">
         <v>64</v>
       </c>
-      <c r="G115" s="11">
-        <v>49</v>
-      </c>
+      <c r="G115" s="11"/>
       <c r="H115" s="21">
         <v>90.322580645161281</v>
       </c>
@@ -5042,9 +4814,7 @@
       <c r="F116" s="17">
         <v>40</v>
       </c>
-      <c r="G116" s="11">
-        <v>63</v>
-      </c>
+      <c r="G116" s="11"/>
       <c r="H116" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -5068,9 +4838,7 @@
       <c r="F117" s="17">
         <v>83.5</v>
       </c>
-      <c r="G117" s="11">
-        <v>43</v>
-      </c>
+      <c r="G117" s="11"/>
       <c r="H117" s="21">
         <v>83.870967741935488</v>
       </c>
@@ -5094,9 +4862,7 @@
       <c r="F118" s="17">
         <v>82</v>
       </c>
-      <c r="G118" s="11">
-        <v>24</v>
-      </c>
+      <c r="G118" s="11"/>
       <c r="H118" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -5120,9 +4886,7 @@
       <c r="F119" s="17">
         <v>56.5</v>
       </c>
-      <c r="G119" s="11">
-        <v>43</v>
-      </c>
+      <c r="G119" s="11"/>
       <c r="H119" s="21">
         <v>80.645161290322577</v>
       </c>
@@ -5146,9 +4910,7 @@
       <c r="F120" s="17">
         <v>42.5</v>
       </c>
-      <c r="G120" s="11">
-        <v>37</v>
-      </c>
+      <c r="G120" s="11"/>
       <c r="H120" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -5172,9 +4934,7 @@
       <c r="F121" s="17">
         <v>59</v>
       </c>
-      <c r="G121" s="11">
-        <v>28</v>
-      </c>
+      <c r="G121" s="11"/>
       <c r="H121" s="21">
         <v>67.741935483870961</v>
       </c>
@@ -5198,9 +4958,7 @@
       <c r="F122" s="17">
         <v>41.5</v>
       </c>
-      <c r="G122" s="11">
-        <v>19</v>
-      </c>
+      <c r="G122" s="11"/>
       <c r="H122" s="21">
         <v>87.096774193548384</v>
       </c>
@@ -5224,9 +4982,7 @@
       <c r="F123" s="17">
         <v>59</v>
       </c>
-      <c r="G123" s="11">
-        <v>34</v>
-      </c>
+      <c r="G123" s="11"/>
       <c r="H123" s="21">
         <v>83.870967741935488</v>
       </c>
@@ -5250,9 +5006,7 @@
       <c r="F124" s="17">
         <v>41.5</v>
       </c>
-      <c r="G124" s="11">
-        <v>17</v>
-      </c>
+      <c r="G124" s="11"/>
       <c r="H124" s="21">
         <v>83.870967741935488</v>
       </c>
@@ -5276,9 +5030,7 @@
       <c r="F125" s="17">
         <v>77.5</v>
       </c>
-      <c r="G125" s="11">
-        <v>73</v>
-      </c>
+      <c r="G125" s="11"/>
       <c r="H125" s="21">
         <v>96.774193548387103</v>
       </c>
@@ -5302,9 +5054,7 @@
       <c r="F126" s="17">
         <v>81.5</v>
       </c>
-      <c r="G126" s="11">
-        <v>43</v>
-      </c>
+      <c r="G126" s="11"/>
       <c r="H126" s="21">
         <v>80.645161290322577</v>
       </c>
@@ -5328,9 +5078,7 @@
       <c r="F127" s="17">
         <v>51.5</v>
       </c>
-      <c r="G127" s="11">
-        <v>45</v>
-      </c>
+      <c r="G127" s="11"/>
       <c r="H127" s="21">
         <v>83.870967741935488</v>
       </c>
@@ -5354,9 +5102,7 @@
       <c r="F128" s="17">
         <v>48.5</v>
       </c>
-      <c r="G128" s="11">
-        <v>56</v>
-      </c>
+      <c r="G128" s="11"/>
       <c r="H128" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -5380,9 +5126,7 @@
       <c r="F129" s="17">
         <v>56.5</v>
       </c>
-      <c r="G129" s="11">
-        <v>27</v>
-      </c>
+      <c r="G129" s="11"/>
       <c r="H129" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -5406,9 +5150,7 @@
       <c r="F130" s="17">
         <v>37</v>
       </c>
-      <c r="G130" s="11">
-        <v>33</v>
-      </c>
+      <c r="G130" s="11"/>
       <c r="H130" s="21">
         <v>67.741935483870961</v>
       </c>
@@ -5432,9 +5174,7 @@
       <c r="F131" s="17">
         <v>57</v>
       </c>
-      <c r="G131" s="11">
-        <v>30</v>
-      </c>
+      <c r="G131" s="11"/>
       <c r="H131" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -5458,9 +5198,7 @@
       <c r="F132" s="17">
         <v>50.5</v>
       </c>
-      <c r="G132" s="11">
-        <v>42</v>
-      </c>
+      <c r="G132" s="11"/>
       <c r="H132" s="21">
         <v>83.870967741935488</v>
       </c>
@@ -5484,9 +5222,7 @@
       <c r="F133" s="17">
         <v>60.5</v>
       </c>
-      <c r="G133" s="11">
-        <v>54</v>
-      </c>
+      <c r="G133" s="11"/>
       <c r="H133" s="21">
         <v>93.548387096774192</v>
       </c>
@@ -5510,9 +5246,7 @@
       <c r="F134" s="17">
         <v>67.5</v>
       </c>
-      <c r="G134" s="11">
-        <v>34</v>
-      </c>
+      <c r="G134" s="11"/>
       <c r="H134" s="21">
         <v>96.774193548387103</v>
       </c>
@@ -5536,9 +5270,7 @@
       <c r="F135" s="17">
         <v>42</v>
       </c>
-      <c r="G135" s="11">
-        <v>39</v>
-      </c>
+      <c r="G135" s="11"/>
       <c r="H135" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -5562,9 +5294,7 @@
       <c r="F136" s="17">
         <v>30.5</v>
       </c>
-      <c r="G136" s="11">
-        <v>29</v>
-      </c>
+      <c r="G136" s="11"/>
       <c r="H136" s="21">
         <v>80.645161290322577</v>
       </c>
@@ -5588,9 +5318,7 @@
       <c r="F137" s="17">
         <v>35.5</v>
       </c>
-      <c r="G137" s="11">
-        <v>40</v>
-      </c>
+      <c r="G137" s="11"/>
       <c r="H137" s="21">
         <v>90.322580645161281</v>
       </c>
@@ -5614,9 +5342,7 @@
       <c r="F138" s="17">
         <v>56</v>
       </c>
-      <c r="G138" s="11">
-        <v>44</v>
-      </c>
+      <c r="G138" s="11"/>
       <c r="H138" s="21">
         <v>93.548387096774192</v>
       </c>
@@ -5640,9 +5366,7 @@
       <c r="F139" s="17">
         <v>0</v>
       </c>
-      <c r="G139" s="11">
-        <v>39</v>
-      </c>
+      <c r="G139" s="11"/>
       <c r="H139" s="21">
         <v>67.741935483870961</v>
       </c>
@@ -5666,9 +5390,7 @@
       <c r="F140" s="17">
         <v>17.5</v>
       </c>
-      <c r="G140" s="11">
-        <v>29</v>
-      </c>
+      <c r="G140" s="11"/>
       <c r="H140" s="21">
         <v>67.741935483870961</v>
       </c>
@@ -5692,9 +5414,7 @@
       <c r="F141" s="17">
         <v>62</v>
       </c>
-      <c r="G141" s="11">
-        <v>15</v>
-      </c>
+      <c r="G141" s="11"/>
       <c r="H141" s="21">
         <v>54.838709677419352</v>
       </c>
@@ -5718,9 +5438,7 @@
       <c r="F142" s="17">
         <v>50.5</v>
       </c>
-      <c r="G142" s="11">
-        <v>35</v>
-      </c>
+      <c r="G142" s="11"/>
       <c r="H142" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -5744,9 +5462,7 @@
       <c r="F143" s="17">
         <v>72.5</v>
       </c>
-      <c r="G143" s="11">
-        <v>66</v>
-      </c>
+      <c r="G143" s="11"/>
       <c r="H143" s="21">
         <v>80.645161290322577</v>
       </c>
@@ -5770,9 +5486,7 @@
       <c r="F144" s="17">
         <v>57.5</v>
       </c>
-      <c r="G144" s="11">
-        <v>37</v>
-      </c>
+      <c r="G144" s="11"/>
       <c r="H144" s="21">
         <v>90.322580645161281</v>
       </c>
@@ -5796,9 +5510,7 @@
       <c r="F145" s="17">
         <v>71.5</v>
       </c>
-      <c r="G145" s="11">
-        <v>29</v>
-      </c>
+      <c r="G145" s="11"/>
       <c r="H145" s="21">
         <v>87.096774193548384</v>
       </c>
@@ -5822,9 +5534,7 @@
       <c r="F146" s="17">
         <v>76.5</v>
       </c>
-      <c r="G146" s="11">
-        <v>45</v>
-      </c>
+      <c r="G146" s="11"/>
       <c r="H146" s="21">
         <v>80.645161290322577</v>
       </c>
@@ -5848,9 +5558,7 @@
       <c r="F147" s="17">
         <v>60</v>
       </c>
-      <c r="G147" s="11">
-        <v>37</v>
-      </c>
+      <c r="G147" s="11"/>
       <c r="H147" s="21">
         <v>83.870967741935488</v>
       </c>
@@ -5874,9 +5582,7 @@
       <c r="F148" s="17">
         <v>40</v>
       </c>
-      <c r="G148" s="11">
-        <v>63</v>
-      </c>
+      <c r="G148" s="11"/>
       <c r="H148" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -5900,9 +5606,7 @@
       <c r="F149" s="17">
         <v>56</v>
       </c>
-      <c r="G149" s="11">
-        <v>48</v>
-      </c>
+      <c r="G149" s="11"/>
       <c r="H149" s="21">
         <v>80.645161290322577</v>
       </c>
@@ -5926,9 +5630,7 @@
       <c r="F150" s="17">
         <v>68</v>
       </c>
-      <c r="G150" s="11">
-        <v>30</v>
-      </c>
+      <c r="G150" s="11"/>
       <c r="H150" s="21">
         <v>61.29032258064516</v>
       </c>
@@ -5952,9 +5654,7 @@
       <c r="F151" s="17">
         <v>46.5</v>
       </c>
-      <c r="G151" s="11">
-        <v>17</v>
-      </c>
+      <c r="G151" s="11"/>
       <c r="H151" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -5978,9 +5678,7 @@
       <c r="F152" s="17">
         <v>26.5</v>
       </c>
-      <c r="G152" s="11">
-        <v>26</v>
-      </c>
+      <c r="G152" s="11"/>
       <c r="H152" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -6004,9 +5702,7 @@
       <c r="F153" s="17">
         <v>61</v>
       </c>
-      <c r="G153" s="11">
-        <v>31</v>
-      </c>
+      <c r="G153" s="11"/>
       <c r="H153" s="21">
         <v>51.612903225806448</v>
       </c>
@@ -6030,9 +5726,7 @@
       <c r="F154" s="17">
         <v>60</v>
       </c>
-      <c r="G154" s="11">
-        <v>65</v>
-      </c>
+      <c r="G154" s="11"/>
       <c r="H154" s="21">
         <v>80.645161290322577</v>
       </c>
@@ -6056,9 +5750,7 @@
       <c r="F155" s="17">
         <v>28</v>
       </c>
-      <c r="G155" s="11">
-        <v>36</v>
-      </c>
+      <c r="G155" s="11"/>
       <c r="H155" s="21">
         <v>64.516129032258064</v>
       </c>
@@ -6082,9 +5774,7 @@
       <c r="F156" s="17">
         <v>53.5</v>
       </c>
-      <c r="G156" s="11">
-        <v>34</v>
-      </c>
+      <c r="G156" s="11"/>
       <c r="H156" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -6108,9 +5798,7 @@
       <c r="F157" s="17">
         <v>53</v>
       </c>
-      <c r="G157" s="11">
-        <v>39</v>
-      </c>
+      <c r="G157" s="11"/>
       <c r="H157" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -6134,9 +5822,7 @@
       <c r="F158" s="17">
         <v>40.5</v>
       </c>
-      <c r="G158" s="11">
-        <v>45</v>
-      </c>
+      <c r="G158" s="11"/>
       <c r="H158" s="21">
         <v>67.741935483870961</v>
       </c>
@@ -6160,9 +5846,7 @@
       <c r="F159" s="17">
         <v>33.5</v>
       </c>
-      <c r="G159" s="11">
-        <v>43</v>
-      </c>
+      <c r="G159" s="11"/>
       <c r="H159" s="21">
         <v>74.193548387096769</v>
       </c>
@@ -6186,9 +5870,7 @@
       <c r="F160" s="17">
         <v>73</v>
       </c>
-      <c r="G160" s="11">
-        <v>40</v>
-      </c>
+      <c r="G160" s="11"/>
       <c r="H160" s="21">
         <v>100</v>
       </c>
@@ -6212,9 +5894,7 @@
       <c r="F161" s="17">
         <v>51.5</v>
       </c>
-      <c r="G161" s="11">
-        <v>39</v>
-      </c>
+      <c r="G161" s="11"/>
       <c r="H161" s="21">
         <v>74.193548387096769</v>
       </c>
@@ -6238,9 +5918,7 @@
       <c r="F162" s="17">
         <v>40</v>
       </c>
-      <c r="G162" s="11">
-        <v>18</v>
-      </c>
+      <c r="G162" s="11"/>
       <c r="H162" s="21">
         <v>74.193548387096769</v>
       </c>
@@ -6264,9 +5942,7 @@
       <c r="F163" s="17">
         <v>60</v>
       </c>
-      <c r="G163" s="11">
-        <v>45</v>
-      </c>
+      <c r="G163" s="11"/>
       <c r="H163" s="21">
         <v>87.096774193548384</v>
       </c>
@@ -6290,9 +5966,7 @@
       <c r="F164" s="17">
         <v>66.5</v>
       </c>
-      <c r="G164" s="11">
-        <v>45</v>
-      </c>
+      <c r="G164" s="11"/>
       <c r="H164" s="21">
         <v>83.870967741935488</v>
       </c>
@@ -6316,9 +5990,7 @@
       <c r="F165" s="17">
         <v>72</v>
       </c>
-      <c r="G165" s="11">
-        <v>69</v>
-      </c>
+      <c r="G165" s="11"/>
       <c r="H165" s="21">
         <v>66.666666666666657</v>
       </c>
@@ -6342,9 +6014,7 @@
       <c r="F166" s="17">
         <v>64</v>
       </c>
-      <c r="G166" s="11">
-        <v>43</v>
-      </c>
+      <c r="G166" s="11"/>
       <c r="H166" s="21">
         <v>80.645161290322577</v>
       </c>
@@ -6368,9 +6038,7 @@
       <c r="F167" s="17">
         <v>40.5</v>
       </c>
-      <c r="G167" s="11">
-        <v>27</v>
-      </c>
+      <c r="G167" s="11"/>
       <c r="H167" s="21">
         <v>80.645161290322577</v>
       </c>
@@ -6394,9 +6062,7 @@
       <c r="F168" s="17">
         <v>62</v>
       </c>
-      <c r="G168" s="11">
-        <v>36</v>
-      </c>
+      <c r="G168" s="11"/>
       <c r="H168" s="21">
         <v>90.322580645161281</v>
       </c>
@@ -6420,9 +6086,7 @@
       <c r="F169" s="17">
         <v>40</v>
       </c>
-      <c r="G169" s="11">
-        <v>34</v>
-      </c>
+      <c r="G169" s="11"/>
       <c r="H169" s="21">
         <v>83.870967741935488</v>
       </c>
@@ -6446,9 +6110,7 @@
       <c r="F170" s="17">
         <v>79</v>
       </c>
-      <c r="G170" s="11">
-        <v>18</v>
-      </c>
+      <c r="G170" s="11"/>
       <c r="H170" s="21">
         <v>74.193548387096769</v>
       </c>
@@ -6472,9 +6134,7 @@
       <c r="F171" s="17">
         <v>75</v>
       </c>
-      <c r="G171" s="11">
-        <v>56</v>
-      </c>
+      <c r="G171" s="11"/>
       <c r="H171" s="21">
         <v>87.096774193548384</v>
       </c>
@@ -6498,9 +6158,7 @@
       <c r="F172" s="17">
         <v>74.5</v>
       </c>
-      <c r="G172" s="11">
-        <v>69</v>
-      </c>
+      <c r="G172" s="11"/>
       <c r="H172" s="21">
         <v>83.870967741935488</v>
       </c>
@@ -6524,9 +6182,7 @@
       <c r="F173" s="17">
         <v>59.5</v>
       </c>
-      <c r="G173" s="11">
-        <v>45</v>
-      </c>
+      <c r="G173" s="11"/>
       <c r="H173" s="21">
         <v>80.645161290322577</v>
       </c>
@@ -6550,9 +6206,7 @@
       <c r="F174" s="17">
         <v>48.5</v>
       </c>
-      <c r="G174" s="11">
-        <v>60</v>
-      </c>
+      <c r="G174" s="11"/>
       <c r="H174" s="21">
         <v>80.645161290322577</v>
       </c>
@@ -6576,9 +6230,7 @@
       <c r="F175" s="17">
         <v>23.5</v>
       </c>
-      <c r="G175" s="11">
-        <v>46</v>
-      </c>
+      <c r="G175" s="11"/>
       <c r="H175" s="21">
         <v>74.193548387096769</v>
       </c>
@@ -6602,9 +6254,7 @@
       <c r="F176" s="17">
         <v>69.5</v>
       </c>
-      <c r="G176" s="11">
-        <v>55</v>
-      </c>
+      <c r="G176" s="11"/>
       <c r="H176" s="21">
         <v>74.193548387096769</v>
       </c>
@@ -6628,9 +6278,7 @@
       <c r="F177" s="17">
         <v>66.5</v>
       </c>
-      <c r="G177" s="11">
-        <v>42</v>
-      </c>
+      <c r="G177" s="11"/>
       <c r="H177" s="21">
         <v>80.645161290322577</v>
       </c>
@@ -6654,9 +6302,7 @@
       <c r="F178" s="17">
         <v>96.5</v>
       </c>
-      <c r="G178" s="11">
-        <v>49</v>
-      </c>
+      <c r="G178" s="11"/>
       <c r="H178" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -6680,9 +6326,7 @@
       <c r="F179" s="17">
         <v>55</v>
       </c>
-      <c r="G179" s="11">
-        <v>35</v>
-      </c>
+      <c r="G179" s="11"/>
       <c r="H179" s="21">
         <v>93.548387096774192</v>
       </c>
@@ -6706,9 +6350,7 @@
       <c r="F180" s="17">
         <v>71.5</v>
       </c>
-      <c r="G180" s="11">
-        <v>46</v>
-      </c>
+      <c r="G180" s="11"/>
       <c r="H180" s="21">
         <v>74.193548387096769</v>
       </c>
@@ -6732,9 +6374,7 @@
       <c r="F181" s="17">
         <v>49.5</v>
       </c>
-      <c r="G181" s="11">
-        <v>19</v>
-      </c>
+      <c r="G181" s="11"/>
       <c r="H181" s="21">
         <v>70.967741935483872</v>
       </c>
@@ -6758,9 +6398,7 @@
       <c r="F182" s="17">
         <v>32.5</v>
       </c>
-      <c r="G182" s="11">
-        <v>11</v>
-      </c>
+      <c r="G182" s="11"/>
       <c r="H182" s="21">
         <v>64.516129032258064</v>
       </c>
@@ -6784,9 +6422,7 @@
       <c r="F183" s="17">
         <v>71</v>
       </c>
-      <c r="G183" s="11">
-        <v>28</v>
-      </c>
+      <c r="G183" s="11"/>
       <c r="H183" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -6810,9 +6446,7 @@
       <c r="F184" s="17">
         <v>28.5</v>
       </c>
-      <c r="G184" s="11">
-        <v>61</v>
-      </c>
+      <c r="G184" s="11"/>
       <c r="H184" s="21">
         <v>54.838709677419352</v>
       </c>
@@ -6836,9 +6470,7 @@
       <c r="F185" s="17">
         <v>60.5</v>
       </c>
-      <c r="G185" s="11">
-        <v>56</v>
-      </c>
+      <c r="G185" s="11"/>
       <c r="H185" s="21">
         <v>87.096774193548384</v>
       </c>
@@ -6862,9 +6494,7 @@
       <c r="F186" s="17">
         <v>61</v>
       </c>
-      <c r="G186" s="11">
-        <v>64</v>
-      </c>
+      <c r="G186" s="11"/>
       <c r="H186" s="21">
         <v>83.333333333333343</v>
       </c>
@@ -6888,9 +6518,7 @@
       <c r="F187" s="17">
         <v>0.5</v>
       </c>
-      <c r="G187" s="11">
-        <v>46</v>
-      </c>
+      <c r="G187" s="11"/>
       <c r="H187" s="21">
         <v>62.5</v>
       </c>
@@ -6914,9 +6542,7 @@
       <c r="F188" s="17">
         <v>38.5</v>
       </c>
-      <c r="G188" s="11">
-        <v>28</v>
-      </c>
+      <c r="G188" s="11"/>
       <c r="H188" s="21">
         <v>83.333333333333343</v>
       </c>
@@ -6940,9 +6566,7 @@
       <c r="F189" s="17">
         <v>17.5</v>
       </c>
-      <c r="G189" s="11">
-        <v>41</v>
-      </c>
+      <c r="G189" s="11"/>
       <c r="H189" s="21">
         <v>79.166666666666657</v>
       </c>
@@ -6966,9 +6590,7 @@
       <c r="F190" s="17">
         <v>72.5</v>
       </c>
-      <c r="G190" s="11">
-        <v>55</v>
-      </c>
+      <c r="G190" s="11"/>
       <c r="H190" s="21">
         <v>75</v>
       </c>
@@ -6992,9 +6614,7 @@
       <c r="F191" s="17">
         <v>55.5</v>
       </c>
-      <c r="G191" s="11">
-        <v>38</v>
-      </c>
+      <c r="G191" s="11"/>
       <c r="H191" s="21">
         <v>75</v>
       </c>
@@ -7018,9 +6638,7 @@
       <c r="F192" s="17">
         <v>43.5</v>
       </c>
-      <c r="G192" s="11">
-        <v>30</v>
-      </c>
+      <c r="G192" s="11"/>
       <c r="H192" s="21">
         <v>83.333333333333343</v>
       </c>
@@ -7044,9 +6662,7 @@
       <c r="F193" s="17">
         <v>24.5</v>
       </c>
-      <c r="G193" s="11">
-        <v>22</v>
-      </c>
+      <c r="G193" s="11"/>
       <c r="H193" s="21">
         <v>58.333333333333336</v>
       </c>
@@ -7070,9 +6686,7 @@
       <c r="F194" s="17">
         <v>65.5</v>
       </c>
-      <c r="G194" s="11">
-        <v>14</v>
-      </c>
+      <c r="G194" s="11"/>
       <c r="H194" s="18"/>
     </row>
     <row r="195" spans="1:8">
@@ -7094,9 +6708,7 @@
       <c r="F195" s="17">
         <v>72</v>
       </c>
-      <c r="G195" s="11">
-        <v>47</v>
-      </c>
+      <c r="G195" s="11"/>
       <c r="H195" s="18"/>
     </row>
     <row r="196" spans="1:8">
@@ -7118,9 +6730,7 @@
       <c r="F196" s="17">
         <v>83</v>
       </c>
-      <c r="G196" s="11">
-        <v>39</v>
-      </c>
+      <c r="G196" s="11"/>
       <c r="H196" s="18"/>
     </row>
     <row r="197" spans="1:8">
@@ -7142,9 +6752,7 @@
       <c r="F197" s="17">
         <v>74</v>
       </c>
-      <c r="G197" s="11">
-        <v>39</v>
-      </c>
+      <c r="G197" s="11"/>
       <c r="H197" s="18"/>
     </row>
     <row r="198" spans="1:8">
@@ -7166,9 +6774,7 @@
       <c r="F198" s="17">
         <v>69</v>
       </c>
-      <c r="G198" s="11">
-        <v>35</v>
-      </c>
+      <c r="G198" s="11"/>
       <c r="H198" s="18"/>
     </row>
     <row r="199" spans="1:8">
@@ -7190,9 +6796,7 @@
       <c r="F199" s="17" t="s">
         <v>482</v>
       </c>
-      <c r="G199" s="11">
-        <v>26</v>
-      </c>
+      <c r="G199" s="11"/>
       <c r="H199" s="18"/>
     </row>
     <row r="200" spans="1:8">
@@ -7214,9 +6818,7 @@
       <c r="F200" s="17">
         <v>88</v>
       </c>
-      <c r="G200" s="11">
-        <v>52</v>
-      </c>
+      <c r="G200" s="11"/>
       <c r="H200" s="18"/>
     </row>
     <row r="201" spans="1:8">
@@ -7238,9 +6840,7 @@
       <c r="F201" s="17">
         <v>59</v>
       </c>
-      <c r="G201" s="11">
-        <v>41</v>
-      </c>
+      <c r="G201" s="11"/>
       <c r="H201" s="18"/>
     </row>
     <row r="202" spans="1:8">
@@ -7262,9 +6862,7 @@
       <c r="F202" s="17">
         <v>33</v>
       </c>
-      <c r="G202" s="11">
-        <v>27</v>
-      </c>
+      <c r="G202" s="11"/>
       <c r="H202" s="18"/>
     </row>
     <row r="203" spans="1:8">
@@ -7286,9 +6884,7 @@
       <c r="F203" s="17">
         <v>71</v>
       </c>
-      <c r="G203" s="11">
-        <v>42</v>
-      </c>
+      <c r="G203" s="11"/>
       <c r="H203" s="18"/>
     </row>
     <row r="204" spans="1:8">
@@ -7310,9 +6906,7 @@
       <c r="F204" s="17">
         <v>77</v>
       </c>
-      <c r="G204" s="11">
-        <v>31</v>
-      </c>
+      <c r="G204" s="11"/>
       <c r="H204" s="18"/>
     </row>
     <row r="205" spans="1:8">
@@ -7334,9 +6928,7 @@
       <c r="F205" s="17">
         <v>53</v>
       </c>
-      <c r="G205" s="11">
-        <v>47</v>
-      </c>
+      <c r="G205" s="11"/>
       <c r="H205" s="18"/>
     </row>
     <row r="206" spans="1:8">
@@ -7358,9 +6950,7 @@
       <c r="F206" s="17">
         <v>76</v>
       </c>
-      <c r="G206" s="11">
-        <v>30</v>
-      </c>
+      <c r="G206" s="11"/>
       <c r="H206" s="18"/>
     </row>
     <row r="207" spans="1:8">
@@ -7382,9 +6972,7 @@
       <c r="F207" s="20">
         <v>68</v>
       </c>
-      <c r="G207" s="11">
-        <v>21</v>
-      </c>
+      <c r="G207" s="11"/>
       <c r="H207" s="18"/>
     </row>
     <row r="208" spans="1:8">
@@ -7406,9 +6994,7 @@
       <c r="F208" s="17">
         <v>41</v>
       </c>
-      <c r="G208" s="11">
-        <v>35</v>
-      </c>
+      <c r="G208" s="11"/>
       <c r="H208" s="18"/>
     </row>
     <row r="209" spans="1:8">
@@ -7430,9 +7016,7 @@
       <c r="F209" s="17">
         <v>77</v>
       </c>
-      <c r="G209" s="11">
-        <v>17</v>
-      </c>
+      <c r="G209" s="11"/>
       <c r="H209" s="18"/>
     </row>
     <row r="210" spans="1:8">
@@ -7454,9 +7038,7 @@
       <c r="F210" s="17">
         <v>87</v>
       </c>
-      <c r="G210" s="11">
-        <v>30</v>
-      </c>
+      <c r="G210" s="11"/>
       <c r="H210" s="18"/>
     </row>
     <row r="211" spans="1:8">
@@ -7478,9 +7060,7 @@
       <c r="F211" s="17">
         <v>40</v>
       </c>
-      <c r="G211" s="11">
-        <v>28</v>
-      </c>
+      <c r="G211" s="11"/>
       <c r="H211" s="18"/>
     </row>
     <row r="212" spans="1:8">
@@ -7502,9 +7082,7 @@
       <c r="F212" s="17">
         <v>44</v>
       </c>
-      <c r="G212" s="11">
-        <v>47</v>
-      </c>
+      <c r="G212" s="11"/>
       <c r="H212" s="18"/>
     </row>
     <row r="213" spans="1:8">
@@ -7526,9 +7104,7 @@
       <c r="F213" s="17">
         <v>88</v>
       </c>
-      <c r="G213" s="11">
-        <v>48</v>
-      </c>
+      <c r="G213" s="11"/>
       <c r="H213" s="18"/>
     </row>
     <row r="214" spans="1:8">
@@ -7550,9 +7126,7 @@
       <c r="F214" s="17">
         <v>90</v>
       </c>
-      <c r="G214" s="11">
-        <v>28</v>
-      </c>
+      <c r="G214" s="11"/>
       <c r="H214" s="18"/>
     </row>
     <row r="215" spans="1:8">
@@ -7574,9 +7148,7 @@
       <c r="F215" s="17">
         <v>49</v>
       </c>
-      <c r="G215" s="11">
-        <v>27</v>
-      </c>
+      <c r="G215" s="11"/>
       <c r="H215" s="18"/>
     </row>
     <row r="216" spans="1:8">
@@ -7598,9 +7170,7 @@
       <c r="F216" s="17">
         <v>76</v>
       </c>
-      <c r="G216" s="11" t="s">
-        <v>482</v>
-      </c>
+      <c r="G216" s="11"/>
       <c r="H216" s="18"/>
     </row>
     <row r="217" spans="1:8">
@@ -7622,9 +7192,7 @@
       <c r="F217" s="17" t="s">
         <v>482</v>
       </c>
-      <c r="G217" s="11" t="s">
-        <v>482</v>
-      </c>
+      <c r="G217" s="11"/>
       <c r="H217" s="18"/>
     </row>
     <row r="218" spans="1:8">
@@ -7646,9 +7214,7 @@
       <c r="F218" s="17">
         <v>56</v>
       </c>
-      <c r="G218" s="11">
-        <v>62</v>
-      </c>
+      <c r="G218" s="11"/>
       <c r="H218" s="18"/>
     </row>
     <row r="219" spans="1:8">
@@ -7670,9 +7236,7 @@
       <c r="F219" s="17">
         <v>66</v>
       </c>
-      <c r="G219" s="11">
-        <v>28</v>
-      </c>
+      <c r="G219" s="11"/>
       <c r="H219" s="18"/>
     </row>
     <row r="220" spans="1:8">
@@ -7694,9 +7258,7 @@
       <c r="F220" s="17">
         <v>44</v>
       </c>
-      <c r="G220" s="11">
-        <v>34</v>
-      </c>
+      <c r="G220" s="11"/>
       <c r="H220" s="18"/>
     </row>
     <row r="221" spans="1:8">
@@ -7718,9 +7280,7 @@
       <c r="F221" s="17">
         <v>96</v>
       </c>
-      <c r="G221" s="11">
-        <v>28</v>
-      </c>
+      <c r="G221" s="11"/>
       <c r="H221" s="18"/>
     </row>
     <row r="222" spans="1:8">
@@ -7742,9 +7302,7 @@
       <c r="F222" s="17">
         <v>88</v>
       </c>
-      <c r="G222" s="11">
-        <v>33</v>
-      </c>
+      <c r="G222" s="11"/>
       <c r="H222" s="18"/>
     </row>
     <row r="223" spans="1:8">
@@ -7766,9 +7324,7 @@
       <c r="F223" s="17">
         <v>51</v>
       </c>
-      <c r="G223" s="11">
-        <v>33</v>
-      </c>
+      <c r="G223" s="11"/>
       <c r="H223" s="18"/>
     </row>
     <row r="224" spans="1:8">
@@ -7790,9 +7346,7 @@
       <c r="F224" s="17">
         <v>89</v>
       </c>
-      <c r="G224" s="11">
-        <v>31</v>
-      </c>
+      <c r="G224" s="11"/>
       <c r="H224" s="18"/>
     </row>
     <row r="225" spans="1:8">
@@ -7814,9 +7368,7 @@
       <c r="F225" s="17">
         <v>70</v>
       </c>
-      <c r="G225" s="11">
-        <v>48</v>
-      </c>
+      <c r="G225" s="11"/>
       <c r="H225" s="18"/>
     </row>
     <row r="226" spans="1:8">
@@ -7838,9 +7390,7 @@
       <c r="F226" s="17">
         <v>82</v>
       </c>
-      <c r="G226" s="11">
-        <v>31</v>
-      </c>
+      <c r="G226" s="11"/>
       <c r="H226" s="18"/>
     </row>
     <row r="227" spans="1:8">
@@ -7862,9 +7412,7 @@
       <c r="F227" s="17" t="s">
         <v>482</v>
       </c>
-      <c r="G227" s="11">
-        <v>37</v>
-      </c>
+      <c r="G227" s="11"/>
       <c r="H227" s="18"/>
     </row>
     <row r="228" spans="1:8">
@@ -7886,9 +7434,7 @@
       <c r="F228" s="17">
         <v>65</v>
       </c>
-      <c r="G228" s="11">
-        <v>34</v>
-      </c>
+      <c r="G228" s="11"/>
       <c r="H228" s="18"/>
     </row>
     <row r="229" spans="1:8">
@@ -7910,9 +7456,7 @@
       <c r="F229" s="17">
         <v>80</v>
       </c>
-      <c r="G229" s="11">
-        <v>24</v>
-      </c>
+      <c r="G229" s="11"/>
       <c r="H229" s="18"/>
     </row>
     <row r="230" spans="1:8">
@@ -7934,9 +7478,7 @@
       <c r="F230" s="17">
         <v>85</v>
       </c>
-      <c r="G230" s="11">
-        <v>59</v>
-      </c>
+      <c r="G230" s="11"/>
       <c r="H230" s="18"/>
     </row>
     <row r="231" spans="1:8">
@@ -7958,9 +7500,7 @@
       <c r="F231" s="17">
         <v>61</v>
       </c>
-      <c r="G231" s="11">
-        <v>53</v>
-      </c>
+      <c r="G231" s="11"/>
       <c r="H231" s="18"/>
     </row>
     <row r="232" spans="1:8">
@@ -7982,9 +7522,7 @@
       <c r="F232" s="17">
         <v>67</v>
       </c>
-      <c r="G232" s="11">
-        <v>33</v>
-      </c>
+      <c r="G232" s="11"/>
       <c r="H232" s="18"/>
     </row>
     <row r="233" spans="1:8">
@@ -8006,9 +7544,7 @@
       <c r="F233" s="17" t="s">
         <v>482</v>
       </c>
-      <c r="G233" s="11" t="s">
-        <v>482</v>
-      </c>
+      <c r="G233" s="11"/>
       <c r="H233" s="18"/>
     </row>
     <row r="234" spans="1:8">
@@ -8030,9 +7566,7 @@
       <c r="F234" s="17">
         <v>40</v>
       </c>
-      <c r="G234" s="11">
-        <v>62</v>
-      </c>
+      <c r="G234" s="11"/>
       <c r="H234" s="18"/>
     </row>
     <row r="235" spans="1:8">
@@ -8054,9 +7588,7 @@
       <c r="F235" s="17">
         <v>55</v>
       </c>
-      <c r="G235" s="11">
-        <v>53</v>
-      </c>
+      <c r="G235" s="11"/>
       <c r="H235" s="18"/>
     </row>
     <row r="236" spans="1:8">
@@ -8078,9 +7610,7 @@
       <c r="F236" s="17">
         <v>90</v>
       </c>
-      <c r="G236" s="11">
-        <v>41</v>
-      </c>
+      <c r="G236" s="11"/>
       <c r="H236" s="18"/>
     </row>
     <row r="237" spans="1:8">
@@ -8102,9 +7632,7 @@
       <c r="F237" s="17" t="s">
         <v>482</v>
       </c>
-      <c r="G237" s="11">
-        <v>29</v>
-      </c>
+      <c r="G237" s="11"/>
       <c r="H237" s="18"/>
     </row>
     <row r="238" spans="1:8">
@@ -8126,9 +7654,7 @@
       <c r="F238" s="17" t="s">
         <v>482</v>
       </c>
-      <c r="G238" s="11" t="s">
-        <v>482</v>
-      </c>
+      <c r="G238" s="11"/>
       <c r="H238" s="18"/>
     </row>
   </sheetData>
@@ -8138,12 +7664,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8291,24 +7814,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82FD49CE-D196-4C00-BC5E-382EDDDD004F}">
-  <ds:schemaRefs/>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F334BD5B-9873-472F-B0A9-4AE19CD21D29}">
-  <ds:schemaRefs/>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B92832D-94CC-4C5E-A4E8-2D2A44869573}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
@@ -8322,4 +7836,16 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F334BD5B-9873-472F-B0A9-4AE19CD21D29}">
+  <ds:schemaRefs/>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82FD49CE-D196-4C00-BC5E-382EDDDD004F}">
+  <ds:schemaRefs/>
+</ds:datastoreItem>
 </file>
--- a/MC1020_E25.xlsx
+++ b/MC1020_E25.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assignment marks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA9CCB9F-9AE5-424F-BFB2-A51D85F17874}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C9067E9-DFDD-46F2-A688-EE7F3341587E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="483">
   <si>
     <t xml:space="preserve"> Reg.number</t>
   </si>
@@ -1682,7 +1682,7 @@
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1735,6 +1735,9 @@
     <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="12">
@@ -2078,7 +2081,9 @@
       <c r="F2" s="17">
         <v>64</v>
       </c>
-      <c r="G2" s="11"/>
+      <c r="G2" s="23">
+        <v>13</v>
+      </c>
       <c r="H2" s="21">
         <v>61.29032258064516</v>
       </c>
@@ -2091,10 +2096,10 @@
         <v>11</v>
       </c>
       <c r="C3" s="11">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D3" s="22">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E3" s="17">
         <v>49</v>
@@ -2102,7 +2107,9 @@
       <c r="F3" s="17">
         <v>54</v>
       </c>
-      <c r="G3" s="11"/>
+      <c r="G3" s="23">
+        <v>24</v>
+      </c>
       <c r="H3" s="21">
         <v>74.193548387096769</v>
       </c>
@@ -2126,7 +2133,9 @@
       <c r="F4" s="17">
         <v>67.5</v>
       </c>
-      <c r="G4" s="11"/>
+      <c r="G4" s="23">
+        <v>50</v>
+      </c>
       <c r="H4" s="21">
         <v>58.064516129032263</v>
       </c>
@@ -2150,7 +2159,9 @@
       <c r="F5" s="17">
         <v>61.5</v>
       </c>
-      <c r="G5" s="11"/>
+      <c r="G5" s="23">
+        <v>26</v>
+      </c>
       <c r="H5" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -2174,7 +2185,9 @@
       <c r="F6" s="17">
         <v>61</v>
       </c>
-      <c r="G6" s="11"/>
+      <c r="G6" s="23">
+        <v>32</v>
+      </c>
       <c r="H6" s="21">
         <v>61.29032258064516</v>
       </c>
@@ -2198,7 +2211,9 @@
       <c r="F7" s="17">
         <v>16</v>
       </c>
-      <c r="G7" s="11"/>
+      <c r="G7" s="23">
+        <v>20</v>
+      </c>
       <c r="H7" s="21">
         <v>83.870967741935488</v>
       </c>
@@ -2222,7 +2237,9 @@
       <c r="F8" s="17">
         <v>79</v>
       </c>
-      <c r="G8" s="11"/>
+      <c r="G8" s="23">
+        <v>32</v>
+      </c>
       <c r="H8" s="21">
         <v>87.096774193548384</v>
       </c>
@@ -2246,7 +2263,9 @@
       <c r="F9" s="17">
         <v>36</v>
       </c>
-      <c r="G9" s="11"/>
+      <c r="G9" s="23">
+        <v>12</v>
+      </c>
       <c r="H9" s="21">
         <v>83.870967741935488</v>
       </c>
@@ -2259,10 +2278,10 @@
         <v>25</v>
       </c>
       <c r="C10" s="11">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D10" s="22">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E10" s="17">
         <v>47</v>
@@ -2270,7 +2289,9 @@
       <c r="F10" s="17">
         <v>61</v>
       </c>
-      <c r="G10" s="11"/>
+      <c r="G10" s="23">
+        <v>18</v>
+      </c>
       <c r="H10" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -2294,7 +2315,9 @@
       <c r="F11" s="17">
         <v>59.5</v>
       </c>
-      <c r="G11" s="11"/>
+      <c r="G11" s="23">
+        <v>58</v>
+      </c>
       <c r="H11" s="21">
         <v>83.870967741935488</v>
       </c>
@@ -2318,7 +2341,9 @@
       <c r="F12" s="17">
         <v>43.5</v>
       </c>
-      <c r="G12" s="11"/>
+      <c r="G12" s="23">
+        <v>22</v>
+      </c>
       <c r="H12" s="21">
         <v>80.645161290322577</v>
       </c>
@@ -2342,7 +2367,9 @@
       <c r="F13" s="17">
         <v>65.5</v>
       </c>
-      <c r="G13" s="11"/>
+      <c r="G13" s="23">
+        <v>19</v>
+      </c>
       <c r="H13" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -2366,7 +2393,9 @@
       <c r="F14" s="17">
         <v>60.5</v>
       </c>
-      <c r="G14" s="11"/>
+      <c r="G14" s="23">
+        <v>34</v>
+      </c>
       <c r="H14" s="21">
         <v>87.096774193548384</v>
       </c>
@@ -2390,7 +2419,9 @@
       <c r="F15" s="17">
         <v>84.5</v>
       </c>
-      <c r="G15" s="11"/>
+      <c r="G15" s="23">
+        <v>50</v>
+      </c>
       <c r="H15" s="21">
         <v>93.548387096774192</v>
       </c>
@@ -2414,7 +2445,9 @@
       <c r="F16" s="17">
         <v>58</v>
       </c>
-      <c r="G16" s="11"/>
+      <c r="G16" s="23">
+        <v>54</v>
+      </c>
       <c r="H16" s="21">
         <v>83.870967741935488</v>
       </c>
@@ -2438,7 +2471,9 @@
       <c r="F17" s="17">
         <v>73.5</v>
       </c>
-      <c r="G17" s="11"/>
+      <c r="G17" s="23">
+        <v>35</v>
+      </c>
       <c r="H17" s="21">
         <v>90.322580645161281</v>
       </c>
@@ -2462,7 +2497,9 @@
       <c r="F18" s="17">
         <v>17.5</v>
       </c>
-      <c r="G18" s="11"/>
+      <c r="G18" s="23">
+        <v>33</v>
+      </c>
       <c r="H18" s="21">
         <v>54.838709677419352</v>
       </c>
@@ -2486,7 +2523,9 @@
       <c r="F19" s="17">
         <v>83</v>
       </c>
-      <c r="G19" s="11"/>
+      <c r="G19" s="23">
+        <v>46</v>
+      </c>
       <c r="H19" s="21">
         <v>70.967741935483872</v>
       </c>
@@ -2510,7 +2549,9 @@
       <c r="F20" s="17">
         <v>55.5</v>
       </c>
-      <c r="G20" s="11"/>
+      <c r="G20" s="23">
+        <v>57</v>
+      </c>
       <c r="H20" s="21">
         <v>83.870967741935488</v>
       </c>
@@ -2534,7 +2575,9 @@
       <c r="F21" s="17">
         <v>69.5</v>
       </c>
-      <c r="G21" s="11"/>
+      <c r="G21" s="23">
+        <v>39</v>
+      </c>
       <c r="H21" s="21">
         <v>87.096774193548384</v>
       </c>
@@ -2558,7 +2601,9 @@
       <c r="F22" s="17">
         <v>50.5</v>
       </c>
-      <c r="G22" s="11"/>
+      <c r="G22" s="23">
+        <v>37</v>
+      </c>
       <c r="H22" s="21">
         <v>93.548387096774192</v>
       </c>
@@ -2582,7 +2627,9 @@
       <c r="F23" s="17">
         <v>61</v>
       </c>
-      <c r="G23" s="11"/>
+      <c r="G23" s="23">
+        <v>42</v>
+      </c>
       <c r="H23" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -2606,7 +2653,9 @@
       <c r="F24" s="17">
         <v>69</v>
       </c>
-      <c r="G24" s="11"/>
+      <c r="G24" s="23">
+        <v>36</v>
+      </c>
       <c r="H24" s="21">
         <v>83.870967741935488</v>
       </c>
@@ -2619,10 +2668,10 @@
         <v>55</v>
       </c>
       <c r="C25" s="11">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D25" s="22">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E25" s="17">
         <v>50</v>
@@ -2630,7 +2679,9 @@
       <c r="F25" s="17">
         <v>35</v>
       </c>
-      <c r="G25" s="11"/>
+      <c r="G25" s="23">
+        <v>19</v>
+      </c>
       <c r="H25" s="21">
         <v>80.645161290322577</v>
       </c>
@@ -2646,7 +2697,7 @@
         <v>31</v>
       </c>
       <c r="D26" s="22">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E26" s="17">
         <v>46</v>
@@ -2654,7 +2705,9 @@
       <c r="F26" s="17">
         <v>57.5</v>
       </c>
-      <c r="G26" s="11"/>
+      <c r="G26" s="23">
+        <v>22</v>
+      </c>
       <c r="H26" s="21">
         <v>64.516129032258064</v>
       </c>
@@ -2678,7 +2731,9 @@
       <c r="F27" s="17">
         <v>64</v>
       </c>
-      <c r="G27" s="11"/>
+      <c r="G27" s="23">
+        <v>48</v>
+      </c>
       <c r="H27" s="21">
         <v>74.193548387096769</v>
       </c>
@@ -2702,7 +2757,9 @@
       <c r="F28" s="17">
         <v>54.5</v>
       </c>
-      <c r="G28" s="11"/>
+      <c r="G28" s="23">
+        <v>38</v>
+      </c>
       <c r="H28" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -2726,7 +2783,9 @@
       <c r="F29" s="17">
         <v>43.5</v>
       </c>
-      <c r="G29" s="11"/>
+      <c r="G29" s="23">
+        <v>49</v>
+      </c>
       <c r="H29" s="21">
         <v>74.193548387096769</v>
       </c>
@@ -2750,7 +2809,9 @@
       <c r="F30" s="17">
         <v>58.5</v>
       </c>
-      <c r="G30" s="11"/>
+      <c r="G30" s="23">
+        <v>55</v>
+      </c>
       <c r="H30" s="21">
         <v>90.322580645161281</v>
       </c>
@@ -2774,7 +2835,9 @@
       <c r="F31" s="17">
         <v>79</v>
       </c>
-      <c r="G31" s="11"/>
+      <c r="G31" s="23">
+        <v>50</v>
+      </c>
       <c r="H31" s="21">
         <v>80.645161290322577</v>
       </c>
@@ -2798,7 +2861,9 @@
       <c r="F32" s="17">
         <v>57.5</v>
       </c>
-      <c r="G32" s="11"/>
+      <c r="G32" s="23">
+        <v>18</v>
+      </c>
       <c r="H32" s="21">
         <v>64.516129032258064</v>
       </c>
@@ -2822,7 +2887,9 @@
       <c r="F33" s="17">
         <v>68.5</v>
       </c>
-      <c r="G33" s="11"/>
+      <c r="G33" s="23">
+        <v>31</v>
+      </c>
       <c r="H33" s="21">
         <v>70.967741935483872</v>
       </c>
@@ -2846,7 +2913,9 @@
       <c r="F34" s="17">
         <v>78</v>
       </c>
-      <c r="G34" s="11"/>
+      <c r="G34" s="23">
+        <v>25</v>
+      </c>
       <c r="H34" s="21">
         <v>80.645161290322577</v>
       </c>
@@ -2870,7 +2939,9 @@
       <c r="F35" s="17">
         <v>49.5</v>
       </c>
-      <c r="G35" s="11"/>
+      <c r="G35" s="23">
+        <v>32</v>
+      </c>
       <c r="H35" s="21">
         <v>87.096774193548384</v>
       </c>
@@ -2894,7 +2965,9 @@
       <c r="F36" s="17">
         <v>33.5</v>
       </c>
-      <c r="G36" s="11"/>
+      <c r="G36" s="23">
+        <v>47</v>
+      </c>
       <c r="H36" s="21">
         <v>67.741935483870961</v>
       </c>
@@ -2918,7 +2991,9 @@
       <c r="F37" s="17">
         <v>60</v>
       </c>
-      <c r="G37" s="11"/>
+      <c r="G37" s="23">
+        <v>50</v>
+      </c>
       <c r="H37" s="21">
         <v>70.967741935483872</v>
       </c>
@@ -2942,7 +3017,9 @@
       <c r="F38" s="17">
         <v>35</v>
       </c>
-      <c r="G38" s="11"/>
+      <c r="G38" s="23">
+        <v>33</v>
+      </c>
       <c r="H38" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -2966,7 +3043,9 @@
       <c r="F39" s="17">
         <v>72</v>
       </c>
-      <c r="G39" s="11"/>
+      <c r="G39" s="23">
+        <v>16</v>
+      </c>
       <c r="H39" s="21">
         <v>83.870967741935488</v>
       </c>
@@ -2990,7 +3069,9 @@
       <c r="F40" s="17">
         <v>72</v>
       </c>
-      <c r="G40" s="11"/>
+      <c r="G40" s="23">
+        <v>56</v>
+      </c>
       <c r="H40" s="21">
         <v>87.096774193548384</v>
       </c>
@@ -3014,7 +3095,9 @@
       <c r="F41" s="17">
         <v>53</v>
       </c>
-      <c r="G41" s="11"/>
+      <c r="G41" s="23">
+        <v>54</v>
+      </c>
       <c r="H41" s="21">
         <v>87.096774193548384</v>
       </c>
@@ -3030,7 +3113,7 @@
         <v>32</v>
       </c>
       <c r="D42" s="22">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E42" s="17">
         <v>47</v>
@@ -3038,7 +3121,9 @@
       <c r="F42" s="17">
         <v>36</v>
       </c>
-      <c r="G42" s="11"/>
+      <c r="G42" s="23">
+        <v>21</v>
+      </c>
       <c r="H42" s="21">
         <v>87.096774193548384</v>
       </c>
@@ -3062,7 +3147,9 @@
       <c r="F43" s="17">
         <v>49</v>
       </c>
-      <c r="G43" s="11"/>
+      <c r="G43" s="23">
+        <v>46</v>
+      </c>
       <c r="H43" s="21">
         <v>61.29032258064516</v>
       </c>
@@ -3086,7 +3173,9 @@
       <c r="F44" s="17">
         <v>76</v>
       </c>
-      <c r="G44" s="11"/>
+      <c r="G44" s="23">
+        <v>32</v>
+      </c>
       <c r="H44" s="21">
         <v>87.096774193548384</v>
       </c>
@@ -3110,7 +3199,9 @@
       <c r="F45" s="17">
         <v>52</v>
       </c>
-      <c r="G45" s="11"/>
+      <c r="G45" s="23">
+        <v>36</v>
+      </c>
       <c r="H45" s="21">
         <v>74.193548387096769</v>
       </c>
@@ -3134,7 +3225,9 @@
       <c r="F46" s="17">
         <v>45</v>
       </c>
-      <c r="G46" s="11"/>
+      <c r="G46" s="23">
+        <v>22</v>
+      </c>
       <c r="H46" s="21">
         <v>90.322580645161281</v>
       </c>
@@ -3158,7 +3251,9 @@
       <c r="F47" s="17">
         <v>86.5</v>
       </c>
-      <c r="G47" s="11"/>
+      <c r="G47" s="23">
+        <v>50</v>
+      </c>
       <c r="H47" s="21">
         <v>80.645161290322577</v>
       </c>
@@ -3182,7 +3277,9 @@
       <c r="F48" s="17">
         <v>43</v>
       </c>
-      <c r="G48" s="11"/>
+      <c r="G48" s="23">
+        <v>34</v>
+      </c>
       <c r="H48" s="21">
         <v>90.322580645161281</v>
       </c>
@@ -3206,7 +3303,9 @@
       <c r="F49" s="17">
         <v>60</v>
       </c>
-      <c r="G49" s="11"/>
+      <c r="G49" s="23">
+        <v>46</v>
+      </c>
       <c r="H49" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -3230,7 +3329,9 @@
       <c r="F50" s="17">
         <v>73.5</v>
       </c>
-      <c r="G50" s="11"/>
+      <c r="G50" s="23">
+        <v>22</v>
+      </c>
       <c r="H50" s="21">
         <v>83.870967741935488</v>
       </c>
@@ -3243,10 +3344,10 @@
         <v>107</v>
       </c>
       <c r="C51" s="11">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D51" s="22">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E51" s="17">
         <v>44</v>
@@ -3254,7 +3355,9 @@
       <c r="F51" s="17">
         <v>52.5</v>
       </c>
-      <c r="G51" s="11"/>
+      <c r="G51" s="23">
+        <v>18</v>
+      </c>
       <c r="H51" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -3278,7 +3381,9 @@
       <c r="F52" s="17">
         <v>60.5</v>
       </c>
-      <c r="G52" s="11"/>
+      <c r="G52" s="23">
+        <v>27</v>
+      </c>
       <c r="H52" s="21">
         <v>80.645161290322577</v>
       </c>
@@ -3302,7 +3407,9 @@
       <c r="F53" s="17">
         <v>63.5</v>
       </c>
-      <c r="G53" s="11"/>
+      <c r="G53" s="23">
+        <v>45</v>
+      </c>
       <c r="H53" s="21">
         <v>96.774193548387103</v>
       </c>
@@ -3326,7 +3433,9 @@
       <c r="F54" s="17">
         <v>17.5</v>
       </c>
-      <c r="G54" s="11"/>
+      <c r="G54" s="23">
+        <v>23</v>
+      </c>
       <c r="H54" s="21">
         <v>80.645161290322577</v>
       </c>
@@ -3350,7 +3459,9 @@
       <c r="F55" s="17">
         <v>75</v>
       </c>
-      <c r="G55" s="11"/>
+      <c r="G55" s="23">
+        <v>35</v>
+      </c>
       <c r="H55" s="21">
         <v>90.322580645161281</v>
       </c>
@@ -3374,7 +3485,9 @@
       <c r="F56" s="17">
         <v>57</v>
       </c>
-      <c r="G56" s="11"/>
+      <c r="G56" s="23">
+        <v>42</v>
+      </c>
       <c r="H56" s="21">
         <v>83.870967741935488</v>
       </c>
@@ -3398,7 +3511,9 @@
       <c r="F57" s="17">
         <v>76.5</v>
       </c>
-      <c r="G57" s="11"/>
+      <c r="G57" s="23">
+        <v>29</v>
+      </c>
       <c r="H57" s="21">
         <v>90.322580645161281</v>
       </c>
@@ -3422,7 +3537,9 @@
       <c r="F58" s="17">
         <v>51.5</v>
       </c>
-      <c r="G58" s="11"/>
+      <c r="G58" s="23">
+        <v>15</v>
+      </c>
       <c r="H58" s="21">
         <v>64.516129032258064</v>
       </c>
@@ -3446,7 +3563,9 @@
       <c r="F59" s="17">
         <v>85.5</v>
       </c>
-      <c r="G59" s="11"/>
+      <c r="G59" s="23">
+        <v>34</v>
+      </c>
       <c r="H59" s="21">
         <v>83.870967741935488</v>
       </c>
@@ -3470,7 +3589,9 @@
       <c r="F60" s="17">
         <v>59.5</v>
       </c>
-      <c r="G60" s="11"/>
+      <c r="G60" s="23">
+        <v>75</v>
+      </c>
       <c r="H60" s="21">
         <v>96.774193548387103</v>
       </c>
@@ -3494,7 +3615,9 @@
       <c r="F61" s="17">
         <v>57.5</v>
       </c>
-      <c r="G61" s="11"/>
+      <c r="G61" s="23">
+        <v>35</v>
+      </c>
       <c r="H61" s="21">
         <v>93.548387096774192</v>
       </c>
@@ -3518,7 +3641,9 @@
       <c r="F62" s="17">
         <v>48</v>
       </c>
-      <c r="G62" s="11"/>
+      <c r="G62" s="23">
+        <v>28</v>
+      </c>
       <c r="H62" s="21">
         <v>90.322580645161281</v>
       </c>
@@ -3542,7 +3667,9 @@
       <c r="F63" s="17">
         <v>95</v>
       </c>
-      <c r="G63" s="11"/>
+      <c r="G63" s="23">
+        <v>56</v>
+      </c>
       <c r="H63" s="21">
         <v>93.548387096774192</v>
       </c>
@@ -3566,7 +3693,9 @@
       <c r="F64" s="17">
         <v>56</v>
       </c>
-      <c r="G64" s="11"/>
+      <c r="G64" s="23">
+        <v>47</v>
+      </c>
       <c r="H64" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -3590,7 +3719,9 @@
       <c r="F65" s="17">
         <v>79</v>
       </c>
-      <c r="G65" s="11"/>
+      <c r="G65" s="23">
+        <v>53</v>
+      </c>
       <c r="H65" s="21">
         <v>90.322580645161281</v>
       </c>
@@ -3614,7 +3745,9 @@
       <c r="F66" s="17">
         <v>59</v>
       </c>
-      <c r="G66" s="11"/>
+      <c r="G66" s="23">
+        <v>15</v>
+      </c>
       <c r="H66" s="21">
         <v>93.548387096774192</v>
       </c>
@@ -3638,7 +3771,9 @@
       <c r="F67" s="17">
         <v>79.5</v>
       </c>
-      <c r="G67" s="11"/>
+      <c r="G67" s="23">
+        <v>43</v>
+      </c>
       <c r="H67" s="21">
         <v>87.096774193548384</v>
       </c>
@@ -3662,7 +3797,9 @@
       <c r="F68" s="17">
         <v>20</v>
       </c>
-      <c r="G68" s="11"/>
+      <c r="G68" s="23">
+        <v>31</v>
+      </c>
       <c r="H68" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -3686,7 +3823,9 @@
       <c r="F69" s="17">
         <v>74</v>
       </c>
-      <c r="G69" s="11"/>
+      <c r="G69" s="23">
+        <v>40</v>
+      </c>
       <c r="H69" s="21">
         <v>93.548387096774192</v>
       </c>
@@ -3710,7 +3849,9 @@
       <c r="F70" s="17">
         <v>50</v>
       </c>
-      <c r="G70" s="11"/>
+      <c r="G70" s="23">
+        <v>62</v>
+      </c>
       <c r="H70" s="21">
         <v>93.548387096774192</v>
       </c>
@@ -3734,7 +3875,9 @@
       <c r="F71" s="17">
         <v>40.5</v>
       </c>
-      <c r="G71" s="11"/>
+      <c r="G71" s="23">
+        <v>51</v>
+      </c>
       <c r="H71" s="21">
         <v>96.774193548387103</v>
       </c>
@@ -3758,7 +3901,9 @@
       <c r="F72" s="17">
         <v>75.5</v>
       </c>
-      <c r="G72" s="11"/>
+      <c r="G72" s="23">
+        <v>31</v>
+      </c>
       <c r="H72" s="21">
         <v>74.193548387096769</v>
       </c>
@@ -3782,7 +3927,9 @@
       <c r="F73" s="17">
         <v>57.5</v>
       </c>
-      <c r="G73" s="11"/>
+      <c r="G73" s="23">
+        <v>23</v>
+      </c>
       <c r="H73" s="21">
         <v>74.193548387096769</v>
       </c>
@@ -3806,7 +3953,9 @@
       <c r="F74" s="17">
         <v>30</v>
       </c>
-      <c r="G74" s="11"/>
+      <c r="G74" s="23">
+        <v>28</v>
+      </c>
       <c r="H74" s="21">
         <v>38.70967741935484</v>
       </c>
@@ -3830,7 +3979,9 @@
       <c r="F75" s="17">
         <v>49.5</v>
       </c>
-      <c r="G75" s="11"/>
+      <c r="G75" s="23">
+        <v>26</v>
+      </c>
       <c r="H75" s="21">
         <v>74.193548387096769</v>
       </c>
@@ -3854,7 +4005,9 @@
       <c r="F76" s="17">
         <v>88.5</v>
       </c>
-      <c r="G76" s="11"/>
+      <c r="G76" s="23">
+        <v>58</v>
+      </c>
       <c r="H76" s="21">
         <v>96.774193548387103</v>
       </c>
@@ -3878,7 +4031,9 @@
       <c r="F77" s="17">
         <v>69</v>
       </c>
-      <c r="G77" s="11"/>
+      <c r="G77" s="23">
+        <v>39</v>
+      </c>
       <c r="H77" s="21">
         <v>90.322580645161281</v>
       </c>
@@ -3902,7 +4057,9 @@
       <c r="F78" s="17">
         <v>69.5</v>
       </c>
-      <c r="G78" s="11"/>
+      <c r="G78" s="23">
+        <v>24</v>
+      </c>
       <c r="H78" s="21">
         <v>80.645161290322577</v>
       </c>
@@ -3926,7 +4083,9 @@
       <c r="F79" s="17">
         <v>64</v>
       </c>
-      <c r="G79" s="11"/>
+      <c r="G79" s="23">
+        <v>45</v>
+      </c>
       <c r="H79" s="21">
         <v>87.096774193548384</v>
       </c>
@@ -3950,7 +4109,9 @@
       <c r="F80" s="17">
         <v>67.5</v>
       </c>
-      <c r="G80" s="11"/>
+      <c r="G80" s="23">
+        <v>19</v>
+      </c>
       <c r="H80" s="21">
         <v>80.645161290322577</v>
       </c>
@@ -3974,7 +4135,9 @@
       <c r="F81" s="17">
         <v>76.5</v>
       </c>
-      <c r="G81" s="11"/>
+      <c r="G81" s="23">
+        <v>48</v>
+      </c>
       <c r="H81" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -3998,7 +4161,9 @@
       <c r="F82" s="17">
         <v>72</v>
       </c>
-      <c r="G82" s="11"/>
+      <c r="G82" s="23">
+        <v>45</v>
+      </c>
       <c r="H82" s="21">
         <v>90.322580645161281</v>
       </c>
@@ -4022,7 +4187,9 @@
       <c r="F83" s="17">
         <v>62.5</v>
       </c>
-      <c r="G83" s="11"/>
+      <c r="G83" s="23">
+        <v>29</v>
+      </c>
       <c r="H83" s="21">
         <v>90.322580645161281</v>
       </c>
@@ -4046,7 +4213,9 @@
       <c r="F84" s="17">
         <v>45.5</v>
       </c>
-      <c r="G84" s="11"/>
+      <c r="G84" s="23">
+        <v>36</v>
+      </c>
       <c r="H84" s="21">
         <v>93.548387096774192</v>
       </c>
@@ -4070,7 +4239,9 @@
       <c r="F85" s="17">
         <v>55.5</v>
       </c>
-      <c r="G85" s="11"/>
+      <c r="G85" s="23">
+        <v>41</v>
+      </c>
       <c r="H85" s="21">
         <v>93.548387096774192</v>
       </c>
@@ -4094,7 +4265,9 @@
       <c r="F86" s="17">
         <v>72.5</v>
       </c>
-      <c r="G86" s="11"/>
+      <c r="G86" s="23">
+        <v>17</v>
+      </c>
       <c r="H86" s="21">
         <v>74.193548387096769</v>
       </c>
@@ -4118,7 +4291,9 @@
       <c r="F87" s="17">
         <v>39</v>
       </c>
-      <c r="G87" s="11"/>
+      <c r="G87" s="23">
+        <v>32</v>
+      </c>
       <c r="H87" s="21">
         <v>96.774193548387103</v>
       </c>
@@ -4142,7 +4317,9 @@
       <c r="F88" s="17">
         <v>17.5</v>
       </c>
-      <c r="G88" s="11"/>
+      <c r="G88" s="23">
+        <v>23</v>
+      </c>
       <c r="H88" s="21">
         <v>54.838709677419352</v>
       </c>
@@ -4166,7 +4343,9 @@
       <c r="F89" s="17">
         <v>47.5</v>
       </c>
-      <c r="G89" s="11"/>
+      <c r="G89" s="23">
+        <v>38</v>
+      </c>
       <c r="H89" s="21">
         <v>90.322580645161281</v>
       </c>
@@ -4190,7 +4369,9 @@
       <c r="F90" s="17">
         <v>60.5</v>
       </c>
-      <c r="G90" s="11"/>
+      <c r="G90" s="23">
+        <v>38</v>
+      </c>
       <c r="H90" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -4214,7 +4395,9 @@
       <c r="F91" s="17">
         <v>92.5</v>
       </c>
-      <c r="G91" s="11"/>
+      <c r="G91" s="23">
+        <v>88</v>
+      </c>
       <c r="H91" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -4238,7 +4421,9 @@
       <c r="F92" s="17">
         <v>70</v>
       </c>
-      <c r="G92" s="11"/>
+      <c r="G92" s="23">
+        <v>52</v>
+      </c>
       <c r="H92" s="21">
         <v>87.096774193548384</v>
       </c>
@@ -4262,7 +4447,9 @@
       <c r="F93" s="17">
         <v>40</v>
       </c>
-      <c r="G93" s="11"/>
+      <c r="G93" s="23">
+        <v>32</v>
+      </c>
       <c r="H93" s="21">
         <v>87.096774193548384</v>
       </c>
@@ -4286,7 +4473,9 @@
       <c r="F94" s="17">
         <v>0</v>
       </c>
-      <c r="G94" s="11"/>
+      <c r="G94" s="23">
+        <v>17</v>
+      </c>
       <c r="H94" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -4310,7 +4499,9 @@
       <c r="F95" s="17">
         <v>64.5</v>
       </c>
-      <c r="G95" s="11"/>
+      <c r="G95" s="23">
+        <v>41</v>
+      </c>
       <c r="H95" s="21">
         <v>45.161290322580641</v>
       </c>
@@ -4334,7 +4525,9 @@
       <c r="F96" s="17">
         <v>33.5</v>
       </c>
-      <c r="G96" s="11"/>
+      <c r="G96" s="23">
+        <v>25</v>
+      </c>
       <c r="H96" s="21">
         <v>87.096774193548384</v>
       </c>
@@ -4358,7 +4551,9 @@
       <c r="F97" s="17">
         <v>71.5</v>
       </c>
-      <c r="G97" s="11"/>
+      <c r="G97" s="23">
+        <v>30</v>
+      </c>
       <c r="H97" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -4382,7 +4577,9 @@
       <c r="F98" s="17">
         <v>78.5</v>
       </c>
-      <c r="G98" s="11"/>
+      <c r="G98" s="23">
+        <v>41</v>
+      </c>
       <c r="H98" s="21">
         <v>74.193548387096769</v>
       </c>
@@ -4406,7 +4603,9 @@
       <c r="F99" s="17">
         <v>70.5</v>
       </c>
-      <c r="G99" s="11"/>
+      <c r="G99" s="23">
+        <v>31</v>
+      </c>
       <c r="H99" s="21">
         <v>90.322580645161281</v>
       </c>
@@ -4430,7 +4629,9 @@
       <c r="F100" s="17">
         <v>65.5</v>
       </c>
-      <c r="G100" s="11"/>
+      <c r="G100" s="23">
+        <v>19</v>
+      </c>
       <c r="H100" s="21">
         <v>87.096774193548384</v>
       </c>
@@ -4454,7 +4655,9 @@
       <c r="F101" s="17">
         <v>46</v>
       </c>
-      <c r="G101" s="11"/>
+      <c r="G101" s="23">
+        <v>17</v>
+      </c>
       <c r="H101" s="21">
         <v>87.096774193548384</v>
       </c>
@@ -4478,7 +4681,9 @@
       <c r="F102" s="17">
         <v>28</v>
       </c>
-      <c r="G102" s="11"/>
+      <c r="G102" s="23">
+        <v>10</v>
+      </c>
       <c r="H102" s="21">
         <v>51.612903225806448</v>
       </c>
@@ -4502,7 +4707,9 @@
       <c r="F103" s="17" t="s">
         <v>482</v>
       </c>
-      <c r="G103" s="11"/>
+      <c r="G103" s="23" t="s">
+        <v>482</v>
+      </c>
       <c r="H103" s="21">
         <v>16.129032258064516</v>
       </c>
@@ -4526,7 +4733,9 @@
       <c r="F104" s="17">
         <v>55</v>
       </c>
-      <c r="G104" s="11"/>
+      <c r="G104" s="23">
+        <v>61</v>
+      </c>
       <c r="H104" s="21">
         <v>83.870967741935488</v>
       </c>
@@ -4550,7 +4759,9 @@
       <c r="F105" s="17">
         <v>42</v>
       </c>
-      <c r="G105" s="11"/>
+      <c r="G105" s="23">
+        <v>48</v>
+      </c>
       <c r="H105" s="21">
         <v>80.645161290322577</v>
       </c>
@@ -4574,7 +4785,9 @@
       <c r="F106" s="17">
         <v>48</v>
       </c>
-      <c r="G106" s="11"/>
+      <c r="G106" s="23">
+        <v>28</v>
+      </c>
       <c r="H106" s="21">
         <v>45.161290322580641</v>
       </c>
@@ -4598,7 +4811,9 @@
       <c r="F107" s="17">
         <v>22</v>
       </c>
-      <c r="G107" s="11"/>
+      <c r="G107" s="23">
+        <v>35</v>
+      </c>
       <c r="H107" s="21">
         <v>83.870967741935488</v>
       </c>
@@ -4622,7 +4837,9 @@
       <c r="F108" s="17">
         <v>25</v>
       </c>
-      <c r="G108" s="11"/>
+      <c r="G108" s="23">
+        <v>41</v>
+      </c>
       <c r="H108" s="21">
         <v>93.548387096774192</v>
       </c>
@@ -4635,10 +4852,10 @@
         <v>223</v>
       </c>
       <c r="C109" s="11">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D109" s="22">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E109" s="17">
         <v>60</v>
@@ -4646,7 +4863,9 @@
       <c r="F109" s="17">
         <v>44.5</v>
       </c>
-      <c r="G109" s="11"/>
+      <c r="G109" s="23">
+        <v>21</v>
+      </c>
       <c r="H109" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -4670,7 +4889,9 @@
       <c r="F110" s="17">
         <v>78</v>
       </c>
-      <c r="G110" s="11"/>
+      <c r="G110" s="23">
+        <v>59</v>
+      </c>
       <c r="H110" s="21">
         <v>87.096774193548384</v>
       </c>
@@ -4694,7 +4915,9 @@
       <c r="F111" s="17">
         <v>64</v>
       </c>
-      <c r="G111" s="11"/>
+      <c r="G111" s="23">
+        <v>40</v>
+      </c>
       <c r="H111" s="21">
         <v>58.064516129032263</v>
       </c>
@@ -4718,7 +4941,9 @@
       <c r="F112" s="17">
         <v>49</v>
       </c>
-      <c r="G112" s="11"/>
+      <c r="G112" s="23">
+        <v>35</v>
+      </c>
       <c r="H112" s="21">
         <v>48.387096774193552</v>
       </c>
@@ -4742,7 +4967,9 @@
       <c r="F113" s="17">
         <v>44</v>
       </c>
-      <c r="G113" s="11"/>
+      <c r="G113" s="23">
+        <v>46</v>
+      </c>
       <c r="H113" s="21">
         <v>83.870967741935488</v>
       </c>
@@ -4766,7 +4993,9 @@
       <c r="F114" s="17">
         <v>58.5</v>
       </c>
-      <c r="G114" s="11"/>
+      <c r="G114" s="23">
+        <v>55</v>
+      </c>
       <c r="H114" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -4790,7 +5019,9 @@
       <c r="F115" s="17">
         <v>64</v>
       </c>
-      <c r="G115" s="11"/>
+      <c r="G115" s="23">
+        <v>49</v>
+      </c>
       <c r="H115" s="21">
         <v>90.322580645161281</v>
       </c>
@@ -4814,7 +5045,9 @@
       <c r="F116" s="17">
         <v>40</v>
       </c>
-      <c r="G116" s="11"/>
+      <c r="G116" s="23">
+        <v>63</v>
+      </c>
       <c r="H116" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -4838,7 +5071,9 @@
       <c r="F117" s="17">
         <v>83.5</v>
       </c>
-      <c r="G117" s="11"/>
+      <c r="G117" s="23">
+        <v>43</v>
+      </c>
       <c r="H117" s="21">
         <v>83.870967741935488</v>
       </c>
@@ -4862,7 +5097,9 @@
       <c r="F118" s="17">
         <v>82</v>
       </c>
-      <c r="G118" s="11"/>
+      <c r="G118" s="23">
+        <v>24</v>
+      </c>
       <c r="H118" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -4886,7 +5123,9 @@
       <c r="F119" s="17">
         <v>56.5</v>
       </c>
-      <c r="G119" s="11"/>
+      <c r="G119" s="23">
+        <v>43</v>
+      </c>
       <c r="H119" s="21">
         <v>80.645161290322577</v>
       </c>
@@ -4910,7 +5149,9 @@
       <c r="F120" s="17">
         <v>42.5</v>
       </c>
-      <c r="G120" s="11"/>
+      <c r="G120" s="23">
+        <v>37</v>
+      </c>
       <c r="H120" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -4934,7 +5175,9 @@
       <c r="F121" s="17">
         <v>59</v>
       </c>
-      <c r="G121" s="11"/>
+      <c r="G121" s="23">
+        <v>28</v>
+      </c>
       <c r="H121" s="21">
         <v>67.741935483870961</v>
       </c>
@@ -4958,7 +5201,9 @@
       <c r="F122" s="17">
         <v>41.5</v>
       </c>
-      <c r="G122" s="11"/>
+      <c r="G122" s="23">
+        <v>19</v>
+      </c>
       <c r="H122" s="21">
         <v>87.096774193548384</v>
       </c>
@@ -4982,7 +5227,9 @@
       <c r="F123" s="17">
         <v>59</v>
       </c>
-      <c r="G123" s="11"/>
+      <c r="G123" s="23">
+        <v>34</v>
+      </c>
       <c r="H123" s="21">
         <v>83.870967741935488</v>
       </c>
@@ -5006,7 +5253,9 @@
       <c r="F124" s="17">
         <v>41.5</v>
       </c>
-      <c r="G124" s="11"/>
+      <c r="G124" s="23">
+        <v>17</v>
+      </c>
       <c r="H124" s="21">
         <v>83.870967741935488</v>
       </c>
@@ -5030,7 +5279,9 @@
       <c r="F125" s="17">
         <v>77.5</v>
       </c>
-      <c r="G125" s="11"/>
+      <c r="G125" s="23">
+        <v>73</v>
+      </c>
       <c r="H125" s="21">
         <v>96.774193548387103</v>
       </c>
@@ -5054,7 +5305,9 @@
       <c r="F126" s="17">
         <v>81.5</v>
       </c>
-      <c r="G126" s="11"/>
+      <c r="G126" s="23">
+        <v>43</v>
+      </c>
       <c r="H126" s="21">
         <v>80.645161290322577</v>
       </c>
@@ -5078,7 +5331,9 @@
       <c r="F127" s="17">
         <v>51.5</v>
       </c>
-      <c r="G127" s="11"/>
+      <c r="G127" s="23">
+        <v>45</v>
+      </c>
       <c r="H127" s="21">
         <v>83.870967741935488</v>
       </c>
@@ -5102,7 +5357,9 @@
       <c r="F128" s="17">
         <v>48.5</v>
       </c>
-      <c r="G128" s="11"/>
+      <c r="G128" s="23">
+        <v>56</v>
+      </c>
       <c r="H128" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -5126,7 +5383,9 @@
       <c r="F129" s="17">
         <v>56.5</v>
       </c>
-      <c r="G129" s="11"/>
+      <c r="G129" s="23">
+        <v>27</v>
+      </c>
       <c r="H129" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -5150,7 +5409,9 @@
       <c r="F130" s="17">
         <v>37</v>
       </c>
-      <c r="G130" s="11"/>
+      <c r="G130" s="23">
+        <v>33</v>
+      </c>
       <c r="H130" s="21">
         <v>67.741935483870961</v>
       </c>
@@ -5174,7 +5435,9 @@
       <c r="F131" s="17">
         <v>57</v>
       </c>
-      <c r="G131" s="11"/>
+      <c r="G131" s="23">
+        <v>30</v>
+      </c>
       <c r="H131" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -5198,7 +5461,9 @@
       <c r="F132" s="17">
         <v>50.5</v>
       </c>
-      <c r="G132" s="11"/>
+      <c r="G132" s="23">
+        <v>42</v>
+      </c>
       <c r="H132" s="21">
         <v>83.870967741935488</v>
       </c>
@@ -5222,7 +5487,9 @@
       <c r="F133" s="17">
         <v>60.5</v>
       </c>
-      <c r="G133" s="11"/>
+      <c r="G133" s="23">
+        <v>54</v>
+      </c>
       <c r="H133" s="21">
         <v>93.548387096774192</v>
       </c>
@@ -5246,7 +5513,9 @@
       <c r="F134" s="17">
         <v>67.5</v>
       </c>
-      <c r="G134" s="11"/>
+      <c r="G134" s="23">
+        <v>34</v>
+      </c>
       <c r="H134" s="21">
         <v>96.774193548387103</v>
       </c>
@@ -5270,7 +5539,9 @@
       <c r="F135" s="17">
         <v>42</v>
       </c>
-      <c r="G135" s="11"/>
+      <c r="G135" s="23">
+        <v>39</v>
+      </c>
       <c r="H135" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -5294,7 +5565,9 @@
       <c r="F136" s="17">
         <v>30.5</v>
       </c>
-      <c r="G136" s="11"/>
+      <c r="G136" s="23">
+        <v>29</v>
+      </c>
       <c r="H136" s="21">
         <v>80.645161290322577</v>
       </c>
@@ -5318,7 +5591,9 @@
       <c r="F137" s="17">
         <v>35.5</v>
       </c>
-      <c r="G137" s="11"/>
+      <c r="G137" s="23">
+        <v>40</v>
+      </c>
       <c r="H137" s="21">
         <v>90.322580645161281</v>
       </c>
@@ -5342,7 +5617,9 @@
       <c r="F138" s="17">
         <v>56</v>
       </c>
-      <c r="G138" s="11"/>
+      <c r="G138" s="23">
+        <v>44</v>
+      </c>
       <c r="H138" s="21">
         <v>93.548387096774192</v>
       </c>
@@ -5366,7 +5643,9 @@
       <c r="F139" s="17">
         <v>0</v>
       </c>
-      <c r="G139" s="11"/>
+      <c r="G139" s="23">
+        <v>39</v>
+      </c>
       <c r="H139" s="21">
         <v>67.741935483870961</v>
       </c>
@@ -5390,7 +5669,9 @@
       <c r="F140" s="17">
         <v>17.5</v>
       </c>
-      <c r="G140" s="11"/>
+      <c r="G140" s="23">
+        <v>29</v>
+      </c>
       <c r="H140" s="21">
         <v>67.741935483870961</v>
       </c>
@@ -5414,7 +5695,9 @@
       <c r="F141" s="17">
         <v>62</v>
       </c>
-      <c r="G141" s="11"/>
+      <c r="G141" s="23">
+        <v>15</v>
+      </c>
       <c r="H141" s="21">
         <v>54.838709677419352</v>
       </c>
@@ -5438,7 +5721,9 @@
       <c r="F142" s="17">
         <v>50.5</v>
       </c>
-      <c r="G142" s="11"/>
+      <c r="G142" s="23">
+        <v>35</v>
+      </c>
       <c r="H142" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -5462,7 +5747,9 @@
       <c r="F143" s="17">
         <v>72.5</v>
       </c>
-      <c r="G143" s="11"/>
+      <c r="G143" s="23">
+        <v>66</v>
+      </c>
       <c r="H143" s="21">
         <v>80.645161290322577</v>
       </c>
@@ -5486,7 +5773,9 @@
       <c r="F144" s="17">
         <v>57.5</v>
       </c>
-      <c r="G144" s="11"/>
+      <c r="G144" s="23">
+        <v>37</v>
+      </c>
       <c r="H144" s="21">
         <v>90.322580645161281</v>
       </c>
@@ -5510,7 +5799,9 @@
       <c r="F145" s="17">
         <v>71.5</v>
       </c>
-      <c r="G145" s="11"/>
+      <c r="G145" s="23">
+        <v>29</v>
+      </c>
       <c r="H145" s="21">
         <v>87.096774193548384</v>
       </c>
@@ -5534,7 +5825,9 @@
       <c r="F146" s="17">
         <v>76.5</v>
       </c>
-      <c r="G146" s="11"/>
+      <c r="G146" s="23">
+        <v>45</v>
+      </c>
       <c r="H146" s="21">
         <v>80.645161290322577</v>
       </c>
@@ -5558,7 +5851,9 @@
       <c r="F147" s="17">
         <v>60</v>
       </c>
-      <c r="G147" s="11"/>
+      <c r="G147" s="23">
+        <v>37</v>
+      </c>
       <c r="H147" s="21">
         <v>83.870967741935488</v>
       </c>
@@ -5582,7 +5877,9 @@
       <c r="F148" s="17">
         <v>40</v>
       </c>
-      <c r="G148" s="11"/>
+      <c r="G148" s="23">
+        <v>63</v>
+      </c>
       <c r="H148" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -5606,7 +5903,9 @@
       <c r="F149" s="17">
         <v>56</v>
       </c>
-      <c r="G149" s="11"/>
+      <c r="G149" s="23">
+        <v>48</v>
+      </c>
       <c r="H149" s="21">
         <v>80.645161290322577</v>
       </c>
@@ -5630,7 +5929,9 @@
       <c r="F150" s="17">
         <v>68</v>
       </c>
-      <c r="G150" s="11"/>
+      <c r="G150" s="23">
+        <v>30</v>
+      </c>
       <c r="H150" s="21">
         <v>61.29032258064516</v>
       </c>
@@ -5654,7 +5955,9 @@
       <c r="F151" s="17">
         <v>46.5</v>
       </c>
-      <c r="G151" s="11"/>
+      <c r="G151" s="23">
+        <v>17</v>
+      </c>
       <c r="H151" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -5678,7 +5981,9 @@
       <c r="F152" s="17">
         <v>26.5</v>
       </c>
-      <c r="G152" s="11"/>
+      <c r="G152" s="23">
+        <v>26</v>
+      </c>
       <c r="H152" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -5702,7 +6007,9 @@
       <c r="F153" s="17">
         <v>61</v>
       </c>
-      <c r="G153" s="11"/>
+      <c r="G153" s="23">
+        <v>31</v>
+      </c>
       <c r="H153" s="21">
         <v>51.612903225806448</v>
       </c>
@@ -5726,7 +6033,9 @@
       <c r="F154" s="17">
         <v>60</v>
       </c>
-      <c r="G154" s="11"/>
+      <c r="G154" s="23">
+        <v>65</v>
+      </c>
       <c r="H154" s="21">
         <v>80.645161290322577</v>
       </c>
@@ -5750,7 +6059,9 @@
       <c r="F155" s="17">
         <v>28</v>
       </c>
-      <c r="G155" s="11"/>
+      <c r="G155" s="23">
+        <v>36</v>
+      </c>
       <c r="H155" s="21">
         <v>64.516129032258064</v>
       </c>
@@ -5774,7 +6085,9 @@
       <c r="F156" s="17">
         <v>53.5</v>
       </c>
-      <c r="G156" s="11"/>
+      <c r="G156" s="23">
+        <v>34</v>
+      </c>
       <c r="H156" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -5798,7 +6111,9 @@
       <c r="F157" s="17">
         <v>53</v>
       </c>
-      <c r="G157" s="11"/>
+      <c r="G157" s="23">
+        <v>39</v>
+      </c>
       <c r="H157" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -5822,7 +6137,9 @@
       <c r="F158" s="17">
         <v>40.5</v>
       </c>
-      <c r="G158" s="11"/>
+      <c r="G158" s="23">
+        <v>45</v>
+      </c>
       <c r="H158" s="21">
         <v>67.741935483870961</v>
       </c>
@@ -5846,7 +6163,9 @@
       <c r="F159" s="17">
         <v>33.5</v>
       </c>
-      <c r="G159" s="11"/>
+      <c r="G159" s="23">
+        <v>43</v>
+      </c>
       <c r="H159" s="21">
         <v>74.193548387096769</v>
       </c>
@@ -5870,7 +6189,9 @@
       <c r="F160" s="17">
         <v>73</v>
       </c>
-      <c r="G160" s="11"/>
+      <c r="G160" s="23">
+        <v>40</v>
+      </c>
       <c r="H160" s="21">
         <v>100</v>
       </c>
@@ -5894,7 +6215,9 @@
       <c r="F161" s="17">
         <v>51.5</v>
       </c>
-      <c r="G161" s="11"/>
+      <c r="G161" s="23">
+        <v>39</v>
+      </c>
       <c r="H161" s="21">
         <v>74.193548387096769</v>
       </c>
@@ -5918,7 +6241,9 @@
       <c r="F162" s="17">
         <v>40</v>
       </c>
-      <c r="G162" s="11"/>
+      <c r="G162" s="23">
+        <v>18</v>
+      </c>
       <c r="H162" s="21">
         <v>74.193548387096769</v>
       </c>
@@ -5942,7 +6267,9 @@
       <c r="F163" s="17">
         <v>60</v>
       </c>
-      <c r="G163" s="11"/>
+      <c r="G163" s="23">
+        <v>45</v>
+      </c>
       <c r="H163" s="21">
         <v>87.096774193548384</v>
       </c>
@@ -5966,7 +6293,9 @@
       <c r="F164" s="17">
         <v>66.5</v>
       </c>
-      <c r="G164" s="11"/>
+      <c r="G164" s="23">
+        <v>45</v>
+      </c>
       <c r="H164" s="21">
         <v>83.870967741935488</v>
       </c>
@@ -5990,7 +6319,9 @@
       <c r="F165" s="17">
         <v>72</v>
       </c>
-      <c r="G165" s="11"/>
+      <c r="G165" s="23">
+        <v>69</v>
+      </c>
       <c r="H165" s="21">
         <v>66.666666666666657</v>
       </c>
@@ -6014,7 +6345,9 @@
       <c r="F166" s="17">
         <v>64</v>
       </c>
-      <c r="G166" s="11"/>
+      <c r="G166" s="23">
+        <v>43</v>
+      </c>
       <c r="H166" s="21">
         <v>80.645161290322577</v>
       </c>
@@ -6038,7 +6371,9 @@
       <c r="F167" s="17">
         <v>40.5</v>
       </c>
-      <c r="G167" s="11"/>
+      <c r="G167" s="23">
+        <v>27</v>
+      </c>
       <c r="H167" s="21">
         <v>80.645161290322577</v>
       </c>
@@ -6062,7 +6397,9 @@
       <c r="F168" s="17">
         <v>62</v>
       </c>
-      <c r="G168" s="11"/>
+      <c r="G168" s="23">
+        <v>36</v>
+      </c>
       <c r="H168" s="21">
         <v>90.322580645161281</v>
       </c>
@@ -6086,7 +6423,9 @@
       <c r="F169" s="17">
         <v>40</v>
       </c>
-      <c r="G169" s="11"/>
+      <c r="G169" s="23">
+        <v>34</v>
+      </c>
       <c r="H169" s="21">
         <v>83.870967741935488</v>
       </c>
@@ -6110,7 +6449,9 @@
       <c r="F170" s="17">
         <v>79</v>
       </c>
-      <c r="G170" s="11"/>
+      <c r="G170" s="23">
+        <v>18</v>
+      </c>
       <c r="H170" s="21">
         <v>74.193548387096769</v>
       </c>
@@ -6134,7 +6475,9 @@
       <c r="F171" s="17">
         <v>75</v>
       </c>
-      <c r="G171" s="11"/>
+      <c r="G171" s="23">
+        <v>56</v>
+      </c>
       <c r="H171" s="21">
         <v>87.096774193548384</v>
       </c>
@@ -6158,7 +6501,9 @@
       <c r="F172" s="17">
         <v>74.5</v>
       </c>
-      <c r="G172" s="11"/>
+      <c r="G172" s="23">
+        <v>69</v>
+      </c>
       <c r="H172" s="21">
         <v>83.870967741935488</v>
       </c>
@@ -6182,7 +6527,9 @@
       <c r="F173" s="17">
         <v>59.5</v>
       </c>
-      <c r="G173" s="11"/>
+      <c r="G173" s="23">
+        <v>45</v>
+      </c>
       <c r="H173" s="21">
         <v>80.645161290322577</v>
       </c>
@@ -6206,7 +6553,9 @@
       <c r="F174" s="17">
         <v>48.5</v>
       </c>
-      <c r="G174" s="11"/>
+      <c r="G174" s="23">
+        <v>60</v>
+      </c>
       <c r="H174" s="21">
         <v>80.645161290322577</v>
       </c>
@@ -6230,7 +6579,9 @@
       <c r="F175" s="17">
         <v>23.5</v>
       </c>
-      <c r="G175" s="11"/>
+      <c r="G175" s="23">
+        <v>46</v>
+      </c>
       <c r="H175" s="21">
         <v>74.193548387096769</v>
       </c>
@@ -6254,7 +6605,9 @@
       <c r="F176" s="17">
         <v>69.5</v>
       </c>
-      <c r="G176" s="11"/>
+      <c r="G176" s="23">
+        <v>55</v>
+      </c>
       <c r="H176" s="21">
         <v>74.193548387096769</v>
       </c>
@@ -6278,7 +6631,9 @@
       <c r="F177" s="17">
         <v>66.5</v>
       </c>
-      <c r="G177" s="11"/>
+      <c r="G177" s="23">
+        <v>42</v>
+      </c>
       <c r="H177" s="21">
         <v>80.645161290322577</v>
       </c>
@@ -6302,7 +6657,9 @@
       <c r="F178" s="17">
         <v>96.5</v>
       </c>
-      <c r="G178" s="11"/>
+      <c r="G178" s="23">
+        <v>49</v>
+      </c>
       <c r="H178" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -6326,7 +6683,9 @@
       <c r="F179" s="17">
         <v>55</v>
       </c>
-      <c r="G179" s="11"/>
+      <c r="G179" s="23">
+        <v>35</v>
+      </c>
       <c r="H179" s="21">
         <v>93.548387096774192</v>
       </c>
@@ -6350,7 +6709,9 @@
       <c r="F180" s="17">
         <v>71.5</v>
       </c>
-      <c r="G180" s="11"/>
+      <c r="G180" s="23">
+        <v>46</v>
+      </c>
       <c r="H180" s="21">
         <v>74.193548387096769</v>
       </c>
@@ -6374,7 +6735,9 @@
       <c r="F181" s="17">
         <v>49.5</v>
       </c>
-      <c r="G181" s="11"/>
+      <c r="G181" s="23">
+        <v>19</v>
+      </c>
       <c r="H181" s="21">
         <v>70.967741935483872</v>
       </c>
@@ -6398,7 +6761,9 @@
       <c r="F182" s="17">
         <v>32.5</v>
       </c>
-      <c r="G182" s="11"/>
+      <c r="G182" s="23">
+        <v>11</v>
+      </c>
       <c r="H182" s="21">
         <v>64.516129032258064</v>
       </c>
@@ -6422,7 +6787,9 @@
       <c r="F183" s="17">
         <v>71</v>
       </c>
-      <c r="G183" s="11"/>
+      <c r="G183" s="23">
+        <v>28</v>
+      </c>
       <c r="H183" s="21">
         <v>77.41935483870968</v>
       </c>
@@ -6446,7 +6813,9 @@
       <c r="F184" s="17">
         <v>28.5</v>
       </c>
-      <c r="G184" s="11"/>
+      <c r="G184" s="23">
+        <v>61</v>
+      </c>
       <c r="H184" s="21">
         <v>54.838709677419352</v>
       </c>
@@ -6470,7 +6839,9 @@
       <c r="F185" s="17">
         <v>60.5</v>
       </c>
-      <c r="G185" s="11"/>
+      <c r="G185" s="23">
+        <v>56</v>
+      </c>
       <c r="H185" s="21">
         <v>87.096774193548384</v>
       </c>
@@ -6494,7 +6865,9 @@
       <c r="F186" s="17">
         <v>61</v>
       </c>
-      <c r="G186" s="11"/>
+      <c r="G186" s="23">
+        <v>64</v>
+      </c>
       <c r="H186" s="21">
         <v>83.333333333333343</v>
       </c>
@@ -6518,7 +6891,9 @@
       <c r="F187" s="17">
         <v>0.5</v>
       </c>
-      <c r="G187" s="11"/>
+      <c r="G187" s="23">
+        <v>46</v>
+      </c>
       <c r="H187" s="21">
         <v>62.5</v>
       </c>
@@ -6542,7 +6917,9 @@
       <c r="F188" s="17">
         <v>38.5</v>
       </c>
-      <c r="G188" s="11"/>
+      <c r="G188" s="23">
+        <v>28</v>
+      </c>
       <c r="H188" s="21">
         <v>83.333333333333343</v>
       </c>
@@ -6566,7 +6943,9 @@
       <c r="F189" s="17">
         <v>17.5</v>
       </c>
-      <c r="G189" s="11"/>
+      <c r="G189" s="23">
+        <v>41</v>
+      </c>
       <c r="H189" s="21">
         <v>79.166666666666657</v>
       </c>
@@ -6590,7 +6969,9 @@
       <c r="F190" s="17">
         <v>72.5</v>
       </c>
-      <c r="G190" s="11"/>
+      <c r="G190" s="23">
+        <v>55</v>
+      </c>
       <c r="H190" s="21">
         <v>75</v>
       </c>
@@ -6614,7 +6995,9 @@
       <c r="F191" s="17">
         <v>55.5</v>
       </c>
-      <c r="G191" s="11"/>
+      <c r="G191" s="23">
+        <v>38</v>
+      </c>
       <c r="H191" s="21">
         <v>75</v>
       </c>
@@ -6638,7 +7021,9 @@
       <c r="F192" s="17">
         <v>43.5</v>
       </c>
-      <c r="G192" s="11"/>
+      <c r="G192" s="23">
+        <v>30</v>
+      </c>
       <c r="H192" s="21">
         <v>83.333333333333343</v>
       </c>
@@ -6662,7 +7047,9 @@
       <c r="F193" s="17">
         <v>24.5</v>
       </c>
-      <c r="G193" s="11"/>
+      <c r="G193" s="23">
+        <v>22</v>
+      </c>
       <c r="H193" s="21">
         <v>58.333333333333336</v>
       </c>
@@ -6686,7 +7073,9 @@
       <c r="F194" s="17">
         <v>65.5</v>
       </c>
-      <c r="G194" s="11"/>
+      <c r="G194" s="23">
+        <v>14</v>
+      </c>
       <c r="H194" s="18"/>
     </row>
     <row r="195" spans="1:8">
@@ -6708,7 +7097,9 @@
       <c r="F195" s="17">
         <v>72</v>
       </c>
-      <c r="G195" s="11"/>
+      <c r="G195" s="23">
+        <v>47</v>
+      </c>
       <c r="H195" s="18"/>
     </row>
     <row r="196" spans="1:8">
@@ -6730,7 +7121,9 @@
       <c r="F196" s="17">
         <v>83</v>
       </c>
-      <c r="G196" s="11"/>
+      <c r="G196" s="23">
+        <v>39</v>
+      </c>
       <c r="H196" s="18"/>
     </row>
     <row r="197" spans="1:8">
@@ -6752,7 +7145,9 @@
       <c r="F197" s="17">
         <v>74</v>
       </c>
-      <c r="G197" s="11"/>
+      <c r="G197" s="23">
+        <v>39</v>
+      </c>
       <c r="H197" s="18"/>
     </row>
     <row r="198" spans="1:8">
@@ -6774,7 +7169,9 @@
       <c r="F198" s="17">
         <v>69</v>
       </c>
-      <c r="G198" s="11"/>
+      <c r="G198" s="23">
+        <v>35</v>
+      </c>
       <c r="H198" s="18"/>
     </row>
     <row r="199" spans="1:8">
@@ -6788,7 +7185,7 @@
         <v>46</v>
       </c>
       <c r="D199" s="22">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E199" s="17">
         <v>47</v>
@@ -6796,7 +7193,9 @@
       <c r="F199" s="17" t="s">
         <v>482</v>
       </c>
-      <c r="G199" s="11"/>
+      <c r="G199" s="23">
+        <v>26</v>
+      </c>
       <c r="H199" s="18"/>
     </row>
     <row r="200" spans="1:8">
@@ -6818,7 +7217,9 @@
       <c r="F200" s="17">
         <v>88</v>
       </c>
-      <c r="G200" s="11"/>
+      <c r="G200" s="23">
+        <v>52</v>
+      </c>
       <c r="H200" s="18"/>
     </row>
     <row r="201" spans="1:8">
@@ -6840,7 +7241,9 @@
       <c r="F201" s="17">
         <v>59</v>
       </c>
-      <c r="G201" s="11"/>
+      <c r="G201" s="23">
+        <v>41</v>
+      </c>
       <c r="H201" s="18"/>
     </row>
     <row r="202" spans="1:8">
@@ -6862,7 +7265,9 @@
       <c r="F202" s="17">
         <v>33</v>
       </c>
-      <c r="G202" s="11"/>
+      <c r="G202" s="23">
+        <v>27</v>
+      </c>
       <c r="H202" s="18"/>
     </row>
     <row r="203" spans="1:8">
@@ -6884,7 +7289,9 @@
       <c r="F203" s="17">
         <v>71</v>
       </c>
-      <c r="G203" s="11"/>
+      <c r="G203" s="23">
+        <v>42</v>
+      </c>
       <c r="H203" s="18"/>
     </row>
     <row r="204" spans="1:8">
@@ -6906,7 +7313,9 @@
       <c r="F204" s="17">
         <v>77</v>
       </c>
-      <c r="G204" s="11"/>
+      <c r="G204" s="23">
+        <v>31</v>
+      </c>
       <c r="H204" s="18"/>
     </row>
     <row r="205" spans="1:8">
@@ -6928,7 +7337,9 @@
       <c r="F205" s="17">
         <v>53</v>
       </c>
-      <c r="G205" s="11"/>
+      <c r="G205" s="23">
+        <v>47</v>
+      </c>
       <c r="H205" s="18"/>
     </row>
     <row r="206" spans="1:8">
@@ -6950,7 +7361,9 @@
       <c r="F206" s="17">
         <v>76</v>
       </c>
-      <c r="G206" s="11"/>
+      <c r="G206" s="23">
+        <v>30</v>
+      </c>
       <c r="H206" s="18"/>
     </row>
     <row r="207" spans="1:8">
@@ -6972,7 +7385,9 @@
       <c r="F207" s="20">
         <v>68</v>
       </c>
-      <c r="G207" s="11"/>
+      <c r="G207" s="23">
+        <v>21</v>
+      </c>
       <c r="H207" s="18"/>
     </row>
     <row r="208" spans="1:8">
@@ -6994,7 +7409,9 @@
       <c r="F208" s="17">
         <v>41</v>
       </c>
-      <c r="G208" s="11"/>
+      <c r="G208" s="23">
+        <v>35</v>
+      </c>
       <c r="H208" s="18"/>
     </row>
     <row r="209" spans="1:8">
@@ -7016,7 +7433,9 @@
       <c r="F209" s="17">
         <v>77</v>
       </c>
-      <c r="G209" s="11"/>
+      <c r="G209" s="23">
+        <v>17</v>
+      </c>
       <c r="H209" s="18"/>
     </row>
     <row r="210" spans="1:8">
@@ -7038,7 +7457,9 @@
       <c r="F210" s="17">
         <v>87</v>
       </c>
-      <c r="G210" s="11"/>
+      <c r="G210" s="23">
+        <v>30</v>
+      </c>
       <c r="H210" s="18"/>
     </row>
     <row r="211" spans="1:8">
@@ -7049,10 +7470,10 @@
         <v>427</v>
       </c>
       <c r="C211" s="11">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D211" s="22">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E211" s="17">
         <v>53</v>
@@ -7060,7 +7481,9 @@
       <c r="F211" s="17">
         <v>40</v>
       </c>
-      <c r="G211" s="11"/>
+      <c r="G211" s="23">
+        <v>28</v>
+      </c>
       <c r="H211" s="18"/>
     </row>
     <row r="212" spans="1:8">
@@ -7082,7 +7505,9 @@
       <c r="F212" s="17">
         <v>44</v>
       </c>
-      <c r="G212" s="11"/>
+      <c r="G212" s="23">
+        <v>47</v>
+      </c>
       <c r="H212" s="18"/>
     </row>
     <row r="213" spans="1:8">
@@ -7104,7 +7529,9 @@
       <c r="F213" s="17">
         <v>88</v>
       </c>
-      <c r="G213" s="11"/>
+      <c r="G213" s="23">
+        <v>48</v>
+      </c>
       <c r="H213" s="18"/>
     </row>
     <row r="214" spans="1:8">
@@ -7126,7 +7553,9 @@
       <c r="F214" s="17">
         <v>90</v>
       </c>
-      <c r="G214" s="11"/>
+      <c r="G214" s="23">
+        <v>28</v>
+      </c>
       <c r="H214" s="18"/>
     </row>
     <row r="215" spans="1:8">
@@ -7148,7 +7577,9 @@
       <c r="F215" s="17">
         <v>49</v>
       </c>
-      <c r="G215" s="11"/>
+      <c r="G215" s="23">
+        <v>27</v>
+      </c>
       <c r="H215" s="18"/>
     </row>
     <row r="216" spans="1:8">
@@ -7170,7 +7601,9 @@
       <c r="F216" s="17">
         <v>76</v>
       </c>
-      <c r="G216" s="11"/>
+      <c r="G216" s="23">
+        <v>65</v>
+      </c>
       <c r="H216" s="18"/>
     </row>
     <row r="217" spans="1:8">
@@ -7192,7 +7625,9 @@
       <c r="F217" s="17" t="s">
         <v>482</v>
       </c>
-      <c r="G217" s="11"/>
+      <c r="G217" s="23" t="s">
+        <v>482</v>
+      </c>
       <c r="H217" s="18"/>
     </row>
     <row r="218" spans="1:8">
@@ -7214,7 +7649,9 @@
       <c r="F218" s="17">
         <v>56</v>
       </c>
-      <c r="G218" s="11"/>
+      <c r="G218" s="23">
+        <v>62</v>
+      </c>
       <c r="H218" s="18"/>
     </row>
     <row r="219" spans="1:8">
@@ -7236,7 +7673,9 @@
       <c r="F219" s="17">
         <v>66</v>
       </c>
-      <c r="G219" s="11"/>
+      <c r="G219" s="23">
+        <v>28</v>
+      </c>
       <c r="H219" s="18"/>
     </row>
     <row r="220" spans="1:8">
@@ -7258,7 +7697,9 @@
       <c r="F220" s="17">
         <v>44</v>
       </c>
-      <c r="G220" s="11"/>
+      <c r="G220" s="23">
+        <v>34</v>
+      </c>
       <c r="H220" s="18"/>
     </row>
     <row r="221" spans="1:8">
@@ -7280,7 +7721,9 @@
       <c r="F221" s="17">
         <v>96</v>
       </c>
-      <c r="G221" s="11"/>
+      <c r="G221" s="23">
+        <v>28</v>
+      </c>
       <c r="H221" s="18"/>
     </row>
     <row r="222" spans="1:8">
@@ -7302,7 +7745,9 @@
       <c r="F222" s="17">
         <v>88</v>
       </c>
-      <c r="G222" s="11"/>
+      <c r="G222" s="23">
+        <v>33</v>
+      </c>
       <c r="H222" s="18"/>
     </row>
     <row r="223" spans="1:8">
@@ -7324,7 +7769,9 @@
       <c r="F223" s="17">
         <v>51</v>
       </c>
-      <c r="G223" s="11"/>
+      <c r="G223" s="23">
+        <v>33</v>
+      </c>
       <c r="H223" s="18"/>
     </row>
     <row r="224" spans="1:8">
@@ -7346,7 +7793,9 @@
       <c r="F224" s="17">
         <v>89</v>
       </c>
-      <c r="G224" s="11"/>
+      <c r="G224" s="23">
+        <v>31</v>
+      </c>
       <c r="H224" s="18"/>
     </row>
     <row r="225" spans="1:8">
@@ -7368,7 +7817,9 @@
       <c r="F225" s="17">
         <v>70</v>
       </c>
-      <c r="G225" s="11"/>
+      <c r="G225" s="23">
+        <v>48</v>
+      </c>
       <c r="H225" s="18"/>
     </row>
     <row r="226" spans="1:8">
@@ -7390,7 +7841,9 @@
       <c r="F226" s="17">
         <v>82</v>
       </c>
-      <c r="G226" s="11"/>
+      <c r="G226" s="23">
+        <v>31</v>
+      </c>
       <c r="H226" s="18"/>
     </row>
     <row r="227" spans="1:8">
@@ -7412,7 +7865,9 @@
       <c r="F227" s="17" t="s">
         <v>482</v>
       </c>
-      <c r="G227" s="11"/>
+      <c r="G227" s="23">
+        <v>37</v>
+      </c>
       <c r="H227" s="18"/>
     </row>
     <row r="228" spans="1:8">
@@ -7434,7 +7889,9 @@
       <c r="F228" s="17">
         <v>65</v>
       </c>
-      <c r="G228" s="11"/>
+      <c r="G228" s="23">
+        <v>34</v>
+      </c>
       <c r="H228" s="18"/>
     </row>
     <row r="229" spans="1:8">
@@ -7456,7 +7913,9 @@
       <c r="F229" s="17">
         <v>80</v>
       </c>
-      <c r="G229" s="11"/>
+      <c r="G229" s="23">
+        <v>24</v>
+      </c>
       <c r="H229" s="18"/>
     </row>
     <row r="230" spans="1:8">
@@ -7478,7 +7937,9 @@
       <c r="F230" s="17">
         <v>85</v>
       </c>
-      <c r="G230" s="11"/>
+      <c r="G230" s="23">
+        <v>59</v>
+      </c>
       <c r="H230" s="18"/>
     </row>
     <row r="231" spans="1:8">
@@ -7500,7 +7961,9 @@
       <c r="F231" s="17">
         <v>61</v>
       </c>
-      <c r="G231" s="11"/>
+      <c r="G231" s="23">
+        <v>53</v>
+      </c>
       <c r="H231" s="18"/>
     </row>
     <row r="232" spans="1:8">
@@ -7522,7 +7985,9 @@
       <c r="F232" s="17">
         <v>67</v>
       </c>
-      <c r="G232" s="11"/>
+      <c r="G232" s="23">
+        <v>33</v>
+      </c>
       <c r="H232" s="18"/>
     </row>
     <row r="233" spans="1:8">
@@ -7544,7 +8009,9 @@
       <c r="F233" s="17" t="s">
         <v>482</v>
       </c>
-      <c r="G233" s="11"/>
+      <c r="G233" s="23" t="s">
+        <v>482</v>
+      </c>
       <c r="H233" s="18"/>
     </row>
     <row r="234" spans="1:8">
@@ -7566,7 +8033,9 @@
       <c r="F234" s="17">
         <v>40</v>
       </c>
-      <c r="G234" s="11"/>
+      <c r="G234" s="23">
+        <v>62</v>
+      </c>
       <c r="H234" s="18"/>
     </row>
     <row r="235" spans="1:8">
@@ -7588,7 +8057,9 @@
       <c r="F235" s="17">
         <v>55</v>
       </c>
-      <c r="G235" s="11"/>
+      <c r="G235" s="23">
+        <v>53</v>
+      </c>
       <c r="H235" s="18"/>
     </row>
     <row r="236" spans="1:8">
@@ -7610,7 +8081,9 @@
       <c r="F236" s="17">
         <v>90</v>
       </c>
-      <c r="G236" s="11"/>
+      <c r="G236" s="23">
+        <v>41</v>
+      </c>
       <c r="H236" s="18"/>
     </row>
     <row r="237" spans="1:8">
@@ -7632,7 +8105,9 @@
       <c r="F237" s="17" t="s">
         <v>482</v>
       </c>
-      <c r="G237" s="11"/>
+      <c r="G237" s="23">
+        <v>29</v>
+      </c>
       <c r="H237" s="18"/>
     </row>
     <row r="238" spans="1:8">
@@ -7654,7 +8129,9 @@
       <c r="F238" s="17" t="s">
         <v>482</v>
       </c>
-      <c r="G238" s="11"/>
+      <c r="G238" s="23" t="s">
+        <v>482</v>
+      </c>
       <c r="H238" s="18"/>
     </row>
   </sheetData>
@@ -7664,12 +8141,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FDB710AC8133AA498CBE2CD8804BFA17" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4eb3d0237cfa0d187f5d6a045860a182">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a5132194-61b6-4507-86ae-3af00c68c385" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="53ffbac00c82fc65a20b2fe1c6581f58" ns2:_="">
     <xsd:import namespace="a5132194-61b6-4507-86ae-3af00c68c385"/>
@@ -7813,7 +8284,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -7822,7 +8293,25 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F334BD5B-9873-472F-B0A9-4AE19CD21D29}">
+  <ds:schemaRefs/>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82FD49CE-D196-4C00-BC5E-382EDDDD004F}">
+  <ds:schemaRefs/>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B92832D-94CC-4C5E-A4E8-2D2A44869573}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
@@ -7836,16 +8325,4 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F334BD5B-9873-472F-B0A9-4AE19CD21D29}">
-  <ds:schemaRefs/>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82FD49CE-D196-4C00-BC5E-382EDDDD004F}">
-  <ds:schemaRefs/>
-</ds:datastoreItem>
 </file>